--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C3AC6D7-BA80-4320-A74B-C52DD65F0128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3BDA80-DEFA-4414-ADC1-09356724A3B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>Fecha</t>
   </si>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI368"/>
+  <dimension ref="A1:AI369"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -32223,8 +32223,8 @@
       <c r="C367">
         <v>149832401.25782579</v>
       </c>
-      <c r="D367" t="s">
-        <v>23</v>
+      <c r="D367">
+        <v>547</v>
       </c>
       <c r="E367">
         <v>8185.43</v>
@@ -32330,11 +32330,11 @@
       <c r="C368">
         <v>149818965.10000464</v>
       </c>
-      <c r="D368" t="s">
-        <v>23</v>
-      </c>
-      <c r="E368" t="s">
-        <v>23</v>
+      <c r="D368">
+        <v>547</v>
+      </c>
+      <c r="E368">
+        <v>18426</v>
       </c>
       <c r="F368">
         <v>5</v>
@@ -32415,15 +32415,122 @@
         <v>5.0749932034504109E-3</v>
       </c>
       <c r="AF368">
+        <v>10047.755000000001</v>
+      </c>
+      <c r="AG368">
+        <v>10952.305</v>
+      </c>
+      <c r="AH368">
+        <v>14013.900000000001</v>
+      </c>
+      <c r="AI368">
+        <v>10191.35</v>
+      </c>
+    </row>
+    <row r="369" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A369" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B369">
+        <v>110.51650281801253</v>
+      </c>
+      <c r="C369">
+        <v>149473570.06136194</v>
+      </c>
+      <c r="D369" t="s">
+        <v>23</v>
+      </c>
+      <c r="E369" t="s">
+        <v>23</v>
+      </c>
+      <c r="F369">
+        <v>2</v>
+      </c>
+      <c r="G369">
+        <v>6.3446830670140324</v>
+      </c>
+      <c r="H369">
+        <v>6.1054163960677226</v>
+      </c>
+      <c r="I369">
+        <v>181.59</v>
+      </c>
+      <c r="J369">
+        <v>6.39</v>
+      </c>
+      <c r="K369">
+        <v>6.1400000000000006</v>
+      </c>
+      <c r="L369">
+        <v>10.51650281801253</v>
+      </c>
+      <c r="M369">
+        <v>10.999726520166186</v>
+      </c>
+      <c r="N369">
+        <v>6.5793096553610697</v>
+      </c>
+      <c r="O369">
+        <v>6.5699999999999994</v>
+      </c>
+      <c r="P369">
+        <v>4.0028261295448481E-3</v>
+      </c>
+      <c r="Q369">
+        <v>4.1065621589436475E-3</v>
+      </c>
+      <c r="R369">
+        <v>0.10887115896571385</v>
+      </c>
+      <c r="S369">
+        <v>0.16976016351848963</v>
+      </c>
+      <c r="T369">
+        <v>4.2175833812119201E-2</v>
+      </c>
+      <c r="U369">
+        <v>8.7007118411608353E-2</v>
+      </c>
+      <c r="V369">
+        <v>0.25599832577658521</v>
+      </c>
+      <c r="W369">
+        <v>0.78494732870286743</v>
+      </c>
+      <c r="X369">
+        <v>111.11764705882354</v>
+      </c>
+      <c r="Y369">
+        <v>-2.573912658080113</v>
+      </c>
+      <c r="Z369">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA369" s="3">
+        <v>5.4394070159902164E-3</v>
+      </c>
+      <c r="AB369" s="3">
+        <v>6.1673453790347908E-3</v>
+      </c>
+      <c r="AC369" s="3">
+        <v>4.7457673040616341E-3</v>
+      </c>
+      <c r="AD369" s="3">
+        <v>4.7018204938509027E-3</v>
+      </c>
+      <c r="AE369" s="3">
+        <v>5.0636664925403311E-3</v>
+      </c>
+      <c r="AF369">
         <v>9994.01</v>
       </c>
-      <c r="AG368">
-        <v>10753.46</v>
-      </c>
-      <c r="AH368">
-        <v>13874.2</v>
-      </c>
-      <c r="AI368">
+      <c r="AG369">
+        <v>11151.15</v>
+      </c>
+      <c r="AH369">
+        <v>14153.6</v>
+      </c>
+      <c r="AI369">
         <v>10167.950000000001</v>
       </c>
     </row>

--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\General\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3BDA80-DEFA-4414-ADC1-09356724A3B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3323B4F-A625-474B-BFE3-6CBEF797F06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>Fecha</t>
   </si>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI369"/>
+  <dimension ref="A1:AI370"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -32437,8 +32437,8 @@
       <c r="C369">
         <v>149473570.06136194</v>
       </c>
-      <c r="D369" t="s">
-        <v>23</v>
+      <c r="D369">
+        <v>547</v>
       </c>
       <c r="E369" t="s">
         <v>23</v>
@@ -32532,6 +32532,113 @@
       </c>
       <c r="AI369">
         <v>10167.950000000001</v>
+      </c>
+    </row>
+    <row r="370" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A370" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B370">
+        <v>110.23394792365949</v>
+      </c>
+      <c r="C370">
+        <v>149091414.56674945</v>
+      </c>
+      <c r="D370" t="s">
+        <v>23</v>
+      </c>
+      <c r="E370" t="s">
+        <v>23</v>
+      </c>
+      <c r="F370">
+        <v>2</v>
+      </c>
+      <c r="G370">
+        <v>6.3352800576060648</v>
+      </c>
+      <c r="H370">
+        <v>6.1461359570404586</v>
+      </c>
+      <c r="I370">
+        <v>181.13</v>
+      </c>
+      <c r="J370">
+        <v>6.38</v>
+      </c>
+      <c r="K370">
+        <v>6.18</v>
+      </c>
+      <c r="L370">
+        <v>10.233947923659482</v>
+      </c>
+      <c r="M370">
+        <v>10.718544328419522</v>
+      </c>
+      <c r="N370">
+        <v>6.5792742636401726</v>
+      </c>
+      <c r="O370">
+        <v>6.5699999999999994</v>
+      </c>
+      <c r="P370">
+        <v>3.941961124018266E-3</v>
+      </c>
+      <c r="Q370">
+        <v>4.0818142246402313E-3</v>
+      </c>
+      <c r="R370">
+        <v>0.10887116393312207</v>
+      </c>
+      <c r="S370">
+        <v>0.16951916150179114</v>
+      </c>
+      <c r="T370">
+        <v>4.0971136960132881E-2</v>
+      </c>
+      <c r="U370">
+        <v>8.0601921707534885E-2</v>
+      </c>
+      <c r="V370">
+        <v>0.25915668837309669</v>
+      </c>
+      <c r="W370">
+        <v>0.59403587027520022</v>
+      </c>
+      <c r="X370">
+        <v>111.11764705882354</v>
+      </c>
+      <c r="Y370">
+        <v>-2.8229996008822811</v>
+      </c>
+      <c r="Z370">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA370" s="3">
+        <v>8.0165788471626698E-3</v>
+      </c>
+      <c r="AB370" s="3">
+        <v>6.28154695770818E-3</v>
+      </c>
+      <c r="AC370" s="3">
+        <v>4.8222644952333471E-3</v>
+      </c>
+      <c r="AD370" s="3">
+        <v>4.7075960424577358E-3</v>
+      </c>
+      <c r="AE370" s="3">
+        <v>5.0509672414460766E-3</v>
+      </c>
+      <c r="AF370">
+        <v>9703.1049999999996</v>
+      </c>
+      <c r="AG370">
+        <v>10952.305</v>
+      </c>
+      <c r="AH370">
+        <v>14182.174999999999</v>
+      </c>
+      <c r="AI370">
+        <v>10191.35</v>
       </c>
     </row>
   </sheetData>

--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\General\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3323B4F-A625-474B-BFE3-6CBEF797F06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD224431-F49A-4C68-88FD-5BF120BE2966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI370"/>
+  <dimension ref="A1:AI371"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -32440,8 +32440,8 @@
       <c r="D369">
         <v>547</v>
       </c>
-      <c r="E369" t="s">
-        <v>23</v>
+      <c r="E369">
+        <v>5667.2</v>
       </c>
       <c r="F369">
         <v>2</v>
@@ -32498,7 +32498,7 @@
         <v>0.78494732870286743</v>
       </c>
       <c r="X369">
-        <v>111.11764705882354</v>
+        <v>111.12</v>
       </c>
       <c r="Y369">
         <v>-2.573912658080113</v>
@@ -32507,31 +32507,31 @@
         <v>-3.9109511967821864</v>
       </c>
       <c r="AA369" s="3">
-        <v>5.4394070159902164E-3</v>
+        <v>5.4606974216444559E-3</v>
       </c>
       <c r="AB369" s="3">
-        <v>6.1673453790347908E-3</v>
+        <v>6.1680550592232656E-3</v>
       </c>
       <c r="AC369" s="3">
-        <v>4.7457673040616341E-3</v>
+        <v>4.7461221441558715E-3</v>
       </c>
       <c r="AD369" s="3">
-        <v>4.7018204938509027E-3</v>
+        <v>4.7019387738823151E-3</v>
       </c>
       <c r="AE369" s="3">
-        <v>5.0636664925403311E-3</v>
+        <v>5.0637256325560369E-3</v>
       </c>
       <c r="AF369">
-        <v>9994.01</v>
+        <v>9703.1049999999996</v>
       </c>
       <c r="AG369">
-        <v>11151.15</v>
+        <v>10952.305</v>
       </c>
       <c r="AH369">
-        <v>14153.6</v>
+        <v>14013.900000000001</v>
       </c>
       <c r="AI369">
-        <v>10167.950000000001</v>
+        <v>10166.85</v>
       </c>
     </row>
     <row r="370" spans="1:35" x14ac:dyDescent="0.3">
@@ -32547,8 +32547,8 @@
       <c r="D370" t="s">
         <v>23</v>
       </c>
-      <c r="E370" t="s">
-        <v>23</v>
+      <c r="E370">
+        <v>5782.4</v>
       </c>
       <c r="F370">
         <v>2</v>
@@ -32605,7 +32605,7 @@
         <v>0.59403587027520022</v>
       </c>
       <c r="X370">
-        <v>111.11764705882354</v>
+        <v>111.2</v>
       </c>
       <c r="Y370">
         <v>-2.8229996008822811</v>
@@ -32614,31 +32614,135 @@
         <v>-3.9109511967821864</v>
       </c>
       <c r="AA370" s="3">
-        <v>8.0165788471626698E-3</v>
+        <v>8.7636530718244732E-3</v>
       </c>
       <c r="AB370" s="3">
-        <v>6.28154695770818E-3</v>
+        <v>6.3071591120520487E-3</v>
       </c>
       <c r="AC370" s="3">
-        <v>4.8222644952333471E-3</v>
+        <v>4.8350705724052815E-3</v>
       </c>
       <c r="AD370" s="3">
-        <v>4.7075960424577358E-3</v>
+        <v>4.7118647348483806E-3</v>
       </c>
       <c r="AE370" s="3">
-        <v>5.0509672414460766E-3</v>
+        <v>5.053101587641399E-3</v>
       </c>
       <c r="AF370">
-        <v>9703.1049999999996</v>
+        <v>9283.66</v>
       </c>
       <c r="AG370">
-        <v>10952.305</v>
+        <v>10696.294999999998</v>
       </c>
       <c r="AH370">
-        <v>14182.174999999999</v>
+        <v>13787.69</v>
       </c>
       <c r="AI370">
-        <v>10191.35</v>
+        <v>10166.85</v>
+      </c>
+    </row>
+    <row r="371" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A371" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B371">
+        <v>110.06916681064973</v>
+      </c>
+      <c r="C371">
+        <v>148868548.11140376</v>
+      </c>
+      <c r="D371" t="s">
+        <v>23</v>
+      </c>
+      <c r="E371" t="s">
+        <v>23</v>
+      </c>
+      <c r="G371">
+        <v>6.3185937106521504</v>
+      </c>
+      <c r="H371">
+        <v>6.168713017231477</v>
+      </c>
+      <c r="I371">
+        <v>180.86</v>
+      </c>
+      <c r="J371">
+        <v>6.37</v>
+      </c>
+      <c r="K371">
+        <v>6.2</v>
+      </c>
+      <c r="L371">
+        <v>10.069166810649733</v>
+      </c>
+      <c r="M371">
+        <v>10.553502607176913</v>
+      </c>
+      <c r="N371">
+        <v>6.5794657389502191</v>
+      </c>
+      <c r="O371">
+        <v>6.5699999999999994</v>
+      </c>
+      <c r="P371">
+        <v>3.8675603745273114E-3</v>
+      </c>
+      <c r="Q371">
+        <v>3.9779264566958726E-3</v>
+      </c>
+      <c r="R371">
+        <v>0.10887095011979397</v>
+      </c>
+      <c r="S371">
+        <v>0.16945661788136732</v>
+      </c>
+      <c r="T371">
+        <v>3.6500207921963401E-2</v>
+      </c>
+      <c r="U371">
+        <v>7.7933383117290145E-2</v>
+      </c>
+      <c r="V371">
+        <v>0.26095331919895326</v>
+      </c>
+      <c r="W371">
+        <v>0.49703011629733673</v>
+      </c>
+      <c r="X371">
+        <v>109.24</v>
+      </c>
+      <c r="Y371">
+        <v>-2.9682627851039478</v>
+      </c>
+      <c r="Z371">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA371" s="3">
+        <v>7.5331433377354706E-3</v>
+      </c>
+      <c r="AB371" s="3">
+        <v>6.4163688831632669E-3</v>
+      </c>
+      <c r="AC371" s="3">
+        <v>4.9138158416539898E-3</v>
+      </c>
+      <c r="AD371" s="3">
+        <v>4.7138805236957909E-3</v>
+      </c>
+      <c r="AE371" s="3">
+        <v>5.0637836814497652E-3</v>
+      </c>
+      <c r="AF371">
+        <v>9155.1200000000008</v>
+      </c>
+      <c r="AG371">
+        <v>10753.46</v>
+      </c>
+      <c r="AH371">
+        <v>13701.18</v>
+      </c>
+      <c r="AI371">
+        <v>10167.950000000001</v>
       </c>
     </row>
   </sheetData>

--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\General\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD224431-F49A-4C68-88FD-5BF120BE2966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3F4BC0-B413-4AF0-B858-50A15D133DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Fecha</t>
   </si>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI371"/>
+  <dimension ref="A1:AI372"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -32544,8 +32544,8 @@
       <c r="C370">
         <v>149091414.56674945</v>
       </c>
-      <c r="D370" t="s">
-        <v>23</v>
+      <c r="D370">
+        <v>547</v>
       </c>
       <c r="E370">
         <v>5782.4</v>
@@ -32651,11 +32651,14 @@
       <c r="C371">
         <v>148868548.11140376</v>
       </c>
-      <c r="D371" t="s">
-        <v>23</v>
-      </c>
-      <c r="E371" t="s">
-        <v>23</v>
+      <c r="D371">
+        <v>547</v>
+      </c>
+      <c r="E371">
+        <v>709285.2</v>
+      </c>
+      <c r="F371">
+        <v>4</v>
       </c>
       <c r="G371">
         <v>6.3185937106521504</v>
@@ -32733,16 +32736,123 @@
         <v>5.0637836814497652E-3</v>
       </c>
       <c r="AF371">
-        <v>9155.1200000000008</v>
+        <v>9283.66</v>
       </c>
       <c r="AG371">
-        <v>10753.46</v>
+        <v>10952.305</v>
       </c>
       <c r="AH371">
-        <v>13701.18</v>
+        <v>13787.69</v>
       </c>
       <c r="AI371">
-        <v>10167.950000000001</v>
+        <v>10191.35</v>
+      </c>
+    </row>
+    <row r="372" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A372" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B372">
+        <v>109.97377612104519</v>
+      </c>
+      <c r="C372">
+        <v>148739532.20371363</v>
+      </c>
+      <c r="D372" t="s">
+        <v>23</v>
+      </c>
+      <c r="E372">
+        <v>6565</v>
+      </c>
+      <c r="F372">
+        <v>2</v>
+      </c>
+      <c r="G372">
+        <v>6.3124454467641122</v>
+      </c>
+      <c r="H372">
+        <v>6.1827716320945401</v>
+      </c>
+      <c r="I372">
+        <v>180.7</v>
+      </c>
+      <c r="J372">
+        <v>6.36</v>
+      </c>
+      <c r="K372">
+        <v>6.22</v>
+      </c>
+      <c r="L372">
+        <v>9.9737761210451978</v>
+      </c>
+      <c r="M372">
+        <v>10.455700105699805</v>
+      </c>
+      <c r="N372">
+        <v>6.5795822843073264</v>
+      </c>
+      <c r="O372">
+        <v>6.5699999999999994</v>
+      </c>
+      <c r="P372">
+        <v>3.8926626749955311E-3</v>
+      </c>
+      <c r="Q372">
+        <v>3.9931162400106733E-3</v>
+      </c>
+      <c r="R372">
+        <v>0.10887099973933771</v>
+      </c>
+      <c r="S372">
+        <v>0.16937004922154192</v>
+      </c>
+      <c r="T372">
+        <v>3.4273960351505206E-2</v>
+      </c>
+      <c r="U372">
+        <v>7.6721311798055858E-2</v>
+      </c>
+      <c r="V372">
+        <v>0.25825969930505233</v>
+      </c>
+      <c r="W372">
+        <v>0.6061472189963224</v>
+      </c>
+      <c r="X372">
+        <v>109.42</v>
+      </c>
+      <c r="Y372">
+        <v>-3.0523546756365483</v>
+      </c>
+      <c r="Z372">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA372" s="3">
+        <v>5.0355288376718876E-3</v>
+      </c>
+      <c r="AB372" s="3">
+        <v>6.3753665077984521E-3</v>
+      </c>
+      <c r="AC372" s="3">
+        <v>4.9803390346139804E-3</v>
+      </c>
+      <c r="AD372" s="3">
+        <v>4.6897096563352503E-3</v>
+      </c>
+      <c r="AE372" s="3">
+        <v>5.0655203315954521E-3</v>
+      </c>
+      <c r="AF372">
+        <v>9107.5250000000015</v>
+      </c>
+      <c r="AG372">
+        <v>10696.294999999998</v>
+      </c>
+      <c r="AH372">
+        <v>13651.24</v>
+      </c>
+      <c r="AI372">
+        <v>10191.35</v>
       </c>
     </row>
   </sheetData>

--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\General\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3F4BC0-B413-4AF0-B858-50A15D133DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFB0D36-FF7F-496A-A691-09FC6612DA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>Fecha</t>
   </si>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI372"/>
+  <dimension ref="A1:AI373"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -32855,6 +32855,113 @@
         <v>10191.35</v>
       </c>
     </row>
+    <row r="373" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A373" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B373">
+        <v>110.04027514086383</v>
+      </c>
+      <c r="C373">
+        <v>148829472.12801832</v>
+      </c>
+      <c r="D373" t="s">
+        <v>23</v>
+      </c>
+      <c r="E373">
+        <v>9216</v>
+      </c>
+      <c r="F373">
+        <v>4</v>
+      </c>
+      <c r="G373">
+        <v>6.3098808980713414</v>
+      </c>
+      <c r="H373">
+        <v>6.1732827533232069</v>
+      </c>
+      <c r="I373">
+        <v>180.82</v>
+      </c>
+      <c r="J373">
+        <v>6.36</v>
+      </c>
+      <c r="K373">
+        <v>6.21</v>
+      </c>
+      <c r="L373">
+        <v>10.04027514086383</v>
+      </c>
+      <c r="M373">
+        <v>10.529051981807624</v>
+      </c>
+      <c r="N373">
+        <v>6.5793252872454184</v>
+      </c>
+      <c r="O373">
+        <v>6.5699999999999994</v>
+      </c>
+      <c r="P373">
+        <v>3.9270610450159692E-3</v>
+      </c>
+      <c r="Q373">
+        <v>4.0287019274068544E-3</v>
+      </c>
+      <c r="R373">
+        <v>0.10887147198982014</v>
+      </c>
+      <c r="S373">
+        <v>0.16873983743943705</v>
+      </c>
+      <c r="T373">
+        <v>3.6519767403031533E-2</v>
+      </c>
+      <c r="U373">
+        <v>8.2341566020638357E-2</v>
+      </c>
+      <c r="V373">
+        <v>0.25575453002362192</v>
+      </c>
+      <c r="W373">
+        <v>0.30954690310247557</v>
+      </c>
+      <c r="X373">
+        <v>109.71</v>
+      </c>
+      <c r="Y373">
+        <v>-2.9937323056935639</v>
+      </c>
+      <c r="Z373">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA373" s="3">
+        <v>3.0014023541929946E-3</v>
+      </c>
+      <c r="AB373" s="3">
+        <v>6.4262727819597888E-3</v>
+      </c>
+      <c r="AC373" s="3">
+        <v>5.0165150681131289E-3</v>
+      </c>
+      <c r="AD373" s="3">
+        <v>4.670660178310645E-3</v>
+      </c>
+      <c r="AE373" s="3">
+        <v>5.0441480385520184E-3</v>
+      </c>
+      <c r="AF373">
+        <v>9107.5250000000015</v>
+      </c>
+      <c r="AG373">
+        <v>10634.04</v>
+      </c>
+      <c r="AH373">
+        <v>13264.45</v>
+      </c>
+      <c r="AI373">
+        <v>10191.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\General\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFB0D36-FF7F-496A-A691-09FC6612DA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5FE599-DC5E-48B7-8715-4ACD5008C9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Fecha</t>
   </si>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI373"/>
+  <dimension ref="A1:AI374"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -32758,8 +32758,8 @@
       <c r="C372">
         <v>148739532.20371363</v>
       </c>
-      <c r="D372" t="s">
-        <v>23</v>
+      <c r="D372">
+        <v>547</v>
       </c>
       <c r="E372">
         <v>6565</v>
@@ -32865,8 +32865,8 @@
       <c r="C373">
         <v>148829472.12801832</v>
       </c>
-      <c r="D373" t="s">
-        <v>23</v>
+      <c r="D373">
+        <v>547</v>
       </c>
       <c r="E373">
         <v>9216</v>
@@ -32960,6 +32960,113 @@
       </c>
       <c r="AI373">
         <v>10191.35</v>
+      </c>
+    </row>
+    <row r="374" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A374" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B374">
+        <v>110.0561610849722</v>
+      </c>
+      <c r="C374">
+        <v>148300677.06200004</v>
+      </c>
+      <c r="D374" t="s">
+        <v>23</v>
+      </c>
+      <c r="E374">
+        <v>11043</v>
+      </c>
+      <c r="F374">
+        <v>3</v>
+      </c>
+      <c r="G374">
+        <v>6.3062108907526504</v>
+      </c>
+      <c r="H374">
+        <v>6.1742971841428052</v>
+      </c>
+      <c r="I374">
+        <v>180.85</v>
+      </c>
+      <c r="J374">
+        <v>6.39</v>
+      </c>
+      <c r="K374">
+        <v>6.23</v>
+      </c>
+      <c r="L374">
+        <v>10.056161084972203</v>
+      </c>
+      <c r="M374">
+        <v>10.547389950834596</v>
+      </c>
+      <c r="N374">
+        <v>6.5797071271928651</v>
+      </c>
+      <c r="O374">
+        <v>6.59</v>
+      </c>
+      <c r="P374">
+        <v>3.9264697638287209E-3</v>
+      </c>
+      <c r="Q374">
+        <v>4.0267569054436283E-3</v>
+      </c>
+      <c r="R374">
+        <v>0.10887016523291408</v>
+      </c>
+      <c r="S374">
+        <v>0.1686935401814014</v>
+      </c>
+      <c r="T374">
+        <v>3.445772696256677E-2</v>
+      </c>
+      <c r="U374">
+        <v>8.2025181744471709E-2</v>
+      </c>
+      <c r="V374">
+        <v>0.25740780154617227</v>
+      </c>
+      <c r="W374">
+        <v>0.22933567530840637</v>
+      </c>
+      <c r="X374">
+        <v>109.34</v>
+      </c>
+      <c r="Y374">
+        <v>-2.9797280136761084</v>
+      </c>
+      <c r="Z374">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA374" s="3">
+        <v>6.5072330155080405E-3</v>
+      </c>
+      <c r="AB374" s="3">
+        <v>6.4340995143716238E-3</v>
+      </c>
+      <c r="AC374" s="3">
+        <v>5.0542437435336374E-3</v>
+      </c>
+      <c r="AD374" s="3">
+        <v>4.6433091523154788E-3</v>
+      </c>
+      <c r="AE374" s="3">
+        <v>5.0531193743696308E-3</v>
+      </c>
+      <c r="AF374">
+        <v>9107.5250000000015</v>
+      </c>
+      <c r="AG374">
+        <v>10696.294999999998</v>
+      </c>
+      <c r="AH374">
+        <v>12845.174999999999</v>
+      </c>
+      <c r="AI374">
+        <v>10229.825000000001</v>
       </c>
     </row>
   </sheetData>

--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\General\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5FE599-DC5E-48B7-8715-4ACD5008C9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51CD255B-2FE0-46EA-BAF2-A441570ACF4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI374"/>
+  <dimension ref="A1:AI375"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -32972,8 +32972,8 @@
       <c r="C374">
         <v>148300677.06200004</v>
       </c>
-      <c r="D374" t="s">
-        <v>23</v>
+      <c r="D374">
+        <v>547</v>
       </c>
       <c r="E374">
         <v>11043</v>
@@ -33067,6 +33067,113 @@
       </c>
       <c r="AI374">
         <v>10229.825000000001</v>
+      </c>
+    </row>
+    <row r="375" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A375" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B375">
+        <v>110.1566913893008</v>
+      </c>
+      <c r="C375">
+        <v>148436141.64708284</v>
+      </c>
+      <c r="D375" t="s">
+        <v>23</v>
+      </c>
+      <c r="E375">
+        <v>6380</v>
+      </c>
+      <c r="F375">
+        <v>2</v>
+      </c>
+      <c r="G375">
+        <v>6.306544492913841</v>
+      </c>
+      <c r="H375">
+        <v>6.1675311200874035</v>
+      </c>
+      <c r="I375">
+        <v>181.03</v>
+      </c>
+      <c r="J375">
+        <v>6.39</v>
+      </c>
+      <c r="K375">
+        <v>6.22</v>
+      </c>
+      <c r="L375">
+        <v>10.156691389300798</v>
+      </c>
+      <c r="M375">
+        <v>10.657417764996335</v>
+      </c>
+      <c r="N375">
+        <v>6.5797246302552246</v>
+      </c>
+      <c r="O375">
+        <v>6.59</v>
+      </c>
+      <c r="P375">
+        <v>4.0938724747343353E-3</v>
+      </c>
+      <c r="Q375">
+        <v>4.118273980719382E-3</v>
+      </c>
+      <c r="R375">
+        <v>0.10887126689780467</v>
+      </c>
+      <c r="S375">
+        <v>0.16791255371302136</v>
+      </c>
+      <c r="T375">
+        <v>3.7220101166857145E-2</v>
+      </c>
+      <c r="U375">
+        <v>8.9032042197201289E-2</v>
+      </c>
+      <c r="V375">
+        <v>0.26343031296958141</v>
+      </c>
+      <c r="W375">
+        <v>0.57382461272028618</v>
+      </c>
+      <c r="X375">
+        <v>110</v>
+      </c>
+      <c r="Y375">
+        <v>-2.8911052834929341</v>
+      </c>
+      <c r="Z375">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA375" s="3">
+        <v>1.4224409550124273E-3</v>
+      </c>
+      <c r="AB375" s="3">
+        <v>6.1855844794708658E-3</v>
+      </c>
+      <c r="AC375" s="3">
+        <v>5.0260401886109748E-3</v>
+      </c>
+      <c r="AD375" s="3">
+        <v>4.5861239234798465E-3</v>
+      </c>
+      <c r="AE375" s="3">
+        <v>5.0341785117826374E-3</v>
+      </c>
+      <c r="AF375">
+        <v>8622.68</v>
+      </c>
+      <c r="AG375">
+        <v>10691.205</v>
+      </c>
+      <c r="AH375">
+        <v>12734.575000000001</v>
+      </c>
+      <c r="AI375">
+        <v>10191.35</v>
       </c>
     </row>
   </sheetData>

--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\General\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51CD255B-2FE0-46EA-BAF2-A441570ACF4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{913FB43D-7FC1-472A-B50F-ADD43239BF2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI375"/>
+  <dimension ref="A1:AI376"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -33079,8 +33079,8 @@
       <c r="C375">
         <v>148436141.64708284</v>
       </c>
-      <c r="D375" t="s">
-        <v>23</v>
+      <c r="D375">
+        <v>547</v>
       </c>
       <c r="E375">
         <v>6380</v>
@@ -33174,6 +33174,113 @@
       </c>
       <c r="AI375">
         <v>10191.35</v>
+      </c>
+    </row>
+    <row r="376" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A376" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B376">
+        <v>110.36358554391856</v>
+      </c>
+      <c r="C376">
+        <v>148714931.52043027</v>
+      </c>
+      <c r="D376" t="s">
+        <v>23</v>
+      </c>
+      <c r="E376">
+        <v>6467</v>
+      </c>
+      <c r="F376">
+        <v>2</v>
+      </c>
+      <c r="G376">
+        <v>6.3034286413699423</v>
+      </c>
+      <c r="H376">
+        <v>6.1485693128884726</v>
+      </c>
+      <c r="I376">
+        <v>181.38</v>
+      </c>
+      <c r="J376">
+        <v>6.38</v>
+      </c>
+      <c r="K376">
+        <v>6.2</v>
+      </c>
+      <c r="L376">
+        <v>10.363585543918564</v>
+      </c>
+      <c r="M376">
+        <v>10.871360736977476</v>
+      </c>
+      <c r="N376">
+        <v>6.5798017264558704</v>
+      </c>
+      <c r="O376">
+        <v>6.59</v>
+      </c>
+      <c r="P376">
+        <v>4.1259019960708096E-3</v>
+      </c>
+      <c r="Q376">
+        <v>4.1496453853131603E-3</v>
+      </c>
+      <c r="R376">
+        <v>0.10887164304902791</v>
+      </c>
+      <c r="S376">
+        <v>0.16752484744707552</v>
+      </c>
+      <c r="T376">
+        <v>4.1438839506346969E-2</v>
+      </c>
+      <c r="U376">
+        <v>9.4910760493227553E-2</v>
+      </c>
+      <c r="V376">
+        <v>0.26980252808229688</v>
+      </c>
+      <c r="W376">
+        <v>0.3426289397444604</v>
+      </c>
+      <c r="X376">
+        <v>109.61</v>
+      </c>
+      <c r="Y376">
+        <v>-2.7087172467350706</v>
+      </c>
+      <c r="Z376">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA376" s="3">
+        <v>6.8282082373870567E-3</v>
+      </c>
+      <c r="AB376" s="3">
+        <v>6.1708479639235904E-3</v>
+      </c>
+      <c r="AC376" s="3">
+        <v>5.0928407590361468E-3</v>
+      </c>
+      <c r="AD376" s="3">
+        <v>4.5824246138035304E-3</v>
+      </c>
+      <c r="AE376" s="3">
+        <v>5.025851343083745E-3</v>
+      </c>
+      <c r="AF376">
+        <v>8023.5650000000005</v>
+      </c>
+      <c r="AG376">
+        <v>10691.205</v>
+      </c>
+      <c r="AH376">
+        <v>12430.7</v>
+      </c>
+      <c r="AI376">
+        <v>10166.85</v>
       </c>
     </row>
   </sheetData>

--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\General\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{913FB43D-7FC1-472A-B50F-ADD43239BF2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADD1AFF-4FA5-4052-9E58-760D42295145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI376"/>
+  <dimension ref="A1:AI377"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -33186,8 +33186,8 @@
       <c r="C376">
         <v>148714931.52043027</v>
       </c>
-      <c r="D376" t="s">
-        <v>23</v>
+      <c r="D376">
+        <v>547</v>
       </c>
       <c r="E376">
         <v>6467</v>
@@ -33281,6 +33281,113 @@
       </c>
       <c r="AI376">
         <v>10166.85</v>
+      </c>
+    </row>
+    <row r="377" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A377" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B377">
+        <v>110.58573206729599</v>
+      </c>
+      <c r="C377">
+        <v>149014273.96068135</v>
+      </c>
+      <c r="D377" t="s">
+        <v>23</v>
+      </c>
+      <c r="E377">
+        <v>8266</v>
+      </c>
+      <c r="F377">
+        <v>2</v>
+      </c>
+      <c r="G377">
+        <v>6.3080142870850784</v>
+      </c>
+      <c r="H377">
+        <v>6.1253515981301447</v>
+      </c>
+      <c r="I377">
+        <v>181.76</v>
+      </c>
+      <c r="J377">
+        <v>6.39</v>
+      </c>
+      <c r="K377">
+        <v>6.18</v>
+      </c>
+      <c r="L377">
+        <v>10.585732067295982</v>
+      </c>
+      <c r="M377">
+        <v>11.103641677985587</v>
+      </c>
+      <c r="N377">
+        <v>6.5797470319790827</v>
+      </c>
+      <c r="O377">
+        <v>6.59</v>
+      </c>
+      <c r="P377">
+        <v>4.2428430565842655E-3</v>
+      </c>
+      <c r="Q377">
+        <v>4.2285381896227494E-3</v>
+      </c>
+      <c r="R377">
+        <v>0.10887267370046715</v>
+      </c>
+      <c r="S377">
+        <v>0.16662897880607513</v>
+      </c>
+      <c r="T377">
+        <v>4.8078238457460731E-2</v>
+      </c>
+      <c r="U377">
+        <v>0.1022173850398489</v>
+      </c>
+      <c r="V377">
+        <v>0.28043767765268957</v>
+      </c>
+      <c r="W377">
+        <v>0.71172388641118634</v>
+      </c>
+      <c r="X377">
+        <v>110.21</v>
+      </c>
+      <c r="Y377">
+        <v>-2.5128834478234996</v>
+      </c>
+      <c r="Z377">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA377" s="3">
+        <v>3.397654112081594E-3</v>
+      </c>
+      <c r="AB377" s="3">
+        <v>6.1745803511004671E-3</v>
+      </c>
+      <c r="AC377" s="3">
+        <v>5.0712286773296625E-3</v>
+      </c>
+      <c r="AD377" s="3">
+        <v>4.5562752261185026E-3</v>
+      </c>
+      <c r="AE377" s="3">
+        <v>5.0182121004602002E-3</v>
+      </c>
+      <c r="AF377">
+        <v>8225.7150000000001</v>
+      </c>
+      <c r="AG377">
+        <v>10398.450000000001</v>
+      </c>
+      <c r="AH377">
+        <v>12072.7</v>
+      </c>
+      <c r="AI377">
+        <v>10133.625</v>
       </c>
     </row>
   </sheetData>

--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\General\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADD1AFF-4FA5-4052-9E58-760D42295145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809B8FE9-015C-4E64-8688-6DCEED566DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI377"/>
+  <dimension ref="A1:AI378"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -33293,8 +33293,8 @@
       <c r="C377">
         <v>149014273.96068135</v>
       </c>
-      <c r="D377" t="s">
-        <v>23</v>
+      <c r="D377">
+        <v>547</v>
       </c>
       <c r="E377">
         <v>8266</v>
@@ -33388,6 +33388,113 @@
       </c>
       <c r="AI377">
         <v>10133.625</v>
+      </c>
+    </row>
+    <row r="378" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A378" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B378">
+        <v>110.64823549108205</v>
+      </c>
+      <c r="C378">
+        <v>149098497.32423306</v>
+      </c>
+      <c r="D378" t="s">
+        <v>23</v>
+      </c>
+      <c r="E378">
+        <v>8163.35</v>
+      </c>
+      <c r="F378">
+        <v>2</v>
+      </c>
+      <c r="G378">
+        <v>6.3076750208385759</v>
+      </c>
+      <c r="H378">
+        <v>6.1229935712785943</v>
+      </c>
+      <c r="I378">
+        <v>181.87</v>
+      </c>
+      <c r="J378">
+        <v>6.39</v>
+      </c>
+      <c r="K378">
+        <v>6.18</v>
+      </c>
+      <c r="L378">
+        <v>10.648235491082048</v>
+      </c>
+      <c r="M378">
+        <v>11.170880897751111</v>
+      </c>
+      <c r="N378">
+        <v>6.5798089751677233</v>
+      </c>
+      <c r="O378">
+        <v>6.59</v>
+      </c>
+      <c r="P378">
+        <v>4.2626391051231276E-3</v>
+      </c>
+      <c r="Q378">
+        <v>4.2369139909858257E-3</v>
+      </c>
+      <c r="R378">
+        <v>0.10887249077647018</v>
+      </c>
+      <c r="S378">
+        <v>0.16620546527518704</v>
+      </c>
+      <c r="T378">
+        <v>5.3185446670767078E-2</v>
+      </c>
+      <c r="U378">
+        <v>0.10397973666003146</v>
+      </c>
+      <c r="V378">
+        <v>0.2812248676518303</v>
+      </c>
+      <c r="W378">
+        <v>0.9596593388668806</v>
+      </c>
+      <c r="X378">
+        <v>110.32</v>
+      </c>
+      <c r="Y378">
+        <v>-2.4577834051178638</v>
+      </c>
+      <c r="Z378">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA378" s="3">
+        <v>2.9664774103741465E-3</v>
+      </c>
+      <c r="AB378" s="3">
+        <v>6.1008417537624241E-3</v>
+      </c>
+      <c r="AC378" s="3">
+        <v>5.0101905218575549E-3</v>
+      </c>
+      <c r="AD378" s="3">
+        <v>4.5214108804700458E-3</v>
+      </c>
+      <c r="AE378" s="3">
+        <v>5.0051425111514022E-3</v>
+      </c>
+      <c r="AF378">
+        <v>8174.39</v>
+      </c>
+      <c r="AG378">
+        <v>10134.725</v>
+      </c>
+      <c r="AH378">
+        <v>11951.045</v>
+      </c>
+      <c r="AI378">
+        <v>10047.755000000001</v>
       </c>
     </row>
   </sheetData>

--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\General\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809B8FE9-015C-4E64-8688-6DCEED566DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0936971E-4969-4150-AAA8-FDB0B898B899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>Fecha</t>
   </si>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI378"/>
+  <dimension ref="A1:AI379"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -33497,6 +33497,113 @@
         <v>10047.755000000001</v>
       </c>
     </row>
+    <row r="379" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A379" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B379">
+        <v>110.88260010972837</v>
+      </c>
+      <c r="C379">
+        <v>149414303.64785898</v>
+      </c>
+      <c r="D379" t="s">
+        <v>23</v>
+      </c>
+      <c r="E379">
+        <v>17442</v>
+      </c>
+      <c r="F379">
+        <v>3</v>
+      </c>
+      <c r="G379">
+        <v>6.3059358787518152</v>
+      </c>
+      <c r="H379">
+        <v>6.0949756312604544</v>
+      </c>
+      <c r="I379">
+        <v>182.26</v>
+      </c>
+      <c r="J379">
+        <v>6.39</v>
+      </c>
+      <c r="K379">
+        <v>6.15</v>
+      </c>
+      <c r="L379">
+        <v>10.882600109728369</v>
+      </c>
+      <c r="M379">
+        <v>11.40927449510154</v>
+      </c>
+      <c r="N379">
+        <v>6.5798987783452922</v>
+      </c>
+      <c r="O379">
+        <v>6.59</v>
+      </c>
+      <c r="P379">
+        <v>4.2652378036881211E-3</v>
+      </c>
+      <c r="Q379">
+        <v>4.2379670923861825E-3</v>
+      </c>
+      <c r="R379">
+        <v>0.10887245118319396</v>
+      </c>
+      <c r="S379">
+        <v>0.16383933890471372</v>
+      </c>
+      <c r="T379">
+        <v>5.5690181942791295E-2</v>
+      </c>
+      <c r="U379">
+        <v>0.10438346416064004</v>
+      </c>
+      <c r="V379">
+        <v>0.28105356859540187</v>
+      </c>
+      <c r="W379">
+        <v>1.5378507161572852</v>
+      </c>
+      <c r="X379">
+        <v>110.39</v>
+      </c>
+      <c r="Y379">
+        <v>-2.2511787151043627</v>
+      </c>
+      <c r="Z379">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA379" s="3">
+        <v>4.4425375058024796E-3</v>
+      </c>
+      <c r="AB379" s="3">
+        <v>6.0650218497618532E-3</v>
+      </c>
+      <c r="AC379" s="3">
+        <v>5.0430432619877896E-3</v>
+      </c>
+      <c r="AD379" s="3">
+        <v>4.5199825311000143E-3</v>
+      </c>
+      <c r="AE379" s="3">
+        <v>5.0157251776762543E-3</v>
+      </c>
+      <c r="AF379">
+        <v>8174.39</v>
+      </c>
+      <c r="AG379">
+        <v>10134.725</v>
+      </c>
+      <c r="AH379">
+        <v>11951.045</v>
+      </c>
+      <c r="AI379">
+        <v>10133.625</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\General\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0936971E-4969-4150-AAA8-FDB0B898B899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>Fecha</t>
   </si>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI379"/>
+  <dimension ref="A1:AI380"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -33604,6 +33604,113 @@
         <v>10133.625</v>
       </c>
     </row>
+    <row r="380" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A380" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B380">
+        <v>110.93759620233544</v>
+      </c>
+      <c r="C380">
+        <v>149488410.88264701</v>
+      </c>
+      <c r="D380" t="s">
+        <v>23</v>
+      </c>
+      <c r="E380">
+        <v>12013</v>
+      </c>
+      <c r="F380">
+        <v>2</v>
+      </c>
+      <c r="G380">
+        <v>6.2981005887571557</v>
+      </c>
+      <c r="H380">
+        <v>6.0943229798683847</v>
+      </c>
+      <c r="I380">
+        <v>182.36</v>
+      </c>
+      <c r="J380">
+        <v>6.38</v>
+      </c>
+      <c r="K380">
+        <v>6.15</v>
+      </c>
+      <c r="L380">
+        <v>10.937596202335431</v>
+      </c>
+      <c r="M380">
+        <v>11.470401058524725</v>
+      </c>
+      <c r="N380">
+        <v>6.5800912687767124</v>
+      </c>
+      <c r="O380">
+        <v>6.59</v>
+      </c>
+      <c r="P380">
+        <v>4.2726974508023379E-3</v>
+      </c>
+      <c r="Q380">
+        <v>4.2607787733794219E-3</v>
+      </c>
+      <c r="R380">
+        <v>0.10887269044339092</v>
+      </c>
+      <c r="S380">
+        <v>0.16333515934545925</v>
+      </c>
+      <c r="T380">
+        <v>5.7475149457286712E-2</v>
+      </c>
+      <c r="U380">
+        <v>0.10816691283528357</v>
+      </c>
+      <c r="V380">
+        <v>0.28650086160606492</v>
+      </c>
+      <c r="W380">
+        <v>1.2730321207119255</v>
+      </c>
+      <c r="X380">
+        <v>110.21100917431193</v>
+      </c>
+      <c r="Y380">
+        <v>-2.2026967781521578</v>
+      </c>
+      <c r="Z380">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA380" s="3">
+        <v>6.5495111927458272E-3</v>
+      </c>
+      <c r="AB380" s="3">
+        <v>6.0890359411225562E-3</v>
+      </c>
+      <c r="AC380" s="3">
+        <v>5.1218642139079004E-3</v>
+      </c>
+      <c r="AD380" s="3">
+        <v>4.5261643750875167E-3</v>
+      </c>
+      <c r="AE380" s="3">
+        <v>5.0278478997764393E-3</v>
+      </c>
+      <c r="AF380">
+        <v>8174.39</v>
+      </c>
+      <c r="AG380">
+        <v>10134.725</v>
+      </c>
+      <c r="AH380">
+        <v>11951.045</v>
+      </c>
+      <c r="AI380">
+        <v>10166.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\General\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eldorado275.sharepoint.com/sites/Compartidos/Documentos compartidos/INVERSIONES/Claude - Fernando/Dashboards ETFs/Dashboards/ETFPESOV/General/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE39A42B-A1C0-4488-9EA7-05A8A58D69F3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Fecha</t>
   </si>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI380"/>
+  <dimension ref="A1:AI381"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -33400,8 +33400,8 @@
       <c r="C378">
         <v>149098497.32423306</v>
       </c>
-      <c r="D378" t="s">
-        <v>23</v>
+      <c r="D378">
+        <v>547</v>
       </c>
       <c r="E378">
         <v>8163.35</v>
@@ -33507,8 +33507,8 @@
       <c r="C379">
         <v>149414303.64785898</v>
       </c>
-      <c r="D379" t="s">
-        <v>23</v>
+      <c r="D379">
+        <v>547</v>
       </c>
       <c r="E379">
         <v>17442</v>
@@ -33614,8 +33614,8 @@
       <c r="C380">
         <v>149488410.88264701</v>
       </c>
-      <c r="D380" t="s">
-        <v>23</v>
+      <c r="D380">
+        <v>547</v>
       </c>
       <c r="E380">
         <v>12013</v>
@@ -33675,7 +33675,7 @@
         <v>1.2730321207119255</v>
       </c>
       <c r="X380">
-        <v>110.21100917431193</v>
+        <v>110.21</v>
       </c>
       <c r="Y380">
         <v>-2.2026967781521578</v>
@@ -33684,19 +33684,19 @@
         <v>-3.9109511967821864</v>
       </c>
       <c r="AA380" s="3">
-        <v>6.5495111927458272E-3</v>
+        <v>6.5586079673874975E-3</v>
       </c>
       <c r="AB380" s="3">
-        <v>6.0890359411225562E-3</v>
+        <v>6.0893391669439448E-3</v>
       </c>
       <c r="AC380" s="3">
-        <v>5.1218642139079004E-3</v>
+        <v>5.1220158268185951E-3</v>
       </c>
       <c r="AD380" s="3">
-        <v>4.5261643750875167E-3</v>
+        <v>4.5262149127244149E-3</v>
       </c>
       <c r="AE380" s="3">
-        <v>5.0278478997764393E-3</v>
+        <v>5.0278731685948885E-3</v>
       </c>
       <c r="AF380">
         <v>8174.39</v>
@@ -33708,10 +33708,430 @@
         <v>11951.045</v>
       </c>
       <c r="AI380">
+        <v>10166.85</v>
+      </c>
+    </row>
+    <row r="381" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A381" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B381">
+        <v>110.96282388231509</v>
+      </c>
+      <c r="C381">
+        <v>149522405.18141958</v>
+      </c>
+      <c r="D381" t="s">
+        <v>23</v>
+      </c>
+      <c r="E381">
+        <v>6330</v>
+      </c>
+      <c r="F381">
+        <v>1</v>
+      </c>
+      <c r="G381">
+        <v>6.2929012643511895</v>
+      </c>
+      <c r="H381">
+        <v>6.0855058477006061</v>
+      </c>
+      <c r="I381">
+        <v>182.39</v>
+      </c>
+      <c r="J381">
+        <v>6.37</v>
+      </c>
+      <c r="K381">
+        <v>6.1400000000000006</v>
+      </c>
+      <c r="L381">
+        <v>10.962823882315087</v>
+      </c>
+      <c r="M381">
+        <v>11.488739027551675</v>
+      </c>
+      <c r="N381">
+        <v>6.5800342782742991</v>
+      </c>
+      <c r="O381">
+        <v>6.59</v>
+      </c>
+      <c r="P381">
+        <v>4.5155474527189968E-3</v>
+      </c>
+      <c r="Q381">
+        <v>4.3881562329353913E-3</v>
+      </c>
+      <c r="R381">
+        <v>0.10887423283591198</v>
+      </c>
+      <c r="S381">
+        <v>0.16180186346515854</v>
+      </c>
+      <c r="T381">
+        <v>6.3806905287266957E-2</v>
+      </c>
+      <c r="U381">
+        <v>9.6631147641912385E-2</v>
+      </c>
+      <c r="V381">
+        <v>0.2744533850668196</v>
+      </c>
+      <c r="W381">
+        <v>0.79918902747961873</v>
+      </c>
+      <c r="X381">
+        <v>111.05</v>
+      </c>
+      <c r="Y381">
+        <v>-2.1804572565380931</v>
+      </c>
+      <c r="Z381">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA381" s="3">
+        <v>7.8563355396732426E-4</v>
+      </c>
+      <c r="AB381" s="3">
+        <v>6.1053776480864486E-3</v>
+      </c>
+      <c r="AC381" s="3">
+        <v>5.1144808154072689E-3</v>
+      </c>
+      <c r="AD381" s="3">
+        <v>4.497820667830975E-3</v>
+      </c>
+      <c r="AE381" s="3">
+        <v>5.0299142352809457E-3</v>
+      </c>
+      <c r="AF381">
+        <v>8012.5249999999996</v>
+      </c>
+      <c r="AG381">
+        <v>10047.755000000001</v>
+      </c>
+      <c r="AH381">
+        <v>11860.42</v>
+      </c>
+      <c r="AI381">
         <v>10166.85</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006CC87EF38A8DD0408B89B7B34D0336DC" ma:contentTypeVersion="20" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a30c2ca5bc864785a186dec6b0346788">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe" xmlns:ns3="dd854d95-092e-48c7-992a-80d5cc5badc3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2932ec1554b414302dd4a6579c5666bc" ns2:_="" ns3:_="">
+    <xsd:import namespace="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
+    <xsd:import namespace="dd854d95-092e-48c7-992a-80d5cc5badc3"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="79e0f7db-8182-4759-9b2a-fe8a1e4ed8f9" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="dd854d95-092e-48c7-992a-80d5cc5badc3" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{10da0788-77cb-43eb-86d7-8924f47adefb}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="dd854d95-092e-48c7-992a-80d5cc5badc3">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="dd854d95-092e-48c7-992a-80d5cc5badc3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BABE8802-F313-4DEC-9147-95F411D9A097}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
+    <ds:schemaRef ds:uri="dd854d95-092e-48c7-992a-80d5cc5badc3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dd854d95-092e-48c7-992a-80d5cc5badc3"/>
+    <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eldorado275.sharepoint.com/sites/Compartidos/Documentos compartidos/INVERSIONES/Claude - Fernando/Dashboards ETFs/Dashboards/ETFPESOV/General/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE39A42B-A1C0-4488-9EA7-05A8A58D69F3}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7C32A59-1137-4938-AC21-925F17D9BB51}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>Fecha</t>
   </si>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI381"/>
+  <dimension ref="A1:AI382"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -33818,21 +33818,119 @@
         <v>10166.85</v>
       </c>
     </row>
+    <row r="382" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A382" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B382">
+        <v>110.93324331103148</v>
+      </c>
+      <c r="C382">
+        <v>149482545.36161491</v>
+      </c>
+      <c r="D382" t="s">
+        <v>23</v>
+      </c>
+      <c r="E382">
+        <v>7081</v>
+      </c>
+      <c r="F382">
+        <v>3</v>
+      </c>
+      <c r="G382">
+        <v>6.288239921945328</v>
+      </c>
+      <c r="H382">
+        <v>6.0903486862256191</v>
+      </c>
+      <c r="I382">
+        <v>182.35</v>
+      </c>
+      <c r="J382">
+        <v>6.37</v>
+      </c>
+      <c r="K382">
+        <v>6.1400000000000006</v>
+      </c>
+      <c r="L382">
+        <v>10.933243311031472</v>
+      </c>
+      <c r="M382">
+        <v>11.46428840218241</v>
+      </c>
+      <c r="N382">
+        <v>6.5801933195998439</v>
+      </c>
+      <c r="O382">
+        <v>6.59</v>
+      </c>
+      <c r="P382">
+        <v>4.5363769667598388E-3</v>
+      </c>
+      <c r="Q382">
+        <v>4.3801355153983736E-3</v>
+      </c>
+      <c r="R382">
+        <v>0.10887413000386073</v>
+      </c>
+      <c r="S382">
+        <v>0.16180189630928665</v>
+      </c>
+      <c r="T382">
+        <v>6.9598406231108356E-2</v>
+      </c>
+      <c r="U382">
+        <v>0.10206207688402413</v>
+      </c>
+      <c r="V382">
+        <v>0.27708819090093151</v>
+      </c>
+      <c r="W382">
+        <v>0.80353982728544882</v>
+      </c>
+      <c r="X382">
+        <v>110.64</v>
+      </c>
+      <c r="Y382">
+        <v>-2.2065340798904209</v>
+      </c>
+      <c r="Z382">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA382" s="3">
+        <v>2.6434214152496471E-3</v>
+      </c>
+      <c r="AB382" s="3">
+        <v>6.1196594259988503E-3</v>
+      </c>
+      <c r="AC382" s="3">
+        <v>5.0996755716583072E-3</v>
+      </c>
+      <c r="AD382" s="3">
+        <v>4.4939128242007E-3</v>
+      </c>
+      <c r="AE382" s="3">
+        <v>5.0225149276161727E-3</v>
+      </c>
+      <c r="AF382">
+        <v>8012.5249999999996</v>
+      </c>
+      <c r="AG382">
+        <v>9703.1049999999996</v>
+      </c>
+      <c r="AH382">
+        <v>11769.724999999999</v>
+      </c>
+      <c r="AI382">
+        <v>10133.625</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006CC87EF38A8DD0408B89B7B34D0336DC" ma:contentTypeVersion="20" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a30c2ca5bc864785a186dec6b0346788">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe" xmlns:ns3="dd854d95-092e-48c7-992a-80d5cc5badc3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2932ec1554b414302dd4a6579c5666bc" ns2:_="" ns3:_="">
     <xsd:import namespace="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
@@ -34087,6 +34185,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -34099,14 +34206,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BABE8802-F313-4DEC-9147-95F411D9A097}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34125,6 +34224,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
   <ds:schemaRefs>

--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eldorado275.sharepoint.com/sites/Compartidos/Documentos compartidos/INVERSIONES/Claude - Fernando/Dashboards ETFs/Dashboards/ETFPESOV/General/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7C32A59-1137-4938-AC21-925F17D9BB51}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46E1BE6E-3CD5-4B25-B6B5-847DBB7D6BCD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>Fecha</t>
   </si>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI382"/>
+  <dimension ref="A1:AI383"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -33925,12 +33925,130 @@
         <v>10133.625</v>
       </c>
     </row>
+    <row r="383" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A383" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B383">
+        <v>111.00291718372182</v>
+      </c>
+      <c r="C383">
+        <v>149576430.90506515</v>
+      </c>
+      <c r="D383" t="s">
+        <v>23</v>
+      </c>
+      <c r="E383">
+        <v>5626</v>
+      </c>
+      <c r="F383">
+        <v>0</v>
+      </c>
+      <c r="G383">
+        <v>6.2844734273861818</v>
+      </c>
+      <c r="H383">
+        <v>6.0775785996445233</v>
+      </c>
+      <c r="I383">
+        <v>182.46</v>
+      </c>
+      <c r="J383">
+        <v>6.37</v>
+      </c>
+      <c r="K383">
+        <v>6.13</v>
+      </c>
+      <c r="L383">
+        <v>11.002917183721816</v>
+      </c>
+      <c r="M383">
+        <v>11.531527621947912</v>
+      </c>
+      <c r="N383">
+        <v>6.5802389363795344</v>
+      </c>
+      <c r="O383">
+        <v>6.59</v>
+      </c>
+      <c r="P383">
+        <v>3.7651254182885976E-3</v>
+      </c>
+      <c r="Q383">
+        <v>4.4009893427019746E-3</v>
+      </c>
+      <c r="R383">
+        <v>0.10887456566897875</v>
+      </c>
+      <c r="S383">
+        <v>0.16176920419437477</v>
+      </c>
+      <c r="T383">
+        <v>6.6216530631635351E-2</v>
+      </c>
+      <c r="U383">
+        <v>9.6219291162780163E-2</v>
+      </c>
+      <c r="V383">
+        <v>0.2686153053359952</v>
+      </c>
+      <c r="W383">
+        <v>0.73013291473398301</v>
+      </c>
+      <c r="X383">
+        <v>110.31</v>
+      </c>
+      <c r="Y383">
+        <v>-2.1451129108062239</v>
+      </c>
+      <c r="Z383">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA383" s="3">
+        <v>6.2423330963001789E-3</v>
+      </c>
+      <c r="AB383" s="3">
+        <v>6.2623817475528252E-3</v>
+      </c>
+      <c r="AC383" s="3">
+        <v>5.1958176410386121E-3</v>
+      </c>
+      <c r="AD383" s="3">
+        <v>4.5274259400711796E-3</v>
+      </c>
+      <c r="AE383" s="3">
+        <v>5.0356170096278923E-3</v>
+      </c>
+      <c r="AF383">
+        <v>8012.5249999999996</v>
+      </c>
+      <c r="AG383">
+        <v>9411.880000000001</v>
+      </c>
+      <c r="AH383">
+        <v>11551.599999999999</v>
+      </c>
+      <c r="AI383">
+        <v>10133.625</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="dd854d95-092e-48c7-992a-80d5cc5badc3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006CC87EF38A8DD0408B89B7B34D0336DC" ma:contentTypeVersion="20" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a30c2ca5bc864785a186dec6b0346788">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe" xmlns:ns3="dd854d95-092e-48c7-992a-80d5cc5badc3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2932ec1554b414302dd4a6579c5666bc" ns2:_="" ns3:_="">
     <xsd:import namespace="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
@@ -34185,7 +34303,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -34194,18 +34312,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="dd854d95-092e-48c7-992a-80d5cc5badc3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dd854d95-092e-48c7-992a-80d5cc5badc3"/>
+    <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BABE8802-F313-4DEC-9147-95F411D9A097}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34224,21 +34342,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="dd854d95-092e-48c7-992a-80d5cc5badc3"/>
-    <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eldorado275.sharepoint.com/sites/Compartidos/Documentos compartidos/INVERSIONES/Claude - Fernando/Dashboards ETFs/Dashboards/ETFPESOV/General/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46E1BE6E-3CD5-4B25-B6B5-847DBB7D6BCD}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2551843B-4ABC-48D4-A6AB-35263E529AF9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Fecha</t>
   </si>
@@ -33721,8 +33721,8 @@
       <c r="C381">
         <v>149522405.18141958</v>
       </c>
-      <c r="D381" t="s">
-        <v>23</v>
+      <c r="D381">
+        <v>547</v>
       </c>
       <c r="E381">
         <v>6330</v>
@@ -33828,8 +33828,8 @@
       <c r="C382">
         <v>149482545.36161491</v>
       </c>
-      <c r="D382" t="s">
-        <v>23</v>
+      <c r="D382">
+        <v>547</v>
       </c>
       <c r="E382">
         <v>7081</v>
@@ -34038,17 +34038,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="dd854d95-092e-48c7-992a-80d5cc5badc3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006CC87EF38A8DD0408B89B7B34D0336DC" ma:contentTypeVersion="20" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a30c2ca5bc864785a186dec6b0346788">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe" xmlns:ns3="dd854d95-092e-48c7-992a-80d5cc5badc3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2932ec1554b414302dd4a6579c5666bc" ns2:_="" ns3:_="">
     <xsd:import namespace="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
@@ -34303,6 +34292,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="dd854d95-092e-48c7-992a-80d5cc5badc3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -34313,17 +34313,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="dd854d95-092e-48c7-992a-80d5cc5badc3"/>
-    <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BABE8802-F313-4DEC-9147-95F411D9A097}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34342,6 +34331,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dd854d95-092e-48c7-992a-80d5cc5badc3"/>
+    <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
   <ds:schemaRefs>

--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eldorado275.sharepoint.com/sites/Compartidos/Documentos compartidos/INVERSIONES/Claude - Fernando/Dashboards ETFs/Dashboards/ETFPESOV/General/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2551843B-4ABC-48D4-A6AB-35263E529AF9}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FD8F9CE-4411-4A5E-B27C-F1276393B866}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI383"/>
+  <dimension ref="A1:AI384"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -33935,8 +33935,8 @@
       <c r="C383">
         <v>149576430.90506515</v>
       </c>
-      <c r="D383" t="s">
-        <v>23</v>
+      <c r="D383">
+        <v>547</v>
       </c>
       <c r="E383">
         <v>5626</v>
@@ -34029,6 +34029,113 @@
         <v>11551.599999999999</v>
       </c>
       <c r="AI383">
+        <v>10133.625</v>
+      </c>
+    </row>
+    <row r="384" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A384" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B384">
+        <v>110.97623471985419</v>
+      </c>
+      <c r="C384">
+        <v>149540476.28500351</v>
+      </c>
+      <c r="D384" t="s">
+        <v>23</v>
+      </c>
+      <c r="E384">
+        <v>3640</v>
+      </c>
+      <c r="F384">
+        <v>4</v>
+      </c>
+      <c r="G384">
+        <v>6.2805929937581944</v>
+      </c>
+      <c r="H384">
+        <v>6.0816649836833481</v>
+      </c>
+      <c r="I384">
+        <v>182.41</v>
+      </c>
+      <c r="J384">
+        <v>6.36</v>
+      </c>
+      <c r="K384">
+        <v>6.1400000000000006</v>
+      </c>
+      <c r="L384">
+        <v>10.976234719854183</v>
+      </c>
+      <c r="M384">
+        <v>11.500964340236308</v>
+      </c>
+      <c r="N384">
+        <v>6.5804516284538277</v>
+      </c>
+      <c r="O384">
+        <v>6.59</v>
+      </c>
+      <c r="P384">
+        <v>3.850815397768304E-3</v>
+      </c>
+      <c r="Q384">
+        <v>4.4417928758354033E-3</v>
+      </c>
+      <c r="R384">
+        <v>0.10887471534382859</v>
+      </c>
+      <c r="S384">
+        <v>0.16164506699333742</v>
+      </c>
+      <c r="T384">
+        <v>6.3394660549775939E-2</v>
+      </c>
+      <c r="U384">
+        <v>9.4837944022285736E-2</v>
+      </c>
+      <c r="V384">
+        <v>0.26352267466290824</v>
+      </c>
+      <c r="W384">
+        <v>0.85319385399147407</v>
+      </c>
+      <c r="X384">
+        <v>110.3</v>
+      </c>
+      <c r="Y384">
+        <v>-2.1686349006356131</v>
+      </c>
+      <c r="Z384">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA384" s="3">
+        <v>6.0935093136045282E-3</v>
+      </c>
+      <c r="AB384" s="3">
+        <v>6.4334827566881504E-3</v>
+      </c>
+      <c r="AC384" s="3">
+        <v>5.2157077984132921E-3</v>
+      </c>
+      <c r="AD384" s="3">
+        <v>4.556874568558713E-3</v>
+      </c>
+      <c r="AE384" s="3">
+        <v>5.0504394127232934E-3</v>
+      </c>
+      <c r="AF384">
+        <v>7699.6</v>
+      </c>
+      <c r="AG384">
+        <v>9313.7799999999988</v>
+      </c>
+      <c r="AH384">
+        <v>11262.025</v>
+      </c>
+      <c r="AI384">
         <v>10133.625</v>
       </c>
     </row>
@@ -34293,6 +34400,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="dd854d95-092e-48c7-992a-80d5cc5badc3" xsi:nil="true"/>
@@ -34301,15 +34417,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -34332,6 +34439,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -34340,12 +34455,4 @@
     <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eldorado275.sharepoint.com/sites/Compartidos/Documentos compartidos/INVERSIONES/Claude - Fernando/Dashboards ETFs/Dashboards/ETFPESOV/General/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FD8F9CE-4411-4A5E-B27C-F1276393B866}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7374E15-A041-4DBF-BB08-8F4F00249DD6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI384"/>
+  <dimension ref="A1:AI385"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -34042,8 +34042,8 @@
       <c r="C384">
         <v>149540476.28500351</v>
       </c>
-      <c r="D384" t="s">
-        <v>23</v>
+      <c r="D384">
+        <v>547</v>
       </c>
       <c r="E384">
         <v>3640</v>
@@ -34137,6 +34137,113 @@
       </c>
       <c r="AI384">
         <v>10133.625</v>
+      </c>
+    </row>
+    <row r="385" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A385" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B385">
+        <v>110.66204782017122</v>
+      </c>
+      <c r="C385">
+        <v>149117109.43768072</v>
+      </c>
+      <c r="D385" t="s">
+        <v>23</v>
+      </c>
+      <c r="E385">
+        <v>3875</v>
+      </c>
+      <c r="F385">
+        <v>1</v>
+      </c>
+      <c r="G385">
+        <v>6.257994912695966</v>
+      </c>
+      <c r="H385">
+        <v>6.1178635602105329</v>
+      </c>
+      <c r="I385">
+        <v>181.86</v>
+      </c>
+      <c r="J385">
+        <v>6.34</v>
+      </c>
+      <c r="K385">
+        <v>6.18</v>
+      </c>
+      <c r="L385">
+        <v>10.662047820171217</v>
+      </c>
+      <c r="M385">
+        <v>11.164768241408796</v>
+      </c>
+      <c r="N385">
+        <v>6.5802089420869345</v>
+      </c>
+      <c r="O385">
+        <v>6.59</v>
+      </c>
+      <c r="P385">
+        <v>5.3274140873484253E-3</v>
+      </c>
+      <c r="Q385">
+        <v>5.1201673453697997E-3</v>
+      </c>
+      <c r="R385">
+        <v>0.10888490052658138</v>
+      </c>
+      <c r="S385">
+        <v>0.16162454220478117</v>
+      </c>
+      <c r="T385">
+        <v>3.97819975342939E-2</v>
+      </c>
+      <c r="U385">
+        <v>7.7602417112676569E-2</v>
+      </c>
+      <c r="V385">
+        <v>0.24290535903727095</v>
+      </c>
+      <c r="W385">
+        <v>0.88550105268481172</v>
+      </c>
+      <c r="X385">
+        <v>110.71</v>
+      </c>
+      <c r="Y385">
+        <v>-2.4456071133793111</v>
+      </c>
+      <c r="Z385">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA385" s="3">
+        <v>4.3332091510439597E-4</v>
+      </c>
+      <c r="AB385" s="3">
+        <v>6.3636340066774546E-3</v>
+      </c>
+      <c r="AC385" s="3">
+        <v>5.2063039663814703E-3</v>
+      </c>
+      <c r="AD385" s="3">
+        <v>4.5295848565040956E-3</v>
+      </c>
+      <c r="AE385" s="3">
+        <v>5.0422406809099854E-3</v>
+      </c>
+      <c r="AF385">
+        <v>7699.6</v>
+      </c>
+      <c r="AG385">
+        <v>9185.5600000000013</v>
+      </c>
+      <c r="AH385">
+        <v>11262.025</v>
+      </c>
+      <c r="AI385">
+        <v>10047.755000000001</v>
       </c>
     </row>
   </sheetData>
@@ -34145,6 +34252,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006CC87EF38A8DD0408B89B7B34D0336DC" ma:contentTypeVersion="20" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a30c2ca5bc864785a186dec6b0346788">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe" xmlns:ns3="dd854d95-092e-48c7-992a-80d5cc5badc3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2932ec1554b414302dd4a6579c5666bc" ns2:_="" ns3:_="">
     <xsd:import namespace="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
@@ -34399,15 +34515,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -34420,6 +34527,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BABE8802-F313-4DEC-9147-95F411D9A097}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34438,14 +34553,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
   <ds:schemaRefs>

--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eldorado275.sharepoint.com/sites/Compartidos/Documentos compartidos/INVERSIONES/Claude - Fernando/Dashboards ETFs/Dashboards/ETFPESOV/General/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7374E15-A041-4DBF-BB08-8F4F00249DD6}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DFE71AC-73D6-4C04-B582-D4C61979B77F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>Fecha</t>
   </si>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI385"/>
+  <dimension ref="A1:AI386"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -34246,21 +34246,119 @@
         <v>10047.755000000001</v>
       </c>
     </row>
+    <row r="386" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A386" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B386">
+        <v>110.70075809273899</v>
+      </c>
+      <c r="C386">
+        <v>149169271.52996579</v>
+      </c>
+      <c r="D386" t="s">
+        <v>23</v>
+      </c>
+      <c r="E386">
+        <v>4207</v>
+      </c>
+      <c r="F386">
+        <v>1</v>
+      </c>
+      <c r="G386">
+        <v>6.2535662709234412</v>
+      </c>
+      <c r="H386">
+        <v>6.1074799672460438</v>
+      </c>
+      <c r="I386">
+        <v>181.91</v>
+      </c>
+      <c r="J386">
+        <v>6.33</v>
+      </c>
+      <c r="K386">
+        <v>6.17</v>
+      </c>
+      <c r="L386">
+        <v>10.700758092739004</v>
+      </c>
+      <c r="M386">
+        <v>11.195331523120377</v>
+      </c>
+      <c r="N386">
+        <v>6.5801247994769483</v>
+      </c>
+      <c r="O386">
+        <v>6.59</v>
+      </c>
+      <c r="P386">
+        <v>5.5558377229501833E-3</v>
+      </c>
+      <c r="Q386">
+        <v>5.2370325567100019E-3</v>
+      </c>
+      <c r="R386">
+        <v>0.10888694254458398</v>
+      </c>
+      <c r="S386">
+        <v>0.16020987650211513</v>
+      </c>
+      <c r="T386">
+        <v>3.3845142585198218E-2</v>
+      </c>
+      <c r="U386">
+        <v>6.7183424765249189E-2</v>
+      </c>
+      <c r="V386">
+        <v>0.23164322254511927</v>
+      </c>
+      <c r="W386">
+        <v>1.3062801901675192</v>
+      </c>
+      <c r="X386">
+        <v>110.71</v>
+      </c>
+      <c r="Y386">
+        <v>-2.4114819800277076</v>
+      </c>
+      <c r="Z386">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA386" s="3">
+        <v>8.3485492061941002E-5</v>
+      </c>
+      <c r="AB386" s="3">
+        <v>6.3608324852667984E-3</v>
+      </c>
+      <c r="AC386" s="3">
+        <v>5.1734594067870858E-3</v>
+      </c>
+      <c r="AD386" s="3">
+        <v>4.489232869199597E-3</v>
+      </c>
+      <c r="AE386" s="3">
+        <v>5.0351787096865469E-3</v>
+      </c>
+      <c r="AF386">
+        <v>7309.25</v>
+      </c>
+      <c r="AG386">
+        <v>9185.5600000000013</v>
+      </c>
+      <c r="AH386">
+        <v>11097.075000000001</v>
+      </c>
+      <c r="AI386">
+        <v>10047.755000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006CC87EF38A8DD0408B89B7B34D0336DC" ma:contentTypeVersion="20" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a30c2ca5bc864785a186dec6b0346788">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe" xmlns:ns3="dd854d95-092e-48c7-992a-80d5cc5badc3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2932ec1554b414302dd4a6579c5666bc" ns2:_="" ns3:_="">
     <xsd:import namespace="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
@@ -34515,6 +34613,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -34527,14 +34634,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BABE8802-F313-4DEC-9147-95F411D9A097}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34553,6 +34652,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
   <ds:schemaRefs>

--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eldorado275.sharepoint.com/sites/Compartidos/Documentos compartidos/INVERSIONES/Claude - Fernando/Dashboards ETFs/Dashboards/ETFPESOV/General/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DFE71AC-73D6-4C04-B582-D4C61979B77F}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6BA0012-12F2-4CBA-A0AF-4BBA180F91D9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Fecha</t>
   </si>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI386"/>
+  <dimension ref="A1:AI387"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -34149,8 +34149,8 @@
       <c r="C385">
         <v>149117109.43768072</v>
       </c>
-      <c r="D385" t="s">
-        <v>23</v>
+      <c r="D385">
+        <v>547</v>
       </c>
       <c r="E385">
         <v>3875</v>
@@ -34256,8 +34256,8 @@
       <c r="C386">
         <v>149169271.52996579</v>
       </c>
-      <c r="D386" t="s">
-        <v>23</v>
+      <c r="D386">
+        <v>547</v>
       </c>
       <c r="E386">
         <v>4207</v>
@@ -34350,6 +34350,113 @@
         <v>11097.075000000001</v>
       </c>
       <c r="AI386">
+        <v>10047.755000000001</v>
+      </c>
+    </row>
+    <row r="387" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A387" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B387">
+        <v>110.56514855473955</v>
+      </c>
+      <c r="C387">
+        <v>148986537.67751154</v>
+      </c>
+      <c r="D387" t="s">
+        <v>23</v>
+      </c>
+      <c r="E387">
+        <v>1661</v>
+      </c>
+      <c r="F387">
+        <v>0</v>
+      </c>
+      <c r="G387">
+        <v>6.2447554962820693</v>
+      </c>
+      <c r="H387">
+        <v>6.1236818868259881</v>
+      </c>
+      <c r="I387">
+        <v>181.69</v>
+      </c>
+      <c r="J387">
+        <v>6.33</v>
+      </c>
+      <c r="K387">
+        <v>6.18</v>
+      </c>
+      <c r="L387">
+        <v>10.565148554739556</v>
+      </c>
+      <c r="M387">
+        <v>11.060853083589372</v>
+      </c>
+      <c r="N387">
+        <v>6.5801848419009143</v>
+      </c>
+      <c r="O387">
+        <v>6.59</v>
+      </c>
+      <c r="P387">
+        <v>5.5056735938059089E-3</v>
+      </c>
+      <c r="Q387">
+        <v>5.2308816689338811E-3</v>
+      </c>
+      <c r="R387">
+        <v>0.10888683573370395</v>
+      </c>
+      <c r="S387">
+        <v>0.15742296462881389</v>
+      </c>
+      <c r="T387">
+        <v>3.5802485459057731E-2</v>
+      </c>
+      <c r="U387">
+        <v>7.0734026280738771E-2</v>
+      </c>
+      <c r="V387">
+        <v>0.23536755742641358</v>
+      </c>
+      <c r="W387">
+        <v>0.69268353362095247</v>
+      </c>
+      <c r="X387">
+        <v>110.73</v>
+      </c>
+      <c r="Y387">
+        <v>-2.5310288925398328</v>
+      </c>
+      <c r="Z387">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA387" s="3">
+        <v>1.4909892259480362E-3</v>
+      </c>
+      <c r="AB387" s="3">
+        <v>6.326647911982097E-3</v>
+      </c>
+      <c r="AC387" s="3">
+        <v>5.1695087203325555E-3</v>
+      </c>
+      <c r="AD387" s="3">
+        <v>4.4552992191686947E-3</v>
+      </c>
+      <c r="AE387" s="3">
+        <v>5.0246184530679588E-3</v>
+      </c>
+      <c r="AF387">
+        <v>7309.25</v>
+      </c>
+      <c r="AG387">
+        <v>9107.5250000000015</v>
+      </c>
+      <c r="AH387">
+        <v>11002.15</v>
+      </c>
+      <c r="AI387">
         <v>10047.755000000001</v>
       </c>
     </row>
@@ -34359,6 +34466,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="dd854d95-092e-48c7-992a-80d5cc5badc3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006CC87EF38A8DD0408B89B7B34D0336DC" ma:contentTypeVersion="20" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a30c2ca5bc864785a186dec6b0346788">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe" xmlns:ns3="dd854d95-092e-48c7-992a-80d5cc5badc3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2932ec1554b414302dd4a6579c5666bc" ns2:_="" ns3:_="">
     <xsd:import namespace="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
@@ -34613,27 +34740,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dd854d95-092e-48c7-992a-80d5cc5badc3"/>
+    <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="dd854d95-092e-48c7-992a-80d5cc5badc3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BABE8802-F313-4DEC-9147-95F411D9A097}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34650,23 +34776,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="dd854d95-092e-48c7-992a-80d5cc5badc3"/>
-    <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eldorado275.sharepoint.com/sites/Compartidos/Documentos compartidos/INVERSIONES/Claude - Fernando/Dashboards ETFs/Dashboards/ETFPESOV/General/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6BA0012-12F2-4CBA-A0AF-4BBA180F91D9}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAADA12D-C4D9-4D5B-92A4-5C09ADB4CEF1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI387"/>
+  <dimension ref="A1:AI388"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -34363,8 +34363,8 @@
       <c r="C387">
         <v>148986537.67751154</v>
       </c>
-      <c r="D387" t="s">
-        <v>23</v>
+      <c r="D387">
+        <v>547</v>
       </c>
       <c r="E387">
         <v>1661</v>
@@ -34457,6 +34457,113 @@
         <v>11002.15</v>
       </c>
       <c r="AI387">
+        <v>10047.755000000001</v>
+      </c>
+    </row>
+    <row r="388" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A388" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B388">
+        <v>110.58423558292399</v>
+      </c>
+      <c r="C388">
+        <v>149012257.44799009</v>
+      </c>
+      <c r="D388" t="s">
+        <v>23</v>
+      </c>
+      <c r="E388">
+        <v>4901</v>
+      </c>
+      <c r="F388">
+        <v>0</v>
+      </c>
+      <c r="G388">
+        <v>6.2429520537401331</v>
+      </c>
+      <c r="H388">
+        <v>6.122656671910419</v>
+      </c>
+      <c r="I388">
+        <v>181.72</v>
+      </c>
+      <c r="J388">
+        <v>6.32</v>
+      </c>
+      <c r="K388">
+        <v>6.18</v>
+      </c>
+      <c r="L388">
+        <v>10.584235582923984</v>
+      </c>
+      <c r="M388">
+        <v>11.079191052616322</v>
+      </c>
+      <c r="N388">
+        <v>6.5802634505977471</v>
+      </c>
+      <c r="O388">
+        <v>6.59</v>
+      </c>
+      <c r="P388">
+        <v>5.4971790400755944E-3</v>
+      </c>
+      <c r="Q388">
+        <v>5.2190993416640907E-3</v>
+      </c>
+      <c r="R388">
+        <v>0.10888648013886966</v>
+      </c>
+      <c r="S388">
+        <v>0.15742295613487764</v>
+      </c>
+      <c r="T388">
+        <v>3.7165276177741902E-2</v>
+      </c>
+      <c r="U388">
+        <v>6.7268705945622287E-2</v>
+      </c>
+      <c r="V388">
+        <v>0.38391924093205132</v>
+      </c>
+      <c r="W388">
+        <v>0.69240833664638846</v>
+      </c>
+      <c r="X388">
+        <v>111.39</v>
+      </c>
+      <c r="Y388">
+        <v>-2.514202677200239</v>
+      </c>
+      <c r="Z388">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA388" s="3">
+        <v>7.2864311339546628E-3</v>
+      </c>
+      <c r="AB388" s="3">
+        <v>6.5077773272583569E-3</v>
+      </c>
+      <c r="AC388" s="3">
+        <v>5.2311016256708903E-3</v>
+      </c>
+      <c r="AD388" s="3">
+        <v>4.4636686001837244E-3</v>
+      </c>
+      <c r="AE388" s="3">
+        <v>5.0362676944243302E-3</v>
+      </c>
+      <c r="AF388">
+        <v>7309.25</v>
+      </c>
+      <c r="AG388">
+        <v>9107.5250000000015</v>
+      </c>
+      <c r="AH388">
+        <v>11002.15</v>
+      </c>
+      <c r="AI388">
         <v>10047.755000000001</v>
       </c>
     </row>
@@ -34466,26 +34573,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="dd854d95-092e-48c7-992a-80d5cc5badc3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006CC87EF38A8DD0408B89B7B34D0336DC" ma:contentTypeVersion="20" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a30c2ca5bc864785a186dec6b0346788">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe" xmlns:ns3="dd854d95-092e-48c7-992a-80d5cc5badc3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2932ec1554b414302dd4a6579c5666bc" ns2:_="" ns3:_="">
     <xsd:import namespace="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
@@ -34740,26 +34827,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="dd854d95-092e-48c7-992a-80d5cc5badc3"/>
-    <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="dd854d95-092e-48c7-992a-80d5cc5badc3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BABE8802-F313-4DEC-9147-95F411D9A097}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34776,4 +34864,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dd854d95-092e-48c7-992a-80d5cc5badc3"/>
+    <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eldorado275.sharepoint.com/sites/Compartidos/Documentos compartidos/INVERSIONES/Claude - Fernando/Dashboards ETFs/Dashboards/ETFPESOV/General/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAADA12D-C4D9-4D5B-92A4-5C09ADB4CEF1}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04F98192-866C-41F4-83E7-79F6E06BA807}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI388"/>
+  <dimension ref="A1:AI389"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -34470,8 +34470,8 @@
       <c r="C388">
         <v>149012257.44799009</v>
       </c>
-      <c r="D388" t="s">
-        <v>23</v>
+      <c r="D388">
+        <v>547</v>
       </c>
       <c r="E388">
         <v>4901</v>
@@ -34564,6 +34564,113 @@
         <v>11002.15</v>
       </c>
       <c r="AI388">
+        <v>10047.755000000001</v>
+      </c>
+    </row>
+    <row r="389" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A389" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B389">
+        <v>110.63281666031268</v>
+      </c>
+      <c r="C389">
+        <v>149077720.44977134</v>
+      </c>
+      <c r="D389" t="s">
+        <v>23</v>
+      </c>
+      <c r="E389">
+        <v>5982.21</v>
+      </c>
+      <c r="F389">
+        <v>1</v>
+      </c>
+      <c r="G389">
+        <v>6.2415686970464197</v>
+      </c>
+      <c r="H389">
+        <v>6.1189093714566933</v>
+      </c>
+      <c r="I389">
+        <v>181.8</v>
+      </c>
+      <c r="J389">
+        <v>6.32</v>
+      </c>
+      <c r="K389">
+        <v>6.18</v>
+      </c>
+      <c r="L389">
+        <v>10.632816660312683</v>
+      </c>
+      <c r="M389">
+        <v>11.128092303354876</v>
+      </c>
+      <c r="N389">
+        <v>6.5804636810530992</v>
+      </c>
+      <c r="O389">
+        <v>6.59</v>
+      </c>
+      <c r="P389">
+        <v>5.492734709737223E-3</v>
+      </c>
+      <c r="Q389">
+        <v>5.2167169673811376E-3</v>
+      </c>
+      <c r="R389">
+        <v>0.10828629997367131</v>
+      </c>
+      <c r="S389">
+        <v>0.15703411239196041</v>
+      </c>
+      <c r="T389">
+        <v>3.4154539787378813E-2</v>
+      </c>
+      <c r="U389">
+        <v>6.3370987070965334E-2</v>
+      </c>
+      <c r="V389">
+        <v>0.25273781275788609</v>
+      </c>
+      <c r="W389">
+        <v>0.46557458543317054</v>
+      </c>
+      <c r="X389">
+        <v>110.78</v>
+      </c>
+      <c r="Y389">
+        <v>-2.4713759122542922</v>
+      </c>
+      <c r="Z389">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA389" s="3">
+        <v>1.3303768640295921E-3</v>
+      </c>
+      <c r="AB389" s="3">
+        <v>6.2342213568824445E-3</v>
+      </c>
+      <c r="AC389" s="3">
+        <v>5.2280246597041944E-3</v>
+      </c>
+      <c r="AD389" s="3">
+        <v>4.459940166150804E-3</v>
+      </c>
+      <c r="AE389" s="3">
+        <v>5.0227889299083008E-3</v>
+      </c>
+      <c r="AF389">
+        <v>7309.25</v>
+      </c>
+      <c r="AG389">
+        <v>8662.9650000000001</v>
+      </c>
+      <c r="AH389">
+        <v>10857.38</v>
+      </c>
+      <c r="AI389">
         <v>10047.755000000001</v>
       </c>
     </row>
@@ -34573,6 +34680,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="dd854d95-092e-48c7-992a-80d5cc5badc3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006CC87EF38A8DD0408B89B7B34D0336DC" ma:contentTypeVersion="20" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a30c2ca5bc864785a186dec6b0346788">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe" xmlns:ns3="dd854d95-092e-48c7-992a-80d5cc5badc3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2932ec1554b414302dd4a6579c5666bc" ns2:_="" ns3:_="">
     <xsd:import namespace="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
@@ -34827,27 +34954,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dd854d95-092e-48c7-992a-80d5cc5badc3"/>
+    <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="dd854d95-092e-48c7-992a-80d5cc5badc3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BABE8802-F313-4DEC-9147-95F411D9A097}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34864,23 +34990,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="dd854d95-092e-48c7-992a-80d5cc5badc3"/>
-    <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eldorado275.sharepoint.com/sites/Compartidos/Documentos compartidos/INVERSIONES/Claude - Fernando/Dashboards ETFs/Dashboards/ETFPESOV/General/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04F98192-866C-41F4-83E7-79F6E06BA807}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8BF8D58-7A32-47FC-AE16-FBBAC81ABD6C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -2341,9 +2341,6 @@
       <c r="O30">
         <v>6.5699999999999994</v>
       </c>
-      <c r="T30">
-        <v>1.7723245210277128E-2</v>
-      </c>
       <c r="X30">
         <v>101.66</v>
       </c>
@@ -2410,7 +2407,7 @@
         <v>0.30294945219025993</v>
       </c>
       <c r="T31">
-        <v>5.8147885571013802E-2</v>
+        <v>-0.16586847056285769</v>
       </c>
       <c r="X31">
         <v>102.5</v>
@@ -2481,7 +2478,7 @@
         <v>0.30431344337139582</v>
       </c>
       <c r="T32">
-        <v>0.1095750508933957</v>
+        <v>0.13277207632080845</v>
       </c>
       <c r="X32">
         <v>101.94</v>
@@ -2552,7 +2549,7 @@
         <v>0.305100491964586</v>
       </c>
       <c r="T33">
-        <v>0.66516461856134246</v>
+        <v>0.23717380542305211</v>
       </c>
       <c r="X33">
         <v>102.51</v>
@@ -2623,7 +2620,7 @@
         <v>0.2961945061194588</v>
       </c>
       <c r="T34">
-        <v>6.105895348751389E-2</v>
+        <v>0.4771538732093461</v>
       </c>
       <c r="X34">
         <v>102.5</v>
@@ -2694,7 +2691,7 @@
         <v>0.28824596820532106</v>
       </c>
       <c r="T35">
-        <v>6.7067240843221576E-2</v>
+        <v>0.23823230697217479</v>
       </c>
       <c r="X35">
         <v>101.56</v>
@@ -2765,7 +2762,7 @@
         <v>0.2894240740853784</v>
       </c>
       <c r="T36">
-        <v>6.4922105325604385E-2</v>
+        <v>-0.1525297900064837</v>
       </c>
       <c r="X36">
         <v>102.5</v>
@@ -2836,7 +2833,7 @@
         <v>0.28869207388967699</v>
       </c>
       <c r="T37">
-        <v>0.57119334935649135</v>
+        <v>0.25504715969324465</v>
       </c>
       <c r="X37">
         <v>101.18</v>
@@ -2907,7 +2904,7 @@
         <v>0.28636629100858579</v>
       </c>
       <c r="T38">
-        <v>0.3084941941993824</v>
+        <v>0.32584039102421247</v>
       </c>
       <c r="X38">
         <v>101.6</v>
@@ -2978,7 +2975,7 @@
         <v>0.26476418610496177</v>
       </c>
       <c r="T39">
-        <v>9.8897291643229579E-2</v>
+        <v>-0.55458279029683144</v>
       </c>
       <c r="X39">
         <v>101.53</v>
@@ -3049,7 +3046,7 @@
         <v>0.25189060153654891</v>
       </c>
       <c r="T40">
-        <v>0.2874755949376917</v>
+        <v>-0.11427332877713692</v>
       </c>
       <c r="X40">
         <v>102.12</v>
@@ -3120,7 +3117,7 @@
         <v>0.25050790859340955</v>
       </c>
       <c r="T41">
-        <v>0.50044416937256031</v>
+        <v>-0.4109019663137925</v>
       </c>
       <c r="X41">
         <v>101</v>
@@ -3191,7 +3188,7 @@
         <v>0.28713443969229363</v>
       </c>
       <c r="T42">
-        <v>0.36781511598540373</v>
+        <v>0.26476650728568529</v>
       </c>
       <c r="X42">
         <v>102.5</v>
@@ -3262,7 +3259,7 @@
         <v>0.2864162976244643</v>
       </c>
       <c r="T43">
-        <v>7.5744986559955763E-2</v>
+        <v>0.35668669435469091</v>
       </c>
       <c r="X43">
         <v>102.5</v>
@@ -3333,7 +3330,7 @@
         <v>0.28311279057165339</v>
       </c>
       <c r="T44">
-        <v>0.13837408339880675</v>
+        <v>-6.1872812771901486E-2</v>
       </c>
       <c r="X44">
         <v>101.82</v>
@@ -3404,7 +3401,7 @@
         <v>0.28960896676111031</v>
       </c>
       <c r="T45">
-        <v>0.18115171457881996</v>
+        <v>-0.4915256361817999</v>
       </c>
       <c r="X45">
         <v>101.01</v>
@@ -3475,7 +3472,7 @@
         <v>0.30363810212026271</v>
       </c>
       <c r="T46">
-        <v>0.1832870415434007</v>
+        <v>0.40367253175106477</v>
       </c>
       <c r="X46">
         <v>100.79</v>
@@ -3546,7 +3543,7 @@
         <v>0.30273888424643219</v>
       </c>
       <c r="T47">
-        <v>0.35003818783683194</v>
+        <v>1.9013064346040665E-2</v>
       </c>
       <c r="X47">
         <v>102</v>
@@ -3617,7 +3614,7 @@
         <v>0.29834924169731902</v>
       </c>
       <c r="T48">
-        <v>0.39727256521366883</v>
+        <v>0.17240067653474522</v>
       </c>
       <c r="X48">
         <v>100.45</v>
@@ -3688,7 +3685,7 @@
         <v>0.29650548129182319</v>
       </c>
       <c r="T49">
-        <v>1.0925094604515184</v>
+        <v>0.56405159102548286</v>
       </c>
       <c r="X49">
         <v>101.57</v>
@@ -3759,7 +3756,7 @@
         <v>0.28110282218802563</v>
       </c>
       <c r="T50">
-        <v>0.6553408241845915</v>
+        <v>0.90496544303184656</v>
       </c>
       <c r="X50">
         <v>102.2</v>
@@ -3830,7 +3827,7 @@
         <v>0.3048210151140594</v>
       </c>
       <c r="T51">
-        <v>0.44334590449734979</v>
+        <v>-1.0538747993882325E-2</v>
       </c>
       <c r="X51">
         <v>101.01</v>
@@ -3901,7 +3898,7 @@
         <v>0.33600856497188569</v>
       </c>
       <c r="T52">
-        <v>0.44526802217546013</v>
+        <v>0.44572035979875135</v>
       </c>
       <c r="X52">
         <v>102.2</v>
@@ -3972,7 +3969,7 @@
         <v>0.33601684622617856</v>
       </c>
       <c r="T53">
-        <v>0.37506942122884634</v>
+        <v>0.4405180546191767</v>
       </c>
       <c r="X53">
         <v>102.54</v>
@@ -4043,7 +4040,7 @@
         <v>0.33656083566355521</v>
       </c>
       <c r="T54">
-        <v>0.388134783108951</v>
+        <v>0.26937410533030004</v>
       </c>
       <c r="X54">
         <v>101.3</v>
@@ -4114,7 +4111,7 @@
         <v>0.33644475684751057</v>
       </c>
       <c r="T55">
-        <v>0.57620843908330333</v>
+        <v>0.5250273739976663</v>
       </c>
       <c r="X55">
         <v>103.45</v>
@@ -4185,7 +4182,7 @@
         <v>0.33699756791654228</v>
       </c>
       <c r="T56">
-        <v>0.86729326732615242</v>
+        <v>0.46724512128679674</v>
       </c>
       <c r="X56">
         <v>101.32</v>
@@ -4256,7 +4253,7 @@
         <v>0.32792654243765784</v>
       </c>
       <c r="T57">
-        <v>0.25944541643700969</v>
+        <v>0.82931903581133781</v>
       </c>
       <c r="X57">
         <v>103.25</v>
@@ -4327,7 +4324,7 @@
         <v>0.31178800395628492</v>
       </c>
       <c r="T58">
-        <v>0.25713959327258173</v>
+        <v>0.25641910996507811</v>
       </c>
       <c r="X58">
         <v>101.52</v>
@@ -4398,7 +4395,7 @@
         <v>0.31239213488297052</v>
       </c>
       <c r="T59">
-        <v>5.4353095076198343E-2</v>
+        <v>0.15879269596359435</v>
       </c>
       <c r="X59">
         <v>103.25</v>
@@ -4469,10 +4466,7 @@
         <v>0.31136397195063997</v>
       </c>
       <c r="T60">
-        <v>3.744209225415851E-2</v>
-      </c>
-      <c r="U60">
-        <v>0.20615879480894161</v>
+        <v>-0.2191773322663737</v>
       </c>
       <c r="X60">
         <v>101.5</v>
@@ -4549,10 +4543,10 @@
         <v>0.30434202531812099</v>
       </c>
       <c r="T61">
-        <v>7.7938380191855394E-2</v>
+        <v>0.11130541826362972</v>
       </c>
       <c r="U61">
-        <v>5.4920390824753085E-2</v>
+        <v>-5.4242095293743908E-2</v>
       </c>
       <c r="X61">
         <v>103</v>
@@ -4632,10 +4626,10 @@
         <v>0.3048710315682831</v>
       </c>
       <c r="T62">
-        <v>2.6808266121336466E-2</v>
+        <v>0.100360578944092</v>
       </c>
       <c r="U62">
-        <v>0.213615611841389</v>
+        <v>0.23744651087276303</v>
       </c>
       <c r="X62">
         <v>104</v>
@@ -4715,10 +4709,10 @@
         <v>0.3055912478610609</v>
       </c>
       <c r="T63">
-        <v>1.6029619952506735E-3</v>
+        <v>-0.18937741376567896</v>
       </c>
       <c r="U63">
-        <v>0.48520818062549598</v>
+        <v>4.8263845890250678E-2</v>
       </c>
       <c r="X63">
         <v>104</v>
@@ -4798,10 +4792,10 @@
         <v>0.30044276710532941</v>
       </c>
       <c r="T64">
-        <v>0.23185960532829952</v>
+        <v>-5.0600309464465809E-2</v>
       </c>
       <c r="U64">
-        <v>1.1605236625178428E-2</v>
+        <v>0.43652774262814553</v>
       </c>
       <c r="X64">
         <v>104.25</v>
@@ -4881,10 +4875,10 @@
         <v>0.29566615100092081</v>
       </c>
       <c r="T65">
-        <v>1.6485822850387244E-2</v>
+        <v>-0.20749215875262017</v>
       </c>
       <c r="U65">
-        <v>0.14006792177831962</v>
+        <v>3.6366438592705386E-2</v>
       </c>
       <c r="X65">
         <v>104.25</v>
@@ -4964,10 +4958,10 @@
         <v>0.29549329311978223</v>
       </c>
       <c r="T66">
-        <v>2.1620301794111896E-2</v>
+        <v>0.17216062618543582</v>
       </c>
       <c r="U66">
-        <v>0.24034792629568091</v>
+        <v>1.633400259504203E-2</v>
       </c>
       <c r="X66">
         <v>103.16</v>
@@ -5047,10 +5041,10 @@
         <v>0.29428971285306094</v>
       </c>
       <c r="T67">
-        <v>0.1562185027358165</v>
+        <v>-9.371941386722149E-2</v>
       </c>
       <c r="U67">
-        <v>0.49266376638554821</v>
+        <v>0.1678107990768174</v>
       </c>
       <c r="X67">
         <v>104.5</v>
@@ -5130,10 +5124,10 @@
         <v>0.2923119128282623</v>
       </c>
       <c r="T68">
-        <v>0.5983383986641666</v>
+        <v>0.34921060349255573</v>
       </c>
       <c r="U68">
-        <v>3.5160727383587442E-2</v>
+        <v>0.68812067061949644</v>
       </c>
       <c r="X68">
         <v>102.75</v>
@@ -5213,10 +5207,10 @@
         <v>0.28077074598859109</v>
       </c>
       <c r="T69">
-        <v>0.59149312944135612</v>
+        <v>0.57608831852047349</v>
       </c>
       <c r="U69">
-        <v>0.48194822355505096</v>
+        <v>1.2462117354195001E-2</v>
       </c>
       <c r="X69">
         <v>104.5</v>
@@ -5296,10 +5290,10 @@
         <v>0.2758692418831542</v>
       </c>
       <c r="T70">
-        <v>0.50470190938123327</v>
+        <v>0.37979608404357101</v>
       </c>
       <c r="U70">
-        <v>8.7976212021789735E-2</v>
+        <v>0.26737718841292057</v>
       </c>
       <c r="X70">
         <v>102.77</v>
@@ -5379,10 +5373,10 @@
         <v>0.27513509219369092</v>
       </c>
       <c r="T71">
-        <v>0.1969497751800775</v>
+        <v>0.57964449709142496</v>
       </c>
       <c r="U71">
-        <v>7.1913737691042812E-2</v>
+        <v>0.16361967430429392</v>
       </c>
       <c r="X71">
         <v>104.5</v>
@@ -5462,10 +5456,10 @@
         <v>0.27549964208727562</v>
       </c>
       <c r="T72">
-        <v>4.1298263140676639E-2</v>
+        <v>-5.2159896193981758E-2</v>
       </c>
       <c r="U72">
-        <v>0.32393248735302915</v>
+        <v>0.21845648353326919</v>
       </c>
       <c r="X72">
         <v>103.12</v>
@@ -5545,10 +5539,10 @@
         <v>0.27520300471504167</v>
       </c>
       <c r="T73">
-        <v>6.3640676938692131E-2</v>
+        <v>-7.572169786351779E-2</v>
       </c>
       <c r="U73">
-        <v>9.8347120418562639E-4</v>
+        <v>0.28913420023759517</v>
       </c>
       <c r="X73">
         <v>103.25</v>
@@ -5628,10 +5622,10 @@
         <v>0.27402045842780243</v>
       </c>
       <c r="T74">
-        <v>0.61842062314387825</v>
+        <v>0.26348073682957995</v>
       </c>
       <c r="U74">
-        <v>0.12516622219334028</v>
+        <v>0.20345450907375273</v>
       </c>
       <c r="X74">
         <v>104.53</v>
@@ -5711,10 +5705,10 @@
         <v>0.27391958659078125</v>
       </c>
       <c r="T75">
-        <v>7.8398543310753688E-2</v>
+        <v>0.6666986310522427</v>
       </c>
       <c r="U75">
-        <v>0.4916447773132937</v>
+        <v>0.17453300347749501</v>
       </c>
       <c r="X75">
         <v>104.75</v>
@@ -5794,10 +5788,10 @@
         <v>0.27091916960983436</v>
       </c>
       <c r="T76">
-        <v>0.23161594714196099</v>
+        <v>6.6392380503632609E-2</v>
       </c>
       <c r="U76">
-        <v>0.25424847417399032</v>
+        <v>0.47892168775085509</v>
       </c>
       <c r="X76">
         <v>103.49</v>
@@ -5877,10 +5871,10 @@
         <v>0.26958271296067776</v>
       </c>
       <c r="T77">
-        <v>0.45942817718711559</v>
+        <v>0.28104290803347975</v>
       </c>
       <c r="U77">
-        <v>0.64209861498023546</v>
+        <v>0.30434451800576134</v>
       </c>
       <c r="X77">
         <v>104.75</v>
@@ -5960,10 +5954,10 @@
         <v>0.26864838176409989</v>
       </c>
       <c r="T78">
-        <v>9.0579192274287124E-3</v>
+        <v>0.17649388956055834</v>
       </c>
       <c r="U78">
-        <v>0.58393271136241154</v>
+        <v>0.35494757473324423</v>
       </c>
       <c r="X78">
         <v>104.75</v>
@@ -6043,10 +6037,10 @@
         <v>0.26807217245172865</v>
       </c>
       <c r="T79">
-        <v>1.6901390289292273E-2</v>
+        <v>-0.17264079153496148</v>
       </c>
       <c r="U79">
-        <v>0.93939745590319035</v>
+        <v>0.40006263469034575</v>
       </c>
       <c r="X79">
         <v>103.3</v>
@@ -6126,10 +6120,10 @@
         <v>0.25942231680543143</v>
       </c>
       <c r="T80">
-        <v>0.84038912365891338</v>
+        <v>0.1726325058544198</v>
       </c>
       <c r="U80">
-        <v>0.84324002616151805</v>
+        <v>1.0979708851545311</v>
       </c>
       <c r="X80">
         <v>103.44</v>
@@ -6209,10 +6203,10 @@
         <v>0.25931016820421837</v>
       </c>
       <c r="T81">
-        <v>0.25996702141273254</v>
+        <v>0.62741805730919253</v>
       </c>
       <c r="U81">
-        <v>0.18689544530554603</v>
+        <v>0.6268124387514451</v>
       </c>
       <c r="X81">
         <v>103.1</v>
@@ -6292,10 +6286,10 @@
         <v>0.25453031504029922</v>
       </c>
       <c r="T82">
-        <v>7.4720528203320313E-2</v>
+        <v>-7.9425563956525558E-2</v>
       </c>
       <c r="U82">
-        <v>0.37199870081523478</v>
+        <v>0.37241665443319416</v>
       </c>
       <c r="X82">
         <v>103.1</v>
@@ -6375,10 +6369,10 @@
         <v>0.25460218481223845</v>
       </c>
       <c r="T83">
-        <v>8.5101680331423069E-2</v>
+        <v>-2.0487719904060953E-2</v>
       </c>
       <c r="U83">
-        <v>0.36052695059869411</v>
+        <v>0.42704144118119736</v>
       </c>
       <c r="X83">
         <v>103.07</v>
@@ -6458,10 +6452,10 @@
         <v>0.2597211988327276</v>
       </c>
       <c r="T84">
-        <v>0.45502569333653042</v>
+        <v>-0.31708950793074564</v>
       </c>
       <c r="U84">
-        <v>7.3683110088373915E-2</v>
+        <v>-4.8221518696722754E-2</v>
       </c>
       <c r="X84">
         <v>104.75</v>
@@ -6541,10 +6535,10 @@
         <v>0.25981546970534919</v>
       </c>
       <c r="T85">
-        <v>0.21141141622260662</v>
+        <v>-0.32103377549155265</v>
       </c>
       <c r="U85">
-        <v>0.26286868038052358</v>
+        <v>0.21045808944302191</v>
       </c>
       <c r="X85">
         <v>103.25</v>
@@ -6624,10 +6618,10 @@
         <v>0.25994572451340098</v>
       </c>
       <c r="T86">
-        <v>0.25444208263112333</v>
+        <v>-0.29325599026068794</v>
       </c>
       <c r="U86">
-        <v>0.59103512422988835</v>
+        <v>0.18038162998019747</v>
       </c>
       <c r="X86">
         <v>104.74</v>
@@ -6707,10 +6701,10 @@
         <v>0.254482297358672</v>
       </c>
       <c r="T87">
-        <v>0.23345039853557292</v>
+        <v>-0.23710927772604418</v>
       </c>
       <c r="U87">
-        <v>2.7459761412385042E-2</v>
+        <v>0.61120888189845068</v>
       </c>
       <c r="X87">
         <v>104.22</v>
@@ -6790,10 +6784,10 @@
         <v>0.24400101328765966</v>
       </c>
       <c r="T88">
-        <v>5.4361854143314403E-2</v>
+        <v>-0.15486061074869717</v>
       </c>
       <c r="U88">
-        <v>0.10792730417934493</v>
+        <v>0.1070559420852879</v>
       </c>
       <c r="X88">
         <v>105.79</v>
@@ -6873,10 +6867,10 @@
         <v>0.24416673299195407</v>
       </c>
       <c r="T89">
-        <v>0.18517499143761995</v>
+        <v>1.8808636546729929E-2</v>
       </c>
       <c r="U89">
-        <v>3.6744381490882994E-2</v>
+        <v>0.18184327526700184</v>
       </c>
       <c r="X89">
         <v>105.43</v>
@@ -6956,10 +6950,10 @@
         <v>0.24266356764227068</v>
       </c>
       <c r="T90">
-        <v>6.2579952960750695E-2</v>
+        <v>0.21312240273978489</v>
       </c>
       <c r="U90">
-        <v>0.17727440732278055</v>
+        <v>-8.7144885698720032E-3</v>
       </c>
       <c r="X90">
         <v>105.65</v>
@@ -7039,10 +7033,10 @@
         <v>0.24277497438618431</v>
       </c>
       <c r="T91">
-        <v>0.30957308007220075</v>
+        <v>-0.12978836687695949</v>
       </c>
       <c r="U91">
-        <v>0.21150231899758065</v>
+        <v>-1.7519673932953062E-2</v>
       </c>
       <c r="X91">
         <v>106.2</v>
@@ -7122,10 +7116,10 @@
         <v>0.24696107729170552</v>
       </c>
       <c r="T92">
-        <v>0.25842232692752098</v>
+        <v>9.5196805924180339E-2</v>
       </c>
       <c r="U92">
-        <v>6.9250658470521032E-2</v>
+        <v>0.1994358251707018</v>
       </c>
       <c r="X92">
         <v>106.14</v>
@@ -7205,10 +7199,10 @@
         <v>0.24676334915942968</v>
       </c>
       <c r="T93">
-        <v>0.40780614313160601</v>
+        <v>0.3593938631895055</v>
       </c>
       <c r="U93">
-        <v>0.36503896213280207</v>
+        <v>0.17199032617507548</v>
       </c>
       <c r="X93">
         <v>106.4</v>
@@ -7288,10 +7282,10 @@
         <v>0.24588432580840533</v>
       </c>
       <c r="T94">
-        <v>0.49038413472037856</v>
+        <v>0.51564013364808758</v>
       </c>
       <c r="U94">
-        <v>0.29158505785786826</v>
+        <v>0.47532837274280038</v>
       </c>
       <c r="X94">
         <v>105.51</v>
@@ -7371,10 +7365,10 @@
         <v>0.24502290499909471</v>
       </c>
       <c r="T95">
-        <v>0.40633730760388787</v>
+        <v>0.5604552923748285</v>
       </c>
       <c r="U95">
-        <v>0.59228696128119651</v>
+        <v>0.36366482543028766</v>
       </c>
       <c r="X95">
         <v>106.2</v>
@@ -7454,10 +7448,10 @@
         <v>0.24409085322714461</v>
       </c>
       <c r="T96">
-        <v>0.64550871130377718</v>
+        <v>0.57467243637374654</v>
       </c>
       <c r="U96">
-        <v>0.56870419624530655</v>
+        <v>0.76497993599617953</v>
       </c>
       <c r="X96">
         <v>106.2</v>
@@ -7537,10 +7531,10 @@
         <v>0.24299058947557031</v>
       </c>
       <c r="T97">
-        <v>0.4631199440407574</v>
+        <v>0.65358020448542664</v>
       </c>
       <c r="U97">
-        <v>0.82919351462338309</v>
+        <v>0.57717286181795391</v>
       </c>
       <c r="X97">
         <v>105.7</v>
@@ -7620,10 +7614,10 @@
         <v>0.24939709482174185</v>
       </c>
       <c r="T98">
-        <v>1.1424467273180028E-2</v>
+        <v>-3.3719781034635687E-2</v>
       </c>
       <c r="U98">
-        <v>0.57323278385348342</v>
+        <v>0.32011494468136004</v>
       </c>
       <c r="X98">
         <v>104.15</v>
@@ -7703,10 +7697,10 @@
         <v>0.24727965122663029</v>
       </c>
       <c r="T99">
-        <v>0.17640667497202944</v>
+        <v>-3.3090260285795203E-2</v>
       </c>
       <c r="U99">
-        <v>0.56568549620212849</v>
+        <v>0.55006086213813532</v>
       </c>
       <c r="X99">
         <v>106.5</v>
@@ -7786,10 +7780,10 @@
         <v>0.24770644886637477</v>
       </c>
       <c r="T100">
-        <v>0.22841531490207512</v>
+        <v>0.30239270077903058</v>
       </c>
       <c r="U100">
-        <v>0.8214564806451774</v>
+        <v>0.69517769454652267</v>
       </c>
       <c r="X100">
         <v>105.65</v>
@@ -7869,10 +7863,10 @@
         <v>0.24713807229731125</v>
       </c>
       <c r="T101">
-        <v>5.9746711888308823E-2</v>
+        <v>0.20296212724753016</v>
       </c>
       <c r="U101">
-        <v>8.3877486956041025E-3</v>
+        <v>0.79531416800475707</v>
       </c>
       <c r="X101">
         <v>106</v>
@@ -7952,10 +7946,10 @@
         <v>0.2269077514804535</v>
       </c>
       <c r="T102">
-        <v>9.2091316312692406E-2</v>
+        <v>5.8110151570667234E-2</v>
       </c>
       <c r="U102">
-        <v>1.7754745212616996E-2</v>
+        <v>6.6956234438420026E-3</v>
       </c>
       <c r="X102">
         <v>106</v>
@@ -8035,10 +8029,10 @@
         <v>0.2270670152903306</v>
       </c>
       <c r="T103">
-        <v>0.17333669921910655</v>
+        <v>2.4759762355830439E-2</v>
       </c>
       <c r="U103">
-        <v>8.9880700584044071E-2</v>
+        <v>-5.1333977562628696E-2</v>
       </c>
       <c r="X103">
         <v>105.21</v>
@@ -8118,10 +8112,10 @@
         <v>0.23427842684394432</v>
       </c>
       <c r="T104">
-        <v>0.69580405355240682</v>
+        <v>-0.64672724533747505</v>
       </c>
       <c r="U104">
-        <v>3.1732135562267949E-2</v>
+        <v>-0.39418540160935933</v>
       </c>
       <c r="X104">
         <v>104.7</v>
@@ -8201,10 +8195,10 @@
         <v>0.23238257438899379</v>
       </c>
       <c r="T105">
-        <v>0.41997002368472369</v>
+        <v>-0.43132956116540555</v>
       </c>
       <c r="U105">
-        <v>0.36037710249148258</v>
+        <v>0.23864827686550516</v>
       </c>
       <c r="X105">
         <v>106</v>
@@ -8284,10 +8278,10 @@
         <v>0.2200227685886656</v>
       </c>
       <c r="T106">
-        <v>0.53834045170231271</v>
+        <v>-0.48802320103100705</v>
       </c>
       <c r="U106">
-        <v>0.26129759224249316</v>
+        <v>-0.42957003612986711</v>
       </c>
       <c r="X106">
         <v>105.84</v>
@@ -8367,10 +8361,10 @@
         <v>0.21916697381554928</v>
       </c>
       <c r="T107">
-        <v>0.21136205198815095</v>
+        <v>-0.49631677293611176</v>
       </c>
       <c r="U107">
-        <v>3.4517350616480869E-2</v>
+        <v>-0.21784168580061269</v>
       </c>
       <c r="X107">
         <v>105.5</v>
@@ -8450,10 +8444,10 @@
         <v>0.22326205299828963</v>
       </c>
       <c r="T108">
-        <v>0.41173496388617892</v>
+        <v>-0.59549361087249952</v>
       </c>
       <c r="U108">
-        <v>0.59745899470540209</v>
+        <v>-0.42544284597416659</v>
       </c>
       <c r="X108">
         <v>106.9</v>
@@ -8533,10 +8527,10 @@
         <v>0.22348566183104573</v>
       </c>
       <c r="T109">
-        <v>0.38370915809666784</v>
+        <v>-0.22672699630754689</v>
       </c>
       <c r="U109">
-        <v>0.2136385523616724</v>
+        <v>-0.40923019372558489</v>
       </c>
       <c r="X109">
         <v>107.4</v>
@@ -8616,10 +8610,10 @@
         <v>0.22995520347818257</v>
       </c>
       <c r="T110">
-        <v>0.30054948270537007</v>
+        <v>8.3755622093684146E-2</v>
       </c>
       <c r="U110">
-        <v>0.9512188370236041</v>
+        <v>0.26337714382669297</v>
       </c>
       <c r="X110">
         <v>107.7</v>
@@ -8699,10 +8693,10 @@
         <v>0.21540457911946564</v>
       </c>
       <c r="T111">
-        <v>0.13636349938814796</v>
+        <v>4.7004986292820128E-2</v>
       </c>
       <c r="U111">
-        <v>0.22039528054618174</v>
+        <v>0.6948279098613952</v>
       </c>
       <c r="X111">
         <v>107.57</v>
@@ -8782,10 +8776,10 @@
         <v>0.1859227484499687</v>
       </c>
       <c r="T112">
-        <v>0.45397301872518447</v>
+        <v>-0.39887047597444436</v>
       </c>
       <c r="U112">
-        <v>0.48270920703543663</v>
+        <v>-0.48752433974186271</v>
       </c>
       <c r="X112">
         <v>107</v>
@@ -8865,10 +8859,10 @@
         <v>0.19159021570548326</v>
       </c>
       <c r="T113">
-        <v>0.31243083058165588</v>
+        <v>-9.377635323202238E-2</v>
       </c>
       <c r="U113">
-        <v>7.6154810471074086E-3</v>
+        <v>-0.11647618452903519</v>
       </c>
       <c r="X113">
         <v>108.2</v>
@@ -8948,10 +8942,10 @@
         <v>0.2012171886494655</v>
       </c>
       <c r="T114">
-        <v>0.67605956498810738</v>
+        <v>0.81202610866766278</v>
       </c>
       <c r="U114">
-        <v>0.36240683829560361</v>
+        <v>0.50316184625716076</v>
       </c>
       <c r="X114">
         <v>108.4</v>
@@ -9031,10 +9025,10 @@
         <v>0.20538678769212571</v>
       </c>
       <c r="T115">
-        <v>1.1126638570559066</v>
+        <v>1.0324625573207458</v>
       </c>
       <c r="U115">
-        <v>0.838976452406337</v>
+        <v>0.726997119700723</v>
       </c>
       <c r="X115">
         <v>108</v>
@@ -9114,10 +9108,10 @@
         <v>0.2307657573804282</v>
       </c>
       <c r="T116">
-        <v>0.26716808735087749</v>
+        <v>0.28602310631313799</v>
       </c>
       <c r="U116">
-        <v>3.3292241068783035E-2</v>
+        <v>-6.1476236171698062E-3</v>
       </c>
       <c r="X116">
         <v>107.5</v>
@@ -9197,10 +9191,10 @@
         <v>0.23077179250732655</v>
       </c>
       <c r="T117">
-        <v>0.1481586520399869</v>
+        <v>0.22650774335788437</v>
       </c>
       <c r="U117">
-        <v>4.9288873470221262E-3</v>
+        <v>-8.3729439149360374E-3</v>
       </c>
       <c r="X117">
         <v>107.17</v>
@@ -9280,10 +9274,10 @@
         <v>0.23080633160768274</v>
       </c>
       <c r="T118">
-        <v>0.10708924765958638</v>
+        <v>0.17965099888463953</v>
       </c>
       <c r="U118">
-        <v>0.12891950326214818</v>
+        <v>2.7146709000347435E-2</v>
       </c>
       <c r="X118">
         <v>107.8</v>
@@ -9363,10 +9357,10 @@
         <v>0.23048210443713202</v>
       </c>
       <c r="T119">
-        <v>0.11394647581868256</v>
+        <v>0.1415297221213585</v>
       </c>
       <c r="U119">
-        <v>0.33272546380449519</v>
+        <v>0.16426081005671556</v>
       </c>
       <c r="X119">
         <v>107.01</v>
@@ -9446,10 +9440,10 @@
         <v>0.22945630946908371</v>
       </c>
       <c r="T120">
-        <v>0.30800414702136791</v>
+        <v>0.11817131974407591</v>
       </c>
       <c r="U120">
-        <v>0.18432250386155591</v>
+        <v>0.3372835600634394</v>
       </c>
       <c r="X120">
         <v>107.7</v>
@@ -9529,10 +9523,10 @@
         <v>0.22907592714945377</v>
       </c>
       <c r="T121">
-        <v>1.3806716821762599E-2</v>
+        <v>0.41348911058090021</v>
       </c>
       <c r="U121">
-        <v>0.11035904606251368</v>
+        <v>0.29256446096310729</v>
       </c>
       <c r="X121">
         <v>107.7</v>
@@ -9612,10 +9606,10 @@
         <v>0.22809461959824093</v>
       </c>
       <c r="T122">
-        <v>2.4983121747679249E-2</v>
+        <v>7.4746882628629052E-2</v>
       </c>
       <c r="U122">
-        <v>0.33745459064042915</v>
+        <v>0.17271167037851143</v>
       </c>
       <c r="X122">
         <v>107.01</v>
@@ -9695,10 +9689,10 @@
         <v>0.2279975399464414</v>
       </c>
       <c r="T123">
-        <v>0.28657375854383993</v>
+        <v>-0.17827217482873081</v>
       </c>
       <c r="U123">
-        <v>0.23013090053354279</v>
+        <v>0.18092238360123414</v>
       </c>
       <c r="X123">
         <v>107.95</v>
@@ -9778,10 +9772,10 @@
         <v>0.22841601667406114</v>
       </c>
       <c r="T124">
-        <v>0.47475072075595648</v>
+        <v>-0.40371994531223088</v>
       </c>
       <c r="U124">
-        <v>8.6551745723517648E-2</v>
+        <v>0.11158020921380185</v>
       </c>
       <c r="X124">
         <v>107.05</v>
@@ -9861,10 +9855,10 @@
         <v>0.22841869991788089</v>
       </c>
       <c r="T125">
-        <v>0.61898552859500633</v>
+        <v>-0.44930908288656202</v>
       </c>
       <c r="U125">
-        <v>4.3493449860299016E-2</v>
+        <v>0.11317914294735054</v>
       </c>
       <c r="X125">
         <v>107.65</v>
@@ -9944,10 +9938,10 @@
         <v>0.22767052140411681</v>
       </c>
       <c r="T126">
-        <v>0.68483751644738966</v>
+        <v>-0.67435222876106593</v>
       </c>
       <c r="U126">
-        <v>2.6249357547136754E-2</v>
+        <v>-9.8822432512424285E-2</v>
       </c>
       <c r="X126">
         <v>107.79</v>
@@ -10027,10 +10021,10 @@
         <v>0.23007500322865471</v>
       </c>
       <c r="T127">
-        <v>8.7069913491588657E-2</v>
+        <v>-0.41363097531010862</v>
       </c>
       <c r="U127">
-        <v>5.4107970507999426E-2</v>
+        <v>0.24857345942839171</v>
       </c>
       <c r="X127">
         <v>108</v>
@@ -10110,10 +10104,10 @@
         <v>0.22947181475881628</v>
       </c>
       <c r="T128">
-        <v>0.24813963605128109</v>
+        <v>0.22597372916444147</v>
       </c>
       <c r="U128">
-        <v>0.21782649173995861</v>
+        <v>0.19524105954462634</v>
       </c>
       <c r="X128">
         <v>107.32</v>
@@ -10193,10 +10187,10 @@
         <v>0.2294915209250169</v>
       </c>
       <c r="T129">
-        <v>0.15985514294174497</v>
+        <v>0.2864674121396904</v>
       </c>
       <c r="U129">
-        <v>0.4696445788287873</v>
+        <v>0.2567177827104361</v>
       </c>
       <c r="X129">
         <v>107.77</v>
@@ -10276,10 +10270,10 @@
         <v>0.22801918370904664</v>
       </c>
       <c r="T130">
-        <v>0.11637702525664206</v>
+        <v>9.0824269267431035E-2</v>
       </c>
       <c r="U130">
-        <v>0.32429181799682461</v>
+        <v>0.39953048989407325</v>
       </c>
       <c r="X130">
         <v>107.8</v>
@@ -10359,10 +10353,10 @@
         <v>0.22857298889539718</v>
       </c>
       <c r="T131">
-        <v>0.26604932474578735</v>
+        <v>0.26446998213229822</v>
       </c>
       <c r="U131">
-        <v>0.32845727601460428</v>
+        <v>0.4739233687379496</v>
       </c>
       <c r="X131">
         <v>107.14</v>
@@ -10442,10 +10436,10 @@
         <v>0.227932641472535</v>
       </c>
       <c r="T132">
-        <v>0.37020420691633582</v>
+        <v>0.30301510122978659</v>
       </c>
       <c r="U132">
-        <v>0.4001872223516445</v>
+        <v>0.36579822857243371</v>
       </c>
       <c r="X132">
         <v>107.6</v>
@@ -10525,10 +10519,10 @@
         <v>0.22788420678328958</v>
       </c>
       <c r="T133">
-        <v>0.82872529541544449</v>
+        <v>0.36008544667300857</v>
       </c>
       <c r="U133">
-        <v>0.18979381404151674</v>
+        <v>0.38994838798873666</v>
       </c>
       <c r="X133">
         <v>107.28</v>
@@ -10608,10 +10602,10 @@
         <v>0.23094184841984219</v>
       </c>
       <c r="T134">
-        <v>0.21718665556866856</v>
+        <v>0.47970014651050885</v>
       </c>
       <c r="U134">
-        <v>0.2141859548040026</v>
+        <v>-0.16498637432473817</v>
       </c>
       <c r="X134">
         <v>107.3</v>
@@ -10691,10 +10685,10 @@
         <v>0.23183548219453329</v>
       </c>
       <c r="T135">
-        <v>0.11244257963263227</v>
+        <v>4.6551211628620415E-2</v>
       </c>
       <c r="U135">
-        <v>0.37714141962246206</v>
+        <v>-0.38868785055476973</v>
       </c>
       <c r="X135">
         <v>106.81</v>
@@ -10774,10 +10768,10 @@
         <v>0.23201946302388454</v>
       </c>
       <c r="T136">
-        <v>0.13577317552813106</v>
+        <v>0.17850427697416738</v>
       </c>
       <c r="U136">
-        <v>0.36061156103726066</v>
+        <v>-0.31000332551156529</v>
       </c>
       <c r="X136">
         <v>107.13</v>
@@ -10857,10 +10851,10 @@
         <v>0.2319246038235451</v>
       </c>
       <c r="T137">
-        <v>0.48419488164805902</v>
+        <v>0.11090301635401367</v>
       </c>
       <c r="U137">
-        <v>9.9332952350694725E-2</v>
+        <v>-0.38652766153353113</v>
       </c>
       <c r="X137">
         <v>106.9</v>
@@ -10940,10 +10934,10 @@
         <v>0.22917474737888954</v>
       </c>
       <c r="T138">
-        <v>0.31197931855773131</v>
+        <v>0.4941409216229431</v>
       </c>
       <c r="U138">
-        <v>9.4172160885630518E-2</v>
+        <v>-9.0354586409380211E-2</v>
       </c>
       <c r="X138">
         <v>107.8</v>
@@ -11023,10 +11017,10 @@
         <v>0.22802410206859675</v>
       </c>
       <c r="T139">
-        <v>0.16939232844825902</v>
+        <v>0.28652744856234591</v>
       </c>
       <c r="U139">
-        <v>9.0449875312503814E-2</v>
+        <v>6.7636724900088652E-2</v>
       </c>
       <c r="X139">
         <v>107.99</v>
@@ -11106,10 +11100,10 @@
         <v>0.22830531855111266</v>
       </c>
       <c r="T140">
-        <v>0.25440093954055554</v>
+        <v>7.5325130670655938E-3</v>
       </c>
       <c r="U140">
-        <v>0.30939446263411607</v>
+        <v>9.1824806232043699E-2</v>
       </c>
       <c r="X140">
         <v>108</v>
@@ -11189,10 +11183,10 @@
         <v>0.22661620696769977</v>
       </c>
       <c r="T141">
-        <v>0.48826274249273993</v>
+        <v>0.23330900941431754</v>
       </c>
       <c r="U141">
-        <v>0.10332942842989912</v>
+        <v>0.28766014673582418</v>
       </c>
       <c r="X141">
         <v>107.46</v>
@@ -11272,10 +11266,10 @@
         <v>0.22643523727510481</v>
       </c>
       <c r="T142">
-        <v>2.3050227838261605E-2</v>
+        <v>0.32722096304126369</v>
       </c>
       <c r="U142">
-        <v>0.11751854701538278</v>
+        <v>-6.255365043086325E-2</v>
       </c>
       <c r="X142">
         <v>108</v>
@@ -11355,10 +11349,10 @@
         <v>0.2270084227649799</v>
       </c>
       <c r="T143">
-        <v>0.38089895143023078</v>
+        <v>0.11138139898569932</v>
       </c>
       <c r="U143">
-        <v>0.42757400861070938</v>
+        <v>2.0869160093739403E-2</v>
       </c>
       <c r="X143">
         <v>107.2</v>
@@ -11438,10 +11432,10 @@
         <v>0.22150323347788839</v>
       </c>
       <c r="T144">
-        <v>0.84777347126832048</v>
+        <v>-0.49325561235988857</v>
       </c>
       <c r="U144">
-        <v>0.17683458289619036</v>
+        <v>0.31302940705530968</v>
       </c>
       <c r="X144">
         <v>107.41</v>
@@ -11521,10 +11515,10 @@
         <v>0.22153791904756709</v>
       </c>
       <c r="T145">
-        <v>0.10730945859027674</v>
+        <v>-0.71160457022736434</v>
       </c>
       <c r="U145">
-        <v>0.39829198956231604</v>
+        <v>0.31651646248282983</v>
       </c>
       <c r="X145">
         <v>108</v>
@@ -11604,10 +11598,10 @@
         <v>0.2214576864088541</v>
       </c>
       <c r="T146">
-        <v>0.22791616089770095</v>
+        <v>0.18746223368319992</v>
       </c>
       <c r="U146">
-        <v>0.46014063992962928</v>
+        <v>0.47978581308112389</v>
       </c>
       <c r="X146">
         <v>107.2</v>
@@ -11687,10 +11681,10 @@
         <v>0.22146489066150166</v>
       </c>
       <c r="T147">
-        <v>0.22134928453743097</v>
+        <v>0.25279277609948636</v>
       </c>
       <c r="U147">
-        <v>0.40579003867668995</v>
+        <v>0.48531090121424203</v>
       </c>
       <c r="X147">
         <v>108.8</v>
@@ -11770,10 +11764,10 @@
         <v>0.22169032115875903</v>
       </c>
       <c r="T148">
-        <v>8.8438223999109944E-2</v>
+        <v>0.12269426037452291</v>
       </c>
       <c r="U148">
-        <v>0.23250457788579482</v>
+        <v>0.30588403471243364</v>
       </c>
       <c r="X148">
         <v>108.94</v>
@@ -11853,10 +11847,10 @@
         <v>0.22216005968669297</v>
       </c>
       <c r="T149">
-        <v>4.3700156251702538E-2</v>
+        <v>-3.9661716418071258E-2</v>
       </c>
       <c r="U149">
-        <v>7.4847391905108474E-2</v>
+        <v>0.10264442924319273</v>
       </c>
       <c r="X149">
         <v>109.18</v>
@@ -11936,10 +11930,10 @@
         <v>0.22427760862462112</v>
       </c>
       <c r="T150">
-        <v>9.3740140292797314E-2</v>
+        <v>0.1990650171509234</v>
       </c>
       <c r="U150">
-        <v>0.51180809700963614</v>
+        <v>0.32099404731047443</v>
       </c>
       <c r="X150">
         <v>108.34</v>
@@ -12019,10 +12013,10 @@
         <v>0.22405500052299493</v>
       </c>
       <c r="T151">
-        <v>0.14103239899609932</v>
+        <v>-7.9978265063895826E-2</v>
       </c>
       <c r="U151">
-        <v>6.6889185664353867E-2</v>
+        <v>0.33680177888699703</v>
       </c>
       <c r="X151">
         <v>108.34</v>
@@ -12102,10 +12096,10 @@
         <v>0.21812385494207495</v>
       </c>
       <c r="T152">
-        <v>8.8089752946052258E-3</v>
+        <v>-0.1444697243025761</v>
       </c>
       <c r="U152">
-        <v>0.17117339360002148</v>
+        <v>-7.036388283832018E-2</v>
       </c>
       <c r="X152">
         <v>107.7</v>
@@ -12185,10 +12179,10 @@
         <v>0.21817887784961579</v>
       </c>
       <c r="T153">
-        <v>0.2313338154154243</v>
+        <v>0.1154668606887066</v>
       </c>
       <c r="U153">
-        <v>0.17261734933766704</v>
+        <v>-6.3421144473085889E-2</v>
       </c>
       <c r="X153">
         <v>108.2</v>
@@ -12268,10 +12262,10 @@
         <v>0.2177795581671215</v>
       </c>
       <c r="T154">
-        <v>0.1629859619912466</v>
+        <v>0.18909056136540148</v>
       </c>
       <c r="U154">
-        <v>0.2871057356057527</v>
+        <v>-0.21564195242680384</v>
       </c>
       <c r="X154">
         <v>108</v>
@@ -12351,10 +12345,10 @@
         <v>0.21778907197612038</v>
       </c>
       <c r="T155">
-        <v>0.13531044193226816</v>
+        <v>8.1659754039309362E-2</v>
       </c>
       <c r="U155">
-        <v>0.54125470831505318</v>
+        <v>-0.37018829151662658</v>
       </c>
       <c r="X155">
         <v>108.6</v>
@@ -12434,10 +12428,10 @@
         <v>0.21797078302504472</v>
       </c>
       <c r="T156">
-        <v>4.824741835478541E-2</v>
+        <v>0.31565828258361961</v>
       </c>
       <c r="U156">
-        <v>0.36707803158475549</v>
+        <v>-0.35709277807798312</v>
       </c>
       <c r="X156">
         <v>109.2</v>
@@ -12517,10 +12511,10 @@
         <v>0.21833392936460574</v>
       </c>
       <c r="T157">
-        <v>3.9028914814887017E-3</v>
+        <v>0.141341981405807</v>
       </c>
       <c r="U157">
-        <v>0.23154935412112998</v>
+        <v>-0.27182035438633179</v>
       </c>
       <c r="X157">
         <v>108.94</v>
@@ -12600,10 +12594,10 @@
         <v>0.20891913434482795</v>
       </c>
       <c r="T158">
-        <v>9.6728610310559127E-2</v>
+        <v>-5.8425110761728405E-2</v>
       </c>
       <c r="U158">
-        <v>0.19043713152400166</v>
+        <v>0.16820339032341813</v>
       </c>
       <c r="X158">
         <v>109.01</v>
@@ -12683,10 +12677,10 @@
         <v>0.20954465463950667</v>
       </c>
       <c r="T159">
-        <v>0.15417876247261209</v>
+        <v>-0.22246237508241062</v>
       </c>
       <c r="U159">
-        <v>6.5113607008426833E-2</v>
+        <v>6.2539346481993441E-2</v>
       </c>
       <c r="X159">
         <v>108.27</v>
@@ -12766,10 +12760,10 @@
         <v>0.20917014083065866</v>
       </c>
       <c r="T160">
-        <v>0.38432688598522002</v>
+        <v>-0.2360271777374523</v>
       </c>
       <c r="U160">
-        <v>0.12242966767408436</v>
+        <v>-0.14824427060866618</v>
       </c>
       <c r="X160">
         <v>109</v>
@@ -12849,10 +12843,10 @@
         <v>0.2096712666752919</v>
       </c>
       <c r="T161">
-        <v>0.54176627967645885</v>
+        <v>-0.50335690922462817</v>
       </c>
       <c r="U161">
-        <v>0.24090120546087501</v>
+        <v>-0.24265528535967196</v>
       </c>
       <c r="X161">
         <v>108.61</v>
@@ -12932,10 +12926,10 @@
         <v>0.20971076747614931</v>
       </c>
       <c r="T162">
-        <v>0.56789421742102775</v>
+        <v>-0.57858333323812516</v>
       </c>
       <c r="U162">
-        <v>0.20924556482957435</v>
+        <v>-0.27790877106221856</v>
       </c>
       <c r="X162">
         <v>109</v>
@@ -13015,10 +13009,10 @@
         <v>0.20976349372491251</v>
       </c>
       <c r="T163">
-        <v>0.14702797112700061</v>
+        <v>-0.49847967855896069</v>
       </c>
       <c r="U163">
-        <v>0.34045870768042441</v>
+        <v>-0.13829825330182732</v>
       </c>
       <c r="X163">
         <v>108.89</v>
@@ -13098,10 +13092,10 @@
         <v>0.20096262302658896</v>
       </c>
       <c r="T164">
-        <v>4.4093243423293238E-2</v>
+        <v>-0.21672467914106708</v>
       </c>
       <c r="U164">
-        <v>2.852240641915138E-3</v>
+        <v>0.27067420207991244</v>
       </c>
       <c r="X164">
         <v>109.2</v>
@@ -13181,10 +13175,10 @@
         <v>0.19824901131054753</v>
       </c>
       <c r="T165">
-        <v>5.8715890727367714E-2</v>
+        <v>7.8378729542194492E-3</v>
       </c>
       <c r="U165">
-        <v>0.12249545880589352</v>
+        <v>5.5365621200409443E-2</v>
       </c>
       <c r="X165">
         <v>108.94</v>
@@ -13264,10 +13258,10 @@
         <v>0.19863391301325339</v>
       </c>
       <c r="T166">
-        <v>0.15073671858167881</v>
+        <v>-0.17610912769512321</v>
       </c>
       <c r="U166">
-        <v>3.9028863866508168E-2</v>
+        <v>4.1440716202156835E-3</v>
       </c>
       <c r="X166">
         <v>109.49</v>
@@ -13347,10 +13341,10 @@
         <v>0.20215282908732948</v>
       </c>
       <c r="T167">
-        <v>0.13836345699125285</v>
+        <v>0.14769801730061261</v>
       </c>
       <c r="U167">
-        <v>0.64189871640456531</v>
+        <v>0.26194391239253711</v>
       </c>
       <c r="X167">
         <v>109.53</v>
@@ -13430,10 +13424,10 @@
         <v>0.19627062393468253</v>
       </c>
       <c r="T168">
-        <v>8.9576533310542494E-2</v>
+        <v>6.3513747110843788E-2</v>
       </c>
       <c r="U168">
-        <v>0.38129884337438913</v>
+        <v>0.5668618960751548</v>
       </c>
       <c r="X168">
         <v>109.8</v>
@@ -13513,10 +13507,10 @@
         <v>0.19497349120694479</v>
       </c>
       <c r="T169">
-        <v>8.2096356352567845E-2</v>
+        <v>9.7139688537861701E-2</v>
       </c>
       <c r="U169">
-        <v>7.4727158350595957E-2</v>
+        <v>0.38908332998388584</v>
       </c>
       <c r="X169">
         <v>109.8</v>
@@ -13596,10 +13590,10 @@
         <v>0.18590417131818632</v>
       </c>
       <c r="T170">
-        <v>6.222608471440072E-2</v>
+        <v>-8.3800777845555174E-2</v>
       </c>
       <c r="U170">
-        <v>0.17541745050131397</v>
+        <v>-7.6428795186855858E-2</v>
       </c>
       <c r="X170">
         <v>109.91</v>
@@ -13679,10 +13673,10 @@
         <v>0.18307911990349665</v>
       </c>
       <c r="T171">
-        <v>0.10447995435363122</v>
+        <v>-5.9733161016661818E-2</v>
       </c>
       <c r="U171">
-        <v>0.43813152381224629</v>
+        <v>0.17809566743585137</v>
       </c>
       <c r="X171">
         <v>109.8</v>
@@ -13762,10 +13756,10 @@
         <v>0.17992308809325749</v>
       </c>
       <c r="T172">
-        <v>3.6162684974727632E-2</v>
+        <v>0.10075237201643272</v>
       </c>
       <c r="U172">
-        <v>7.7203763485322874E-2</v>
+        <v>0.43483174554164172</v>
       </c>
       <c r="X172">
         <v>110.56</v>
@@ -13845,10 +13839,10 @@
         <v>0.17418750829181004</v>
       </c>
       <c r="T173">
-        <v>8.6170539337437901E-2</v>
+        <v>-2.7396878311747308E-2</v>
       </c>
       <c r="U173">
-        <v>0.41626192929244965</v>
+        <v>8.6207685847106141E-2</v>
       </c>
       <c r="X173">
         <v>111.04</v>
@@ -13928,10 +13922,10 @@
         <v>0.16208535544083</v>
       </c>
       <c r="T174">
-        <v>5.8011160535209605E-2</v>
+        <v>8.0303028040096258E-2</v>
       </c>
       <c r="U174">
-        <v>0.7848103609576329</v>
+        <v>-0.42288157855447928</v>
       </c>
       <c r="X174">
         <v>112.5</v>
@@ -14011,10 +14005,10 @@
         <v>0.15571358238887623</v>
       </c>
       <c r="T175">
-        <v>4.9445839995376772E-2</v>
+        <v>3.1581570430994077E-2</v>
       </c>
       <c r="U175">
-        <v>0.14137915971819126</v>
+        <v>-0.69402685449262425</v>
       </c>
       <c r="X175">
         <v>111.2</v>
@@ -14094,10 +14088,10 @@
         <v>0.1155415262000794</v>
       </c>
       <c r="T176">
-        <v>0.15554755959821254</v>
+        <v>-0.13020486454491387</v>
       </c>
       <c r="U176">
-        <v>0.10168616004966324</v>
+        <v>6.0311127787837648E-2</v>
       </c>
       <c r="X176">
         <v>111.2</v>
@@ -14177,10 +14171,10 @@
         <v>0.11541691058669495</v>
       </c>
       <c r="T177">
-        <v>5.0701896875637864E-2</v>
+        <v>-0.15113899663712349</v>
       </c>
       <c r="U177">
-        <v>7.4338038312493637E-2</v>
+        <v>0.10631735945827447</v>
       </c>
       <c r="X177">
         <v>110.81</v>
@@ -14260,10 +14254,10 @@
         <v>0.11535353474835022</v>
       </c>
       <c r="T178">
-        <v>8.2213753899407216E-2</v>
+        <v>-4.7814121655553876E-2</v>
       </c>
       <c r="U178">
-        <v>4.2388757030065172E-2</v>
+        <v>7.7458640093208686E-2</v>
       </c>
       <c r="X178">
         <v>111.2</v>
@@ -14343,10 +14337,10 @@
         <v>0.1152743756831454</v>
       </c>
       <c r="T179">
-        <v>0.16702244654651643</v>
+        <v>7.9724812572457004E-2</v>
       </c>
       <c r="U179">
-        <v>3.5669888207712219E-2</v>
+        <v>3.9888893607908926E-2</v>
       </c>
       <c r="X179">
         <v>111.2</v>
@@ -14426,13 +14420,10 @@
         <v>0.11527349003511125</v>
       </c>
       <c r="T180">
-        <v>9.9359720720615385E-3</v>
+        <v>-0.16607151250811469</v>
       </c>
       <c r="U180">
-        <v>7.1628470757745255E-2</v>
-      </c>
-      <c r="V180">
-        <v>0.17818345187776696</v>
+        <v>3.6246326358146952E-2</v>
       </c>
       <c r="X180">
         <v>110.79</v>
@@ -14518,13 +14509,13 @@
         <v>0.22836758145830718</v>
       </c>
       <c r="T181">
-        <v>1.9342513915887594E-2</v>
+        <v>1.5867701095340081E-2</v>
       </c>
       <c r="U181">
-        <v>0.12780448109572795</v>
+        <v>-6.5544497272251867E-2</v>
       </c>
       <c r="V181">
-        <v>0.30085581736600808</v>
+        <v>-0.18443909503138567</v>
       </c>
       <c r="X181">
         <v>111</v>
@@ -14613,13 +14604,13 @@
         <v>0.22822902128229952</v>
       </c>
       <c r="T182">
-        <v>8.4904737128055352E-2</v>
+        <v>2.2371713088276124E-2</v>
       </c>
       <c r="U182">
-        <v>3.1552242924681728E-2</v>
+        <v>-0.12423688190867921</v>
       </c>
       <c r="V182">
-        <v>0.27771476845988019</v>
+        <v>-0.30318462588976303</v>
       </c>
       <c r="X182">
         <v>111.5</v>
@@ -14708,13 +14699,13 @@
         <v>0.22822369869438269</v>
       </c>
       <c r="T183">
-        <v>3.820829157601402E-2</v>
+        <v>-8.0911040124154177E-2</v>
       </c>
       <c r="U183">
-        <v>0.15373128004336767</v>
+        <v>3.5721320448089955E-2</v>
       </c>
       <c r="V183">
-        <v>0.7449337028833547</v>
+        <v>-0.2824625158833749</v>
       </c>
       <c r="X183">
         <v>110.07</v>
@@ -14803,13 +14794,13 @@
         <v>0.22594600926735001</v>
       </c>
       <c r="T184">
-        <v>2.6912008925239483E-2</v>
+        <v>-5.5209740151385134E-2</v>
       </c>
       <c r="U184">
-        <v>0.11013385452434132</v>
+        <v>0.13661056236884406</v>
       </c>
       <c r="V184">
-        <v>0.27460878805818378</v>
+        <v>-0.72680466200087945</v>
       </c>
       <c r="X184">
         <v>111</v>
@@ -14898,13 +14889,13 @@
         <v>0.22384220417968759</v>
       </c>
       <c r="T185">
-        <v>0.14135583107097727</v>
+        <v>4.0909623469875811E-2</v>
       </c>
       <c r="U185">
-        <v>0.17878049175066302</v>
+        <v>0.12429355059297986</v>
       </c>
       <c r="V185">
-        <v>0.10383848564741172</v>
+        <v>-0.28971663159698124</v>
       </c>
       <c r="X185">
         <v>111.01</v>
@@ -14993,13 +14984,13 @@
         <v>0.22348380024425435</v>
       </c>
       <c r="T186">
-        <v>0.2337261781255151</v>
+        <v>-0.13943069697774924</v>
       </c>
       <c r="U186">
-        <v>9.1238025344919649E-2</v>
+        <v>0.18094582620744593</v>
       </c>
       <c r="V186">
-        <v>0.34406363441497056</v>
+        <v>-0.10608957263136265</v>
       </c>
       <c r="X186">
         <v>111.01</v>
@@ -15088,13 +15079,13 @@
         <v>0.22289825031949953</v>
       </c>
       <c r="T187">
-        <v>0.16214811489707603</v>
+        <v>-0.22520432165014093</v>
       </c>
       <c r="U187">
-        <v>0.22282892165166324</v>
+        <v>-8.2661544851858615E-2</v>
       </c>
       <c r="V187">
-        <v>0.69814901877860436</v>
+        <v>-0.35326785934335359</v>
       </c>
       <c r="X187">
         <v>111.01</v>
@@ -15183,13 +15174,13 @@
         <v>0.22166273801026679</v>
       </c>
       <c r="T188">
-        <v>4.6407355542688045E-2</v>
+        <v>-0.17328805093892452</v>
       </c>
       <c r="U188">
-        <v>0.27325316593294069</v>
+        <v>-0.23406124189397914</v>
       </c>
       <c r="V188">
-        <v>5.8155602095322223E-3</v>
+        <v>-0.68623515299630622</v>
       </c>
       <c r="X188">
         <v>111.05</v>
@@ -15278,13 +15269,13 @@
         <v>0.21661639430741686</v>
       </c>
       <c r="T189">
-        <v>4.3970917675228982E-2</v>
+        <v>-3.8248998782108856E-2</v>
       </c>
       <c r="U189">
-        <v>0.19559797994508354</v>
+        <v>-0.26510084359225861</v>
       </c>
       <c r="V189">
-        <v>0.50065170650757107</v>
+        <v>-2.9919578151016424E-3</v>
       </c>
       <c r="X189">
         <v>111.33</v>
@@ -15373,13 +15364,13 @@
         <v>0.21397117752824016</v>
       </c>
       <c r="T190">
-        <v>0.1642459894539483</v>
+        <v>4.6230264281854616E-2</v>
       </c>
       <c r="U190">
-        <v>0.34407021155209438</v>
+        <v>-0.19332504799973727</v>
       </c>
       <c r="V190">
-        <v>0.31225518336053248</v>
+        <v>-0.50311807221234961</v>
       </c>
       <c r="X190">
         <v>111.45</v>
@@ -15468,13 +15459,13 @@
         <v>0.21358982625314088</v>
       </c>
       <c r="T191">
-        <v>0.1987407665688945</v>
+        <v>0.16272571026936244</v>
       </c>
       <c r="U191">
-        <v>0.38448888845847851</v>
+        <v>-0.34578592164584698</v>
       </c>
       <c r="V191">
-        <v>0.21356017033762331</v>
+        <v>-0.31065754673784696</v>
       </c>
       <c r="X191">
         <v>111.51</v>
@@ -15563,13 +15554,13 @@
         <v>0.21349027155207903</v>
       </c>
       <c r="T192">
-        <v>0.12683099836638956</v>
+        <v>0.19701321594358667</v>
       </c>
       <c r="U192">
-        <v>0.37492128712601769</v>
+        <v>-0.38563676958665027</v>
       </c>
       <c r="V192">
-        <v>0.32323853532134628</v>
+        <v>-0.21169215571339439</v>
       </c>
       <c r="X192">
         <v>111.64</v>
@@ -15658,13 +15649,13 @@
         <v>0.21335307956147692</v>
       </c>
       <c r="T193">
-        <v>0.19616387423846415</v>
+        <v>0.1275264413773014</v>
       </c>
       <c r="U193">
-        <v>1.8690182517921983E-2</v>
+        <v>-0.37415547454717757</v>
       </c>
       <c r="V193">
-        <v>1.9236947133305371E-2</v>
+        <v>-0.32397252500886431</v>
       </c>
       <c r="X193">
         <v>111.3</v>
@@ -15753,13 +15744,13 @@
         <v>0.21234988595716292</v>
       </c>
       <c r="T194">
-        <v>0.1534192695468839</v>
+        <v>0.20488826704756491</v>
       </c>
       <c r="U194">
-        <v>0.16426261870550185</v>
+        <v>-9.6925957193683132E-3</v>
       </c>
       <c r="V194">
-        <v>5.4120896826637122E-2</v>
+        <v>-2.8809835127119321E-2</v>
       </c>
       <c r="X194">
         <v>111.8</v>
@@ -15848,13 +15839,13 @@
         <v>0.21227462566659008</v>
       </c>
       <c r="T195">
-        <v>0.27000008937165809</v>
+        <v>0.15398976350833316</v>
       </c>
       <c r="U195">
-        <v>9.7546658485025972E-2</v>
+        <v>0.16484180777911472</v>
       </c>
       <c r="V195">
-        <v>0.28243928438798083</v>
+        <v>5.3438482164747114E-2</v>
       </c>
       <c r="X195">
         <v>111.8</v>
@@ -15943,13 +15934,13 @@
         <v>0.21103620650496893</v>
       </c>
       <c r="T196">
-        <v>2.2850234808657888E-2</v>
+        <v>0.27240843741718201</v>
       </c>
       <c r="U196">
-        <v>0.12540551167286029</v>
+        <v>0.10005194037085996</v>
       </c>
       <c r="V196">
-        <v>4.6901699559276366E-2</v>
+        <v>-0.28506541189332602</v>
       </c>
       <c r="X196">
         <v>111.3</v>
@@ -16038,13 +16029,13 @@
         <v>0.21041643826091444</v>
       </c>
       <c r="T197">
-        <v>5.1004597858272938E-2</v>
+        <v>-2.3032464182959345E-2</v>
       </c>
       <c r="U197">
-        <v>0.11578680488046889</v>
+        <v>0.1251295467911584</v>
       </c>
       <c r="V197">
-        <v>0.40476485044784738</v>
+        <v>-4.665949898952082E-2</v>
       </c>
       <c r="X197">
         <v>111.3</v>
@@ -16133,13 +16124,13 @@
         <v>0.20899091059683822</v>
       </c>
       <c r="T198">
-        <v>4.1669319932258198E-2</v>
+        <v>4.9117781797636262E-2</v>
       </c>
       <c r="U198">
-        <v>0.1400238742716553</v>
+        <v>0.11387396964874785</v>
       </c>
       <c r="V198">
-        <v>0.64552567483420198</v>
+        <v>-0.40274762744831882</v>
       </c>
       <c r="X198">
         <v>111.44</v>
@@ -16228,13 +16219,13 @@
         <v>0.20831253511963752</v>
       </c>
       <c r="T199">
-        <v>4.6480322319175649E-2</v>
+        <v>4.494850690361929E-2</v>
       </c>
       <c r="U199">
-        <v>3.6794444159093942E-2</v>
+        <v>0.14340646424191306</v>
       </c>
       <c r="V199">
-        <v>1.2205686754933831</v>
+        <v>-0.64938937694116738</v>
       </c>
       <c r="X199">
         <v>110.99</v>
@@ -16323,13 +16314,13 @@
         <v>0.20450761302709444</v>
       </c>
       <c r="T200">
-        <v>4.7492050483044501E-2</v>
+        <v>5.0029119615313533E-2</v>
       </c>
       <c r="U200">
-        <v>1.1484757903512666E-2</v>
+        <v>-3.3124519061611402E-2</v>
       </c>
       <c r="V200">
-        <v>0.95407745963398405</v>
+        <v>-1.223699819031987</v>
       </c>
       <c r="X200">
         <v>111</v>
@@ -16418,13 +16409,13 @@
         <v>0.20371235305348054</v>
       </c>
       <c r="T201">
-        <v>5.1116409999130141E-2</v>
+        <v>4.7384734362676539E-2</v>
       </c>
       <c r="U201">
-        <v>0.15314368821577329</v>
+        <v>-1.1620718256710738E-2</v>
       </c>
       <c r="V201">
-        <v>0.48973477552025635</v>
+        <v>-0.95436009205129846</v>
       </c>
       <c r="X201">
         <v>111.1</v>
@@ -16513,13 +16504,13 @@
         <v>0.2012605914380162</v>
       </c>
       <c r="T202">
-        <v>4.7744694340678961E-2</v>
+        <v>5.6529720882525503E-2</v>
       </c>
       <c r="U202">
-        <v>2.1273986999847949E-2</v>
+        <v>0.1588278025432599</v>
       </c>
       <c r="V202">
-        <v>0.49583110103563754</v>
+        <v>-0.4963260149436044</v>
       </c>
       <c r="X202">
         <v>110.99</v>
@@ -16608,13 +16599,13 @@
         <v>0.20126053302524019</v>
       </c>
       <c r="T203">
-        <v>5.5194631368737923E-2</v>
+        <v>4.938744486351343E-2</v>
       </c>
       <c r="U203">
-        <v>0.13684644633080723</v>
+        <v>2.2902084465159511E-2</v>
       </c>
       <c r="V203">
-        <v>0.42796788898138427</v>
+        <v>-0.49840590660670259</v>
       </c>
       <c r="X203">
         <v>110.79</v>
@@ -16703,13 +16694,13 @@
         <v>0.20120844929209458</v>
       </c>
       <c r="T204">
-        <v>2.6878206528491155E-2</v>
+        <v>6.1189226285618403E-2</v>
       </c>
       <c r="U204">
-        <v>4.2681379604614378E-3</v>
+        <v>0.14302839450754945</v>
       </c>
       <c r="V204">
-        <v>0.56223383156277507</v>
+        <v>-0.43478971541073275</v>
       </c>
       <c r="X204">
         <v>110.98</v>
@@ -16798,13 +16789,13 @@
         <v>0.20100696754337799</v>
       </c>
       <c r="T205">
-        <v>5.3351668683698783E-2</v>
+        <v>-2.5702139856309536E-2</v>
       </c>
       <c r="U205">
-        <v>7.5923246075149109E-2</v>
+        <v>5.519955542232502E-3</v>
       </c>
       <c r="V205">
-        <v>0.61969467029852066</v>
+        <v>-0.56448734206455686</v>
       </c>
       <c r="X205">
         <v>110.48</v>
@@ -16893,13 +16884,13 @@
         <v>0.20096703112390982</v>
       </c>
       <c r="T206">
-        <v>5.0049598822843322E-2</v>
+        <v>5.4510669968266257E-2</v>
       </c>
       <c r="U206">
-        <v>0.10035112451218797</v>
+        <v>-7.4930142691131962E-2</v>
       </c>
       <c r="V206">
-        <v>1.0533857764740695</v>
+        <v>-0.6217892997822716</v>
       </c>
       <c r="X206">
         <v>110.42</v>
@@ -16988,13 +16979,13 @@
         <v>0.19867140266119024</v>
       </c>
       <c r="T207">
-        <v>5.0618402016011643E-2</v>
+        <v>5.361498786022878E-2</v>
       </c>
       <c r="U207">
-        <v>3.8916836323954485E-3</v>
+        <v>-9.6987480480259514E-2</v>
       </c>
       <c r="V207">
-        <v>0.44202255407874702</v>
+        <v>-1.0591600872294382</v>
       </c>
       <c r="X207">
         <v>110.6</v>
@@ -17083,13 +17074,13 @@
         <v>0.19418409145472776</v>
       </c>
       <c r="T208">
-        <v>5.0239238402460806E-2</v>
+        <v>4.7804793381844846E-2</v>
       </c>
       <c r="U208">
-        <v>0.13159114315863807</v>
+        <v>9.2379988769764054E-4</v>
       </c>
       <c r="V208">
-        <v>0.4402954513346824</v>
+        <v>-0.43965255677944626</v>
       </c>
       <c r="X208">
         <v>111</v>
@@ -17178,13 +17169,13 @@
         <v>0.19451901680769801</v>
       </c>
       <c r="T209">
-        <v>0.10229189225063884</v>
+        <v>-0.10147232322377242</v>
       </c>
       <c r="U209">
-        <v>0.2720368884321589</v>
+        <v>-2.3644778555387269E-2</v>
       </c>
       <c r="V209">
-        <v>4.5738095354819208E-2</v>
+        <v>-0.27612920293194065</v>
       </c>
       <c r="X209">
         <v>111.59</v>
@@ -17273,13 +17264,13 @@
         <v>0.19413502201932009</v>
       </c>
       <c r="T210">
-        <v>2.511547173051909E-2</v>
+        <v>3.0972015506436357E-2</v>
       </c>
       <c r="U210">
-        <v>4.1660242568708483E-2</v>
+        <v>-0.13605432181853505</v>
       </c>
       <c r="V210">
-        <v>0.386721305279214</v>
+        <v>-0.19060886135984223</v>
       </c>
       <c r="X210">
         <v>111.45</v>
@@ -17368,13 +17359,13 @@
         <v>0.19367461021635698</v>
       </c>
       <c r="T211">
-        <v>5.2713355425337838E-2</v>
+        <v>5.561073885795853E-2</v>
       </c>
       <c r="U211">
-        <v>7.627292759155857E-2</v>
+        <v>7.275836396258839E-2</v>
       </c>
       <c r="V211">
-        <v>0.21544585228727708</v>
+        <v>-0.41962043419230266</v>
       </c>
       <c r="X211">
         <v>111.8</v>
@@ -17463,13 +17454,13 @@
         <v>0.19318056303065473</v>
       </c>
       <c r="T212">
-        <v>5.4901913123472923E-2</v>
+        <v>5.9045509171973265E-2</v>
       </c>
       <c r="U212">
-        <v>2.6172993737749728E-2</v>
+        <v>8.2724768500619383E-2</v>
       </c>
       <c r="V212">
-        <v>8.5278252719023229E-2</v>
+        <v>-0.22238570691441861</v>
       </c>
       <c r="X212">
         <v>111.8</v>
@@ -17558,13 +17549,13 @@
         <v>0.19295654755227906</v>
       </c>
       <c r="T213">
-        <v>7.2283603633405136E-2</v>
+        <v>5.5358996639154334E-2</v>
       </c>
       <c r="U213">
-        <v>1.756018880678667E-2</v>
+        <v>-2.5707785814232942E-2</v>
       </c>
       <c r="V213">
-        <v>0.28884123590300348</v>
+        <v>-8.5772316405652305E-2</v>
       </c>
       <c r="X213">
         <v>111.51</v>
@@ -17653,13 +17644,13 @@
         <v>0.19246241905804506</v>
       </c>
       <c r="T214">
-        <v>7.0584588460342879E-2</v>
+        <v>8.4560091760410572E-2</v>
       </c>
       <c r="U214">
-        <v>0.11321305299589746</v>
+        <v>3.004725433106703E-2</v>
       </c>
       <c r="V214">
-        <v>0.10786689330359867</v>
+        <v>-0.30215065522909423</v>
       </c>
       <c r="X214">
         <v>111</v>
@@ -17748,13 +17739,13 @@
         <v>0.19201434442268508</v>
       </c>
       <c r="T215">
-        <v>6.4740641906202434E-2</v>
+        <v>6.6802209893723763E-2</v>
       </c>
       <c r="U215">
-        <v>7.5268925873528403E-2</v>
+        <v>0.10937035400873096</v>
       </c>
       <c r="V215">
-        <v>0.34486457461673226</v>
+        <v>-0.10375853527395673</v>
       </c>
       <c r="X215">
         <v>111.96</v>
@@ -17843,13 +17834,13 @@
         <v>0.19131434623776111</v>
       </c>
       <c r="T216">
-        <v>5.6874975076737222E-2</v>
+        <v>6.5349158806426999E-2</v>
       </c>
       <c r="U216">
-        <v>0.1700289843527214</v>
+        <v>-7.461062039895161E-2</v>
       </c>
       <c r="V216">
-        <v>0.13752497113459494</v>
+        <v>-0.34545190743404675</v>
       </c>
       <c r="X216">
         <v>112</v>
@@ -17938,13 +17929,13 @@
         <v>0.1908025080953038</v>
       </c>
       <c r="T217">
-        <v>7.8373779953877509E-2</v>
+        <v>6.7344628493004599E-2</v>
       </c>
       <c r="U217">
-        <v>9.5484036609061462E-2</v>
+        <v>-0.15925602501936087</v>
       </c>
       <c r="V217">
-        <v>0.41654892242957153</v>
+        <v>-0.14890263851596863</v>
       </c>
       <c r="X217">
         <v>112.07</v>
@@ -18033,13 +18024,13 @@
         <v>0.18992109730143822</v>
       </c>
       <c r="T218">
-        <v>6.906863638977967E-2</v>
+        <v>7.721419169302024E-2</v>
       </c>
       <c r="U218">
-        <v>3.1645478867559085E-2</v>
+        <v>-9.6684854492212757E-2</v>
       </c>
       <c r="V218">
-        <v>0.68246202047650417</v>
+        <v>-0.41532468846161574</v>
       </c>
       <c r="X218">
         <v>112.35</v>
@@ -18128,13 +18119,13 @@
         <v>0.18902533238095859</v>
       </c>
       <c r="T219">
-        <v>6.8259273091553219E-2</v>
+        <v>7.050800212204944E-2</v>
       </c>
       <c r="U219">
-        <v>0.11619520101560088</v>
+        <v>3.3092348483343415E-2</v>
       </c>
       <c r="V219">
-        <v>0.70082768469461598</v>
+        <v>-0.68432088652048417</v>
       </c>
       <c r="X219">
         <v>112.6</v>
@@ -18223,13 +18214,13 @@
         <v>0.18902034159433223</v>
       </c>
       <c r="T220">
-        <v>7.0410663452169509E-2</v>
+        <v>6.8862372256961457E-2</v>
       </c>
       <c r="U220">
-        <v>0.23619105127121731</v>
+        <v>0.11684921753865041</v>
       </c>
       <c r="V220">
-        <v>0.83572928786621592</v>
+        <v>-0.70202782064887614</v>
       </c>
       <c r="X220">
         <v>112.37</v>
@@ -18318,13 +18309,13 @@
         <v>0.18878632846363513</v>
       </c>
       <c r="T221">
-        <v>6.96253987436668E-2</v>
+        <v>6.8033159873270854E-2</v>
       </c>
       <c r="U221">
-        <v>0.27017070633608142</v>
+        <v>0.23377974807099466</v>
       </c>
       <c r="V221">
-        <v>1.0209347387490908E-4</v>
+        <v>-0.83315450583862916</v>
       </c>
       <c r="X221">
         <v>112.39</v>
@@ -18413,13 +18404,13 @@
         <v>0.18011794798157094</v>
       </c>
       <c r="T222">
-        <v>7.0067143214069816E-2</v>
+        <v>7.0770582837620388E-2</v>
       </c>
       <c r="U222">
-        <v>0.20009963878473425</v>
+        <v>0.27134051902577561</v>
       </c>
       <c r="V222">
-        <v>1.3038528291930973E-2</v>
+        <v>-1.3394022828183694E-3</v>
       </c>
       <c r="X222">
         <v>112.2</v>
@@ -18508,13 +18499,13 @@
         <v>0.1801162667539975</v>
       </c>
       <c r="T223">
-        <v>6.3286185033573084E-2</v>
+        <v>7.2097527602177358E-2</v>
       </c>
       <c r="U223">
-        <v>0.27151663437832152</v>
+        <v>0.20208110149837477</v>
       </c>
       <c r="V223">
-        <v>0.16458763263478282</v>
+        <v>-1.5275545569681803E-2</v>
       </c>
       <c r="X223">
         <v>112.33</v>
@@ -18603,13 +18594,13 @@
         <v>0.1798281192724869</v>
       </c>
       <c r="T224">
-        <v>6.3579829822102418E-2</v>
+        <v>6.4178052555652343E-2</v>
       </c>
       <c r="U224">
-        <v>0.22026718609049478</v>
+        <v>0.2724386951301172</v>
       </c>
       <c r="V224">
-        <v>0.54666141014876324</v>
+        <v>-0.16556472426152435</v>
       </c>
       <c r="X224">
         <v>112.26</v>
@@ -18698,13 +18689,13 @@
         <v>0.1779135211733596</v>
       </c>
       <c r="T225">
-        <v>6.20989018146334E-2</v>
+        <v>6.4581256509033125E-2</v>
       </c>
       <c r="U225">
-        <v>0.33883476809029034</v>
+        <v>0.22127695373403977</v>
       </c>
       <c r="V225">
-        <v>8.3891763451870993E-2</v>
+        <v>-0.54774254176763737</v>
       </c>
       <c r="X225">
         <v>112.31</v>
@@ -18793,13 +18784,13 @@
         <v>0.17264069340213634</v>
       </c>
       <c r="T226">
-        <v>6.3805764562707701E-2</v>
+        <v>6.3569475362812433E-2</v>
       </c>
       <c r="U226">
-        <v>4.0833546470708804E-2</v>
+        <v>0.34027005733077154</v>
       </c>
       <c r="V226">
-        <v>9.5129243254143958E-2</v>
+        <v>8.2276486460464149E-2</v>
       </c>
       <c r="X226">
         <v>112.33</v>
@@ -18888,13 +18879,13 @@
         <v>0.17221825139009439</v>
       </c>
       <c r="T227">
-        <v>6.8699235034341832E-2</v>
+        <v>6.6799068782730231E-2</v>
       </c>
       <c r="U227">
-        <v>0.11889319312559099</v>
+        <v>4.385713448100681E-2</v>
       </c>
       <c r="V227">
-        <v>0.29034845889699401</v>
+        <v>-9.8354099910546999E-2</v>
       </c>
       <c r="X227">
         <v>112.5</v>
@@ -18983,13 +18974,13 @@
         <v>0.17171388431926501</v>
       </c>
       <c r="T228">
-        <v>7.0238232927777311E-2</v>
+        <v>7.3552089471284887E-2</v>
       </c>
       <c r="U228">
-        <v>0.11610104100334695</v>
+        <v>0.12368594959619728</v>
       </c>
       <c r="V228">
-        <v>0.11545291165175886</v>
+        <v>-0.29521336331821413</v>
       </c>
       <c r="X228">
         <v>112.4</v>
@@ -19078,13 +19069,13 @@
         <v>0.17128988099084894</v>
       </c>
       <c r="T229">
-        <v>9.2809831762141748E-2</v>
+        <v>9.6349041542831415E-2</v>
       </c>
       <c r="U229">
-        <v>0.14368542421512309</v>
+        <v>0.1422531140128136</v>
       </c>
       <c r="V229">
-        <v>0.34623329492555754</v>
+        <v>-0.14358858325838053</v>
       </c>
       <c r="X229">
         <v>112.29</v>
@@ -19173,13 +19164,13 @@
         <v>0.17072720539142999</v>
       </c>
       <c r="T230">
-        <v>9.2868897711340104E-2</v>
+        <v>9.2781058537472205E-2</v>
       </c>
       <c r="U230">
-        <v>0.14094720036956776</v>
+        <v>0.14357637397179879</v>
       </c>
       <c r="V230">
-        <v>1.0576722295333019</v>
+        <v>-0.34581185917241797</v>
       </c>
       <c r="X230">
         <v>111.72</v>
@@ -19268,13 +19259,13 @@
         <v>0.1633335162948826</v>
       </c>
       <c r="T231">
-        <v>8.829636457570178E-2</v>
+        <v>9.3773070847436024E-2</v>
       </c>
       <c r="U231">
-        <v>0.14533259324081005</v>
+        <v>0.14170511402107344</v>
       </c>
       <c r="V231">
-        <v>0.11228356388501837</v>
+        <v>-1.0556481047270472</v>
       </c>
       <c r="X231">
         <v>111.5</v>
@@ -19363,13 +19354,13 @@
         <v>0.14974919334195222</v>
       </c>
       <c r="T232">
-        <v>8.7325202364718635E-2</v>
+        <v>8.9034347292460403E-2</v>
       </c>
       <c r="U232">
-        <v>0.13701336560456578</v>
+        <v>0.14598585162042266</v>
       </c>
       <c r="V232">
-        <v>0.11803479368661662</v>
+        <v>-0.11304890558900826</v>
       </c>
       <c r="X232">
         <v>110.71</v>
@@ -19458,13 +19449,13 @@
         <v>0.14975190221267753</v>
       </c>
       <c r="T233">
-        <v>6.8556593049340364E-2</v>
+        <v>7.4522410677602124E-2</v>
       </c>
       <c r="U233">
-        <v>0.12967758678066321</v>
+        <v>0.12399679394246022</v>
       </c>
       <c r="V233">
-        <v>0.21546174452302669</v>
+        <v>-0.10418214232710277</v>
       </c>
       <c r="X233">
         <v>110.01</v>
@@ -19553,13 +19544,13 @@
         <v>0.14954901044867067</v>
       </c>
       <c r="T234">
-        <v>7.8702678948927574E-2</v>
+        <v>8.0040457257890552E-2</v>
       </c>
       <c r="U234">
-        <v>5.3558232612127554E-2</v>
+        <v>0.1411676190746558</v>
       </c>
       <c r="V234">
-        <v>8.3096678330463192E-2</v>
+        <v>-0.22775918202648793</v>
       </c>
       <c r="X234">
         <v>110.49</v>
@@ -19648,13 +19639,13 @@
         <v>0.14921260636822206</v>
       </c>
       <c r="T235">
-        <v>7.856257604411665E-2</v>
+        <v>7.9747980423838793E-2</v>
       </c>
       <c r="U235">
-        <v>0.13295730231867031</v>
+        <v>5.4603232961103476E-2</v>
       </c>
       <c r="V235">
-        <v>0.19933076306632991</v>
+        <v>-8.4223807282701735E-2</v>
       </c>
       <c r="X235">
         <v>110.5</v>
@@ -19743,13 +19734,13 @@
         <v>0.14899351585146897</v>
       </c>
       <c r="T236">
-        <v>7.8316137294209831E-2</v>
+        <v>8.189081257700126E-2</v>
       </c>
       <c r="U236">
-        <v>0.13180827903658265</v>
+        <v>0.13629149096273663</v>
       </c>
       <c r="V236">
-        <v>0.24344674275484923</v>
+        <v>-0.20291198803457089</v>
       </c>
       <c r="X236">
         <v>109.9</v>
@@ -19838,13 +19829,13 @@
         <v>0.14896481119152793</v>
       </c>
       <c r="T237">
-        <v>8.1306900257394066E-2</v>
+        <v>7.859493072936985E-2</v>
       </c>
       <c r="U237">
-        <v>0.12891427486778628</v>
+        <v>0.13200624693293639</v>
       </c>
       <c r="V237">
-        <v>0.24674997381595176</v>
+        <v>-0.24350262379151388</v>
       </c>
       <c r="X237">
         <v>109.78</v>
@@ -19933,13 +19924,13 @@
         <v>0.14896472514335693</v>
       </c>
       <c r="T238">
-        <v>0.2269562624228838</v>
+        <v>7.8460019940285175E-2</v>
       </c>
       <c r="U238">
-        <v>0.12842083870889809</v>
+        <v>0.125995812297508</v>
       </c>
       <c r="V238">
-        <v>0.34754105753049824</v>
+        <v>-0.24347645006408403</v>
       </c>
       <c r="X238">
         <v>110.7</v>
@@ -20028,13 +20019,13 @@
         <v>0.16684020170631186</v>
       </c>
       <c r="T239">
-        <v>1.0940940097592167</v>
+        <v>1.2255601757383161</v>
       </c>
       <c r="U239">
-        <v>1.1353089095342717</v>
+        <v>1.1337998682038442</v>
       </c>
       <c r="V239">
-        <v>1.5966491527248383</v>
+        <v>-1.4277789051623246</v>
       </c>
       <c r="X239">
         <v>110.16</v>
@@ -20123,13 +20114,13 @@
         <v>0.18308400193708302</v>
       </c>
       <c r="T240">
-        <v>7.2126257811733208E-2</v>
+        <v>0.10170792730889167</v>
       </c>
       <c r="U240">
-        <v>0.1274773594492129</v>
+        <v>0.13310649280395825</v>
       </c>
       <c r="V240">
-        <v>0.36770213844858901</v>
+        <v>-0.52424016127528006</v>
       </c>
       <c r="X240">
         <v>110.2</v>
@@ -20218,13 +20209,13 @@
         <v>0.18276530482685716</v>
       </c>
       <c r="T241">
-        <v>5.9621269499510188E-2</v>
+        <v>6.5728280103105607E-2</v>
       </c>
       <c r="U241">
-        <v>0.11821649129737377</v>
+        <v>0.12082108544552161</v>
       </c>
       <c r="V241">
-        <v>0.17417685341087896</v>
+        <v>-0.35979269075534503</v>
       </c>
       <c r="X241">
         <v>110</v>
@@ -20313,13 +20304,13 @@
         <v>0.18229964292875214</v>
       </c>
       <c r="T242">
-        <v>6.0624442299994641E-2</v>
+        <v>6.1064363117646625E-2</v>
       </c>
       <c r="U242">
-        <v>0.11548002237027344</v>
+        <v>0.11959391883242798</v>
       </c>
       <c r="V242">
-        <v>0.34320158973804027</v>
+        <v>-0.17556754484098214</v>
       </c>
       <c r="X242">
         <v>109.33</v>
@@ -20408,13 +20399,13 @@
         <v>0.18190018242363623</v>
       </c>
       <c r="T243">
-        <v>4.7573013406865261E-2</v>
+        <v>5.937181930940616E-2</v>
       </c>
       <c r="U243">
-        <v>0.13059550964250599</v>
+        <v>0.11411998256123379</v>
       </c>
       <c r="V243">
-        <v>0.39110415988925507</v>
+        <v>-0.34138868275597201</v>
       </c>
       <c r="X243">
         <v>109.55</v>
@@ -20503,13 +20494,13 @@
         <v>0.18186190388909204</v>
       </c>
       <c r="T244">
-        <v>5.0481591778395174E-2</v>
+        <v>4.683853804314797E-2</v>
       </c>
       <c r="U244">
-        <v>0.11631007219571332</v>
+        <v>0.12996649920476999</v>
       </c>
       <c r="V244">
-        <v>0.36498967137064131</v>
+        <v>-0.39079068147680474</v>
       </c>
       <c r="X244">
         <v>109.65</v>
@@ -20598,13 +20589,13 @@
         <v>0.18185449399141951</v>
       </c>
       <c r="T245">
-        <v>4.9653681665051685E-2</v>
+        <v>5.0243518943182686E-2</v>
       </c>
       <c r="U245">
-        <v>0.11401138922569887</v>
+        <v>0.11605802314017533</v>
       </c>
       <c r="V245">
-        <v>0.20587798741549257</v>
+        <v>-0.36468228947823533</v>
       </c>
       <c r="X245">
         <v>109.8</v>
@@ -20693,13 +20684,13 @@
         <v>0.1815084007218781</v>
       </c>
       <c r="T246">
-        <v>4.016132233195524E-2</v>
+        <v>5.0257463937475322E-2</v>
       </c>
       <c r="U246">
-        <v>0.10631740953741531</v>
+        <v>0.11457961402907557</v>
       </c>
       <c r="V246">
-        <v>0.27965271264580593</v>
+        <v>-0.20642353307152028</v>
       </c>
       <c r="X246">
         <v>109.99</v>
@@ -20788,13 +20779,13 @@
         <v>0.18142983702298929</v>
       </c>
       <c r="T247">
-        <v>4.0594229340773502E-2</v>
+        <v>3.9474322605581591E-2</v>
       </c>
       <c r="U247">
-        <v>0.11622845135051962</v>
+        <v>0.10549781070171571</v>
       </c>
       <c r="V247">
-        <v>8.2210011917371872E-2</v>
+        <v>-0.27846720249922186</v>
       </c>
       <c r="X247">
         <v>110.3</v>
@@ -20883,13 +20874,13 @@
         <v>0.18089157018849539</v>
       </c>
       <c r="T248">
-        <v>3.2799365127889057E-2</v>
+        <v>3.4159909212549966E-2</v>
       </c>
       <c r="U248">
-        <v>0.10138147878379078</v>
+        <v>0.10927567845937514</v>
       </c>
       <c r="V248">
-        <v>9.7812196909163873E-2</v>
+        <v>-7.5080874694744004E-2</v>
       </c>
       <c r="X248">
         <v>109.6</v>
@@ -20978,13 +20969,13 @@
         <v>0.1808838547616328</v>
       </c>
       <c r="T249">
-        <v>3.4871266387737077E-2</v>
+        <v>3.5419971386996263E-2</v>
       </c>
       <c r="U249">
-        <v>0.10172906788984415</v>
+        <v>0.10390143864643653</v>
       </c>
       <c r="V249">
-        <v>0.31431713183609489</v>
+        <v>-0.10050220262676213</v>
       </c>
       <c r="X249">
         <v>108.92</v>
@@ -21073,13 +21064,13 @@
         <v>0.18021281537136738</v>
       </c>
       <c r="T250">
-        <v>4.002511037813905E-2</v>
+        <v>3.7762090806725546E-2</v>
       </c>
       <c r="U250">
-        <v>0.10605908187596436</v>
+        <v>0.1045803974027204</v>
       </c>
       <c r="V250">
-        <v>0.24165539525646818</v>
+        <v>-0.31710012184491543</v>
       </c>
       <c r="X250">
         <v>108.92</v>
@@ -21168,13 +21159,13 @@
         <v>0.18013802541873219</v>
       </c>
       <c r="T251">
-        <v>2.3881196012476291E-2</v>
+        <v>2.4966249205848889E-2</v>
       </c>
       <c r="U251">
-        <v>9.2278470289974823E-2</v>
+        <v>9.0720441979874611E-2</v>
       </c>
       <c r="V251">
-        <v>7.9366135388658776E-2</v>
+        <v>-0.22522148369643613</v>
       </c>
       <c r="X251">
         <v>108.7</v>
@@ -21263,13 +21254,13 @@
         <v>0.17983285075735317</v>
       </c>
       <c r="T252">
-        <v>3.1667912199950798E-2</v>
+        <v>3.3618885345199079E-2</v>
       </c>
       <c r="U252">
-        <v>0.10159229877463316</v>
+        <v>0.10226628325666898</v>
       </c>
       <c r="V252">
-        <v>0.12455262253867616</v>
+        <v>-8.9899651081659648E-2</v>
       </c>
       <c r="X252">
         <v>108.5</v>
@@ -21358,13 +21349,13 @@
         <v>0.17981475370855848</v>
       </c>
       <c r="T253">
-        <v>3.3333507908706039E-2</v>
+        <v>3.417693342204764E-2</v>
       </c>
       <c r="U253">
-        <v>9.5490223304028898E-2</v>
+        <v>0.10394836108666983</v>
       </c>
       <c r="V253">
-        <v>7.4237504795138243E-2</v>
+        <v>-0.1269987291214747</v>
       </c>
       <c r="X253">
         <v>108.8</v>
@@ -21453,13 +21444,13 @@
         <v>0.17922476877894061</v>
       </c>
       <c r="T254">
-        <v>3.4671002864883338E-2</v>
+        <v>3.562361795004243E-2</v>
       </c>
       <c r="U254">
-        <v>9.7418436949470166E-2</v>
+        <v>9.7985175491310805E-2</v>
       </c>
       <c r="V254">
-        <v>0.12155252690526641</v>
+        <v>7.2090210302833135E-2</v>
       </c>
       <c r="X254">
         <v>108.32</v>
@@ -21548,13 +21539,13 @@
         <v>0.17918923681305937</v>
       </c>
       <c r="T255">
-        <v>3.8934092314091284E-2</v>
+        <v>4.0343590717484279E-2</v>
       </c>
       <c r="U255">
-        <v>0.10110675548339332</v>
+        <v>0.10350126101833501</v>
       </c>
       <c r="V255">
-        <v>0.10428405783999839</v>
+        <v>0.11630804128250904</v>
       </c>
       <c r="X255">
         <v>108.71</v>
@@ -21643,13 +21634,13 @@
         <v>0.1791875352811047</v>
       </c>
       <c r="T256">
-        <v>3.9418333787033522E-2</v>
+        <v>4.2303134366061812E-2</v>
       </c>
       <c r="U256">
-        <v>0.1050302276713877</v>
+        <v>0.10477417342986683</v>
       </c>
       <c r="V256">
-        <v>0.15236013184312114</v>
+        <v>0.10125879385234349</v>
       </c>
       <c r="X256">
         <v>108.72</v>
@@ -21738,13 +21729,13 @@
         <v>0.17915514035746388</v>
       </c>
       <c r="T257">
-        <v>5.2441648696421872E-2</v>
+        <v>5.7164805181464384E-2</v>
       </c>
       <c r="U257">
-        <v>0.12527041039340769</v>
+        <v>0.12341552396178956</v>
       </c>
       <c r="V257">
-        <v>0.15813251180329946</v>
+        <v>0.13444243987574822</v>
       </c>
       <c r="X257">
         <v>108.7</v>
@@ -21833,13 +21824,13 @@
         <v>0.17794813860586808</v>
       </c>
       <c r="T258">
-        <v>1.888568110174349E-2</v>
+        <v>4.4300692889576165E-2</v>
       </c>
       <c r="U258">
-        <v>0.11350294188635646</v>
+        <v>0.11676528047442902</v>
       </c>
       <c r="V258">
-        <v>0.33581987283390902</v>
+        <v>-0.14902030401959809</v>
       </c>
       <c r="X258">
         <v>109.65</v>
@@ -21928,13 +21919,13 @@
         <v>0.17744225086632956</v>
       </c>
       <c r="T259">
-        <v>1.0927053067566472E-2</v>
+        <v>1.1024710307405705E-2</v>
       </c>
       <c r="U259">
-        <v>0.1019483307897473</v>
+        <v>0.10540450058867945</v>
       </c>
       <c r="V259">
-        <v>0.16688273363876238</v>
+        <v>-0.32685775048189036</v>
       </c>
       <c r="X259">
         <v>108.59</v>
@@ -22023,13 +22014,13 @@
         <v>0.17708166808633885</v>
       </c>
       <c r="T260">
-        <v>1.7483379720650838E-2</v>
+        <v>1.8596434448903132E-2</v>
       </c>
       <c r="U260">
-        <v>0.1099384994385999</v>
+        <v>0.10986053949241237</v>
       </c>
       <c r="V260">
-        <v>0.39561815417974433</v>
+        <v>-0.1753733254257428</v>
       </c>
       <c r="X260">
         <v>109.2</v>
@@ -22118,13 +22109,13 @@
         <v>0.17636538624158302</v>
       </c>
       <c r="T261">
-        <v>1.425784692095089E-2</v>
+        <v>1.509921635439726E-2</v>
       </c>
       <c r="U261">
-        <v>0.10247964826289868</v>
+        <v>0.10792050912618034</v>
       </c>
       <c r="V261">
-        <v>0.20689264020621323</v>
+        <v>-0.39462707363324689</v>
       </c>
       <c r="X261">
         <v>108.65</v>
@@ -22213,13 +22204,13 @@
         <v>0.17587032064410221</v>
       </c>
       <c r="T262">
-        <v>3.9980941217931942E-2</v>
+        <v>2.7347435534752496E-2</v>
       </c>
       <c r="U262">
-        <v>0.11429430811069619</v>
+        <v>0.11604420212917299</v>
       </c>
       <c r="V262">
-        <v>0.16572481988359478</v>
+        <v>-0.22171680071436661</v>
       </c>
       <c r="X262">
         <v>109</v>
@@ -22308,13 +22299,13 @@
         <v>0.17590649671194902</v>
       </c>
       <c r="T263">
-        <v>0.10026085290338882</v>
+        <v>0.11178034473057208</v>
       </c>
       <c r="U263">
-        <v>0.17981522372719771</v>
+        <v>0.18586050684452626</v>
       </c>
       <c r="V263">
-        <v>0.65567272651207986</v>
+        <v>-0.24144268347494613</v>
       </c>
       <c r="X263">
         <v>109.3</v>
@@ -22403,13 +22394,13 @@
         <v>0.17346388053131859</v>
       </c>
       <c r="T264">
-        <v>2.6121939950374262E-2</v>
+        <v>2.7159730118664349E-2</v>
       </c>
       <c r="U264">
-        <v>0.10548997900566848</v>
+        <v>0.1068687653973277</v>
       </c>
       <c r="V264">
-        <v>0.43863617352093431</v>
+        <v>-0.57750380756684816</v>
       </c>
       <c r="X264">
         <v>109.4</v>
@@ -22498,13 +22489,13 @@
         <v>0.17319476184318694</v>
       </c>
       <c r="T265">
-        <v>2.9372953022310799E-2</v>
+        <v>3.2722778021576637E-2</v>
       </c>
       <c r="U265">
-        <v>0.11077796402874096</v>
+        <v>0.11200748048132425</v>
       </c>
       <c r="V265">
-        <v>0.52825278955723753</v>
+        <v>-0.44534528440349774</v>
       </c>
       <c r="X265">
         <v>109.43</v>
@@ -22593,13 +22584,13 @@
         <v>0.17308490934284051</v>
       </c>
       <c r="T266">
-        <v>2.9782220912921709E-2</v>
+        <v>3.0139061869582928E-2</v>
       </c>
       <c r="U266">
-        <v>0.10783965407465956</v>
+        <v>0.11145634016795913</v>
       </c>
       <c r="V266">
-        <v>0.50848781017625022</v>
+        <v>-0.52855770287671966</v>
       </c>
       <c r="X266">
         <v>109.76</v>
@@ -22688,13 +22679,13 @@
         <v>0.17308134976541611</v>
       </c>
       <c r="T267">
-        <v>3.673038572912235E-2</v>
+        <v>3.3908007457672529E-2</v>
       </c>
       <c r="U267">
-        <v>0.1144733182920632</v>
+        <v>0.11183051248093712</v>
       </c>
       <c r="V267">
-        <v>0.4315748853188861</v>
+        <v>-0.51225274933195397</v>
       </c>
       <c r="X267">
         <v>109.75</v>
@@ -22783,13 +22774,13 @@
         <v>0.17299290580511478</v>
       </c>
       <c r="T268">
-        <v>0.98955121181778516</v>
+        <v>3.0592957681763178E-2</v>
       </c>
       <c r="U268">
-        <v>0.2559898665548066</v>
+        <v>0.10823830450971128</v>
       </c>
       <c r="V268">
-        <v>0.34999198546161736</v>
+        <v>-0.42426212181430056</v>
       </c>
       <c r="X268">
         <v>109.65</v>
@@ -22878,13 +22869,13 @@
         <v>0.17291548559415024</v>
       </c>
       <c r="T269">
-        <v>2.3736780767691368E-2</v>
+        <v>-0.99075017678539323</v>
       </c>
       <c r="U269">
-        <v>0.12470526887131683</v>
+        <v>0.25441473740013265</v>
       </c>
       <c r="V269">
-        <v>0.31993942181283153</v>
+        <v>-0.34830403883703287</v>
       </c>
       <c r="X269">
         <v>109.27</v>
@@ -22973,13 +22964,13 @@
         <v>0.17290536455498953</v>
       </c>
       <c r="T270">
-        <v>2.8708912789865426E-2</v>
+        <v>2.2348146573225591E-2</v>
       </c>
       <c r="U270">
-        <v>9.3764609563362633E-2</v>
+        <v>0.12321945604614193</v>
       </c>
       <c r="V270">
-        <v>0.51071304937126971</v>
+        <v>-0.31814156217400136</v>
       </c>
       <c r="X270">
         <v>108.7</v>
@@ -23068,13 +23059,13 @@
         <v>0.17231787333479034</v>
       </c>
       <c r="T271">
-        <v>3.2418318423776959E-2</v>
+        <v>3.3939640648716907E-2</v>
       </c>
       <c r="U271">
-        <v>9.2752405360585488E-2</v>
+        <v>9.8878132093072058E-2</v>
       </c>
       <c r="V271">
-        <v>0.10927343864171046</v>
+        <v>-0.51608645443730339</v>
       </c>
       <c r="X271">
         <v>108.99</v>
@@ -23163,13 +23154,13 @@
         <v>0.16978681234915324</v>
       </c>
       <c r="T272">
-        <v>3.4437525021568938E-2</v>
+        <v>3.3197643393800824E-2</v>
       </c>
       <c r="U272">
-        <v>9.3038544498136311E-2</v>
+        <v>9.3478540227154294E-2</v>
       </c>
       <c r="V272">
-        <v>8.518750364494565E-3</v>
+        <v>-0.11003173169872316</v>
       </c>
       <c r="X272">
         <v>108.85</v>
@@ -23258,13 +23249,13 @@
         <v>0.16962762478637108</v>
       </c>
       <c r="T273">
-        <v>3.344402927170087E-2</v>
+        <v>3.2667261127250491E-2</v>
       </c>
       <c r="U273">
-        <v>7.9534698713290553E-2</v>
+        <v>9.1367659777008559E-2</v>
       </c>
       <c r="V273">
-        <v>0.10321842299512163</v>
+        <v>-6.6781877730459627E-3</v>
       </c>
       <c r="X273">
         <v>109.15</v>
@@ -23353,13 +23344,13 @@
         <v>0.16944077286904433</v>
       </c>
       <c r="T274">
-        <v>3.7899889417625232E-2</v>
+        <v>3.7657464375451255E-2</v>
       </c>
       <c r="U274">
-        <v>8.7348991067526249E-2</v>
+        <v>8.369893902038239E-2</v>
       </c>
       <c r="V274">
-        <v>0.170966956165719</v>
+        <v>9.9038839926945954E-2</v>
       </c>
       <c r="X274">
         <v>109.2</v>
@@ -23448,13 +23439,13 @@
         <v>0.16936011929487055</v>
       </c>
       <c r="T275">
-        <v>4.0924154076438235E-2</v>
+        <v>4.1551977473375246E-2</v>
       </c>
       <c r="U275">
-        <v>9.0324058326263224E-2</v>
+        <v>9.0904320785745174E-2</v>
       </c>
       <c r="V275">
-        <v>0.33929268924715039</v>
+        <v>0.16717614756047716</v>
       </c>
       <c r="X275">
         <v>109</v>
@@ -23543,13 +23534,13 @@
         <v>0.16889767394900748</v>
       </c>
       <c r="T276">
-        <v>4.2386208269573622E-2</v>
+        <v>4.1676514216049121E-2</v>
       </c>
       <c r="U276">
-        <v>8.0931330029088144E-2</v>
+        <v>9.1037694334872299E-2</v>
       </c>
       <c r="V276">
-        <v>0.34838885085637372</v>
+        <v>0.33836693503941362</v>
       </c>
       <c r="X276">
         <v>109</v>
@@ -23638,13 +23629,13 @@
         <v>0.16889601129328527</v>
       </c>
       <c r="T277">
-        <v>5.1514510036110295E-2</v>
+        <v>4.4779065717448496E-2</v>
       </c>
       <c r="U277">
-        <v>8.4371647462411214E-2</v>
+        <v>8.3251541017603792E-2</v>
       </c>
       <c r="V277">
-        <v>0.16160073776305683</v>
+        <v>0.34583025544836499</v>
       </c>
       <c r="X277">
         <v>109.75</v>
@@ -23733,13 +23724,13 @@
         <v>0.16485261398574036</v>
       </c>
       <c r="T278">
-        <v>5.0212636224022944E-2</v>
+        <v>5.2926437538447502E-2</v>
       </c>
       <c r="U278">
-        <v>8.434905167756801E-2</v>
+        <v>8.5749234213161607E-2</v>
       </c>
       <c r="V278">
-        <v>0.18547263873809339</v>
+        <v>-0.16307894314460114</v>
       </c>
       <c r="X278">
         <v>109.45</v>
@@ -23828,13 +23819,13 @@
         <v>0.16484415789871876</v>
       </c>
       <c r="T279">
-        <v>4.7289375262637989E-2</v>
+        <v>5.0317072350192227E-2</v>
       </c>
       <c r="U279">
-        <v>8.385780494645223E-2</v>
+        <v>8.4455844680508818E-2</v>
       </c>
       <c r="V279">
-        <v>5.6949282698837145E-2</v>
+        <v>-0.18560165924443872</v>
       </c>
       <c r="X279">
         <v>109.52</v>
@@ -23923,13 +23914,13 @@
         <v>0.16458494882326127</v>
       </c>
       <c r="T280">
-        <v>6.1738095250252201E-2</v>
+        <v>4.5855311032383383E-2</v>
       </c>
       <c r="U280">
-        <v>8.4714683350417541E-2</v>
+        <v>8.242317551112599E-2</v>
       </c>
       <c r="V280">
-        <v>8.1425279854707711E-2</v>
+        <v>-5.5474699020896523E-2</v>
       </c>
       <c r="X280">
         <v>109.3</v>
@@ -24018,13 +24009,13 @@
         <v>0.1645740910935376</v>
       </c>
       <c r="T281">
-        <v>4.8189367535966809E-2</v>
+        <v>5.8465326058421141E-2</v>
       </c>
       <c r="U281">
-        <v>8.0429614207633282E-2</v>
+        <v>8.1531395526890371E-2</v>
       </c>
       <c r="V281">
-        <v>7.9727807042817567E-2</v>
+        <v>-7.8066717568603394E-2</v>
       </c>
       <c r="X281">
         <v>109.4</v>
@@ -24113,13 +24104,13 @@
         <v>0.16457407414327896</v>
       </c>
       <c r="T282">
-        <v>4.4179277454414745E-2</v>
+        <v>4.6788308923195743E-2</v>
       </c>
       <c r="U282">
-        <v>7.7130295398875059E-2</v>
+        <v>7.9077833293927924E-2</v>
       </c>
       <c r="V282">
-        <v>0.14679245892816883</v>
+        <v>-7.8297381934389065E-2</v>
       </c>
       <c r="X282">
         <v>109.2</v>
@@ -24208,13 +24199,13 @@
         <v>0.16449757638943205</v>
       </c>
       <c r="T283">
-        <v>4.5942769173112907E-2</v>
+        <v>4.8384845633675511E-2</v>
       </c>
       <c r="U283">
-        <v>8.0366631127481991E-2</v>
+        <v>8.1227847346709847E-2</v>
       </c>
       <c r="V283">
-        <v>0.62921767218029334</v>
+        <v>-0.15122527907274197</v>
       </c>
       <c r="X283">
         <v>109.18</v>
@@ -24303,13 +24294,13 @@
         <v>0.16073251696284144</v>
       </c>
       <c r="T284">
-        <v>4.4967285452113259E-2</v>
+        <v>5.0943500521372087E-2</v>
       </c>
       <c r="U284">
-        <v>8.4252648522165074E-2</v>
+        <v>8.5217685646599151E-2</v>
       </c>
       <c r="V284">
-        <v>0.36691821050967022</v>
+        <v>-0.63477500298945166</v>
       </c>
       <c r="X284">
         <v>109.04</v>
@@ -24398,13 +24389,13 @@
         <v>0.15957905598622973</v>
       </c>
       <c r="T285">
-        <v>4.1846188630323411E-2</v>
+        <v>4.5343426454547142E-2</v>
       </c>
       <c r="U285">
-        <v>8.3236830803889994E-2</v>
+        <v>8.4651172052174761E-2</v>
       </c>
       <c r="V285">
-        <v>0.43390398142397757</v>
+        <v>-0.36757018712370026</v>
       </c>
       <c r="X285">
         <v>109</v>
@@ -24493,13 +24484,13 @@
         <v>0.15949845371859575</v>
       </c>
       <c r="T286">
-        <v>2.4361406659734186E-2</v>
+        <v>4.2470061056176789E-2</v>
       </c>
       <c r="U286">
-        <v>8.0986536109906027E-2</v>
+        <v>8.3865322890053218E-2</v>
       </c>
       <c r="V286">
-        <v>0.39066574602248938</v>
+        <v>-0.43473709511303582</v>
       </c>
       <c r="X286">
         <v>109.25</v>
@@ -24588,13 +24579,13 @@
         <v>0.15947094032617376</v>
       </c>
       <c r="T287">
-        <v>3.0870871992072502E-2</v>
+        <v>2.2618884402003658E-2</v>
       </c>
       <c r="U287">
-        <v>7.4716304694366631E-2</v>
+        <v>7.9406764557843346E-2</v>
       </c>
       <c r="V287">
-        <v>0.76953288145951149</v>
+        <v>-0.38969253404592674</v>
       </c>
       <c r="X287">
         <v>108.93</v>
@@ -24683,13 +24674,13 @@
         <v>0.15696183821982507</v>
       </c>
       <c r="T288">
-        <v>4.1865968165222256E-2</v>
+        <v>3.3743831674759583E-2</v>
       </c>
       <c r="U288">
-        <v>5.2077779173442806E-2</v>
+        <v>7.7572236267742234E-2</v>
       </c>
       <c r="V288">
-        <v>0.58689601705521621</v>
+        <v>-0.77322944807847183</v>
       </c>
       <c r="X288">
         <v>108.9</v>
@@ -24778,13 +24769,13 @@
         <v>0.15640372182401308</v>
       </c>
       <c r="T289">
-        <v>3.3405969855437867E-2</v>
+        <v>4.1334948651172709E-2</v>
       </c>
       <c r="U289">
-        <v>5.154298930116763E-2</v>
+        <v>5.1577306302019732E-2</v>
       </c>
       <c r="V289">
-        <v>0.12216561151623395</v>
+        <v>-0.58729423700605299</v>
       </c>
       <c r="X289">
         <v>108.81</v>
@@ -24873,13 +24864,13 @@
         <v>0.15271245381138462</v>
       </c>
       <c r="T290">
-        <v>3.5575001287324604E-2</v>
+        <v>3.3215369976535847E-2</v>
       </c>
       <c r="U290">
-        <v>5.0360047469988345E-2</v>
+        <v>5.1380735464656713E-2</v>
       </c>
       <c r="V290">
-        <v>0.37413738129645768</v>
+        <v>-0.12208908480926262</v>
       </c>
       <c r="X290">
         <v>109.7</v>
@@ -24968,13 +24959,13 @@
         <v>0.15157787763906991</v>
       </c>
       <c r="T291">
-        <v>1.8242504386578595E-2</v>
+        <v>3.1507270821884426E-2</v>
       </c>
       <c r="U291">
-        <v>4.5577661052420559E-2</v>
+        <v>4.6377232865546514E-2</v>
       </c>
       <c r="V291">
-        <v>0.63200338515927434</v>
+        <v>-0.3708986819063842</v>
       </c>
       <c r="X291">
         <v>109.69</v>
@@ -25063,13 +25054,13 @@
         <v>0.15034628151220789</v>
       </c>
       <c r="T292">
-        <v>4.8207377251530126E-2</v>
+        <v>2.4060242757983907E-2</v>
       </c>
       <c r="U292">
-        <v>6.4278563494291063E-2</v>
+        <v>5.1481637590589102E-2</v>
       </c>
       <c r="V292">
-        <v>0.27988113923849145</v>
+        <v>-0.64043803428375234</v>
       </c>
       <c r="X292">
         <v>112.41</v>
@@ -25158,13 +25149,13 @@
         <v>0.14808197946039273</v>
       </c>
       <c r="T293">
-        <v>3.0865958265446913E-2</v>
+        <v>-4.293773708394788E-2</v>
       </c>
       <c r="U293">
-        <v>5.8271887585803483E-2</v>
+        <v>6.9919176936839023E-2</v>
       </c>
       <c r="V293">
-        <v>0.2196209424556228</v>
+        <v>-0.28635926110653909</v>
       </c>
       <c r="X293">
         <v>110.74</v>
@@ -25253,13 +25244,13 @@
         <v>0.14353927005616507</v>
       </c>
       <c r="T294">
-        <v>2.7257105337730181E-2</v>
+        <v>3.3965302640615036E-2</v>
       </c>
       <c r="U294">
-        <v>6.0334506496850793E-2</v>
+        <v>6.1393110580865162E-2</v>
       </c>
       <c r="V294">
-        <v>0.58136401736952337</v>
+        <v>0.21671797149214189</v>
       </c>
       <c r="X294">
         <v>110.5</v>
@@ -25348,13 +25339,13 @@
         <v>0.14110880548407775</v>
       </c>
       <c r="T295">
-        <v>1.8699864294235979E-2</v>
+        <v>1.9488113993926248E-2</v>
       </c>
       <c r="U295">
-        <v>4.9099934711915871E-2</v>
+        <v>5.2481485001076855E-2</v>
       </c>
       <c r="V295">
-        <v>0.2528777648955538</v>
+        <v>0.58732157795973183</v>
       </c>
       <c r="X295">
         <v>111</v>
@@ -25443,13 +25434,13 @@
         <v>0.12747646841595753</v>
       </c>
       <c r="T296">
-        <v>1.7164321600771082E-2</v>
+        <v>2.1358086665523857E-2</v>
       </c>
       <c r="U296">
-        <v>5.1357817262220884E-2</v>
+        <v>5.1684929495632304E-2</v>
       </c>
       <c r="V296">
-        <v>0.2965686473843876</v>
+        <v>-0.25512529160711672</v>
       </c>
       <c r="X296">
         <v>111.29</v>
@@ -25538,13 +25529,13 @@
         <v>0.12744130784843197</v>
       </c>
       <c r="T297">
-        <v>3.6686631395621561E-2</v>
+        <v>3.0398446138235613E-2</v>
       </c>
       <c r="U297">
-        <v>6.7785256801577987E-2</v>
+        <v>6.4870086204105171E-2</v>
       </c>
       <c r="V297">
-        <v>0.28018521487844783</v>
+        <v>-0.3127864950185355</v>
       </c>
       <c r="X297">
         <v>110.81</v>
@@ -25633,13 +25624,13 @@
         <v>0.12742294637427556</v>
       </c>
       <c r="T298">
-        <v>3.6071976626628199E-2</v>
+        <v>3.4503772577587632E-2</v>
       </c>
       <c r="U298">
-        <v>0.97739583508302808</v>
+        <v>6.5620155906520594E-2</v>
       </c>
       <c r="V298">
-        <v>0.24251195209035181</v>
+        <v>-0.27801387242445408</v>
       </c>
       <c r="X298">
         <v>111.7</v>
@@ -25728,13 +25719,13 @@
         <v>0.12740104690249771</v>
       </c>
       <c r="T299">
-        <v>3.1597583937958973E-2</v>
+        <v>3.0160901985643029E-2</v>
       </c>
       <c r="U299">
-        <v>5.4384697988063557E-2</v>
+        <v>-0.98449412391024005</v>
       </c>
       <c r="V299">
-        <v>0.23226039967694234</v>
+        <v>-0.23672909968519562</v>
       </c>
       <c r="X299">
         <v>112.04</v>
@@ -25823,13 +25814,13 @@
         <v>0.12740090097056819</v>
       </c>
       <c r="T300">
-        <v>2.6845455112467498E-2</v>
+        <v>3.2228606516016001E-2</v>
       </c>
       <c r="U300">
-        <v>6.1736532363365626E-2</v>
+        <v>5.5082859633337478E-2</v>
       </c>
       <c r="V300">
-        <v>0.12422081642411431</v>
+        <v>-0.23351072213875224</v>
       </c>
       <c r="X300">
         <v>111.87</v>
@@ -25918,13 +25909,13 @@
         <v>0.12716608901256907</v>
       </c>
       <c r="T301">
-        <v>2.9747457843654068E-2</v>
+        <v>3.0553004058209154E-2</v>
       </c>
       <c r="U301">
-        <v>6.4014905977738401E-2</v>
+        <v>6.5537664908243976E-2</v>
       </c>
       <c r="V301">
-        <v>6.4963785642824234E-2</v>
+        <v>-0.12826028421493163</v>
       </c>
       <c r="X301">
         <v>112.29</v>
@@ -26013,13 +26004,13 @@
         <v>0.12708778348638528</v>
       </c>
       <c r="T302">
-        <v>3.1988857079312538E-2</v>
+        <v>3.0163378619829651E-2</v>
       </c>
       <c r="U302">
-        <v>6.5778069165811637E-2</v>
+        <v>6.4447563062075552E-2</v>
       </c>
       <c r="V302">
-        <v>0.22462781929071252</v>
+        <v>-6.540395035408153E-2</v>
       </c>
       <c r="X302">
         <v>112.6</v>
@@ -26108,13 +26099,13 @@
         <v>0.12657592726487477</v>
       </c>
       <c r="T303">
-        <v>2.1709885878773427E-2</v>
+        <v>2.60246885446902E-2</v>
       </c>
       <c r="U303">
-        <v>6.0519367884270814E-2</v>
+        <v>5.9755640267633581E-2</v>
       </c>
       <c r="V303">
-        <v>0.33845395196445693</v>
+        <v>-0.21832228859701708</v>
       </c>
       <c r="X303">
         <v>112.72</v>
@@ -26203,13 +26194,13 @@
         <v>0.12627487007093235</v>
       </c>
       <c r="T304">
-        <v>1.570005310465028E-2</v>
+        <v>1.9448166588675875E-2</v>
       </c>
       <c r="U304">
-        <v>5.8473132206748879E-2</v>
+        <v>5.8220618973470195E-2</v>
       </c>
       <c r="V304">
-        <v>0.30864356426800743</v>
+        <v>-0.33589899855432925</v>
       </c>
       <c r="X304">
         <v>111.98</v>
@@ -26298,13 +26289,13 @@
         <v>0.12626278269246408</v>
       </c>
       <c r="T305">
-        <v>1.1699504517537207E-2</v>
+        <v>1.2481851917511833E-2</v>
       </c>
       <c r="U305">
-        <v>5.4557312868741548E-2</v>
+        <v>5.5193721466872958E-2</v>
       </c>
       <c r="V305">
-        <v>0.36019377667906305</v>
+        <v>-0.3050133991441939</v>
       </c>
       <c r="X305">
         <v>112.03</v>
@@ -26393,13 +26384,13 @@
         <v>0.12619500552191396</v>
       </c>
       <c r="T306">
-        <v>1.1553885830162258E-2</v>
+        <v>1.4009033437289986E-2</v>
       </c>
       <c r="U306">
-        <v>5.7636221128709586E-2</v>
+        <v>5.6880197140696254E-2</v>
       </c>
       <c r="V306">
-        <v>8.5722087884598785E-2</v>
+        <v>-0.36258896502829874</v>
       </c>
       <c r="X306">
         <v>111.8</v>
@@ -26488,13 +26479,13 @@
         <v>0.12463858095765616</v>
       </c>
       <c r="T307">
-        <v>1.2690843475327007E-2</v>
+        <v>1.41139174577809E-2</v>
       </c>
       <c r="U307">
-        <v>6.7232284268992082E-2</v>
+        <v>6.0222539651966223E-2</v>
       </c>
       <c r="V307">
-        <v>5.4110914764282647E-2</v>
+        <v>-8.8340787964868994E-2</v>
       </c>
       <c r="X307">
         <v>112.38</v>
@@ -26583,13 +26574,13 @@
         <v>0.12422240907296114</v>
       </c>
       <c r="T308">
-        <v>1.852465521476887E-2</v>
+        <v>1.8625316362186339E-2</v>
       </c>
       <c r="U308">
-        <v>7.0530211233643669E-2</v>
+        <v>7.3286112952364313E-2</v>
       </c>
       <c r="V308">
-        <v>8.78532481607186E-2</v>
+        <v>4.8153668337858058E-2</v>
       </c>
       <c r="X308">
         <v>112.4</v>
@@ -26678,13 +26669,13 @@
         <v>0.12418976306395837</v>
       </c>
       <c r="T309">
-        <v>1.7713999325219554E-2</v>
+        <v>1.6300038778660486E-2</v>
       </c>
       <c r="U309">
-        <v>6.5157533336379636E-2</v>
+        <v>6.8251881277991977E-2</v>
       </c>
       <c r="V309">
-        <v>1.9237380164871531E-2</v>
+        <v>9.0063565873577112E-2</v>
       </c>
       <c r="X309">
         <v>112.15</v>
@@ -26773,13 +26764,13 @@
         <v>0.12408721024594847</v>
       </c>
       <c r="T310">
-        <v>1.881056342318832E-2</v>
+        <v>1.5547043479613443E-2</v>
       </c>
       <c r="U310">
-        <v>7.928202292228903E-2</v>
+        <v>6.2919836205077573E-2</v>
       </c>
       <c r="V310">
-        <v>0.174323773717866</v>
+        <v>2.1404343661979297E-2</v>
       </c>
       <c r="X310">
         <v>112.02</v>
@@ -26868,13 +26859,13 @@
         <v>0.12360686332959159</v>
       </c>
       <c r="T311">
-        <v>2.90747176565187E-2</v>
+        <v>2.7646059048058724E-2</v>
       </c>
       <c r="U311">
-        <v>7.7669452960860141E-2</v>
+        <v>8.8320204632363897E-2</v>
       </c>
       <c r="V311">
-        <v>0.20469675743504112</v>
+        <v>0.16563203149819739</v>
       </c>
       <c r="X311">
         <v>112.25</v>
@@ -26963,13 +26954,13 @@
         <v>0.12357500163103821</v>
       </c>
       <c r="T312">
-        <v>2.7922207978603453E-2</v>
+        <v>3.217154204886441E-2</v>
       </c>
       <c r="U312">
-        <v>7.8217202335806313E-2</v>
+        <v>8.0823312721967078E-2</v>
       </c>
       <c r="V312">
-        <v>0.19084243708555881</v>
+        <v>0.20165568455088323</v>
       </c>
       <c r="X312">
         <v>112.5</v>
@@ -27058,13 +27049,13 @@
         <v>0.12357306701649164</v>
       </c>
       <c r="T313">
-        <v>2.2159153280476573E-2</v>
+        <v>2.7229348356283545E-2</v>
       </c>
       <c r="U313">
-        <v>7.4955127410114564E-2</v>
+        <v>7.7551653363983064E-2</v>
       </c>
       <c r="V313">
-        <v>0.17098972056348583</v>
+        <v>0.19171505444528503</v>
       </c>
       <c r="X313">
         <v>112.61</v>
@@ -27153,13 +27144,13 @@
         <v>0.12085365695090272</v>
       </c>
       <c r="T314">
-        <v>2.202403978586176E-2</v>
+        <v>2.2388431535769193E-2</v>
       </c>
       <c r="U314">
-        <v>6.8915561599292019E-2</v>
+        <v>7.5195908250380583E-2</v>
       </c>
       <c r="V314">
-        <v>0.34851805080959863</v>
+        <v>-0.17124751314883113</v>
       </c>
       <c r="X314">
         <v>113.2</v>
@@ -27248,13 +27239,13 @@
         <v>0.12017728378211157</v>
       </c>
       <c r="T315">
-        <v>2.3899850686115442E-2</v>
+        <v>2.453021864052829E-2</v>
       </c>
       <c r="U315">
-        <v>6.778270729663749E-2</v>
+        <v>7.14885455773695E-2</v>
       </c>
       <c r="V315">
-        <v>0.28245799983395159</v>
+        <v>-0.35138615486272062</v>
       </c>
       <c r="X315">
         <v>113.18</v>
@@ -27343,13 +27334,13 @@
         <v>0.12008313629595584</v>
       </c>
       <c r="T316">
-        <v>2.6792020582333542E-2</v>
+        <v>2.5002542609620093E-2</v>
       </c>
       <c r="U316">
-        <v>5.0087829834066788E-2</v>
+        <v>6.890030093480437E-2</v>
       </c>
       <c r="V316">
-        <v>0.30941228832865875</v>
+        <v>-0.28363607221180143</v>
       </c>
       <c r="X316">
         <v>113.17</v>
@@ -27438,13 +27429,13 @@
         <v>0.12006692598108841</v>
       </c>
       <c r="T317">
-        <v>2.3591055445160158E-2</v>
+        <v>2.6516628328843161E-2</v>
       </c>
       <c r="U317">
-        <v>5.8369959857129672E-2</v>
+        <v>4.9793255267993608E-2</v>
       </c>
       <c r="V317">
-        <v>0.29897168658712392</v>
+        <v>-0.30890324470798092</v>
       </c>
       <c r="X317">
         <v>113.29</v>
@@ -27533,13 +27524,13 @@
         <v>0.1200657426146229</v>
       </c>
       <c r="T318">
-        <v>2.510981814702884E-2</v>
+        <v>2.4539711318238844E-2</v>
       </c>
       <c r="U318">
-        <v>6.7720094711010148E-2</v>
+        <v>5.9337373062051668E-2</v>
       </c>
       <c r="V318">
-        <v>0.32654795098974176</v>
+        <v>-0.30004146372684115</v>
       </c>
       <c r="X318">
         <v>113.55</v>
@@ -27628,13 +27619,13 @@
         <v>0.12004812994274575</v>
       </c>
       <c r="T319">
-        <v>2.7574444885125615E-2</v>
+        <v>2.7372195052977055E-2</v>
       </c>
       <c r="U319">
-        <v>6.1846267979404068E-2</v>
+        <v>7.0033534565427935E-2</v>
       </c>
       <c r="V319">
-        <v>0.14493420257333245</v>
+        <v>-0.32906328716175715</v>
       </c>
       <c r="X319">
         <v>112.6</v>
@@ -27723,13 +27714,13 @@
         <v>0.11933659727102097</v>
       </c>
       <c r="T320">
-        <v>3.4200852959020978E-2</v>
+        <v>3.0059466326370909E-2</v>
       </c>
       <c r="U320">
-        <v>6.6652776834397187E-2</v>
+        <v>6.435870556378287E-2</v>
       </c>
       <c r="V320">
-        <v>0.16957952226277495</v>
+        <v>-0.1474917663661035</v>
       </c>
       <c r="X320">
         <v>113.1</v>
@@ -27818,13 +27809,13 @@
         <v>0.11932516978100133</v>
       </c>
       <c r="T321">
-        <v>2.9523008706289211E-2</v>
+        <v>3.5490165676121954E-2</v>
       </c>
       <c r="U321">
-        <v>5.4267028025867248E-2</v>
+        <v>6.8041963189990895E-2</v>
       </c>
       <c r="V321">
-        <v>0.3402330266921938</v>
+        <v>-0.17127711012188129</v>
       </c>
       <c r="X321">
         <v>113.35</v>
@@ -27913,13 +27904,13 @@
         <v>0.11870492917352107</v>
       </c>
       <c r="T322">
-        <v>2.943627023512807E-2</v>
+        <v>3.5031768876847558E-2</v>
       </c>
       <c r="U322">
-        <v>1.4025622245661395E-2</v>
+        <v>5.9849002985612465E-2</v>
       </c>
       <c r="V322">
-        <v>0.20486851929015781</v>
+        <v>-0.34637270163153655</v>
       </c>
       <c r="X322">
         <v>112.98</v>
@@ -28008,13 +27999,13 @@
         <v>0.11828835880848798</v>
       </c>
       <c r="T323">
-        <v>2.542685345141571E-2</v>
+        <v>2.8538980576042761E-2</v>
       </c>
       <c r="U323">
-        <v>6.0336936435589905E-2</v>
+        <v>-1.4952719805227943E-2</v>
       </c>
       <c r="V323">
-        <v>0.32067140735829724</v>
+        <v>-0.20402994632124916</v>
       </c>
       <c r="X323">
         <v>113.49</v>
@@ -28103,13 +28094,13 @@
         <v>0.11798708290523938</v>
       </c>
       <c r="T324">
-        <v>3.6923241641217963E-2</v>
+        <v>2.9065218827084571E-2</v>
       </c>
       <c r="U324">
-        <v>5.7199415453079716E-2</v>
+        <v>6.4010884284892988E-2</v>
       </c>
       <c r="V324">
-        <v>0.182175229465531</v>
+        <v>-0.32431884870942618</v>
       </c>
       <c r="X324">
         <v>112.84</v>
@@ -28198,13 +28189,13 @@
         <v>0.11756062420778284</v>
       </c>
       <c r="T325">
-        <v>3.2273226781409647E-2</v>
+        <v>3.4934186629276276E-2</v>
       </c>
       <c r="U325">
-        <v>5.4410481076150319E-2</v>
+        <v>5.5179559654949806E-2</v>
       </c>
       <c r="V325">
-        <v>9.6965782254332389E-2</v>
+        <v>-0.18005862053849242</v>
       </c>
       <c r="X325">
         <v>113.45</v>
@@ -28293,13 +28284,13 @@
         <v>0.11741403437787808</v>
       </c>
       <c r="T326">
-        <v>1.7967337791691129E-2</v>
+        <v>3.1224039521848823E-2</v>
       </c>
       <c r="U326">
-        <v>4.9072280534989687E-2</v>
+        <v>5.3318933616086639E-2</v>
       </c>
       <c r="V326">
-        <v>6.9971968822790664E-2</v>
+        <v>-9.5795326178449436E-2</v>
       </c>
       <c r="X326">
         <v>113.4</v>
@@ -28388,13 +28379,13 @@
         <v>0.11740031202038663</v>
       </c>
       <c r="T327">
-        <v>2.3341692840261885E-2</v>
+        <v>2.1179113261737825E-2</v>
       </c>
       <c r="U327">
-        <v>5.876875259904768E-2</v>
+        <v>5.2355913255563991E-2</v>
       </c>
       <c r="V327">
-        <v>0.17564244851469013</v>
+        <v>-7.3307183717696844E-2</v>
       </c>
       <c r="X327">
         <v>113.39</v>
@@ -28483,13 +28474,13 @@
         <v>0.11716770994223548</v>
       </c>
       <c r="T328">
-        <v>2.7023577638152219E-2</v>
+        <v>2.1176954717860852E-2</v>
       </c>
       <c r="U328">
-        <v>5.8138951222841406E-2</v>
+        <v>5.6546091864784209E-2</v>
       </c>
       <c r="V328">
-        <v>0.30579451892622789</v>
+        <v>-0.17336636350713253</v>
       </c>
       <c r="X328">
         <v>112.76</v>
@@ -28578,13 +28569,13 @@
         <v>0.11677389009921647</v>
       </c>
       <c r="T329">
-        <v>2.9237355456235292E-2</v>
+        <v>2.9851674225223057E-2</v>
       </c>
       <c r="U329">
-        <v>6.2528360669267258E-2</v>
+        <v>6.1039768789550308E-2</v>
       </c>
       <c r="V329">
-        <v>5.723521046561153E-2</v>
+        <v>-0.30875916141233084</v>
       </c>
       <c r="X329">
         <v>113.01</v>
@@ -28673,13 +28664,13 @@
         <v>0.11539276043865676</v>
       </c>
       <c r="T330">
-        <v>2.9709801639232758E-2</v>
+        <v>3.3343405422758821E-2</v>
       </c>
       <c r="U330">
-        <v>6.1357936456718498E-2</v>
+        <v>6.6783928863412001E-2</v>
       </c>
       <c r="V330">
-        <v>0.24125020837533206</v>
+        <v>-6.1523805140129006E-2</v>
       </c>
       <c r="X330">
         <v>113.87</v>
@@ -28768,13 +28759,13 @@
         <v>0.11466348699232362</v>
       </c>
       <c r="T331">
-        <v>3.0882531960862991E-2</v>
+        <v>3.1287845455896246E-2</v>
       </c>
       <c r="U331">
-        <v>6.2145237867916592E-2</v>
+        <v>6.2935665000218854E-2</v>
       </c>
       <c r="V331">
-        <v>0.24611147278588152</v>
+        <v>-0.24254910339869262</v>
       </c>
       <c r="X331">
         <v>113.21</v>
@@ -28863,13 +28854,13 @@
         <v>0.11466698773076806</v>
       </c>
       <c r="T332">
-        <v>2.5129985658844944E-2</v>
+        <v>1.9326573883882148E-2</v>
       </c>
       <c r="U332">
-        <v>5.2043701119264263E-2</v>
+        <v>5.0229368256959894E-2</v>
       </c>
       <c r="V332">
-        <v>0.12400933783067725</v>
+        <v>-0.23420132507594449</v>
       </c>
       <c r="X332">
         <v>112.96</v>
@@ -28958,13 +28949,13 @@
         <v>0.11440051520907794</v>
       </c>
       <c r="T333">
-        <v>2.8521716631391136E-2</v>
+        <v>2.630796267288904E-2</v>
       </c>
       <c r="U333">
-        <v>4.8864026006811834E-2</v>
+        <v>5.3226182712640124E-2</v>
       </c>
       <c r="V333">
-        <v>0.16876485989556489</v>
+        <v>-0.12511575509914774</v>
       </c>
       <c r="X333">
         <v>113.07</v>
@@ -29053,13 +29044,13 @@
         <v>0.11435579224014145</v>
       </c>
       <c r="T334">
-        <v>3.0155636294160182E-2</v>
+        <v>2.6998093568164627E-2</v>
       </c>
       <c r="U334">
-        <v>4.3494226697626814E-2</v>
+        <v>4.7245946790575033E-2</v>
       </c>
       <c r="V334">
-        <v>0.25050599977638477</v>
+        <v>-0.16681859053380155</v>
       </c>
       <c r="X334">
         <v>113.89</v>
@@ -29148,13 +29139,13 @@
         <v>0.11419132442678957</v>
       </c>
       <c r="T335">
-        <v>3.1419370160978843E-2</v>
+        <v>3.3676684134098522E-2</v>
       </c>
       <c r="U335">
-        <v>4.6338671936108078E-2</v>
+        <v>4.7109814704815456E-2</v>
       </c>
       <c r="V335">
-        <v>6.8169124801031877E-2</v>
+        <v>-0.25413361355057784</v>
       </c>
       <c r="X335">
         <v>113.89</v>
@@ -29243,13 +29234,13 @@
         <v>0.113413467214541</v>
       </c>
       <c r="T336">
-        <v>3.6358298855043714E-2</v>
+        <v>3.8863507859421276E-2</v>
       </c>
       <c r="U336">
-        <v>5.1537226986497764E-2</v>
+        <v>5.3990503334944151E-2</v>
       </c>
       <c r="V336">
-        <v>2.0232673588727046E-2</v>
+        <v>-7.5880809003514571E-2</v>
       </c>
       <c r="X336">
         <v>113.2</v>
@@ -29338,13 +29329,13 @@
         <v>0.11320380814378012</v>
       </c>
       <c r="T337">
-        <v>3.2983191027491365E-2</v>
+        <v>3.8789428578578367E-2</v>
       </c>
       <c r="U337">
-        <v>5.2601609658320392E-2</v>
+        <v>5.4042160892975311E-2</v>
       </c>
       <c r="V337">
-        <v>4.6553318696074264E-2</v>
+        <v>1.7735005999619524E-2</v>
       </c>
       <c r="X337">
         <v>113.19</v>
@@ -29433,13 +29424,13 @@
         <v>0.11311309033608995</v>
       </c>
       <c r="T338">
-        <v>4.8934668125499847E-2</v>
+        <v>4.6750667401807E-2</v>
       </c>
       <c r="U338">
-        <v>6.6669097269600464E-2</v>
+        <v>6.6778040756654278E-2</v>
       </c>
       <c r="V338">
-        <v>0.19029891253321551</v>
+        <v>-6.0834636413376053E-2</v>
       </c>
       <c r="X338">
         <v>113.4</v>
@@ -29528,13 +29519,13 @@
         <v>0.11272434726375247</v>
       </c>
       <c r="T339">
-        <v>4.8442446781460369E-2</v>
+        <v>4.6299625622392426E-2</v>
       </c>
       <c r="U339">
-        <v>6.5455810326153774E-2</v>
+        <v>6.3970399508783693E-2</v>
       </c>
       <c r="V339">
-        <v>0.27136517169616958</v>
+        <v>-0.18766137701258234</v>
       </c>
       <c r="X339">
         <v>113.4</v>
@@ -29623,13 +29614,13 @@
         <v>0.1125571455509386</v>
       </c>
       <c r="T340">
-        <v>3.6953046567300696E-2</v>
+        <v>4.5590492667124671E-2</v>
       </c>
       <c r="U340">
-        <v>6.5877077845333254E-2</v>
+        <v>6.2531360588935492E-2</v>
       </c>
       <c r="V340">
-        <v>0.38863913009656859</v>
+        <v>-0.26855130183525144</v>
       </c>
       <c r="X340">
         <v>113.5</v>
@@ -29718,13 +29709,13 @@
         <v>0.11220785566502144</v>
       </c>
       <c r="T341">
-        <v>3.743141579000131E-2</v>
+        <v>4.0446971102192641E-2</v>
       </c>
       <c r="U341">
-        <v>7.091271628976159E-2</v>
+        <v>6.9476739413976141E-2</v>
       </c>
       <c r="V341">
-        <v>0.42875283240393358</v>
+        <v>-0.39218526530324649</v>
       </c>
       <c r="X341">
         <v>113.44</v>
@@ -29813,13 +29804,13 @@
         <v>0.11217203153208227</v>
       </c>
       <c r="T342">
-        <v>4.3050149175560826E-2</v>
+        <v>4.238870995278976E-2</v>
       </c>
       <c r="U342">
-        <v>7.1683532101363134E-2</v>
+        <v>7.6011553909505203E-2</v>
       </c>
       <c r="V342">
-        <v>0.36154757523993997</v>
+        <v>-0.43365081530410965</v>
       </c>
       <c r="X342">
         <v>113.6</v>
@@ -29908,13 +29899,13 @@
         <v>0.11206044640511142</v>
       </c>
       <c r="T343">
-        <v>4.3261926207294188E-2</v>
+        <v>4.3487976151856955E-2</v>
       </c>
       <c r="U343">
-        <v>6.6987761116732436E-2</v>
+        <v>7.2096794669662678E-2</v>
       </c>
       <c r="V343">
-        <v>0.43131574871146938</v>
+        <v>-0.36155371062047692</v>
       </c>
       <c r="X343">
         <v>112.9</v>
@@ -30003,13 +29994,13 @@
         <v>0.11193670743502521</v>
       </c>
       <c r="T344">
-        <v>4.4465134569315889E-2</v>
+        <v>4.6918392881023507E-2</v>
       </c>
       <c r="U344">
-        <v>7.0344306832414993E-2</v>
+        <v>7.0748983335433557E-2</v>
       </c>
       <c r="V344">
-        <v>0.38238941214456812</v>
+        <v>-0.4349508264149593</v>
       </c>
       <c r="X344">
         <v>113.4</v>
@@ -30098,13 +30089,13 @@
         <v>0.11187773383927557</v>
       </c>
       <c r="T345">
-        <v>4.7625929338146467E-2</v>
+        <v>4.8697280099796458E-2</v>
       </c>
       <c r="U345">
-        <v>7.3991252091620829E-2</v>
+        <v>7.4644372923149405E-2</v>
       </c>
       <c r="V345">
-        <v>0.5038550942878306</v>
+        <v>-0.38589185758370892</v>
       </c>
       <c r="X345">
         <v>113.4</v>
@@ -30193,13 +30184,13 @@
         <v>0.11153107920002514</v>
       </c>
       <c r="T346">
-        <v>5.3292546588734613E-2</v>
+        <v>5.3003365120263268E-2</v>
       </c>
       <c r="U346">
-        <v>8.1202102663779918E-2</v>
+        <v>7.9540558635460279E-2</v>
       </c>
       <c r="V346">
-        <v>0.2084017519859982</v>
+        <v>-0.50953296806912629</v>
       </c>
       <c r="X346">
         <v>113.25</v>
@@ -30288,13 +30279,13 @@
         <v>0.10938602615264099</v>
       </c>
       <c r="T347">
-        <v>5.3637904465353436E-2</v>
+        <v>5.4570609056536767E-2</v>
       </c>
       <c r="U347">
-        <v>7.9532613871546864E-2</v>
+        <v>8.2507920423546821E-2</v>
       </c>
       <c r="V347">
-        <v>0.2850100404432121</v>
+        <v>-0.20967370313882405</v>
       </c>
       <c r="X347">
         <v>112.77</v>
@@ -30383,13 +30374,13 @@
         <v>0.10924191851182177</v>
       </c>
       <c r="T348">
-        <v>5.2958325721097488E-2</v>
+        <v>5.517739254989884E-2</v>
       </c>
       <c r="U348">
-        <v>8.1594815288954514E-2</v>
+        <v>8.1123721760545386E-2</v>
       </c>
       <c r="V348">
-        <v>0.27894799069101417</v>
+        <v>-0.28669102858935869</v>
       </c>
       <c r="X348">
         <v>113.03</v>
@@ -30478,13 +30469,13 @@
         <v>0.10924127484528108</v>
       </c>
       <c r="T349">
-        <v>4.9377272957962237E-2</v>
+        <v>5.179828061026015E-2</v>
       </c>
       <c r="U349">
-        <v>8.054352770636708E-2</v>
+        <v>8.0412486912617709E-2</v>
       </c>
       <c r="V349">
-        <v>0.27910633954337793</v>
+        <v>-0.27781705327394324</v>
       </c>
       <c r="X349">
         <v>113.1</v>
@@ -30573,13 +30564,13 @@
         <v>0.10924106738481744</v>
       </c>
       <c r="T350">
-        <v>4.8274359361799579E-2</v>
+        <v>4.9570945993349103E-2</v>
       </c>
       <c r="U350">
-        <v>8.4750264498145711E-2</v>
+        <v>8.0756511509094686E-2</v>
       </c>
       <c r="V350">
-        <v>0.27665294314807021</v>
+        <v>-0.27941635451278479</v>
       </c>
       <c r="X350">
         <v>113.19</v>
@@ -30668,13 +30659,13 @@
         <v>0.10924113795233571</v>
       </c>
       <c r="T351">
-        <v>4.635591236493708E-2</v>
+        <v>5.1740685238033102E-2</v>
       </c>
       <c r="U351">
-        <v>8.2148235038603801E-2</v>
+        <v>8.8293717441012554E-2</v>
       </c>
       <c r="V351">
-        <v>0.28367416258889833</v>
+        <v>-0.28016832119350799</v>
       </c>
       <c r="X351">
         <v>112.54</v>
@@ -30763,13 +30754,13 @@
         <v>0.10924552945376396</v>
       </c>
       <c r="T352">
-        <v>3.4674403348700089E-2</v>
+        <v>3.3804947362736648E-2</v>
       </c>
       <c r="U352">
-        <v>6.3605173116254576E-2</v>
+        <v>6.926424292919009E-2</v>
       </c>
       <c r="V352">
-        <v>0.26102481789160858</v>
+        <v>-0.27036942964226984</v>
       </c>
       <c r="X352">
         <v>112.58</v>
@@ -30858,13 +30849,13 @@
         <v>0.10924441289379412</v>
       </c>
       <c r="T353">
-        <v>3.001135270624955E-2</v>
+        <v>3.3549011939282281E-2</v>
       </c>
       <c r="U353">
-        <v>5.9329577421185498E-2</v>
+        <v>6.2447638717744169E-2</v>
       </c>
       <c r="V353">
-        <v>0.2653786603619146</v>
+        <v>-0.25978345154176186</v>
       </c>
       <c r="X353">
         <v>112.51</v>
@@ -30953,13 +30944,13 @@
         <v>0.10924301526984433</v>
       </c>
       <c r="T354">
-        <v>3.2923011113306089E-2</v>
+        <v>3.0994900690528571E-2</v>
       </c>
       <c r="U354">
-        <v>6.8205388004138889E-2</v>
+        <v>6.0321054869727497E-2</v>
       </c>
       <c r="V354">
-        <v>0.17716311816116104</v>
+        <v>-0.26631070045377569</v>
       </c>
       <c r="X354">
         <v>112.36</v>
@@ -31048,13 +31039,13 @@
         <v>0.10905184190402414</v>
       </c>
       <c r="T355">
-        <v>3.3428406486446516E-2</v>
+        <v>3.2407711755855217E-2</v>
       </c>
       <c r="U355">
-        <v>6.5100940258755458E-2</v>
+        <v>6.7668323229463923E-2</v>
       </c>
       <c r="V355">
-        <v>0.2560087832895741</v>
+        <v>-0.17658796954154177</v>
       </c>
       <c r="X355">
         <v>112.5</v>
@@ -31143,13 +31134,13 @@
         <v>0.1088869238294284</v>
       </c>
       <c r="T356">
-        <v>3.5519820922524925E-2</v>
+        <v>3.8674434887475684E-2</v>
       </c>
       <c r="U356">
-        <v>5.6945762326354732E-2</v>
+        <v>7.0473707799223462E-2</v>
       </c>
       <c r="V356">
-        <v>0.25683512239957906</v>
+        <v>-0.26148534726124772</v>
       </c>
       <c r="X356">
         <v>112.29</v>
@@ -31238,13 +31229,13 @@
         <v>0.10888692680627403</v>
       </c>
       <c r="T357">
-        <v>3.6202755597625202E-2</v>
+        <v>3.4079325793645587E-2</v>
       </c>
       <c r="U357">
-        <v>5.7585839964691132E-2</v>
+        <v>5.5452096308927779E-2</v>
       </c>
       <c r="V357">
-        <v>0.25163737895907978</v>
+        <v>-0.25498228369309484</v>
       </c>
       <c r="X357">
         <v>112.36</v>
@@ -31333,13 +31324,13 @@
         <v>0.10888697401083076</v>
       </c>
       <c r="T358">
-        <v>3.297158950381629E-2</v>
+        <v>3.5745579951584894E-2</v>
       </c>
       <c r="U358">
-        <v>6.2871282463561329E-2</v>
+        <v>5.712244644311415E-2</v>
       </c>
       <c r="V358">
-        <v>0.25367075613274004</v>
+        <v>-0.25116001136744615</v>
       </c>
       <c r="X358">
         <v>112.28</v>
@@ -31428,13 +31419,13 @@
         <v>0.10888690532553644</v>
       </c>
       <c r="T359">
-        <v>2.685536099852337E-2</v>
+        <v>3.087898124526367E-2</v>
       </c>
       <c r="U359">
-        <v>5.9994914140315547E-2</v>
+        <v>6.0696652499836468E-2</v>
       </c>
       <c r="V359">
-        <v>0.25092412770637562</v>
+        <v>-0.25108393619188707</v>
       </c>
       <c r="X359">
         <v>112.91</v>
@@ -31522,20 +31513,14 @@
       <c r="R360">
         <v>0.10888695932742611</v>
       </c>
-      <c r="S360">
-        <v>0.17889689579145737</v>
-      </c>
       <c r="T360">
-        <v>2.8420539722773253E-2</v>
+        <v>2.997226059736624E-2</v>
       </c>
       <c r="U360">
-        <v>5.9432777746148968E-2</v>
+        <v>6.3098983453979685E-2</v>
       </c>
       <c r="V360">
-        <v>0.24825537916202123</v>
-      </c>
-      <c r="W360">
-        <v>0.46142059789138212</v>
+        <v>-0.25385420336201392</v>
       </c>
       <c r="X360">
         <v>112.5</v>
@@ -31627,19 +31612,19 @@
         <v>0.10888652462370721</v>
       </c>
       <c r="S361">
-        <v>0.17880820422636665</v>
+        <v>0.17864757049709673</v>
       </c>
       <c r="T361">
-        <v>3.9834774012814655E-2</v>
+        <v>2.8491151675003046E-2</v>
       </c>
       <c r="U361">
-        <v>5.90245857994387E-2</v>
+        <v>5.9437950532514883E-2</v>
       </c>
       <c r="V361">
-        <v>0.24563485813968722</v>
+        <v>-0.24786161406362694</v>
       </c>
       <c r="W361">
-        <v>0.57779209251447305</v>
+        <v>-0.46058816054095342</v>
       </c>
       <c r="X361">
         <v>112.3</v>
@@ -31734,19 +31719,19 @@
         <v>0.10888658800143597</v>
       </c>
       <c r="S362">
-        <v>0.17880479951604802</v>
+        <v>0.17855903233989817</v>
       </c>
       <c r="T362">
-        <v>4.2282475151578236E-2</v>
+        <v>4.3416150734532089E-2</v>
       </c>
       <c r="U362">
-        <v>6.8357026557475109E-2</v>
+        <v>6.2594045869202031E-2</v>
       </c>
       <c r="V362">
-        <v>0.24469881859168208</v>
+        <v>-0.24903963518061456</v>
       </c>
       <c r="W362">
-        <v>0.55465760373631934</v>
+        <v>-0.5811425948711868</v>
       </c>
       <c r="X362">
         <v>112.52</v>
@@ -31841,19 +31826,19 @@
         <v>0.10888647456276021</v>
       </c>
       <c r="S363">
-        <v>0.17735309454548889</v>
+        <v>0.17855560974703821</v>
       </c>
       <c r="T363">
-        <v>4.3707117532088002E-2</v>
+        <v>4.2171598801277188E-2</v>
       </c>
       <c r="U363">
-        <v>7.0386690394919071E-2</v>
+        <v>6.8177775518007966E-2</v>
       </c>
       <c r="V363">
-        <v>0.26082054641978214</v>
+        <v>-0.24405715057596034</v>
       </c>
       <c r="W363">
-        <v>1.0165396255776171</v>
+        <v>-0.55320313801376919</v>
       </c>
       <c r="X363">
         <v>112.8</v>
@@ -31948,19 +31933,19 @@
         <v>0.10887865624986232</v>
       </c>
       <c r="S364">
-        <v>0.17601003373287821</v>
+        <v>0.17710604764081353</v>
       </c>
       <c r="T364">
-        <v>4.6936158579391485E-2</v>
+        <v>5.0394769067740874E-2</v>
       </c>
       <c r="U364">
-        <v>8.027665312467791E-2</v>
+        <v>7.710227115416135E-2</v>
       </c>
       <c r="V364">
-        <v>0.2538042925302797</v>
+        <v>-0.26777374047470826</v>
       </c>
       <c r="W364">
-        <v>0.56785621043387025</v>
+        <v>-1.024558948029286</v>
       </c>
       <c r="X364">
         <v>112.31</v>
@@ -32055,19 +32040,19 @@
         <v>0.10887495167388754</v>
       </c>
       <c r="S365">
-        <v>0.17578294352292881</v>
+        <v>0.17576476248108275</v>
       </c>
       <c r="T365">
-        <v>4.3116163529788309E-2</v>
+        <v>5.0405785332741093E-2</v>
       </c>
       <c r="U365">
-        <v>8.1408283834649708E-2</v>
+        <v>8.3632683139500674E-2</v>
       </c>
       <c r="V365">
-        <v>0.25440076274632073</v>
+        <v>-0.25657522282063194</v>
       </c>
       <c r="W365">
-        <v>0.38472894237411293</v>
+        <v>-0.56978153985842717</v>
       </c>
       <c r="X365">
         <v>112.44</v>
@@ -32162,19 +32147,19 @@
         <v>0.10887551116599235</v>
       </c>
       <c r="S366">
-        <v>0.17540990947590857</v>
+        <v>0.17553816522156643</v>
       </c>
       <c r="T366">
-        <v>4.6904534051395164E-2</v>
+        <v>4.9291594819744766E-2</v>
       </c>
       <c r="U366">
-        <v>8.5175230862610807E-2</v>
+        <v>8.7653872026094426E-2</v>
       </c>
       <c r="V366">
-        <v>0.25258310084690372</v>
+        <v>-0.26098381653274494</v>
       </c>
       <c r="W366">
-        <v>0.63193635934035708</v>
+        <v>-0.39207718866924868</v>
       </c>
       <c r="X366">
         <v>112.64</v>
@@ -32269,19 +32254,19 @@
         <v>0.10887478134796312</v>
       </c>
       <c r="S367">
-        <v>0.17462653732882122</v>
+        <v>0.1751655740235987</v>
       </c>
       <c r="T367">
-        <v>3.9102529345003134E-2</v>
+        <v>5.2597659179975942E-2</v>
       </c>
       <c r="U367">
-        <v>8.511673695393851E-2</v>
+        <v>9.0874488519987473E-2</v>
       </c>
       <c r="V367">
-        <v>0.26923180283180415</v>
+        <v>-0.25833124101479754</v>
       </c>
       <c r="W367">
-        <v>0.98475968050917295</v>
+        <v>-0.63814567098936514</v>
       </c>
       <c r="X367">
         <v>112.13</v>
@@ -32376,19 +32361,19 @@
         <v>0.10887086985837749</v>
       </c>
       <c r="S368">
-        <v>0.17143019702372669</v>
+        <v>0.17438316264475695</v>
       </c>
       <c r="T368">
-        <v>4.5090410616155374E-2</v>
+        <v>4.2511025216984688E-2</v>
       </c>
       <c r="U368">
-        <v>9.0695918317706958E-2</v>
+        <v>8.8531077197484542E-2</v>
       </c>
       <c r="V368">
-        <v>0.26455507137004286</v>
+        <v>-0.2726953127741405</v>
       </c>
       <c r="W368">
-        <v>0.29329973143967791</v>
+        <v>-0.98852711860852871</v>
       </c>
       <c r="X368">
         <v>111</v>
@@ -32483,19 +32468,19 @@
         <v>0.10887115896571385</v>
       </c>
       <c r="S369">
-        <v>0.16976016351848963</v>
+        <v>0.17119160842529652</v>
       </c>
       <c r="T369">
-        <v>4.2175833812119201E-2</v>
+        <v>3.9395635916150695E-2</v>
       </c>
       <c r="U369">
-        <v>8.7007118411608353E-2</v>
+        <v>8.4873301639376564E-2</v>
       </c>
       <c r="V369">
-        <v>0.25599832577658521</v>
+        <v>-0.25822888642638153</v>
       </c>
       <c r="W369">
-        <v>0.78494732870286743</v>
+        <v>-0.28635089322817109</v>
       </c>
       <c r="X369">
         <v>111.12</v>
@@ -32590,19 +32575,19 @@
         <v>0.10887116393312207</v>
       </c>
       <c r="S370">
-        <v>0.16951916150179114</v>
+        <v>0.16952356485827061</v>
       </c>
       <c r="T370">
-        <v>4.0971136960132881E-2</v>
+        <v>4.4367422602631379E-2</v>
       </c>
       <c r="U370">
-        <v>8.0601921707534885E-2</v>
+        <v>8.9096922907561105E-2</v>
       </c>
       <c r="V370">
-        <v>0.25915668837309669</v>
+        <v>-0.2576961013837753</v>
       </c>
       <c r="W370">
-        <v>0.59403587027520022</v>
+        <v>-0.78553684205746599</v>
       </c>
       <c r="X370">
         <v>111.2</v>
@@ -32697,19 +32682,19 @@
         <v>0.10887095011979397</v>
       </c>
       <c r="S371">
-        <v>0.16945661788136732</v>
+        <v>0.16928290783740557</v>
       </c>
       <c r="T371">
-        <v>3.6500207921963401E-2</v>
+        <v>4.131884113396378E-2</v>
       </c>
       <c r="U371">
-        <v>7.7933383117290145E-2</v>
+        <v>8.08919777811834E-2</v>
       </c>
       <c r="V371">
-        <v>0.26095331919895326</v>
+        <v>-0.25918743747840312</v>
       </c>
       <c r="W371">
-        <v>0.49703011629733673</v>
+        <v>-0.59360729575905768</v>
       </c>
       <c r="X371">
         <v>109.24</v>
@@ -32804,19 +32789,19 @@
         <v>0.10887099973933771</v>
       </c>
       <c r="S372">
-        <v>0.16937004922154192</v>
+        <v>0.16922051937470103</v>
       </c>
       <c r="T372">
-        <v>3.4273960351505206E-2</v>
+        <v>3.4711082075222777E-2</v>
       </c>
       <c r="U372">
-        <v>7.6721311798055858E-2</v>
+        <v>7.610331178944385E-2</v>
       </c>
       <c r="V372">
-        <v>0.25825969930505233</v>
+        <v>-0.25892924036718945</v>
       </c>
       <c r="W372">
-        <v>0.6061472189963224</v>
+        <v>-0.49462641225859194</v>
       </c>
       <c r="X372">
         <v>109.42</v>
@@ -32911,19 +32896,19 @@
         <v>0.10887147198982014</v>
       </c>
       <c r="S373">
-        <v>0.16873983743943705</v>
+        <v>0.16913415092145351</v>
       </c>
       <c r="T373">
-        <v>3.6519767403031533E-2</v>
+        <v>4.0091627254190687E-2</v>
       </c>
       <c r="U373">
-        <v>8.2341566020638357E-2</v>
+        <v>8.2568718441189404E-2</v>
       </c>
       <c r="V373">
-        <v>0.25575453002362192</v>
+        <v>-0.26433850669244086</v>
       </c>
       <c r="W373">
-        <v>0.30954690310247557</v>
+        <v>-0.61302615145395478</v>
       </c>
       <c r="X373">
         <v>109.71</v>
@@ -33018,19 +33003,19 @@
         <v>0.10887016523291408</v>
       </c>
       <c r="S374">
-        <v>0.1686935401814014</v>
+        <v>0.16850467491273685</v>
       </c>
       <c r="T374">
-        <v>3.445772696256677E-2</v>
+        <v>3.8629709181559058E-2</v>
       </c>
       <c r="U374">
-        <v>8.2025181744471709E-2</v>
+        <v>8.4458577746282515E-2</v>
       </c>
       <c r="V374">
-        <v>0.25740780154617227</v>
+        <v>-0.25794189295373915</v>
       </c>
       <c r="W374">
-        <v>0.22933567530840637</v>
+        <v>-0.31195317801231415</v>
       </c>
       <c r="X374">
         <v>109.34</v>
@@ -33125,19 +33110,19 @@
         <v>0.10887126689780467</v>
       </c>
       <c r="S375">
-        <v>0.16791255371302136</v>
+        <v>0.16845890169488661</v>
       </c>
       <c r="T375">
-        <v>3.7220101166857145E-2</v>
+        <v>4.2506632123040511E-2</v>
       </c>
       <c r="U375">
-        <v>8.9032042197201289E-2</v>
+        <v>9.0091137008097011E-2</v>
       </c>
       <c r="V375">
-        <v>0.26343031296958141</v>
+        <v>-0.26581617522299927</v>
       </c>
       <c r="W375">
-        <v>0.57382461272028618</v>
+        <v>-0.23851694533170154</v>
       </c>
       <c r="X375">
         <v>110</v>
@@ -33232,19 +33217,19 @@
         <v>0.10887164304902791</v>
       </c>
       <c r="S376">
-        <v>0.16752484744707552</v>
+        <v>0.16767866478615523</v>
       </c>
       <c r="T376">
-        <v>4.1438839506346969E-2</v>
+        <v>4.270038949053534E-2</v>
       </c>
       <c r="U376">
-        <v>9.4910760493227553E-2</v>
+        <v>9.4592414973537764E-2</v>
       </c>
       <c r="V376">
-        <v>0.26980252808229688</v>
+        <v>-0.26944392952563678</v>
       </c>
       <c r="W376">
-        <v>0.3426289397444604</v>
+        <v>-0.58096889587753164</v>
       </c>
       <c r="X376">
         <v>109.61</v>
@@ -33339,19 +33324,19 @@
         <v>0.10887267370046715</v>
       </c>
       <c r="S377">
-        <v>0.16662897880607513</v>
+        <v>0.16729180986621706</v>
       </c>
       <c r="T377">
-        <v>4.8078238457460731E-2</v>
+        <v>4.9595538686975082E-2</v>
       </c>
       <c r="U377">
-        <v>0.1022173850398489</v>
+        <v>0.10315372406669576</v>
       </c>
       <c r="V377">
-        <v>0.28043767765268957</v>
+        <v>-0.27858351597433995</v>
       </c>
       <c r="W377">
-        <v>0.71172388641118634</v>
+        <v>-0.35235601174192777</v>
       </c>
       <c r="X377">
         <v>110.21</v>
@@ -33446,19 +33431,19 @@
         <v>0.10887249077647018</v>
       </c>
       <c r="S378">
-        <v>0.16620546527518704</v>
+        <v>0.16639678298398802</v>
       </c>
       <c r="T378">
-        <v>5.3185446670767078E-2</v>
+        <v>5.2040151308285765E-2</v>
       </c>
       <c r="U378">
-        <v>0.10397973666003146</v>
+        <v>0.10619970003981072</v>
       </c>
       <c r="V378">
-        <v>0.2812248676518303</v>
+        <v>-0.28461245067359364</v>
       </c>
       <c r="W378">
-        <v>0.9596593388668806</v>
+        <v>-0.71654245358256929</v>
       </c>
       <c r="X378">
         <v>110.32</v>
@@ -33505,7 +33490,7 @@
         <v>110.88260010972837</v>
       </c>
       <c r="C379">
-        <v>149414303.64785898</v>
+        <v>149414303.64785901</v>
       </c>
       <c r="D379">
         <v>547</v>
@@ -33553,19 +33538,19 @@
         <v>0.10887245118319396</v>
       </c>
       <c r="S379">
-        <v>0.16383933890471372</v>
+        <v>0.16597382019209958</v>
       </c>
       <c r="T379">
-        <v>5.5690181942791295E-2</v>
+        <v>5.5885057324223109E-2</v>
       </c>
       <c r="U379">
-        <v>0.10438346416064004</v>
+        <v>0.10677911854315436</v>
       </c>
       <c r="V379">
-        <v>0.28105356859540187</v>
+        <v>-0.28446049482016011</v>
       </c>
       <c r="W379">
-        <v>1.5378507161572852</v>
+        <v>-0.96459482904152072</v>
       </c>
       <c r="X379">
         <v>110.39</v>
@@ -33660,19 +33645,19 @@
         <v>0.10887269044339092</v>
       </c>
       <c r="S380">
-        <v>0.16333515934545925</v>
+        <v>0.16361100676728263</v>
       </c>
       <c r="T380">
-        <v>5.7475149457286712E-2</v>
+        <v>6.0911613457848013E-2</v>
       </c>
       <c r="U380">
-        <v>0.10816691283528357</v>
+        <v>0.10961503750143153</v>
       </c>
       <c r="V380">
-        <v>0.28650086160606492</v>
+        <v>-0.28649899951691538</v>
       </c>
       <c r="W380">
-        <v>1.2730321207119255</v>
+        <v>-1.5444433114711442</v>
       </c>
       <c r="X380">
         <v>110.21</v>
@@ -33767,19 +33752,19 @@
         <v>0.10887423283591198</v>
       </c>
       <c r="S381">
-        <v>0.16180186346515854</v>
+        <v>0.16310828855301121</v>
       </c>
       <c r="T381">
-        <v>6.3806905287266957E-2</v>
+        <v>5.1282821302545134E-2</v>
       </c>
       <c r="U381">
-        <v>9.6631147641912385E-2</v>
+        <v>0.10202149722674525</v>
       </c>
       <c r="V381">
-        <v>0.2744533850668196</v>
+        <v>-0.28023070733911304</v>
       </c>
       <c r="W381">
-        <v>0.79918902747961873</v>
+        <v>-1.2663683248190116</v>
       </c>
       <c r="X381">
         <v>111.05</v>
@@ -33874,19 +33859,19 @@
         <v>0.10887413000386073</v>
       </c>
       <c r="S382">
-        <v>0.16180189630928665</v>
+        <v>0.16157641743668963</v>
       </c>
       <c r="T382">
-        <v>6.9598406231108356E-2</v>
+        <v>6.8462393607660044E-2</v>
       </c>
       <c r="U382">
-        <v>0.10206207688402413</v>
+        <v>0.1012362251734622</v>
       </c>
       <c r="V382">
-        <v>0.27708819090093151</v>
+        <v>-0.2791349187395431</v>
       </c>
       <c r="W382">
-        <v>0.80353982728544882</v>
+        <v>-0.8041961867349956</v>
       </c>
       <c r="X382">
         <v>110.64</v>
@@ -33981,19 +33966,19 @@
         <v>0.10887456566897875</v>
       </c>
       <c r="S383">
-        <v>0.16176920419437477</v>
+        <v>0.16157656546632407</v>
       </c>
       <c r="T383">
-        <v>6.6216530631635351E-2</v>
+        <v>6.7186919820982904E-2</v>
       </c>
       <c r="U383">
-        <v>9.6219291162780163E-2</v>
+        <v>9.9694969108687914E-2</v>
       </c>
       <c r="V383">
-        <v>0.2686153053359952</v>
+        <v>-0.27476917758419983</v>
       </c>
       <c r="W383">
-        <v>0.73013291473398301</v>
+        <v>-0.80130398197000297</v>
       </c>
       <c r="X383">
         <v>110.31</v>
@@ -34088,19 +34073,19 @@
         <v>0.10887471534382859</v>
       </c>
       <c r="S384">
-        <v>0.16164506699333742</v>
+        <v>0.16154397761666051</v>
       </c>
       <c r="T384">
-        <v>6.3394660549775939E-2</v>
+        <v>6.2870199281761519E-2</v>
       </c>
       <c r="U384">
-        <v>9.4837944022285736E-2</v>
+        <v>9.2898299037336152E-2</v>
       </c>
       <c r="V384">
-        <v>0.26352267466290824</v>
+        <v>-0.26517268981973707</v>
       </c>
       <c r="W384">
-        <v>0.85319385399147407</v>
+        <v>-0.72624870189419433</v>
       </c>
       <c r="X384">
         <v>110.3</v>
@@ -34195,19 +34180,19 @@
         <v>0.10888490052658138</v>
       </c>
       <c r="S385">
-        <v>0.16162454220478117</v>
+        <v>0.16142342802116996</v>
       </c>
       <c r="T385">
-        <v>3.97819975342939E-2</v>
+        <v>4.5000227191149822E-2</v>
       </c>
       <c r="U385">
-        <v>7.7602417112676569E-2</v>
+        <v>7.6528703131351072E-2</v>
       </c>
       <c r="V385">
-        <v>0.24290535903727095</v>
+        <v>-0.24433758186694909</v>
       </c>
       <c r="W385">
-        <v>0.88550105268481172</v>
+        <v>-0.83054251236882592</v>
       </c>
       <c r="X385">
         <v>110.71</v>
@@ -34302,19 +34287,19 @@
         <v>0.10888694254458398</v>
       </c>
       <c r="S386">
-        <v>0.16020987650211513</v>
+        <v>0.1614001024569387</v>
       </c>
       <c r="T386">
-        <v>3.3845142585198218E-2</v>
+        <v>3.2413297333167002E-2</v>
       </c>
       <c r="U386">
-        <v>6.7183424765249189E-2</v>
+        <v>7.0302565642876846E-2</v>
       </c>
       <c r="V386">
-        <v>0.23164322254511927</v>
+        <v>-0.23552391129398886</v>
       </c>
       <c r="W386">
-        <v>1.3062801901675192</v>
+        <v>-0.87760601389879067</v>
       </c>
       <c r="X386">
         <v>110.71</v>
@@ -34409,19 +34394,19 @@
         <v>0.10888683573370395</v>
       </c>
       <c r="S387">
-        <v>0.15742296462881389</v>
+        <v>0.15998661596844521</v>
       </c>
       <c r="T387">
-        <v>3.5802485459057731E-2</v>
+        <v>3.5347092367266075E-2</v>
       </c>
       <c r="U387">
-        <v>7.0734026280738771E-2</v>
+        <v>6.8629838043066105E-2</v>
       </c>
       <c r="V387">
-        <v>0.23536755742641358</v>
+        <v>-0.23291469394957076</v>
       </c>
       <c r="W387">
-        <v>0.69268353362095247</v>
+        <v>-1.306386739914922</v>
       </c>
       <c r="X387">
         <v>110.73</v>
@@ -34516,19 +34501,19 @@
         <v>0.10888648013886966</v>
       </c>
       <c r="S388">
-        <v>0.15742295613487764</v>
+        <v>0.15720361749149958</v>
       </c>
       <c r="T388">
-        <v>3.7165276177741902E-2</v>
+        <v>3.5066993932109103E-2</v>
       </c>
       <c r="U388">
-        <v>6.7268705945622287E-2</v>
+        <v>7.0011469697639495E-2</v>
       </c>
       <c r="V388">
-        <v>0.38391924093205132</v>
+        <v>-0.23466218127622396</v>
       </c>
       <c r="W388">
-        <v>0.69240833664638846</v>
+        <v>-0.69198763768851812</v>
       </c>
       <c r="X388">
         <v>111.39</v>
@@ -34623,19 +34608,19 @@
         <v>0.10828629997367131</v>
       </c>
       <c r="S389">
-        <v>0.15703411239196041</v>
+        <v>0.15720357717376332</v>
       </c>
       <c r="T389">
-        <v>3.4154539787378813E-2</v>
+        <v>3.7273082852995465E-2</v>
       </c>
       <c r="U389">
-        <v>6.3370987070965334E-2</v>
+        <v>6.7388684146074684E-2</v>
       </c>
       <c r="V389">
-        <v>0.25273781275788609</v>
+        <v>-0.38417972595126137</v>
       </c>
       <c r="W389">
-        <v>0.46557458543317054</v>
+        <v>-0.69281281085842306</v>
       </c>
       <c r="X389">
         <v>110.78</v>
@@ -34680,26 +34665,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="dd854d95-092e-48c7-992a-80d5cc5badc3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006CC87EF38A8DD0408B89B7B34D0336DC" ma:contentTypeVersion="20" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a30c2ca5bc864785a186dec6b0346788">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe" xmlns:ns3="dd854d95-092e-48c7-992a-80d5cc5badc3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2932ec1554b414302dd4a6579c5666bc" ns2:_="" ns3:_="">
     <xsd:import namespace="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
@@ -34954,26 +34919,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="dd854d95-092e-48c7-992a-80d5cc5badc3"/>
-    <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="dd854d95-092e-48c7-992a-80d5cc5badc3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BABE8802-F313-4DEC-9147-95F411D9A097}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34990,4 +34956,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dd854d95-092e-48c7-992a-80d5cc5badc3"/>
+    <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eldorado275.sharepoint.com/sites/Compartidos/Documentos compartidos/INVERSIONES/Claude - Fernando/Dashboards ETFs/Dashboards/ETFPESOV/General/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8BF8D58-7A32-47FC-AE16-FBBAC81ABD6C}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{832548A3-27EB-4C0C-AC3C-4D25B168E83D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -2407,7 +2407,7 @@
         <v>0.30294945219025993</v>
       </c>
       <c r="T31">
-        <v>-0.16586847056285769</v>
+        <v>0.16586847056285769</v>
       </c>
       <c r="X31">
         <v>102.5</v>
@@ -2478,7 +2478,7 @@
         <v>0.30431344337139582</v>
       </c>
       <c r="T32">
-        <v>0.13277207632080845</v>
+        <v>-0.13277207632080845</v>
       </c>
       <c r="X32">
         <v>101.94</v>
@@ -2549,7 +2549,7 @@
         <v>0.305100491964586</v>
       </c>
       <c r="T33">
-        <v>0.23717380542305211</v>
+        <v>-0.23717380542305211</v>
       </c>
       <c r="X33">
         <v>102.51</v>
@@ -2620,7 +2620,7 @@
         <v>0.2961945061194588</v>
       </c>
       <c r="T34">
-        <v>0.4771538732093461</v>
+        <v>-0.4771538732093461</v>
       </c>
       <c r="X34">
         <v>102.5</v>
@@ -2691,7 +2691,7 @@
         <v>0.28824596820532106</v>
       </c>
       <c r="T35">
-        <v>0.23823230697217479</v>
+        <v>-0.23823230697217479</v>
       </c>
       <c r="X35">
         <v>101.56</v>
@@ -2762,7 +2762,7 @@
         <v>0.2894240740853784</v>
       </c>
       <c r="T36">
-        <v>-0.1525297900064837</v>
+        <v>0.1525297900064837</v>
       </c>
       <c r="X36">
         <v>102.5</v>
@@ -2833,7 +2833,7 @@
         <v>0.28869207388967699</v>
       </c>
       <c r="T37">
-        <v>0.25504715969324465</v>
+        <v>-0.25504715969324465</v>
       </c>
       <c r="X37">
         <v>101.18</v>
@@ -2904,7 +2904,7 @@
         <v>0.28636629100858579</v>
       </c>
       <c r="T38">
-        <v>0.32584039102421247</v>
+        <v>-0.32584039102421247</v>
       </c>
       <c r="X38">
         <v>101.6</v>
@@ -2975,7 +2975,7 @@
         <v>0.26476418610496177</v>
       </c>
       <c r="T39">
-        <v>-0.55458279029683144</v>
+        <v>0.55458279029683144</v>
       </c>
       <c r="X39">
         <v>101.53</v>
@@ -3046,7 +3046,7 @@
         <v>0.25189060153654891</v>
       </c>
       <c r="T40">
-        <v>-0.11427332877713692</v>
+        <v>0.11427332877713692</v>
       </c>
       <c r="X40">
         <v>102.12</v>
@@ -3117,7 +3117,7 @@
         <v>0.25050790859340955</v>
       </c>
       <c r="T41">
-        <v>-0.4109019663137925</v>
+        <v>0.4109019663137925</v>
       </c>
       <c r="X41">
         <v>101</v>
@@ -3188,7 +3188,7 @@
         <v>0.28713443969229363</v>
       </c>
       <c r="T42">
-        <v>0.26476650728568529</v>
+        <v>-0.26476650728568529</v>
       </c>
       <c r="X42">
         <v>102.5</v>
@@ -3259,7 +3259,7 @@
         <v>0.2864162976244643</v>
       </c>
       <c r="T43">
-        <v>0.35668669435469091</v>
+        <v>-0.35668669435469091</v>
       </c>
       <c r="X43">
         <v>102.5</v>
@@ -3330,7 +3330,7 @@
         <v>0.28311279057165339</v>
       </c>
       <c r="T44">
-        <v>-6.1872812771901486E-2</v>
+        <v>6.1872812771901486E-2</v>
       </c>
       <c r="X44">
         <v>101.82</v>
@@ -3401,7 +3401,7 @@
         <v>0.28960896676111031</v>
       </c>
       <c r="T45">
-        <v>-0.4915256361817999</v>
+        <v>0.4915256361817999</v>
       </c>
       <c r="X45">
         <v>101.01</v>
@@ -3472,7 +3472,7 @@
         <v>0.30363810212026271</v>
       </c>
       <c r="T46">
-        <v>0.40367253175106477</v>
+        <v>-0.40367253175106477</v>
       </c>
       <c r="X46">
         <v>100.79</v>
@@ -3543,7 +3543,7 @@
         <v>0.30273888424643219</v>
       </c>
       <c r="T47">
-        <v>1.9013064346040665E-2</v>
+        <v>-1.9013064346040665E-2</v>
       </c>
       <c r="X47">
         <v>102</v>
@@ -3614,7 +3614,7 @@
         <v>0.29834924169731902</v>
       </c>
       <c r="T48">
-        <v>0.17240067653474522</v>
+        <v>-0.17240067653474522</v>
       </c>
       <c r="X48">
         <v>100.45</v>
@@ -3685,7 +3685,7 @@
         <v>0.29650548129182319</v>
       </c>
       <c r="T49">
-        <v>0.56405159102548286</v>
+        <v>-0.56405159102548286</v>
       </c>
       <c r="X49">
         <v>101.57</v>
@@ -3756,7 +3756,7 @@
         <v>0.28110282218802563</v>
       </c>
       <c r="T50">
-        <v>0.90496544303184656</v>
+        <v>-0.90496544303184656</v>
       </c>
       <c r="X50">
         <v>102.2</v>
@@ -3827,7 +3827,7 @@
         <v>0.3048210151140594</v>
       </c>
       <c r="T51">
-        <v>-1.0538747993882325E-2</v>
+        <v>1.0538747993882325E-2</v>
       </c>
       <c r="X51">
         <v>101.01</v>
@@ -3898,7 +3898,7 @@
         <v>0.33600856497188569</v>
       </c>
       <c r="T52">
-        <v>0.44572035979875135</v>
+        <v>-0.44572035979875135</v>
       </c>
       <c r="X52">
         <v>102.2</v>
@@ -3969,7 +3969,7 @@
         <v>0.33601684622617856</v>
       </c>
       <c r="T53">
-        <v>0.4405180546191767</v>
+        <v>-0.4405180546191767</v>
       </c>
       <c r="X53">
         <v>102.54</v>
@@ -4040,7 +4040,7 @@
         <v>0.33656083566355521</v>
       </c>
       <c r="T54">
-        <v>0.26937410533030004</v>
+        <v>-0.26937410533030004</v>
       </c>
       <c r="X54">
         <v>101.3</v>
@@ -4111,7 +4111,7 @@
         <v>0.33644475684751057</v>
       </c>
       <c r="T55">
-        <v>0.5250273739976663</v>
+        <v>-0.5250273739976663</v>
       </c>
       <c r="X55">
         <v>103.45</v>
@@ -4182,7 +4182,7 @@
         <v>0.33699756791654228</v>
       </c>
       <c r="T56">
-        <v>0.46724512128679674</v>
+        <v>-0.46724512128679674</v>
       </c>
       <c r="X56">
         <v>101.32</v>
@@ -4253,7 +4253,7 @@
         <v>0.32792654243765784</v>
       </c>
       <c r="T57">
-        <v>0.82931903581133781</v>
+        <v>-0.82931903581133781</v>
       </c>
       <c r="X57">
         <v>103.25</v>
@@ -4324,7 +4324,7 @@
         <v>0.31178800395628492</v>
       </c>
       <c r="T58">
-        <v>0.25641910996507811</v>
+        <v>-0.25641910996507811</v>
       </c>
       <c r="X58">
         <v>101.52</v>
@@ -4395,7 +4395,7 @@
         <v>0.31239213488297052</v>
       </c>
       <c r="T59">
-        <v>0.15879269596359435</v>
+        <v>-0.15879269596359435</v>
       </c>
       <c r="X59">
         <v>103.25</v>
@@ -4466,7 +4466,7 @@
         <v>0.31136397195063997</v>
       </c>
       <c r="T60">
-        <v>-0.2191773322663737</v>
+        <v>0.2191773322663737</v>
       </c>
       <c r="X60">
         <v>101.5</v>
@@ -4543,10 +4543,10 @@
         <v>0.30434202531812099</v>
       </c>
       <c r="T61">
-        <v>0.11130541826362972</v>
+        <v>-0.11130541826362972</v>
       </c>
       <c r="U61">
-        <v>-5.4242095293743908E-2</v>
+        <v>5.4242095293743908E-2</v>
       </c>
       <c r="X61">
         <v>103</v>
@@ -4626,10 +4626,10 @@
         <v>0.3048710315682831</v>
       </c>
       <c r="T62">
-        <v>0.100360578944092</v>
+        <v>-0.100360578944092</v>
       </c>
       <c r="U62">
-        <v>0.23744651087276303</v>
+        <v>-0.23744651087276303</v>
       </c>
       <c r="X62">
         <v>104</v>
@@ -4709,10 +4709,10 @@
         <v>0.3055912478610609</v>
       </c>
       <c r="T63">
-        <v>-0.18937741376567896</v>
+        <v>0.18937741376567896</v>
       </c>
       <c r="U63">
-        <v>4.8263845890250678E-2</v>
+        <v>-4.8263845890250678E-2</v>
       </c>
       <c r="X63">
         <v>104</v>
@@ -4792,10 +4792,10 @@
         <v>0.30044276710532941</v>
       </c>
       <c r="T64">
-        <v>-5.0600309464465809E-2</v>
+        <v>5.0600309464465809E-2</v>
       </c>
       <c r="U64">
-        <v>0.43652774262814553</v>
+        <v>-0.43652774262814553</v>
       </c>
       <c r="X64">
         <v>104.25</v>
@@ -4875,10 +4875,10 @@
         <v>0.29566615100092081</v>
       </c>
       <c r="T65">
-        <v>-0.20749215875262017</v>
+        <v>0.20749215875262017</v>
       </c>
       <c r="U65">
-        <v>3.6366438592705386E-2</v>
+        <v>-3.6366438592705386E-2</v>
       </c>
       <c r="X65">
         <v>104.25</v>
@@ -4958,10 +4958,10 @@
         <v>0.29549329311978223</v>
       </c>
       <c r="T66">
-        <v>0.17216062618543582</v>
+        <v>-0.17216062618543582</v>
       </c>
       <c r="U66">
-        <v>1.633400259504203E-2</v>
+        <v>-1.633400259504203E-2</v>
       </c>
       <c r="X66">
         <v>103.16</v>
@@ -5041,10 +5041,10 @@
         <v>0.29428971285306094</v>
       </c>
       <c r="T67">
-        <v>-9.371941386722149E-2</v>
+        <v>9.371941386722149E-2</v>
       </c>
       <c r="U67">
-        <v>0.1678107990768174</v>
+        <v>-0.1678107990768174</v>
       </c>
       <c r="X67">
         <v>104.5</v>
@@ -5124,10 +5124,10 @@
         <v>0.2923119128282623</v>
       </c>
       <c r="T68">
-        <v>0.34921060349255573</v>
+        <v>-0.34921060349255573</v>
       </c>
       <c r="U68">
-        <v>0.68812067061949644</v>
+        <v>-0.68812067061949644</v>
       </c>
       <c r="X68">
         <v>102.75</v>
@@ -5207,10 +5207,10 @@
         <v>0.28077074598859109</v>
       </c>
       <c r="T69">
-        <v>0.57608831852047349</v>
+        <v>-0.57608831852047349</v>
       </c>
       <c r="U69">
-        <v>1.2462117354195001E-2</v>
+        <v>-1.2462117354195001E-2</v>
       </c>
       <c r="X69">
         <v>104.5</v>
@@ -5290,10 +5290,10 @@
         <v>0.2758692418831542</v>
       </c>
       <c r="T70">
-        <v>0.37979608404357101</v>
+        <v>-0.37979608404357101</v>
       </c>
       <c r="U70">
-        <v>0.26737718841292057</v>
+        <v>-0.26737718841292057</v>
       </c>
       <c r="X70">
         <v>102.77</v>
@@ -5373,10 +5373,10 @@
         <v>0.27513509219369092</v>
       </c>
       <c r="T71">
-        <v>0.57964449709142496</v>
+        <v>-0.57964449709142496</v>
       </c>
       <c r="U71">
-        <v>0.16361967430429392</v>
+        <v>-0.16361967430429392</v>
       </c>
       <c r="X71">
         <v>104.5</v>
@@ -5456,10 +5456,10 @@
         <v>0.27549964208727562</v>
       </c>
       <c r="T72">
-        <v>-5.2159896193981758E-2</v>
+        <v>5.2159896193981758E-2</v>
       </c>
       <c r="U72">
-        <v>0.21845648353326919</v>
+        <v>-0.21845648353326919</v>
       </c>
       <c r="X72">
         <v>103.12</v>
@@ -5539,10 +5539,10 @@
         <v>0.27520300471504167</v>
       </c>
       <c r="T73">
-        <v>-7.572169786351779E-2</v>
+        <v>7.572169786351779E-2</v>
       </c>
       <c r="U73">
-        <v>0.28913420023759517</v>
+        <v>-0.28913420023759517</v>
       </c>
       <c r="X73">
         <v>103.25</v>
@@ -5622,10 +5622,10 @@
         <v>0.27402045842780243</v>
       </c>
       <c r="T74">
-        <v>0.26348073682957995</v>
+        <v>-0.26348073682957995</v>
       </c>
       <c r="U74">
-        <v>0.20345450907375273</v>
+        <v>-0.20345450907375273</v>
       </c>
       <c r="X74">
         <v>104.53</v>
@@ -5705,10 +5705,10 @@
         <v>0.27391958659078125</v>
       </c>
       <c r="T75">
-        <v>0.6666986310522427</v>
+        <v>-0.6666986310522427</v>
       </c>
       <c r="U75">
-        <v>0.17453300347749501</v>
+        <v>-0.17453300347749501</v>
       </c>
       <c r="X75">
         <v>104.75</v>
@@ -5788,10 +5788,10 @@
         <v>0.27091916960983436</v>
       </c>
       <c r="T76">
-        <v>6.6392380503632609E-2</v>
+        <v>-6.6392380503632609E-2</v>
       </c>
       <c r="U76">
-        <v>0.47892168775085509</v>
+        <v>-0.47892168775085509</v>
       </c>
       <c r="X76">
         <v>103.49</v>
@@ -5871,10 +5871,10 @@
         <v>0.26958271296067776</v>
       </c>
       <c r="T77">
-        <v>0.28104290803347975</v>
+        <v>-0.28104290803347975</v>
       </c>
       <c r="U77">
-        <v>0.30434451800576134</v>
+        <v>-0.30434451800576134</v>
       </c>
       <c r="X77">
         <v>104.75</v>
@@ -5954,10 +5954,10 @@
         <v>0.26864838176409989</v>
       </c>
       <c r="T78">
-        <v>0.17649388956055834</v>
+        <v>-0.17649388956055834</v>
       </c>
       <c r="U78">
-        <v>0.35494757473324423</v>
+        <v>-0.35494757473324423</v>
       </c>
       <c r="X78">
         <v>104.75</v>
@@ -6037,10 +6037,10 @@
         <v>0.26807217245172865</v>
       </c>
       <c r="T79">
-        <v>-0.17264079153496148</v>
+        <v>0.17264079153496148</v>
       </c>
       <c r="U79">
-        <v>0.40006263469034575</v>
+        <v>-0.40006263469034575</v>
       </c>
       <c r="X79">
         <v>103.3</v>
@@ -6120,10 +6120,10 @@
         <v>0.25942231680543143</v>
       </c>
       <c r="T80">
-        <v>0.1726325058544198</v>
+        <v>-0.1726325058544198</v>
       </c>
       <c r="U80">
-        <v>1.0979708851545311</v>
+        <v>-1.0979708851545311</v>
       </c>
       <c r="X80">
         <v>103.44</v>
@@ -6203,10 +6203,10 @@
         <v>0.25931016820421837</v>
       </c>
       <c r="T81">
-        <v>0.62741805730919253</v>
+        <v>-0.62741805730919253</v>
       </c>
       <c r="U81">
-        <v>0.6268124387514451</v>
+        <v>-0.6268124387514451</v>
       </c>
       <c r="X81">
         <v>103.1</v>
@@ -6286,10 +6286,10 @@
         <v>0.25453031504029922</v>
       </c>
       <c r="T82">
-        <v>-7.9425563956525558E-2</v>
+        <v>7.9425563956525558E-2</v>
       </c>
       <c r="U82">
-        <v>0.37241665443319416</v>
+        <v>-0.37241665443319416</v>
       </c>
       <c r="X82">
         <v>103.1</v>
@@ -6369,10 +6369,10 @@
         <v>0.25460218481223845</v>
       </c>
       <c r="T83">
-        <v>-2.0487719904060953E-2</v>
+        <v>2.0487719904060953E-2</v>
       </c>
       <c r="U83">
-        <v>0.42704144118119736</v>
+        <v>-0.42704144118119736</v>
       </c>
       <c r="X83">
         <v>103.07</v>
@@ -6452,10 +6452,10 @@
         <v>0.2597211988327276</v>
       </c>
       <c r="T84">
-        <v>-0.31708950793074564</v>
+        <v>0.31708950793074564</v>
       </c>
       <c r="U84">
-        <v>-4.8221518696722754E-2</v>
+        <v>4.8221518696722754E-2</v>
       </c>
       <c r="X84">
         <v>104.75</v>
@@ -6535,10 +6535,10 @@
         <v>0.25981546970534919</v>
       </c>
       <c r="T85">
-        <v>-0.32103377549155265</v>
+        <v>0.32103377549155265</v>
       </c>
       <c r="U85">
-        <v>0.21045808944302191</v>
+        <v>-0.21045808944302191</v>
       </c>
       <c r="X85">
         <v>103.25</v>
@@ -6618,10 +6618,10 @@
         <v>0.25994572451340098</v>
       </c>
       <c r="T86">
-        <v>-0.29325599026068794</v>
+        <v>0.29325599026068794</v>
       </c>
       <c r="U86">
-        <v>0.18038162998019747</v>
+        <v>-0.18038162998019747</v>
       </c>
       <c r="X86">
         <v>104.74</v>
@@ -6701,10 +6701,10 @@
         <v>0.254482297358672</v>
       </c>
       <c r="T87">
-        <v>-0.23710927772604418</v>
+        <v>0.23710927772604418</v>
       </c>
       <c r="U87">
-        <v>0.61120888189845068</v>
+        <v>-0.61120888189845068</v>
       </c>
       <c r="X87">
         <v>104.22</v>
@@ -6784,10 +6784,10 @@
         <v>0.24400101328765966</v>
       </c>
       <c r="T88">
-        <v>-0.15486061074869717</v>
+        <v>0.15486061074869717</v>
       </c>
       <c r="U88">
-        <v>0.1070559420852879</v>
+        <v>-0.1070559420852879</v>
       </c>
       <c r="X88">
         <v>105.79</v>
@@ -6867,10 +6867,10 @@
         <v>0.24416673299195407</v>
       </c>
       <c r="T89">
-        <v>1.8808636546729929E-2</v>
+        <v>-1.8808636546729929E-2</v>
       </c>
       <c r="U89">
-        <v>0.18184327526700184</v>
+        <v>-0.18184327526700184</v>
       </c>
       <c r="X89">
         <v>105.43</v>
@@ -6950,10 +6950,10 @@
         <v>0.24266356764227068</v>
       </c>
       <c r="T90">
-        <v>0.21312240273978489</v>
+        <v>-0.21312240273978489</v>
       </c>
       <c r="U90">
-        <v>-8.7144885698720032E-3</v>
+        <v>8.7144885698720032E-3</v>
       </c>
       <c r="X90">
         <v>105.65</v>
@@ -7033,10 +7033,10 @@
         <v>0.24277497438618431</v>
       </c>
       <c r="T91">
-        <v>-0.12978836687695949</v>
+        <v>0.12978836687695949</v>
       </c>
       <c r="U91">
-        <v>-1.7519673932953062E-2</v>
+        <v>1.7519673932953062E-2</v>
       </c>
       <c r="X91">
         <v>106.2</v>
@@ -7116,10 +7116,10 @@
         <v>0.24696107729170552</v>
       </c>
       <c r="T92">
-        <v>9.5196805924180339E-2</v>
+        <v>-9.5196805924180339E-2</v>
       </c>
       <c r="U92">
-        <v>0.1994358251707018</v>
+        <v>-0.1994358251707018</v>
       </c>
       <c r="X92">
         <v>106.14</v>
@@ -7199,10 +7199,10 @@
         <v>0.24676334915942968</v>
       </c>
       <c r="T93">
-        <v>0.3593938631895055</v>
+        <v>-0.3593938631895055</v>
       </c>
       <c r="U93">
-        <v>0.17199032617507548</v>
+        <v>-0.17199032617507548</v>
       </c>
       <c r="X93">
         <v>106.4</v>
@@ -7282,10 +7282,10 @@
         <v>0.24588432580840533</v>
       </c>
       <c r="T94">
-        <v>0.51564013364808758</v>
+        <v>-0.51564013364808758</v>
       </c>
       <c r="U94">
-        <v>0.47532837274280038</v>
+        <v>-0.47532837274280038</v>
       </c>
       <c r="X94">
         <v>105.51</v>
@@ -7365,10 +7365,10 @@
         <v>0.24502290499909471</v>
       </c>
       <c r="T95">
-        <v>0.5604552923748285</v>
+        <v>-0.5604552923748285</v>
       </c>
       <c r="U95">
-        <v>0.36366482543028766</v>
+        <v>-0.36366482543028766</v>
       </c>
       <c r="X95">
         <v>106.2</v>
@@ -7448,10 +7448,10 @@
         <v>0.24409085322714461</v>
       </c>
       <c r="T96">
-        <v>0.57467243637374654</v>
+        <v>-0.57467243637374654</v>
       </c>
       <c r="U96">
-        <v>0.76497993599617953</v>
+        <v>-0.76497993599617953</v>
       </c>
       <c r="X96">
         <v>106.2</v>
@@ -7531,10 +7531,10 @@
         <v>0.24299058947557031</v>
       </c>
       <c r="T97">
-        <v>0.65358020448542664</v>
+        <v>-0.65358020448542664</v>
       </c>
       <c r="U97">
-        <v>0.57717286181795391</v>
+        <v>-0.57717286181795391</v>
       </c>
       <c r="X97">
         <v>105.7</v>
@@ -7614,10 +7614,10 @@
         <v>0.24939709482174185</v>
       </c>
       <c r="T98">
-        <v>-3.3719781034635687E-2</v>
+        <v>3.3719781034635687E-2</v>
       </c>
       <c r="U98">
-        <v>0.32011494468136004</v>
+        <v>-0.32011494468136004</v>
       </c>
       <c r="X98">
         <v>104.15</v>
@@ -7697,10 +7697,10 @@
         <v>0.24727965122663029</v>
       </c>
       <c r="T99">
-        <v>-3.3090260285795203E-2</v>
+        <v>3.3090260285795203E-2</v>
       </c>
       <c r="U99">
-        <v>0.55006086213813532</v>
+        <v>-0.55006086213813532</v>
       </c>
       <c r="X99">
         <v>106.5</v>
@@ -7780,10 +7780,10 @@
         <v>0.24770644886637477</v>
       </c>
       <c r="T100">
-        <v>0.30239270077903058</v>
+        <v>-0.30239270077903058</v>
       </c>
       <c r="U100">
-        <v>0.69517769454652267</v>
+        <v>-0.69517769454652267</v>
       </c>
       <c r="X100">
         <v>105.65</v>
@@ -7863,10 +7863,10 @@
         <v>0.24713807229731125</v>
       </c>
       <c r="T101">
-        <v>0.20296212724753016</v>
+        <v>-0.20296212724753016</v>
       </c>
       <c r="U101">
-        <v>0.79531416800475707</v>
+        <v>-0.79531416800475707</v>
       </c>
       <c r="X101">
         <v>106</v>
@@ -7946,10 +7946,10 @@
         <v>0.2269077514804535</v>
       </c>
       <c r="T102">
-        <v>5.8110151570667234E-2</v>
+        <v>-5.8110151570667234E-2</v>
       </c>
       <c r="U102">
-        <v>6.6956234438420026E-3</v>
+        <v>-6.6956234438420026E-3</v>
       </c>
       <c r="X102">
         <v>106</v>
@@ -8029,10 +8029,10 @@
         <v>0.2270670152903306</v>
       </c>
       <c r="T103">
-        <v>2.4759762355830439E-2</v>
+        <v>-2.4759762355830439E-2</v>
       </c>
       <c r="U103">
-        <v>-5.1333977562628696E-2</v>
+        <v>5.1333977562628696E-2</v>
       </c>
       <c r="X103">
         <v>105.21</v>
@@ -8112,10 +8112,10 @@
         <v>0.23427842684394432</v>
       </c>
       <c r="T104">
-        <v>-0.64672724533747505</v>
+        <v>0.64672724533747505</v>
       </c>
       <c r="U104">
-        <v>-0.39418540160935933</v>
+        <v>0.39418540160935933</v>
       </c>
       <c r="X104">
         <v>104.7</v>
@@ -8195,10 +8195,10 @@
         <v>0.23238257438899379</v>
       </c>
       <c r="T105">
-        <v>-0.43132956116540555</v>
+        <v>0.43132956116540555</v>
       </c>
       <c r="U105">
-        <v>0.23864827686550516</v>
+        <v>-0.23864827686550516</v>
       </c>
       <c r="X105">
         <v>106</v>
@@ -8278,10 +8278,10 @@
         <v>0.2200227685886656</v>
       </c>
       <c r="T106">
-        <v>-0.48802320103100705</v>
+        <v>0.48802320103100705</v>
       </c>
       <c r="U106">
-        <v>-0.42957003612986711</v>
+        <v>0.42957003612986711</v>
       </c>
       <c r="X106">
         <v>105.84</v>
@@ -8361,10 +8361,10 @@
         <v>0.21916697381554928</v>
       </c>
       <c r="T107">
-        <v>-0.49631677293611176</v>
+        <v>0.49631677293611176</v>
       </c>
       <c r="U107">
-        <v>-0.21784168580061269</v>
+        <v>0.21784168580061269</v>
       </c>
       <c r="X107">
         <v>105.5</v>
@@ -8444,10 +8444,10 @@
         <v>0.22326205299828963</v>
       </c>
       <c r="T108">
-        <v>-0.59549361087249952</v>
+        <v>0.59549361087249952</v>
       </c>
       <c r="U108">
-        <v>-0.42544284597416659</v>
+        <v>0.42544284597416659</v>
       </c>
       <c r="X108">
         <v>106.9</v>
@@ -8527,10 +8527,10 @@
         <v>0.22348566183104573</v>
       </c>
       <c r="T109">
-        <v>-0.22672699630754689</v>
+        <v>0.22672699630754689</v>
       </c>
       <c r="U109">
-        <v>-0.40923019372558489</v>
+        <v>0.40923019372558489</v>
       </c>
       <c r="X109">
         <v>107.4</v>
@@ -8610,10 +8610,10 @@
         <v>0.22995520347818257</v>
       </c>
       <c r="T110">
-        <v>8.3755622093684146E-2</v>
+        <v>-8.3755622093684146E-2</v>
       </c>
       <c r="U110">
-        <v>0.26337714382669297</v>
+        <v>-0.26337714382669297</v>
       </c>
       <c r="X110">
         <v>107.7</v>
@@ -8693,10 +8693,10 @@
         <v>0.21540457911946564</v>
       </c>
       <c r="T111">
-        <v>4.7004986292820128E-2</v>
+        <v>-4.7004986292820128E-2</v>
       </c>
       <c r="U111">
-        <v>0.6948279098613952</v>
+        <v>-0.6948279098613952</v>
       </c>
       <c r="X111">
         <v>107.57</v>
@@ -8776,10 +8776,10 @@
         <v>0.1859227484499687</v>
       </c>
       <c r="T112">
-        <v>-0.39887047597444436</v>
+        <v>0.39887047597444436</v>
       </c>
       <c r="U112">
-        <v>-0.48752433974186271</v>
+        <v>0.48752433974186271</v>
       </c>
       <c r="X112">
         <v>107</v>
@@ -8859,10 +8859,10 @@
         <v>0.19159021570548326</v>
       </c>
       <c r="T113">
-        <v>-9.377635323202238E-2</v>
+        <v>9.377635323202238E-2</v>
       </c>
       <c r="U113">
-        <v>-0.11647618452903519</v>
+        <v>0.11647618452903519</v>
       </c>
       <c r="X113">
         <v>108.2</v>
@@ -8942,10 +8942,10 @@
         <v>0.2012171886494655</v>
       </c>
       <c r="T114">
-        <v>0.81202610866766278</v>
+        <v>-0.81202610866766278</v>
       </c>
       <c r="U114">
-        <v>0.50316184625716076</v>
+        <v>-0.50316184625716076</v>
       </c>
       <c r="X114">
         <v>108.4</v>
@@ -9025,10 +9025,10 @@
         <v>0.20538678769212571</v>
       </c>
       <c r="T115">
-        <v>1.0324625573207458</v>
+        <v>-1.0324625573207458</v>
       </c>
       <c r="U115">
-        <v>0.726997119700723</v>
+        <v>-0.726997119700723</v>
       </c>
       <c r="X115">
         <v>108</v>
@@ -9108,10 +9108,10 @@
         <v>0.2307657573804282</v>
       </c>
       <c r="T116">
-        <v>0.28602310631313799</v>
+        <v>-0.28602310631313799</v>
       </c>
       <c r="U116">
-        <v>-6.1476236171698062E-3</v>
+        <v>6.1476236171698062E-3</v>
       </c>
       <c r="X116">
         <v>107.5</v>
@@ -9191,10 +9191,10 @@
         <v>0.23077179250732655</v>
       </c>
       <c r="T117">
-        <v>0.22650774335788437</v>
+        <v>-0.22650774335788437</v>
       </c>
       <c r="U117">
-        <v>-8.3729439149360374E-3</v>
+        <v>8.3729439149360374E-3</v>
       </c>
       <c r="X117">
         <v>107.17</v>
@@ -9274,10 +9274,10 @@
         <v>0.23080633160768274</v>
       </c>
       <c r="T118">
-        <v>0.17965099888463953</v>
+        <v>-0.17965099888463953</v>
       </c>
       <c r="U118">
-        <v>2.7146709000347435E-2</v>
+        <v>-2.7146709000347435E-2</v>
       </c>
       <c r="X118">
         <v>107.8</v>
@@ -9357,10 +9357,10 @@
         <v>0.23048210443713202</v>
       </c>
       <c r="T119">
-        <v>0.1415297221213585</v>
+        <v>-0.1415297221213585</v>
       </c>
       <c r="U119">
-        <v>0.16426081005671556</v>
+        <v>-0.16426081005671556</v>
       </c>
       <c r="X119">
         <v>107.01</v>
@@ -9440,10 +9440,10 @@
         <v>0.22945630946908371</v>
       </c>
       <c r="T120">
-        <v>0.11817131974407591</v>
+        <v>-0.11817131974407591</v>
       </c>
       <c r="U120">
-        <v>0.3372835600634394</v>
+        <v>-0.3372835600634394</v>
       </c>
       <c r="X120">
         <v>107.7</v>
@@ -9523,10 +9523,10 @@
         <v>0.22907592714945377</v>
       </c>
       <c r="T121">
-        <v>0.41348911058090021</v>
+        <v>-0.41348911058090021</v>
       </c>
       <c r="U121">
-        <v>0.29256446096310729</v>
+        <v>-0.29256446096310729</v>
       </c>
       <c r="X121">
         <v>107.7</v>
@@ -9606,10 +9606,10 @@
         <v>0.22809461959824093</v>
       </c>
       <c r="T122">
-        <v>7.4746882628629052E-2</v>
+        <v>-7.4746882628629052E-2</v>
       </c>
       <c r="U122">
-        <v>0.17271167037851143</v>
+        <v>-0.17271167037851143</v>
       </c>
       <c r="X122">
         <v>107.01</v>
@@ -9689,10 +9689,10 @@
         <v>0.2279975399464414</v>
       </c>
       <c r="T123">
-        <v>-0.17827217482873081</v>
+        <v>0.17827217482873081</v>
       </c>
       <c r="U123">
-        <v>0.18092238360123414</v>
+        <v>-0.18092238360123414</v>
       </c>
       <c r="X123">
         <v>107.95</v>
@@ -9772,10 +9772,10 @@
         <v>0.22841601667406114</v>
       </c>
       <c r="T124">
-        <v>-0.40371994531223088</v>
+        <v>0.40371994531223088</v>
       </c>
       <c r="U124">
-        <v>0.11158020921380185</v>
+        <v>-0.11158020921380185</v>
       </c>
       <c r="X124">
         <v>107.05</v>
@@ -9855,10 +9855,10 @@
         <v>0.22841869991788089</v>
       </c>
       <c r="T125">
-        <v>-0.44930908288656202</v>
+        <v>0.44930908288656202</v>
       </c>
       <c r="U125">
-        <v>0.11317914294735054</v>
+        <v>-0.11317914294735054</v>
       </c>
       <c r="X125">
         <v>107.65</v>
@@ -9938,10 +9938,10 @@
         <v>0.22767052140411681</v>
       </c>
       <c r="T126">
-        <v>-0.67435222876106593</v>
+        <v>0.67435222876106593</v>
       </c>
       <c r="U126">
-        <v>-9.8822432512424285E-2</v>
+        <v>9.8822432512424285E-2</v>
       </c>
       <c r="X126">
         <v>107.79</v>
@@ -10021,10 +10021,10 @@
         <v>0.23007500322865471</v>
       </c>
       <c r="T127">
-        <v>-0.41363097531010862</v>
+        <v>0.41363097531010862</v>
       </c>
       <c r="U127">
-        <v>0.24857345942839171</v>
+        <v>-0.24857345942839171</v>
       </c>
       <c r="X127">
         <v>108</v>
@@ -10104,10 +10104,10 @@
         <v>0.22947181475881628</v>
       </c>
       <c r="T128">
-        <v>0.22597372916444147</v>
+        <v>-0.22597372916444147</v>
       </c>
       <c r="U128">
-        <v>0.19524105954462634</v>
+        <v>-0.19524105954462634</v>
       </c>
       <c r="X128">
         <v>107.32</v>
@@ -10187,10 +10187,10 @@
         <v>0.2294915209250169</v>
       </c>
       <c r="T129">
-        <v>0.2864674121396904</v>
+        <v>-0.2864674121396904</v>
       </c>
       <c r="U129">
-        <v>0.2567177827104361</v>
+        <v>-0.2567177827104361</v>
       </c>
       <c r="X129">
         <v>107.77</v>
@@ -10270,10 +10270,10 @@
         <v>0.22801918370904664</v>
       </c>
       <c r="T130">
-        <v>9.0824269267431035E-2</v>
+        <v>-9.0824269267431035E-2</v>
       </c>
       <c r="U130">
-        <v>0.39953048989407325</v>
+        <v>-0.39953048989407325</v>
       </c>
       <c r="X130">
         <v>107.8</v>
@@ -10353,10 +10353,10 @@
         <v>0.22857298889539718</v>
       </c>
       <c r="T131">
-        <v>0.26446998213229822</v>
+        <v>-0.26446998213229822</v>
       </c>
       <c r="U131">
-        <v>0.4739233687379496</v>
+        <v>-0.4739233687379496</v>
       </c>
       <c r="X131">
         <v>107.14</v>
@@ -10436,10 +10436,10 @@
         <v>0.227932641472535</v>
       </c>
       <c r="T132">
-        <v>0.30301510122978659</v>
+        <v>-0.30301510122978659</v>
       </c>
       <c r="U132">
-        <v>0.36579822857243371</v>
+        <v>-0.36579822857243371</v>
       </c>
       <c r="X132">
         <v>107.6</v>
@@ -10519,10 +10519,10 @@
         <v>0.22788420678328958</v>
       </c>
       <c r="T133">
-        <v>0.36008544667300857</v>
+        <v>-0.36008544667300857</v>
       </c>
       <c r="U133">
-        <v>0.38994838798873666</v>
+        <v>-0.38994838798873666</v>
       </c>
       <c r="X133">
         <v>107.28</v>
@@ -10602,10 +10602,10 @@
         <v>0.23094184841984219</v>
       </c>
       <c r="T134">
-        <v>0.47970014651050885</v>
+        <v>-0.47970014651050885</v>
       </c>
       <c r="U134">
-        <v>-0.16498637432473817</v>
+        <v>0.16498637432473817</v>
       </c>
       <c r="X134">
         <v>107.3</v>
@@ -10685,10 +10685,10 @@
         <v>0.23183548219453329</v>
       </c>
       <c r="T135">
-        <v>4.6551211628620415E-2</v>
+        <v>-4.6551211628620415E-2</v>
       </c>
       <c r="U135">
-        <v>-0.38868785055476973</v>
+        <v>0.38868785055476973</v>
       </c>
       <c r="X135">
         <v>106.81</v>
@@ -10768,10 +10768,10 @@
         <v>0.23201946302388454</v>
       </c>
       <c r="T136">
-        <v>0.17850427697416738</v>
+        <v>-0.17850427697416738</v>
       </c>
       <c r="U136">
-        <v>-0.31000332551156529</v>
+        <v>0.31000332551156529</v>
       </c>
       <c r="X136">
         <v>107.13</v>
@@ -10851,10 +10851,10 @@
         <v>0.2319246038235451</v>
       </c>
       <c r="T137">
-        <v>0.11090301635401367</v>
+        <v>-0.11090301635401367</v>
       </c>
       <c r="U137">
-        <v>-0.38652766153353113</v>
+        <v>0.38652766153353113</v>
       </c>
       <c r="X137">
         <v>106.9</v>
@@ -10934,10 +10934,10 @@
         <v>0.22917474737888954</v>
       </c>
       <c r="T138">
-        <v>0.4941409216229431</v>
+        <v>-0.4941409216229431</v>
       </c>
       <c r="U138">
-        <v>-9.0354586409380211E-2</v>
+        <v>9.0354586409380211E-2</v>
       </c>
       <c r="X138">
         <v>107.8</v>
@@ -11017,10 +11017,10 @@
         <v>0.22802410206859675</v>
       </c>
       <c r="T139">
-        <v>0.28652744856234591</v>
+        <v>-0.28652744856234591</v>
       </c>
       <c r="U139">
-        <v>6.7636724900088652E-2</v>
+        <v>-6.7636724900088652E-2</v>
       </c>
       <c r="X139">
         <v>107.99</v>
@@ -11100,10 +11100,10 @@
         <v>0.22830531855111266</v>
       </c>
       <c r="T140">
-        <v>7.5325130670655938E-3</v>
+        <v>-7.5325130670655938E-3</v>
       </c>
       <c r="U140">
-        <v>9.1824806232043699E-2</v>
+        <v>-9.1824806232043699E-2</v>
       </c>
       <c r="X140">
         <v>108</v>
@@ -11183,10 +11183,10 @@
         <v>0.22661620696769977</v>
       </c>
       <c r="T141">
-        <v>0.23330900941431754</v>
+        <v>-0.23330900941431754</v>
       </c>
       <c r="U141">
-        <v>0.28766014673582418</v>
+        <v>-0.28766014673582418</v>
       </c>
       <c r="X141">
         <v>107.46</v>
@@ -11266,10 +11266,10 @@
         <v>0.22643523727510481</v>
       </c>
       <c r="T142">
-        <v>0.32722096304126369</v>
+        <v>-0.32722096304126369</v>
       </c>
       <c r="U142">
-        <v>-6.255365043086325E-2</v>
+        <v>6.255365043086325E-2</v>
       </c>
       <c r="X142">
         <v>108</v>
@@ -11349,10 +11349,10 @@
         <v>0.2270084227649799</v>
       </c>
       <c r="T143">
-        <v>0.11138139898569932</v>
+        <v>-0.11138139898569932</v>
       </c>
       <c r="U143">
-        <v>2.0869160093739403E-2</v>
+        <v>-2.0869160093739403E-2</v>
       </c>
       <c r="X143">
         <v>107.2</v>
@@ -11432,10 +11432,10 @@
         <v>0.22150323347788839</v>
       </c>
       <c r="T144">
-        <v>-0.49325561235988857</v>
+        <v>0.49325561235988857</v>
       </c>
       <c r="U144">
-        <v>0.31302940705530968</v>
+        <v>-0.31302940705530968</v>
       </c>
       <c r="X144">
         <v>107.41</v>
@@ -11515,10 +11515,10 @@
         <v>0.22153791904756709</v>
       </c>
       <c r="T145">
-        <v>-0.71160457022736434</v>
+        <v>0.71160457022736434</v>
       </c>
       <c r="U145">
-        <v>0.31651646248282983</v>
+        <v>-0.31651646248282983</v>
       </c>
       <c r="X145">
         <v>108</v>
@@ -11598,10 +11598,10 @@
         <v>0.2214576864088541</v>
       </c>
       <c r="T146">
-        <v>0.18746223368319992</v>
+        <v>-0.18746223368319992</v>
       </c>
       <c r="U146">
-        <v>0.47978581308112389</v>
+        <v>-0.47978581308112389</v>
       </c>
       <c r="X146">
         <v>107.2</v>
@@ -11681,10 +11681,10 @@
         <v>0.22146489066150166</v>
       </c>
       <c r="T147">
-        <v>0.25279277609948636</v>
+        <v>-0.25279277609948636</v>
       </c>
       <c r="U147">
-        <v>0.48531090121424203</v>
+        <v>-0.48531090121424203</v>
       </c>
       <c r="X147">
         <v>108.8</v>
@@ -11764,10 +11764,10 @@
         <v>0.22169032115875903</v>
       </c>
       <c r="T148">
-        <v>0.12269426037452291</v>
+        <v>-0.12269426037452291</v>
       </c>
       <c r="U148">
-        <v>0.30588403471243364</v>
+        <v>-0.30588403471243364</v>
       </c>
       <c r="X148">
         <v>108.94</v>
@@ -11847,10 +11847,10 @@
         <v>0.22216005968669297</v>
       </c>
       <c r="T149">
-        <v>-3.9661716418071258E-2</v>
+        <v>3.9661716418071258E-2</v>
       </c>
       <c r="U149">
-        <v>0.10264442924319273</v>
+        <v>-0.10264442924319273</v>
       </c>
       <c r="X149">
         <v>109.18</v>
@@ -11930,10 +11930,10 @@
         <v>0.22427760862462112</v>
       </c>
       <c r="T150">
-        <v>0.1990650171509234</v>
+        <v>-0.1990650171509234</v>
       </c>
       <c r="U150">
-        <v>0.32099404731047443</v>
+        <v>-0.32099404731047443</v>
       </c>
       <c r="X150">
         <v>108.34</v>
@@ -12013,10 +12013,10 @@
         <v>0.22405500052299493</v>
       </c>
       <c r="T151">
-        <v>-7.9978265063895826E-2</v>
+        <v>7.9978265063895826E-2</v>
       </c>
       <c r="U151">
-        <v>0.33680177888699703</v>
+        <v>-0.33680177888699703</v>
       </c>
       <c r="X151">
         <v>108.34</v>
@@ -12096,10 +12096,10 @@
         <v>0.21812385494207495</v>
       </c>
       <c r="T152">
-        <v>-0.1444697243025761</v>
+        <v>0.1444697243025761</v>
       </c>
       <c r="U152">
-        <v>-7.036388283832018E-2</v>
+        <v>7.036388283832018E-2</v>
       </c>
       <c r="X152">
         <v>107.7</v>
@@ -12179,10 +12179,10 @@
         <v>0.21817887784961579</v>
       </c>
       <c r="T153">
-        <v>0.1154668606887066</v>
+        <v>-0.1154668606887066</v>
       </c>
       <c r="U153">
-        <v>-6.3421144473085889E-2</v>
+        <v>6.3421144473085889E-2</v>
       </c>
       <c r="X153">
         <v>108.2</v>
@@ -12262,10 +12262,10 @@
         <v>0.2177795581671215</v>
       </c>
       <c r="T154">
-        <v>0.18909056136540148</v>
+        <v>-0.18909056136540148</v>
       </c>
       <c r="U154">
-        <v>-0.21564195242680384</v>
+        <v>0.21564195242680384</v>
       </c>
       <c r="X154">
         <v>108</v>
@@ -12345,10 +12345,10 @@
         <v>0.21778907197612038</v>
       </c>
       <c r="T155">
-        <v>8.1659754039309362E-2</v>
+        <v>-8.1659754039309362E-2</v>
       </c>
       <c r="U155">
-        <v>-0.37018829151662658</v>
+        <v>0.37018829151662658</v>
       </c>
       <c r="X155">
         <v>108.6</v>
@@ -12428,10 +12428,10 @@
         <v>0.21797078302504472</v>
       </c>
       <c r="T156">
-        <v>0.31565828258361961</v>
+        <v>-0.31565828258361961</v>
       </c>
       <c r="U156">
-        <v>-0.35709277807798312</v>
+        <v>0.35709277807798312</v>
       </c>
       <c r="X156">
         <v>109.2</v>
@@ -12511,10 +12511,10 @@
         <v>0.21833392936460574</v>
       </c>
       <c r="T157">
-        <v>0.141341981405807</v>
+        <v>-0.141341981405807</v>
       </c>
       <c r="U157">
-        <v>-0.27182035438633179</v>
+        <v>0.27182035438633179</v>
       </c>
       <c r="X157">
         <v>108.94</v>
@@ -12594,10 +12594,10 @@
         <v>0.20891913434482795</v>
       </c>
       <c r="T158">
-        <v>-5.8425110761728405E-2</v>
+        <v>5.8425110761728405E-2</v>
       </c>
       <c r="U158">
-        <v>0.16820339032341813</v>
+        <v>-0.16820339032341813</v>
       </c>
       <c r="X158">
         <v>109.01</v>
@@ -12677,10 +12677,10 @@
         <v>0.20954465463950667</v>
       </c>
       <c r="T159">
-        <v>-0.22246237508241062</v>
+        <v>0.22246237508241062</v>
       </c>
       <c r="U159">
-        <v>6.2539346481993441E-2</v>
+        <v>-6.2539346481993441E-2</v>
       </c>
       <c r="X159">
         <v>108.27</v>
@@ -12760,10 +12760,10 @@
         <v>0.20917014083065866</v>
       </c>
       <c r="T160">
-        <v>-0.2360271777374523</v>
+        <v>0.2360271777374523</v>
       </c>
       <c r="U160">
-        <v>-0.14824427060866618</v>
+        <v>0.14824427060866618</v>
       </c>
       <c r="X160">
         <v>109</v>
@@ -12843,10 +12843,10 @@
         <v>0.2096712666752919</v>
       </c>
       <c r="T161">
-        <v>-0.50335690922462817</v>
+        <v>0.50335690922462817</v>
       </c>
       <c r="U161">
-        <v>-0.24265528535967196</v>
+        <v>0.24265528535967196</v>
       </c>
       <c r="X161">
         <v>108.61</v>
@@ -12926,10 +12926,10 @@
         <v>0.20971076747614931</v>
       </c>
       <c r="T162">
-        <v>-0.57858333323812516</v>
+        <v>0.57858333323812516</v>
       </c>
       <c r="U162">
-        <v>-0.27790877106221856</v>
+        <v>0.27790877106221856</v>
       </c>
       <c r="X162">
         <v>109</v>
@@ -13009,10 +13009,10 @@
         <v>0.20976349372491251</v>
       </c>
       <c r="T163">
-        <v>-0.49847967855896069</v>
+        <v>0.49847967855896069</v>
       </c>
       <c r="U163">
-        <v>-0.13829825330182732</v>
+        <v>0.13829825330182732</v>
       </c>
       <c r="X163">
         <v>108.89</v>
@@ -13092,10 +13092,10 @@
         <v>0.20096262302658896</v>
       </c>
       <c r="T164">
-        <v>-0.21672467914106708</v>
+        <v>0.21672467914106708</v>
       </c>
       <c r="U164">
-        <v>0.27067420207991244</v>
+        <v>-0.27067420207991244</v>
       </c>
       <c r="X164">
         <v>109.2</v>
@@ -13175,10 +13175,10 @@
         <v>0.19824901131054753</v>
       </c>
       <c r="T165">
-        <v>7.8378729542194492E-3</v>
+        <v>-7.8378729542194492E-3</v>
       </c>
       <c r="U165">
-        <v>5.5365621200409443E-2</v>
+        <v>-5.5365621200409443E-2</v>
       </c>
       <c r="X165">
         <v>108.94</v>
@@ -13258,10 +13258,10 @@
         <v>0.19863391301325339</v>
       </c>
       <c r="T166">
-        <v>-0.17610912769512321</v>
+        <v>0.17610912769512321</v>
       </c>
       <c r="U166">
-        <v>4.1440716202156835E-3</v>
+        <v>-4.1440716202156835E-3</v>
       </c>
       <c r="X166">
         <v>109.49</v>
@@ -13341,10 +13341,10 @@
         <v>0.20215282908732948</v>
       </c>
       <c r="T167">
-        <v>0.14769801730061261</v>
+        <v>-0.14769801730061261</v>
       </c>
       <c r="U167">
-        <v>0.26194391239253711</v>
+        <v>-0.26194391239253711</v>
       </c>
       <c r="X167">
         <v>109.53</v>
@@ -13424,10 +13424,10 @@
         <v>0.19627062393468253</v>
       </c>
       <c r="T168">
-        <v>6.3513747110843788E-2</v>
+        <v>-6.3513747110843788E-2</v>
       </c>
       <c r="U168">
-        <v>0.5668618960751548</v>
+        <v>-0.5668618960751548</v>
       </c>
       <c r="X168">
         <v>109.8</v>
@@ -13507,10 +13507,10 @@
         <v>0.19497349120694479</v>
       </c>
       <c r="T169">
-        <v>9.7139688537861701E-2</v>
+        <v>-9.7139688537861701E-2</v>
       </c>
       <c r="U169">
-        <v>0.38908332998388584</v>
+        <v>-0.38908332998388584</v>
       </c>
       <c r="X169">
         <v>109.8</v>
@@ -13590,10 +13590,10 @@
         <v>0.18590417131818632</v>
       </c>
       <c r="T170">
-        <v>-8.3800777845555174E-2</v>
+        <v>8.3800777845555174E-2</v>
       </c>
       <c r="U170">
-        <v>-7.6428795186855858E-2</v>
+        <v>7.6428795186855858E-2</v>
       </c>
       <c r="X170">
         <v>109.91</v>
@@ -13673,10 +13673,10 @@
         <v>0.18307911990349665</v>
       </c>
       <c r="T171">
-        <v>-5.9733161016661818E-2</v>
+        <v>5.9733161016661818E-2</v>
       </c>
       <c r="U171">
-        <v>0.17809566743585137</v>
+        <v>-0.17809566743585137</v>
       </c>
       <c r="X171">
         <v>109.8</v>
@@ -13756,10 +13756,10 @@
         <v>0.17992308809325749</v>
       </c>
       <c r="T172">
-        <v>0.10075237201643272</v>
+        <v>-0.10075237201643272</v>
       </c>
       <c r="U172">
-        <v>0.43483174554164172</v>
+        <v>-0.43483174554164172</v>
       </c>
       <c r="X172">
         <v>110.56</v>
@@ -13839,10 +13839,10 @@
         <v>0.17418750829181004</v>
       </c>
       <c r="T173">
-        <v>-2.7396878311747308E-2</v>
+        <v>2.7396878311747308E-2</v>
       </c>
       <c r="U173">
-        <v>8.6207685847106141E-2</v>
+        <v>-8.6207685847106141E-2</v>
       </c>
       <c r="X173">
         <v>111.04</v>
@@ -13922,10 +13922,10 @@
         <v>0.16208535544083</v>
       </c>
       <c r="T174">
-        <v>8.0303028040096258E-2</v>
+        <v>-8.0303028040096258E-2</v>
       </c>
       <c r="U174">
-        <v>-0.42288157855447928</v>
+        <v>0.42288157855447928</v>
       </c>
       <c r="X174">
         <v>112.5</v>
@@ -14005,10 +14005,10 @@
         <v>0.15571358238887623</v>
       </c>
       <c r="T175">
-        <v>3.1581570430994077E-2</v>
+        <v>-3.1581570430994077E-2</v>
       </c>
       <c r="U175">
-        <v>-0.69402685449262425</v>
+        <v>0.69402685449262425</v>
       </c>
       <c r="X175">
         <v>111.2</v>
@@ -14088,10 +14088,10 @@
         <v>0.1155415262000794</v>
       </c>
       <c r="T176">
-        <v>-0.13020486454491387</v>
+        <v>0.13020486454491387</v>
       </c>
       <c r="U176">
-        <v>6.0311127787837648E-2</v>
+        <v>-6.0311127787837648E-2</v>
       </c>
       <c r="X176">
         <v>111.2</v>
@@ -14171,10 +14171,10 @@
         <v>0.11541691058669495</v>
       </c>
       <c r="T177">
-        <v>-0.15113899663712349</v>
+        <v>0.15113899663712349</v>
       </c>
       <c r="U177">
-        <v>0.10631735945827447</v>
+        <v>-0.10631735945827447</v>
       </c>
       <c r="X177">
         <v>110.81</v>
@@ -14254,10 +14254,10 @@
         <v>0.11535353474835022</v>
       </c>
       <c r="T178">
-        <v>-4.7814121655553876E-2</v>
+        <v>4.7814121655553876E-2</v>
       </c>
       <c r="U178">
-        <v>7.7458640093208686E-2</v>
+        <v>-7.7458640093208686E-2</v>
       </c>
       <c r="X178">
         <v>111.2</v>
@@ -14337,10 +14337,10 @@
         <v>0.1152743756831454</v>
       </c>
       <c r="T179">
-        <v>7.9724812572457004E-2</v>
+        <v>-7.9724812572457004E-2</v>
       </c>
       <c r="U179">
-        <v>3.9888893607908926E-2</v>
+        <v>-3.9888893607908926E-2</v>
       </c>
       <c r="X179">
         <v>111.2</v>
@@ -14420,10 +14420,10 @@
         <v>0.11527349003511125</v>
       </c>
       <c r="T180">
-        <v>-0.16607151250811469</v>
+        <v>0.16607151250811469</v>
       </c>
       <c r="U180">
-        <v>3.6246326358146952E-2</v>
+        <v>-3.6246326358146952E-2</v>
       </c>
       <c r="X180">
         <v>110.79</v>
@@ -14509,10 +14509,10 @@
         <v>0.22836758145830718</v>
       </c>
       <c r="T181">
-        <v>1.5867701095340081E-2</v>
+        <v>-1.5867701095340081E-2</v>
       </c>
       <c r="U181">
-        <v>-6.5544497272251867E-2</v>
+        <v>6.5544497272251867E-2</v>
       </c>
       <c r="V181">
         <v>-0.18443909503138567</v>
@@ -14604,10 +14604,10 @@
         <v>0.22822902128229952</v>
       </c>
       <c r="T182">
-        <v>2.2371713088276124E-2</v>
+        <v>-2.2371713088276124E-2</v>
       </c>
       <c r="U182">
-        <v>-0.12423688190867921</v>
+        <v>0.12423688190867921</v>
       </c>
       <c r="V182">
         <v>-0.30318462588976303</v>
@@ -14699,10 +14699,10 @@
         <v>0.22822369869438269</v>
       </c>
       <c r="T183">
-        <v>-8.0911040124154177E-2</v>
+        <v>8.0911040124154177E-2</v>
       </c>
       <c r="U183">
-        <v>3.5721320448089955E-2</v>
+        <v>-3.5721320448089955E-2</v>
       </c>
       <c r="V183">
         <v>-0.2824625158833749</v>
@@ -14794,10 +14794,10 @@
         <v>0.22594600926735001</v>
       </c>
       <c r="T184">
-        <v>-5.5209740151385134E-2</v>
+        <v>5.5209740151385134E-2</v>
       </c>
       <c r="U184">
-        <v>0.13661056236884406</v>
+        <v>-0.13661056236884406</v>
       </c>
       <c r="V184">
         <v>-0.72680466200087945</v>
@@ -14889,10 +14889,10 @@
         <v>0.22384220417968759</v>
       </c>
       <c r="T185">
-        <v>4.0909623469875811E-2</v>
+        <v>-4.0909623469875811E-2</v>
       </c>
       <c r="U185">
-        <v>0.12429355059297986</v>
+        <v>-0.12429355059297986</v>
       </c>
       <c r="V185">
         <v>-0.28971663159698124</v>
@@ -14984,10 +14984,10 @@
         <v>0.22348380024425435</v>
       </c>
       <c r="T186">
-        <v>-0.13943069697774924</v>
+        <v>0.13943069697774924</v>
       </c>
       <c r="U186">
-        <v>0.18094582620744593</v>
+        <v>-0.18094582620744593</v>
       </c>
       <c r="V186">
         <v>-0.10608957263136265</v>
@@ -15079,10 +15079,10 @@
         <v>0.22289825031949953</v>
       </c>
       <c r="T187">
-        <v>-0.22520432165014093</v>
+        <v>0.22520432165014093</v>
       </c>
       <c r="U187">
-        <v>-8.2661544851858615E-2</v>
+        <v>8.2661544851858615E-2</v>
       </c>
       <c r="V187">
         <v>-0.35326785934335359</v>
@@ -15174,10 +15174,10 @@
         <v>0.22166273801026679</v>
       </c>
       <c r="T188">
-        <v>-0.17328805093892452</v>
+        <v>0.17328805093892452</v>
       </c>
       <c r="U188">
-        <v>-0.23406124189397914</v>
+        <v>0.23406124189397914</v>
       </c>
       <c r="V188">
         <v>-0.68623515299630622</v>
@@ -15269,10 +15269,10 @@
         <v>0.21661639430741686</v>
       </c>
       <c r="T189">
-        <v>-3.8248998782108856E-2</v>
+        <v>3.8248998782108856E-2</v>
       </c>
       <c r="U189">
-        <v>-0.26510084359225861</v>
+        <v>0.26510084359225861</v>
       </c>
       <c r="V189">
         <v>-2.9919578151016424E-3</v>
@@ -15364,10 +15364,10 @@
         <v>0.21397117752824016</v>
       </c>
       <c r="T190">
-        <v>4.6230264281854616E-2</v>
+        <v>-4.6230264281854616E-2</v>
       </c>
       <c r="U190">
-        <v>-0.19332504799973727</v>
+        <v>0.19332504799973727</v>
       </c>
       <c r="V190">
         <v>-0.50311807221234961</v>
@@ -15459,10 +15459,10 @@
         <v>0.21358982625314088</v>
       </c>
       <c r="T191">
-        <v>0.16272571026936244</v>
+        <v>-0.16272571026936244</v>
       </c>
       <c r="U191">
-        <v>-0.34578592164584698</v>
+        <v>0.34578592164584698</v>
       </c>
       <c r="V191">
         <v>-0.31065754673784696</v>
@@ -15554,10 +15554,10 @@
         <v>0.21349027155207903</v>
       </c>
       <c r="T192">
-        <v>0.19701321594358667</v>
+        <v>-0.19701321594358667</v>
       </c>
       <c r="U192">
-        <v>-0.38563676958665027</v>
+        <v>0.38563676958665027</v>
       </c>
       <c r="V192">
         <v>-0.21169215571339439</v>
@@ -15649,10 +15649,10 @@
         <v>0.21335307956147692</v>
       </c>
       <c r="T193">
-        <v>0.1275264413773014</v>
+        <v>-0.1275264413773014</v>
       </c>
       <c r="U193">
-        <v>-0.37415547454717757</v>
+        <v>0.37415547454717757</v>
       </c>
       <c r="V193">
         <v>-0.32397252500886431</v>
@@ -15744,10 +15744,10 @@
         <v>0.21234988595716292</v>
       </c>
       <c r="T194">
-        <v>0.20488826704756491</v>
+        <v>-0.20488826704756491</v>
       </c>
       <c r="U194">
-        <v>-9.6925957193683132E-3</v>
+        <v>9.6925957193683132E-3</v>
       </c>
       <c r="V194">
         <v>-2.8809835127119321E-2</v>
@@ -15839,10 +15839,10 @@
         <v>0.21227462566659008</v>
       </c>
       <c r="T195">
-        <v>0.15398976350833316</v>
+        <v>-0.15398976350833316</v>
       </c>
       <c r="U195">
-        <v>0.16484180777911472</v>
+        <v>-0.16484180777911472</v>
       </c>
       <c r="V195">
         <v>5.3438482164747114E-2</v>
@@ -15934,10 +15934,10 @@
         <v>0.21103620650496893</v>
       </c>
       <c r="T196">
-        <v>0.27240843741718201</v>
+        <v>-0.27240843741718201</v>
       </c>
       <c r="U196">
-        <v>0.10005194037085996</v>
+        <v>-0.10005194037085996</v>
       </c>
       <c r="V196">
         <v>-0.28506541189332602</v>
@@ -16029,10 +16029,10 @@
         <v>0.21041643826091444</v>
       </c>
       <c r="T197">
-        <v>-2.3032464182959345E-2</v>
+        <v>2.3032464182959345E-2</v>
       </c>
       <c r="U197">
-        <v>0.1251295467911584</v>
+        <v>-0.1251295467911584</v>
       </c>
       <c r="V197">
         <v>-4.665949898952082E-2</v>
@@ -16124,10 +16124,10 @@
         <v>0.20899091059683822</v>
       </c>
       <c r="T198">
-        <v>4.9117781797636262E-2</v>
+        <v>-4.9117781797636262E-2</v>
       </c>
       <c r="U198">
-        <v>0.11387396964874785</v>
+        <v>-0.11387396964874785</v>
       </c>
       <c r="V198">
         <v>-0.40274762744831882</v>
@@ -16219,10 +16219,10 @@
         <v>0.20831253511963752</v>
       </c>
       <c r="T199">
-        <v>4.494850690361929E-2</v>
+        <v>-4.494850690361929E-2</v>
       </c>
       <c r="U199">
-        <v>0.14340646424191306</v>
+        <v>-0.14340646424191306</v>
       </c>
       <c r="V199">
         <v>-0.64938937694116738</v>
@@ -16314,10 +16314,10 @@
         <v>0.20450761302709444</v>
       </c>
       <c r="T200">
-        <v>5.0029119615313533E-2</v>
+        <v>-5.0029119615313533E-2</v>
       </c>
       <c r="U200">
-        <v>-3.3124519061611402E-2</v>
+        <v>3.3124519061611402E-2</v>
       </c>
       <c r="V200">
         <v>-1.223699819031987</v>
@@ -16409,10 +16409,10 @@
         <v>0.20371235305348054</v>
       </c>
       <c r="T201">
-        <v>4.7384734362676539E-2</v>
+        <v>-4.7384734362676539E-2</v>
       </c>
       <c r="U201">
-        <v>-1.1620718256710738E-2</v>
+        <v>1.1620718256710738E-2</v>
       </c>
       <c r="V201">
         <v>-0.95436009205129846</v>
@@ -16504,10 +16504,10 @@
         <v>0.2012605914380162</v>
       </c>
       <c r="T202">
-        <v>5.6529720882525503E-2</v>
+        <v>-5.6529720882525503E-2</v>
       </c>
       <c r="U202">
-        <v>0.1588278025432599</v>
+        <v>-0.1588278025432599</v>
       </c>
       <c r="V202">
         <v>-0.4963260149436044</v>
@@ -16599,10 +16599,10 @@
         <v>0.20126053302524019</v>
       </c>
       <c r="T203">
-        <v>4.938744486351343E-2</v>
+        <v>-4.938744486351343E-2</v>
       </c>
       <c r="U203">
-        <v>2.2902084465159511E-2</v>
+        <v>-2.2902084465159511E-2</v>
       </c>
       <c r="V203">
         <v>-0.49840590660670259</v>
@@ -16694,10 +16694,10 @@
         <v>0.20120844929209458</v>
       </c>
       <c r="T204">
-        <v>6.1189226285618403E-2</v>
+        <v>-6.1189226285618403E-2</v>
       </c>
       <c r="U204">
-        <v>0.14302839450754945</v>
+        <v>-0.14302839450754945</v>
       </c>
       <c r="V204">
         <v>-0.43478971541073275</v>
@@ -16789,10 +16789,10 @@
         <v>0.20100696754337799</v>
       </c>
       <c r="T205">
-        <v>-2.5702139856309536E-2</v>
+        <v>2.5702139856309536E-2</v>
       </c>
       <c r="U205">
-        <v>5.519955542232502E-3</v>
+        <v>-5.519955542232502E-3</v>
       </c>
       <c r="V205">
         <v>-0.56448734206455686</v>
@@ -16884,10 +16884,10 @@
         <v>0.20096703112390982</v>
       </c>
       <c r="T206">
-        <v>5.4510669968266257E-2</v>
+        <v>-5.4510669968266257E-2</v>
       </c>
       <c r="U206">
-        <v>-7.4930142691131962E-2</v>
+        <v>7.4930142691131962E-2</v>
       </c>
       <c r="V206">
         <v>-0.6217892997822716</v>
@@ -16979,10 +16979,10 @@
         <v>0.19867140266119024</v>
       </c>
       <c r="T207">
-        <v>5.361498786022878E-2</v>
+        <v>-5.361498786022878E-2</v>
       </c>
       <c r="U207">
-        <v>-9.6987480480259514E-2</v>
+        <v>9.6987480480259514E-2</v>
       </c>
       <c r="V207">
         <v>-1.0591600872294382</v>
@@ -17074,10 +17074,10 @@
         <v>0.19418409145472776</v>
       </c>
       <c r="T208">
-        <v>4.7804793381844846E-2</v>
+        <v>-4.7804793381844846E-2</v>
       </c>
       <c r="U208">
-        <v>9.2379988769764054E-4</v>
+        <v>-9.2379988769764054E-4</v>
       </c>
       <c r="V208">
         <v>-0.43965255677944626</v>
@@ -17169,10 +17169,10 @@
         <v>0.19451901680769801</v>
       </c>
       <c r="T209">
-        <v>-0.10147232322377242</v>
+        <v>0.10147232322377242</v>
       </c>
       <c r="U209">
-        <v>-2.3644778555387269E-2</v>
+        <v>2.3644778555387269E-2</v>
       </c>
       <c r="V209">
         <v>-0.27612920293194065</v>
@@ -17264,10 +17264,10 @@
         <v>0.19413502201932009</v>
       </c>
       <c r="T210">
-        <v>3.0972015506436357E-2</v>
+        <v>-3.0972015506436357E-2</v>
       </c>
       <c r="U210">
-        <v>-0.13605432181853505</v>
+        <v>0.13605432181853505</v>
       </c>
       <c r="V210">
         <v>-0.19060886135984223</v>
@@ -17359,10 +17359,10 @@
         <v>0.19367461021635698</v>
       </c>
       <c r="T211">
-        <v>5.561073885795853E-2</v>
+        <v>-5.561073885795853E-2</v>
       </c>
       <c r="U211">
-        <v>7.275836396258839E-2</v>
+        <v>-7.275836396258839E-2</v>
       </c>
       <c r="V211">
         <v>-0.41962043419230266</v>
@@ -17454,10 +17454,10 @@
         <v>0.19318056303065473</v>
       </c>
       <c r="T212">
-        <v>5.9045509171973265E-2</v>
+        <v>-5.9045509171973265E-2</v>
       </c>
       <c r="U212">
-        <v>8.2724768500619383E-2</v>
+        <v>-8.2724768500619383E-2</v>
       </c>
       <c r="V212">
         <v>-0.22238570691441861</v>
@@ -17549,10 +17549,10 @@
         <v>0.19295654755227906</v>
       </c>
       <c r="T213">
-        <v>5.5358996639154334E-2</v>
+        <v>-5.5358996639154334E-2</v>
       </c>
       <c r="U213">
-        <v>-2.5707785814232942E-2</v>
+        <v>2.5707785814232942E-2</v>
       </c>
       <c r="V213">
         <v>-8.5772316405652305E-2</v>
@@ -17644,10 +17644,10 @@
         <v>0.19246241905804506</v>
       </c>
       <c r="T214">
-        <v>8.4560091760410572E-2</v>
+        <v>-8.4560091760410572E-2</v>
       </c>
       <c r="U214">
-        <v>3.004725433106703E-2</v>
+        <v>-3.004725433106703E-2</v>
       </c>
       <c r="V214">
         <v>-0.30215065522909423</v>
@@ -17739,10 +17739,10 @@
         <v>0.19201434442268508</v>
       </c>
       <c r="T215">
-        <v>6.6802209893723763E-2</v>
+        <v>-6.6802209893723763E-2</v>
       </c>
       <c r="U215">
-        <v>0.10937035400873096</v>
+        <v>-0.10937035400873096</v>
       </c>
       <c r="V215">
         <v>-0.10375853527395673</v>
@@ -17834,10 +17834,10 @@
         <v>0.19131434623776111</v>
       </c>
       <c r="T216">
-        <v>6.5349158806426999E-2</v>
+        <v>-6.5349158806426999E-2</v>
       </c>
       <c r="U216">
-        <v>-7.461062039895161E-2</v>
+        <v>7.461062039895161E-2</v>
       </c>
       <c r="V216">
         <v>-0.34545190743404675</v>
@@ -17929,10 +17929,10 @@
         <v>0.1908025080953038</v>
       </c>
       <c r="T217">
-        <v>6.7344628493004599E-2</v>
+        <v>-6.7344628493004599E-2</v>
       </c>
       <c r="U217">
-        <v>-0.15925602501936087</v>
+        <v>0.15925602501936087</v>
       </c>
       <c r="V217">
         <v>-0.14890263851596863</v>
@@ -18024,10 +18024,10 @@
         <v>0.18992109730143822</v>
       </c>
       <c r="T218">
-        <v>7.721419169302024E-2</v>
+        <v>-7.721419169302024E-2</v>
       </c>
       <c r="U218">
-        <v>-9.6684854492212757E-2</v>
+        <v>9.6684854492212757E-2</v>
       </c>
       <c r="V218">
         <v>-0.41532468846161574</v>
@@ -18119,10 +18119,10 @@
         <v>0.18902533238095859</v>
       </c>
       <c r="T219">
-        <v>7.050800212204944E-2</v>
+        <v>-7.050800212204944E-2</v>
       </c>
       <c r="U219">
-        <v>3.3092348483343415E-2</v>
+        <v>-3.3092348483343415E-2</v>
       </c>
       <c r="V219">
         <v>-0.68432088652048417</v>
@@ -18214,10 +18214,10 @@
         <v>0.18902034159433223</v>
       </c>
       <c r="T220">
-        <v>6.8862372256961457E-2</v>
+        <v>-6.8862372256961457E-2</v>
       </c>
       <c r="U220">
-        <v>0.11684921753865041</v>
+        <v>-0.11684921753865041</v>
       </c>
       <c r="V220">
         <v>-0.70202782064887614</v>
@@ -18309,10 +18309,10 @@
         <v>0.18878632846363513</v>
       </c>
       <c r="T221">
-        <v>6.8033159873270854E-2</v>
+        <v>-6.8033159873270854E-2</v>
       </c>
       <c r="U221">
-        <v>0.23377974807099466</v>
+        <v>-0.23377974807099466</v>
       </c>
       <c r="V221">
         <v>-0.83315450583862916</v>
@@ -18404,10 +18404,10 @@
         <v>0.18011794798157094</v>
       </c>
       <c r="T222">
-        <v>7.0770582837620388E-2</v>
+        <v>-7.0770582837620388E-2</v>
       </c>
       <c r="U222">
-        <v>0.27134051902577561</v>
+        <v>-0.27134051902577561</v>
       </c>
       <c r="V222">
         <v>-1.3394022828183694E-3</v>
@@ -18499,10 +18499,10 @@
         <v>0.1801162667539975</v>
       </c>
       <c r="T223">
-        <v>7.2097527602177358E-2</v>
+        <v>-7.2097527602177358E-2</v>
       </c>
       <c r="U223">
-        <v>0.20208110149837477</v>
+        <v>-0.20208110149837477</v>
       </c>
       <c r="V223">
         <v>-1.5275545569681803E-2</v>
@@ -18594,10 +18594,10 @@
         <v>0.1798281192724869</v>
       </c>
       <c r="T224">
-        <v>6.4178052555652343E-2</v>
+        <v>-6.4178052555652343E-2</v>
       </c>
       <c r="U224">
-        <v>0.2724386951301172</v>
+        <v>-0.2724386951301172</v>
       </c>
       <c r="V224">
         <v>-0.16556472426152435</v>
@@ -18689,10 +18689,10 @@
         <v>0.1779135211733596</v>
       </c>
       <c r="T225">
-        <v>6.4581256509033125E-2</v>
+        <v>-6.4581256509033125E-2</v>
       </c>
       <c r="U225">
-        <v>0.22127695373403977</v>
+        <v>-0.22127695373403977</v>
       </c>
       <c r="V225">
         <v>-0.54774254176763737</v>
@@ -18784,10 +18784,10 @@
         <v>0.17264069340213634</v>
       </c>
       <c r="T226">
-        <v>6.3569475362812433E-2</v>
+        <v>-6.3569475362812433E-2</v>
       </c>
       <c r="U226">
-        <v>0.34027005733077154</v>
+        <v>-0.34027005733077154</v>
       </c>
       <c r="V226">
         <v>8.2276486460464149E-2</v>
@@ -18879,10 +18879,10 @@
         <v>0.17221825139009439</v>
       </c>
       <c r="T227">
-        <v>6.6799068782730231E-2</v>
+        <v>-6.6799068782730231E-2</v>
       </c>
       <c r="U227">
-        <v>4.385713448100681E-2</v>
+        <v>-4.385713448100681E-2</v>
       </c>
       <c r="V227">
         <v>-9.8354099910546999E-2</v>
@@ -18974,10 +18974,10 @@
         <v>0.17171388431926501</v>
       </c>
       <c r="T228">
-        <v>7.3552089471284887E-2</v>
+        <v>-7.3552089471284887E-2</v>
       </c>
       <c r="U228">
-        <v>0.12368594959619728</v>
+        <v>-0.12368594959619728</v>
       </c>
       <c r="V228">
         <v>-0.29521336331821413</v>
@@ -19069,10 +19069,10 @@
         <v>0.17128988099084894</v>
       </c>
       <c r="T229">
-        <v>9.6349041542831415E-2</v>
+        <v>-9.6349041542831415E-2</v>
       </c>
       <c r="U229">
-        <v>0.1422531140128136</v>
+        <v>-0.1422531140128136</v>
       </c>
       <c r="V229">
         <v>-0.14358858325838053</v>
@@ -19164,10 +19164,10 @@
         <v>0.17072720539142999</v>
       </c>
       <c r="T230">
-        <v>9.2781058537472205E-2</v>
+        <v>-9.2781058537472205E-2</v>
       </c>
       <c r="U230">
-        <v>0.14357637397179879</v>
+        <v>-0.14357637397179879</v>
       </c>
       <c r="V230">
         <v>-0.34581185917241797</v>
@@ -19259,10 +19259,10 @@
         <v>0.1633335162948826</v>
       </c>
       <c r="T231">
-        <v>9.3773070847436024E-2</v>
+        <v>-9.3773070847436024E-2</v>
       </c>
       <c r="U231">
-        <v>0.14170511402107344</v>
+        <v>-0.14170511402107344</v>
       </c>
       <c r="V231">
         <v>-1.0556481047270472</v>
@@ -19354,10 +19354,10 @@
         <v>0.14974919334195222</v>
       </c>
       <c r="T232">
-        <v>8.9034347292460403E-2</v>
+        <v>-8.9034347292460403E-2</v>
       </c>
       <c r="U232">
-        <v>0.14598585162042266</v>
+        <v>-0.14598585162042266</v>
       </c>
       <c r="V232">
         <v>-0.11304890558900826</v>
@@ -19449,10 +19449,10 @@
         <v>0.14975190221267753</v>
       </c>
       <c r="T233">
-        <v>7.4522410677602124E-2</v>
+        <v>-7.4522410677602124E-2</v>
       </c>
       <c r="U233">
-        <v>0.12399679394246022</v>
+        <v>-0.12399679394246022</v>
       </c>
       <c r="V233">
         <v>-0.10418214232710277</v>
@@ -19544,10 +19544,10 @@
         <v>0.14954901044867067</v>
       </c>
       <c r="T234">
-        <v>8.0040457257890552E-2</v>
+        <v>-8.0040457257890552E-2</v>
       </c>
       <c r="U234">
-        <v>0.1411676190746558</v>
+        <v>-0.1411676190746558</v>
       </c>
       <c r="V234">
         <v>-0.22775918202648793</v>
@@ -19639,10 +19639,10 @@
         <v>0.14921260636822206</v>
       </c>
       <c r="T235">
-        <v>7.9747980423838793E-2</v>
+        <v>-7.9747980423838793E-2</v>
       </c>
       <c r="U235">
-        <v>5.4603232961103476E-2</v>
+        <v>-5.4603232961103476E-2</v>
       </c>
       <c r="V235">
         <v>-8.4223807282701735E-2</v>
@@ -19734,10 +19734,10 @@
         <v>0.14899351585146897</v>
       </c>
       <c r="T236">
-        <v>8.189081257700126E-2</v>
+        <v>-8.189081257700126E-2</v>
       </c>
       <c r="U236">
-        <v>0.13629149096273663</v>
+        <v>-0.13629149096273663</v>
       </c>
       <c r="V236">
         <v>-0.20291198803457089</v>
@@ -19829,10 +19829,10 @@
         <v>0.14896481119152793</v>
       </c>
       <c r="T237">
-        <v>7.859493072936985E-2</v>
+        <v>-7.859493072936985E-2</v>
       </c>
       <c r="U237">
-        <v>0.13200624693293639</v>
+        <v>-0.13200624693293639</v>
       </c>
       <c r="V237">
         <v>-0.24350262379151388</v>
@@ -19924,10 +19924,10 @@
         <v>0.14896472514335693</v>
       </c>
       <c r="T238">
-        <v>7.8460019940285175E-2</v>
+        <v>-7.8460019940285175E-2</v>
       </c>
       <c r="U238">
-        <v>0.125995812297508</v>
+        <v>-0.125995812297508</v>
       </c>
       <c r="V238">
         <v>-0.24347645006408403</v>
@@ -20019,10 +20019,10 @@
         <v>0.16684020170631186</v>
       </c>
       <c r="T239">
-        <v>1.2255601757383161</v>
+        <v>-1.2255601757383161</v>
       </c>
       <c r="U239">
-        <v>1.1337998682038442</v>
+        <v>-1.1337998682038442</v>
       </c>
       <c r="V239">
         <v>-1.4277789051623246</v>
@@ -20114,10 +20114,10 @@
         <v>0.18308400193708302</v>
       </c>
       <c r="T240">
-        <v>0.10170792730889167</v>
+        <v>-0.10170792730889167</v>
       </c>
       <c r="U240">
-        <v>0.13310649280395825</v>
+        <v>-0.13310649280395825</v>
       </c>
       <c r="V240">
         <v>-0.52424016127528006</v>
@@ -20209,10 +20209,10 @@
         <v>0.18276530482685716</v>
       </c>
       <c r="T241">
-        <v>6.5728280103105607E-2</v>
+        <v>-6.5728280103105607E-2</v>
       </c>
       <c r="U241">
-        <v>0.12082108544552161</v>
+        <v>-0.12082108544552161</v>
       </c>
       <c r="V241">
         <v>-0.35979269075534503</v>
@@ -20304,10 +20304,10 @@
         <v>0.18229964292875214</v>
       </c>
       <c r="T242">
-        <v>6.1064363117646625E-2</v>
+        <v>-6.1064363117646625E-2</v>
       </c>
       <c r="U242">
-        <v>0.11959391883242798</v>
+        <v>-0.11959391883242798</v>
       </c>
       <c r="V242">
         <v>-0.17556754484098214</v>
@@ -20399,10 +20399,10 @@
         <v>0.18190018242363623</v>
       </c>
       <c r="T243">
-        <v>5.937181930940616E-2</v>
+        <v>-5.937181930940616E-2</v>
       </c>
       <c r="U243">
-        <v>0.11411998256123379</v>
+        <v>-0.11411998256123379</v>
       </c>
       <c r="V243">
         <v>-0.34138868275597201</v>
@@ -20494,10 +20494,10 @@
         <v>0.18186190388909204</v>
       </c>
       <c r="T244">
-        <v>4.683853804314797E-2</v>
+        <v>-4.683853804314797E-2</v>
       </c>
       <c r="U244">
-        <v>0.12996649920476999</v>
+        <v>-0.12996649920476999</v>
       </c>
       <c r="V244">
         <v>-0.39079068147680474</v>
@@ -20589,10 +20589,10 @@
         <v>0.18185449399141951</v>
       </c>
       <c r="T245">
-        <v>5.0243518943182686E-2</v>
+        <v>-5.0243518943182686E-2</v>
       </c>
       <c r="U245">
-        <v>0.11605802314017533</v>
+        <v>-0.11605802314017533</v>
       </c>
       <c r="V245">
         <v>-0.36468228947823533</v>
@@ -20684,10 +20684,10 @@
         <v>0.1815084007218781</v>
       </c>
       <c r="T246">
-        <v>5.0257463937475322E-2</v>
+        <v>-5.0257463937475322E-2</v>
       </c>
       <c r="U246">
-        <v>0.11457961402907557</v>
+        <v>-0.11457961402907557</v>
       </c>
       <c r="V246">
         <v>-0.20642353307152028</v>
@@ -20779,10 +20779,10 @@
         <v>0.18142983702298929</v>
       </c>
       <c r="T247">
-        <v>3.9474322605581591E-2</v>
+        <v>-3.9474322605581591E-2</v>
       </c>
       <c r="U247">
-        <v>0.10549781070171571</v>
+        <v>-0.10549781070171571</v>
       </c>
       <c r="V247">
         <v>-0.27846720249922186</v>
@@ -20874,10 +20874,10 @@
         <v>0.18089157018849539</v>
       </c>
       <c r="T248">
-        <v>3.4159909212549966E-2</v>
+        <v>-3.4159909212549966E-2</v>
       </c>
       <c r="U248">
-        <v>0.10927567845937514</v>
+        <v>-0.10927567845937514</v>
       </c>
       <c r="V248">
         <v>-7.5080874694744004E-2</v>
@@ -20969,10 +20969,10 @@
         <v>0.1808838547616328</v>
       </c>
       <c r="T249">
-        <v>3.5419971386996263E-2</v>
+        <v>-3.5419971386996263E-2</v>
       </c>
       <c r="U249">
-        <v>0.10390143864643653</v>
+        <v>-0.10390143864643653</v>
       </c>
       <c r="V249">
         <v>-0.10050220262676213</v>
@@ -21064,10 +21064,10 @@
         <v>0.18021281537136738</v>
       </c>
       <c r="T250">
-        <v>3.7762090806725546E-2</v>
+        <v>-3.7762090806725546E-2</v>
       </c>
       <c r="U250">
-        <v>0.1045803974027204</v>
+        <v>-0.1045803974027204</v>
       </c>
       <c r="V250">
         <v>-0.31710012184491543</v>
@@ -21159,10 +21159,10 @@
         <v>0.18013802541873219</v>
       </c>
       <c r="T251">
-        <v>2.4966249205848889E-2</v>
+        <v>-2.4966249205848889E-2</v>
       </c>
       <c r="U251">
-        <v>9.0720441979874611E-2</v>
+        <v>-9.0720441979874611E-2</v>
       </c>
       <c r="V251">
         <v>-0.22522148369643613</v>
@@ -21254,10 +21254,10 @@
         <v>0.17983285075735317</v>
       </c>
       <c r="T252">
-        <v>3.3618885345199079E-2</v>
+        <v>-3.3618885345199079E-2</v>
       </c>
       <c r="U252">
-        <v>0.10226628325666898</v>
+        <v>-0.10226628325666898</v>
       </c>
       <c r="V252">
         <v>-8.9899651081659648E-2</v>
@@ -21349,10 +21349,10 @@
         <v>0.17981475370855848</v>
       </c>
       <c r="T253">
-        <v>3.417693342204764E-2</v>
+        <v>-3.417693342204764E-2</v>
       </c>
       <c r="U253">
-        <v>0.10394836108666983</v>
+        <v>-0.10394836108666983</v>
       </c>
       <c r="V253">
         <v>-0.1269987291214747</v>
@@ -21444,10 +21444,10 @@
         <v>0.17922476877894061</v>
       </c>
       <c r="T254">
-        <v>3.562361795004243E-2</v>
+        <v>-3.562361795004243E-2</v>
       </c>
       <c r="U254">
-        <v>9.7985175491310805E-2</v>
+        <v>-9.7985175491310805E-2</v>
       </c>
       <c r="V254">
         <v>7.2090210302833135E-2</v>
@@ -21539,10 +21539,10 @@
         <v>0.17918923681305937</v>
       </c>
       <c r="T255">
-        <v>4.0343590717484279E-2</v>
+        <v>-4.0343590717484279E-2</v>
       </c>
       <c r="U255">
-        <v>0.10350126101833501</v>
+        <v>-0.10350126101833501</v>
       </c>
       <c r="V255">
         <v>0.11630804128250904</v>
@@ -21634,10 +21634,10 @@
         <v>0.1791875352811047</v>
       </c>
       <c r="T256">
-        <v>4.2303134366061812E-2</v>
+        <v>-4.2303134366061812E-2</v>
       </c>
       <c r="U256">
-        <v>0.10477417342986683</v>
+        <v>-0.10477417342986683</v>
       </c>
       <c r="V256">
         <v>0.10125879385234349</v>
@@ -21729,10 +21729,10 @@
         <v>0.17915514035746388</v>
       </c>
       <c r="T257">
-        <v>5.7164805181464384E-2</v>
+        <v>-5.7164805181464384E-2</v>
       </c>
       <c r="U257">
-        <v>0.12341552396178956</v>
+        <v>-0.12341552396178956</v>
       </c>
       <c r="V257">
         <v>0.13444243987574822</v>
@@ -21824,10 +21824,10 @@
         <v>0.17794813860586808</v>
       </c>
       <c r="T258">
-        <v>4.4300692889576165E-2</v>
+        <v>-4.4300692889576165E-2</v>
       </c>
       <c r="U258">
-        <v>0.11676528047442902</v>
+        <v>-0.11676528047442902</v>
       </c>
       <c r="V258">
         <v>-0.14902030401959809</v>
@@ -21919,10 +21919,10 @@
         <v>0.17744225086632956</v>
       </c>
       <c r="T259">
-        <v>1.1024710307405705E-2</v>
+        <v>-1.1024710307405705E-2</v>
       </c>
       <c r="U259">
-        <v>0.10540450058867945</v>
+        <v>-0.10540450058867945</v>
       </c>
       <c r="V259">
         <v>-0.32685775048189036</v>
@@ -22014,10 +22014,10 @@
         <v>0.17708166808633885</v>
       </c>
       <c r="T260">
-        <v>1.8596434448903132E-2</v>
+        <v>-1.8596434448903132E-2</v>
       </c>
       <c r="U260">
-        <v>0.10986053949241237</v>
+        <v>-0.10986053949241237</v>
       </c>
       <c r="V260">
         <v>-0.1753733254257428</v>
@@ -22109,10 +22109,10 @@
         <v>0.17636538624158302</v>
       </c>
       <c r="T261">
-        <v>1.509921635439726E-2</v>
+        <v>-1.509921635439726E-2</v>
       </c>
       <c r="U261">
-        <v>0.10792050912618034</v>
+        <v>-0.10792050912618034</v>
       </c>
       <c r="V261">
         <v>-0.39462707363324689</v>
@@ -22204,10 +22204,10 @@
         <v>0.17587032064410221</v>
       </c>
       <c r="T262">
-        <v>2.7347435534752496E-2</v>
+        <v>-2.7347435534752496E-2</v>
       </c>
       <c r="U262">
-        <v>0.11604420212917299</v>
+        <v>-0.11604420212917299</v>
       </c>
       <c r="V262">
         <v>-0.22171680071436661</v>
@@ -22299,10 +22299,10 @@
         <v>0.17590649671194902</v>
       </c>
       <c r="T263">
-        <v>0.11178034473057208</v>
+        <v>-0.11178034473057208</v>
       </c>
       <c r="U263">
-        <v>0.18586050684452626</v>
+        <v>-0.18586050684452626</v>
       </c>
       <c r="V263">
         <v>-0.24144268347494613</v>
@@ -22394,10 +22394,10 @@
         <v>0.17346388053131859</v>
       </c>
       <c r="T264">
-        <v>2.7159730118664349E-2</v>
+        <v>-2.7159730118664349E-2</v>
       </c>
       <c r="U264">
-        <v>0.1068687653973277</v>
+        <v>-0.1068687653973277</v>
       </c>
       <c r="V264">
         <v>-0.57750380756684816</v>
@@ -22489,10 +22489,10 @@
         <v>0.17319476184318694</v>
       </c>
       <c r="T265">
-        <v>3.2722778021576637E-2</v>
+        <v>-3.2722778021576637E-2</v>
       </c>
       <c r="U265">
-        <v>0.11200748048132425</v>
+        <v>-0.11200748048132425</v>
       </c>
       <c r="V265">
         <v>-0.44534528440349774</v>
@@ -22584,10 +22584,10 @@
         <v>0.17308490934284051</v>
       </c>
       <c r="T266">
-        <v>3.0139061869582928E-2</v>
+        <v>-3.0139061869582928E-2</v>
       </c>
       <c r="U266">
-        <v>0.11145634016795913</v>
+        <v>-0.11145634016795913</v>
       </c>
       <c r="V266">
         <v>-0.52855770287671966</v>
@@ -22679,10 +22679,10 @@
         <v>0.17308134976541611</v>
       </c>
       <c r="T267">
-        <v>3.3908007457672529E-2</v>
+        <v>-3.3908007457672529E-2</v>
       </c>
       <c r="U267">
-        <v>0.11183051248093712</v>
+        <v>-0.11183051248093712</v>
       </c>
       <c r="V267">
         <v>-0.51225274933195397</v>
@@ -22774,10 +22774,10 @@
         <v>0.17299290580511478</v>
       </c>
       <c r="T268">
-        <v>3.0592957681763178E-2</v>
+        <v>-3.0592957681763178E-2</v>
       </c>
       <c r="U268">
-        <v>0.10823830450971128</v>
+        <v>-0.10823830450971128</v>
       </c>
       <c r="V268">
         <v>-0.42426212181430056</v>
@@ -22869,10 +22869,10 @@
         <v>0.17291548559415024</v>
       </c>
       <c r="T269">
-        <v>-0.99075017678539323</v>
+        <v>0.99075017678539323</v>
       </c>
       <c r="U269">
-        <v>0.25441473740013265</v>
+        <v>-0.25441473740013265</v>
       </c>
       <c r="V269">
         <v>-0.34830403883703287</v>
@@ -22964,10 +22964,10 @@
         <v>0.17290536455498953</v>
       </c>
       <c r="T270">
-        <v>2.2348146573225591E-2</v>
+        <v>-2.2348146573225591E-2</v>
       </c>
       <c r="U270">
-        <v>0.12321945604614193</v>
+        <v>-0.12321945604614193</v>
       </c>
       <c r="V270">
         <v>-0.31814156217400136</v>
@@ -23059,10 +23059,10 @@
         <v>0.17231787333479034</v>
       </c>
       <c r="T271">
-        <v>3.3939640648716907E-2</v>
+        <v>-3.3939640648716907E-2</v>
       </c>
       <c r="U271">
-        <v>9.8878132093072058E-2</v>
+        <v>-9.8878132093072058E-2</v>
       </c>
       <c r="V271">
         <v>-0.51608645443730339</v>
@@ -23154,10 +23154,10 @@
         <v>0.16978681234915324</v>
       </c>
       <c r="T272">
-        <v>3.3197643393800824E-2</v>
+        <v>-3.3197643393800824E-2</v>
       </c>
       <c r="U272">
-        <v>9.3478540227154294E-2</v>
+        <v>-9.3478540227154294E-2</v>
       </c>
       <c r="V272">
         <v>-0.11003173169872316</v>
@@ -23249,10 +23249,10 @@
         <v>0.16962762478637108</v>
       </c>
       <c r="T273">
-        <v>3.2667261127250491E-2</v>
+        <v>-3.2667261127250491E-2</v>
       </c>
       <c r="U273">
-        <v>9.1367659777008559E-2</v>
+        <v>-9.1367659777008559E-2</v>
       </c>
       <c r="V273">
         <v>-6.6781877730459627E-3</v>
@@ -23344,10 +23344,10 @@
         <v>0.16944077286904433</v>
       </c>
       <c r="T274">
-        <v>3.7657464375451255E-2</v>
+        <v>-3.7657464375451255E-2</v>
       </c>
       <c r="U274">
-        <v>8.369893902038239E-2</v>
+        <v>-8.369893902038239E-2</v>
       </c>
       <c r="V274">
         <v>9.9038839926945954E-2</v>
@@ -23439,10 +23439,10 @@
         <v>0.16936011929487055</v>
       </c>
       <c r="T275">
-        <v>4.1551977473375246E-2</v>
+        <v>-4.1551977473375246E-2</v>
       </c>
       <c r="U275">
-        <v>9.0904320785745174E-2</v>
+        <v>-9.0904320785745174E-2</v>
       </c>
       <c r="V275">
         <v>0.16717614756047716</v>
@@ -23534,10 +23534,10 @@
         <v>0.16889767394900748</v>
       </c>
       <c r="T276">
-        <v>4.1676514216049121E-2</v>
+        <v>-4.1676514216049121E-2</v>
       </c>
       <c r="U276">
-        <v>9.1037694334872299E-2</v>
+        <v>-9.1037694334872299E-2</v>
       </c>
       <c r="V276">
         <v>0.33836693503941362</v>
@@ -23629,10 +23629,10 @@
         <v>0.16889601129328527</v>
       </c>
       <c r="T277">
-        <v>4.4779065717448496E-2</v>
+        <v>-4.4779065717448496E-2</v>
       </c>
       <c r="U277">
-        <v>8.3251541017603792E-2</v>
+        <v>-8.3251541017603792E-2</v>
       </c>
       <c r="V277">
         <v>0.34583025544836499</v>
@@ -23724,10 +23724,10 @@
         <v>0.16485261398574036</v>
       </c>
       <c r="T278">
-        <v>5.2926437538447502E-2</v>
+        <v>-5.2926437538447502E-2</v>
       </c>
       <c r="U278">
-        <v>8.5749234213161607E-2</v>
+        <v>-8.5749234213161607E-2</v>
       </c>
       <c r="V278">
         <v>-0.16307894314460114</v>
@@ -23819,10 +23819,10 @@
         <v>0.16484415789871876</v>
       </c>
       <c r="T279">
-        <v>5.0317072350192227E-2</v>
+        <v>-5.0317072350192227E-2</v>
       </c>
       <c r="U279">
-        <v>8.4455844680508818E-2</v>
+        <v>-8.4455844680508818E-2</v>
       </c>
       <c r="V279">
         <v>-0.18560165924443872</v>
@@ -23914,10 +23914,10 @@
         <v>0.16458494882326127</v>
       </c>
       <c r="T280">
-        <v>4.5855311032383383E-2</v>
+        <v>-4.5855311032383383E-2</v>
       </c>
       <c r="U280">
-        <v>8.242317551112599E-2</v>
+        <v>-8.242317551112599E-2</v>
       </c>
       <c r="V280">
         <v>-5.5474699020896523E-2</v>
@@ -24009,10 +24009,10 @@
         <v>0.1645740910935376</v>
       </c>
       <c r="T281">
-        <v>5.8465326058421141E-2</v>
+        <v>-5.8465326058421141E-2</v>
       </c>
       <c r="U281">
-        <v>8.1531395526890371E-2</v>
+        <v>-8.1531395526890371E-2</v>
       </c>
       <c r="V281">
         <v>-7.8066717568603394E-2</v>
@@ -24104,10 +24104,10 @@
         <v>0.16457407414327896</v>
       </c>
       <c r="T282">
-        <v>4.6788308923195743E-2</v>
+        <v>-4.6788308923195743E-2</v>
       </c>
       <c r="U282">
-        <v>7.9077833293927924E-2</v>
+        <v>-7.9077833293927924E-2</v>
       </c>
       <c r="V282">
         <v>-7.8297381934389065E-2</v>
@@ -24199,10 +24199,10 @@
         <v>0.16449757638943205</v>
       </c>
       <c r="T283">
-        <v>4.8384845633675511E-2</v>
+        <v>-4.8384845633675511E-2</v>
       </c>
       <c r="U283">
-        <v>8.1227847346709847E-2</v>
+        <v>-8.1227847346709847E-2</v>
       </c>
       <c r="V283">
         <v>-0.15122527907274197</v>
@@ -24294,10 +24294,10 @@
         <v>0.16073251696284144</v>
       </c>
       <c r="T284">
-        <v>5.0943500521372087E-2</v>
+        <v>-5.0943500521372087E-2</v>
       </c>
       <c r="U284">
-        <v>8.5217685646599151E-2</v>
+        <v>-8.5217685646599151E-2</v>
       </c>
       <c r="V284">
         <v>-0.63477500298945166</v>
@@ -24389,10 +24389,10 @@
         <v>0.15957905598622973</v>
       </c>
       <c r="T285">
-        <v>4.5343426454547142E-2</v>
+        <v>-4.5343426454547142E-2</v>
       </c>
       <c r="U285">
-        <v>8.4651172052174761E-2</v>
+        <v>-8.4651172052174761E-2</v>
       </c>
       <c r="V285">
         <v>-0.36757018712370026</v>
@@ -24484,10 +24484,10 @@
         <v>0.15949845371859575</v>
       </c>
       <c r="T286">
-        <v>4.2470061056176789E-2</v>
+        <v>-4.2470061056176789E-2</v>
       </c>
       <c r="U286">
-        <v>8.3865322890053218E-2</v>
+        <v>-8.3865322890053218E-2</v>
       </c>
       <c r="V286">
         <v>-0.43473709511303582</v>
@@ -24579,10 +24579,10 @@
         <v>0.15947094032617376</v>
       </c>
       <c r="T287">
-        <v>2.2618884402003658E-2</v>
+        <v>-2.2618884402003658E-2</v>
       </c>
       <c r="U287">
-        <v>7.9406764557843346E-2</v>
+        <v>-7.9406764557843346E-2</v>
       </c>
       <c r="V287">
         <v>-0.38969253404592674</v>
@@ -24674,10 +24674,10 @@
         <v>0.15696183821982507</v>
       </c>
       <c r="T288">
-        <v>3.3743831674759583E-2</v>
+        <v>-3.3743831674759583E-2</v>
       </c>
       <c r="U288">
-        <v>7.7572236267742234E-2</v>
+        <v>-7.7572236267742234E-2</v>
       </c>
       <c r="V288">
         <v>-0.77322944807847183</v>
@@ -24769,10 +24769,10 @@
         <v>0.15640372182401308</v>
       </c>
       <c r="T289">
-        <v>4.1334948651172709E-2</v>
+        <v>-4.1334948651172709E-2</v>
       </c>
       <c r="U289">
-        <v>5.1577306302019732E-2</v>
+        <v>-5.1577306302019732E-2</v>
       </c>
       <c r="V289">
         <v>-0.58729423700605299</v>
@@ -24864,10 +24864,10 @@
         <v>0.15271245381138462</v>
       </c>
       <c r="T290">
-        <v>3.3215369976535847E-2</v>
+        <v>-3.3215369976535847E-2</v>
       </c>
       <c r="U290">
-        <v>5.1380735464656713E-2</v>
+        <v>-5.1380735464656713E-2</v>
       </c>
       <c r="V290">
         <v>-0.12208908480926262</v>
@@ -24959,10 +24959,10 @@
         <v>0.15157787763906991</v>
       </c>
       <c r="T291">
-        <v>3.1507270821884426E-2</v>
+        <v>-3.1507270821884426E-2</v>
       </c>
       <c r="U291">
-        <v>4.6377232865546514E-2</v>
+        <v>-4.6377232865546514E-2</v>
       </c>
       <c r="V291">
         <v>-0.3708986819063842</v>
@@ -25054,10 +25054,10 @@
         <v>0.15034628151220789</v>
       </c>
       <c r="T292">
-        <v>2.4060242757983907E-2</v>
+        <v>-2.4060242757983907E-2</v>
       </c>
       <c r="U292">
-        <v>5.1481637590589102E-2</v>
+        <v>-5.1481637590589102E-2</v>
       </c>
       <c r="V292">
         <v>-0.64043803428375234</v>
@@ -25149,10 +25149,10 @@
         <v>0.14808197946039273</v>
       </c>
       <c r="T293">
-        <v>-4.293773708394788E-2</v>
+        <v>4.293773708394788E-2</v>
       </c>
       <c r="U293">
-        <v>6.9919176936839023E-2</v>
+        <v>-6.9919176936839023E-2</v>
       </c>
       <c r="V293">
         <v>-0.28635926110653909</v>
@@ -25244,10 +25244,10 @@
         <v>0.14353927005616507</v>
       </c>
       <c r="T294">
-        <v>3.3965302640615036E-2</v>
+        <v>-3.3965302640615036E-2</v>
       </c>
       <c r="U294">
-        <v>6.1393110580865162E-2</v>
+        <v>-6.1393110580865162E-2</v>
       </c>
       <c r="V294">
         <v>0.21671797149214189</v>
@@ -25339,10 +25339,10 @@
         <v>0.14110880548407775</v>
       </c>
       <c r="T295">
-        <v>1.9488113993926248E-2</v>
+        <v>-1.9488113993926248E-2</v>
       </c>
       <c r="U295">
-        <v>5.2481485001076855E-2</v>
+        <v>-5.2481485001076855E-2</v>
       </c>
       <c r="V295">
         <v>0.58732157795973183</v>
@@ -25434,10 +25434,10 @@
         <v>0.12747646841595753</v>
       </c>
       <c r="T296">
-        <v>2.1358086665523857E-2</v>
+        <v>-2.1358086665523857E-2</v>
       </c>
       <c r="U296">
-        <v>5.1684929495632304E-2</v>
+        <v>-5.1684929495632304E-2</v>
       </c>
       <c r="V296">
         <v>-0.25512529160711672</v>
@@ -25529,10 +25529,10 @@
         <v>0.12744130784843197</v>
       </c>
       <c r="T297">
-        <v>3.0398446138235613E-2</v>
+        <v>-3.0398446138235613E-2</v>
       </c>
       <c r="U297">
-        <v>6.4870086204105171E-2</v>
+        <v>-6.4870086204105171E-2</v>
       </c>
       <c r="V297">
         <v>-0.3127864950185355</v>
@@ -25624,10 +25624,10 @@
         <v>0.12742294637427556</v>
       </c>
       <c r="T298">
-        <v>3.4503772577587632E-2</v>
+        <v>-3.4503772577587632E-2</v>
       </c>
       <c r="U298">
-        <v>6.5620155906520594E-2</v>
+        <v>-6.5620155906520594E-2</v>
       </c>
       <c r="V298">
         <v>-0.27801387242445408</v>
@@ -25719,10 +25719,10 @@
         <v>0.12740104690249771</v>
       </c>
       <c r="T299">
-        <v>3.0160901985643029E-2</v>
+        <v>-3.0160901985643029E-2</v>
       </c>
       <c r="U299">
-        <v>-0.98449412391024005</v>
+        <v>0.98449412391024005</v>
       </c>
       <c r="V299">
         <v>-0.23672909968519562</v>
@@ -25814,10 +25814,10 @@
         <v>0.12740090097056819</v>
       </c>
       <c r="T300">
-        <v>3.2228606516016001E-2</v>
+        <v>-3.2228606516016001E-2</v>
       </c>
       <c r="U300">
-        <v>5.5082859633337478E-2</v>
+        <v>-5.5082859633337478E-2</v>
       </c>
       <c r="V300">
         <v>-0.23351072213875224</v>
@@ -25909,10 +25909,10 @@
         <v>0.12716608901256907</v>
       </c>
       <c r="T301">
-        <v>3.0553004058209154E-2</v>
+        <v>-3.0553004058209154E-2</v>
       </c>
       <c r="U301">
-        <v>6.5537664908243976E-2</v>
+        <v>-6.5537664908243976E-2</v>
       </c>
       <c r="V301">
         <v>-0.12826028421493163</v>
@@ -26004,10 +26004,10 @@
         <v>0.12708778348638528</v>
       </c>
       <c r="T302">
-        <v>3.0163378619829651E-2</v>
+        <v>-3.0163378619829651E-2</v>
       </c>
       <c r="U302">
-        <v>6.4447563062075552E-2</v>
+        <v>-6.4447563062075552E-2</v>
       </c>
       <c r="V302">
         <v>-6.540395035408153E-2</v>
@@ -26099,10 +26099,10 @@
         <v>0.12657592726487477</v>
       </c>
       <c r="T303">
-        <v>2.60246885446902E-2</v>
+        <v>-2.60246885446902E-2</v>
       </c>
       <c r="U303">
-        <v>5.9755640267633581E-2</v>
+        <v>-5.9755640267633581E-2</v>
       </c>
       <c r="V303">
         <v>-0.21832228859701708</v>
@@ -26194,10 +26194,10 @@
         <v>0.12627487007093235</v>
       </c>
       <c r="T304">
-        <v>1.9448166588675875E-2</v>
+        <v>-1.9448166588675875E-2</v>
       </c>
       <c r="U304">
-        <v>5.8220618973470195E-2</v>
+        <v>-5.8220618973470195E-2</v>
       </c>
       <c r="V304">
         <v>-0.33589899855432925</v>
@@ -26289,10 +26289,10 @@
         <v>0.12626278269246408</v>
       </c>
       <c r="T305">
-        <v>1.2481851917511833E-2</v>
+        <v>-1.2481851917511833E-2</v>
       </c>
       <c r="U305">
-        <v>5.5193721466872958E-2</v>
+        <v>-5.5193721466872958E-2</v>
       </c>
       <c r="V305">
         <v>-0.3050133991441939</v>
@@ -26384,10 +26384,10 @@
         <v>0.12619500552191396</v>
       </c>
       <c r="T306">
-        <v>1.4009033437289986E-2</v>
+        <v>-1.4009033437289986E-2</v>
       </c>
       <c r="U306">
-        <v>5.6880197140696254E-2</v>
+        <v>-5.6880197140696254E-2</v>
       </c>
       <c r="V306">
         <v>-0.36258896502829874</v>
@@ -26479,10 +26479,10 @@
         <v>0.12463858095765616</v>
       </c>
       <c r="T307">
-        <v>1.41139174577809E-2</v>
+        <v>-1.41139174577809E-2</v>
       </c>
       <c r="U307">
-        <v>6.0222539651966223E-2</v>
+        <v>-6.0222539651966223E-2</v>
       </c>
       <c r="V307">
         <v>-8.8340787964868994E-2</v>
@@ -26574,10 +26574,10 @@
         <v>0.12422240907296114</v>
       </c>
       <c r="T308">
-        <v>1.8625316362186339E-2</v>
+        <v>-1.8625316362186339E-2</v>
       </c>
       <c r="U308">
-        <v>7.3286112952364313E-2</v>
+        <v>-7.3286112952364313E-2</v>
       </c>
       <c r="V308">
         <v>4.8153668337858058E-2</v>
@@ -26669,10 +26669,10 @@
         <v>0.12418976306395837</v>
       </c>
       <c r="T309">
-        <v>1.6300038778660486E-2</v>
+        <v>-1.6300038778660486E-2</v>
       </c>
       <c r="U309">
-        <v>6.8251881277991977E-2</v>
+        <v>-6.8251881277991977E-2</v>
       </c>
       <c r="V309">
         <v>9.0063565873577112E-2</v>
@@ -26764,10 +26764,10 @@
         <v>0.12408721024594847</v>
       </c>
       <c r="T310">
-        <v>1.5547043479613443E-2</v>
+        <v>-1.5547043479613443E-2</v>
       </c>
       <c r="U310">
-        <v>6.2919836205077573E-2</v>
+        <v>-6.2919836205077573E-2</v>
       </c>
       <c r="V310">
         <v>2.1404343661979297E-2</v>
@@ -26859,10 +26859,10 @@
         <v>0.12360686332959159</v>
       </c>
       <c r="T311">
-        <v>2.7646059048058724E-2</v>
+        <v>-2.7646059048058724E-2</v>
       </c>
       <c r="U311">
-        <v>8.8320204632363897E-2</v>
+        <v>-8.8320204632363897E-2</v>
       </c>
       <c r="V311">
         <v>0.16563203149819739</v>
@@ -26954,10 +26954,10 @@
         <v>0.12357500163103821</v>
       </c>
       <c r="T312">
-        <v>3.217154204886441E-2</v>
+        <v>-3.217154204886441E-2</v>
       </c>
       <c r="U312">
-        <v>8.0823312721967078E-2</v>
+        <v>-8.0823312721967078E-2</v>
       </c>
       <c r="V312">
         <v>0.20165568455088323</v>
@@ -27049,10 +27049,10 @@
         <v>0.12357306701649164</v>
       </c>
       <c r="T313">
-        <v>2.7229348356283545E-2</v>
+        <v>-2.7229348356283545E-2</v>
       </c>
       <c r="U313">
-        <v>7.7551653363983064E-2</v>
+        <v>-7.7551653363983064E-2</v>
       </c>
       <c r="V313">
         <v>0.19171505444528503</v>
@@ -27144,10 +27144,10 @@
         <v>0.12085365695090272</v>
       </c>
       <c r="T314">
-        <v>2.2388431535769193E-2</v>
+        <v>-2.2388431535769193E-2</v>
       </c>
       <c r="U314">
-        <v>7.5195908250380583E-2</v>
+        <v>-7.5195908250380583E-2</v>
       </c>
       <c r="V314">
         <v>-0.17124751314883113</v>
@@ -27239,10 +27239,10 @@
         <v>0.12017728378211157</v>
       </c>
       <c r="T315">
-        <v>2.453021864052829E-2</v>
+        <v>-2.453021864052829E-2</v>
       </c>
       <c r="U315">
-        <v>7.14885455773695E-2</v>
+        <v>-7.14885455773695E-2</v>
       </c>
       <c r="V315">
         <v>-0.35138615486272062</v>
@@ -27334,10 +27334,10 @@
         <v>0.12008313629595584</v>
       </c>
       <c r="T316">
-        <v>2.5002542609620093E-2</v>
+        <v>-2.5002542609620093E-2</v>
       </c>
       <c r="U316">
-        <v>6.890030093480437E-2</v>
+        <v>-6.890030093480437E-2</v>
       </c>
       <c r="V316">
         <v>-0.28363607221180143</v>
@@ -27429,10 +27429,10 @@
         <v>0.12006692598108841</v>
       </c>
       <c r="T317">
-        <v>2.6516628328843161E-2</v>
+        <v>-2.6516628328843161E-2</v>
       </c>
       <c r="U317">
-        <v>4.9793255267993608E-2</v>
+        <v>-4.9793255267993608E-2</v>
       </c>
       <c r="V317">
         <v>-0.30890324470798092</v>
@@ -27524,10 +27524,10 @@
         <v>0.1200657426146229</v>
       </c>
       <c r="T318">
-        <v>2.4539711318238844E-2</v>
+        <v>-2.4539711318238844E-2</v>
       </c>
       <c r="U318">
-        <v>5.9337373062051668E-2</v>
+        <v>-5.9337373062051668E-2</v>
       </c>
       <c r="V318">
         <v>-0.30004146372684115</v>
@@ -27619,10 +27619,10 @@
         <v>0.12004812994274575</v>
       </c>
       <c r="T319">
-        <v>2.7372195052977055E-2</v>
+        <v>-2.7372195052977055E-2</v>
       </c>
       <c r="U319">
-        <v>7.0033534565427935E-2</v>
+        <v>-7.0033534565427935E-2</v>
       </c>
       <c r="V319">
         <v>-0.32906328716175715</v>
@@ -27714,10 +27714,10 @@
         <v>0.11933659727102097</v>
       </c>
       <c r="T320">
-        <v>3.0059466326370909E-2</v>
+        <v>-3.0059466326370909E-2</v>
       </c>
       <c r="U320">
-        <v>6.435870556378287E-2</v>
+        <v>-6.435870556378287E-2</v>
       </c>
       <c r="V320">
         <v>-0.1474917663661035</v>
@@ -27809,10 +27809,10 @@
         <v>0.11932516978100133</v>
       </c>
       <c r="T321">
-        <v>3.5490165676121954E-2</v>
+        <v>-3.5490165676121954E-2</v>
       </c>
       <c r="U321">
-        <v>6.8041963189990895E-2</v>
+        <v>-6.8041963189990895E-2</v>
       </c>
       <c r="V321">
         <v>-0.17127711012188129</v>
@@ -27904,10 +27904,10 @@
         <v>0.11870492917352107</v>
       </c>
       <c r="T322">
-        <v>3.5031768876847558E-2</v>
+        <v>-3.5031768876847558E-2</v>
       </c>
       <c r="U322">
-        <v>5.9849002985612465E-2</v>
+        <v>-5.9849002985612465E-2</v>
       </c>
       <c r="V322">
         <v>-0.34637270163153655</v>
@@ -27999,10 +27999,10 @@
         <v>0.11828835880848798</v>
       </c>
       <c r="T323">
-        <v>2.8538980576042761E-2</v>
+        <v>-2.8538980576042761E-2</v>
       </c>
       <c r="U323">
-        <v>-1.4952719805227943E-2</v>
+        <v>1.4952719805227943E-2</v>
       </c>
       <c r="V323">
         <v>-0.20402994632124916</v>
@@ -28094,10 +28094,10 @@
         <v>0.11798708290523938</v>
       </c>
       <c r="T324">
-        <v>2.9065218827084571E-2</v>
+        <v>-2.9065218827084571E-2</v>
       </c>
       <c r="U324">
-        <v>6.4010884284892988E-2</v>
+        <v>-6.4010884284892988E-2</v>
       </c>
       <c r="V324">
         <v>-0.32431884870942618</v>
@@ -28189,10 +28189,10 @@
         <v>0.11756062420778284</v>
       </c>
       <c r="T325">
-        <v>3.4934186629276276E-2</v>
+        <v>-3.4934186629276276E-2</v>
       </c>
       <c r="U325">
-        <v>5.5179559654949806E-2</v>
+        <v>-5.5179559654949806E-2</v>
       </c>
       <c r="V325">
         <v>-0.18005862053849242</v>
@@ -28284,10 +28284,10 @@
         <v>0.11741403437787808</v>
       </c>
       <c r="T326">
-        <v>3.1224039521848823E-2</v>
+        <v>-3.1224039521848823E-2</v>
       </c>
       <c r="U326">
-        <v>5.3318933616086639E-2</v>
+        <v>-5.3318933616086639E-2</v>
       </c>
       <c r="V326">
         <v>-9.5795326178449436E-2</v>
@@ -28379,10 +28379,10 @@
         <v>0.11740031202038663</v>
       </c>
       <c r="T327">
-        <v>2.1179113261737825E-2</v>
+        <v>-2.1179113261737825E-2</v>
       </c>
       <c r="U327">
-        <v>5.2355913255563991E-2</v>
+        <v>-5.2355913255563991E-2</v>
       </c>
       <c r="V327">
         <v>-7.3307183717696844E-2</v>
@@ -28474,10 +28474,10 @@
         <v>0.11716770994223548</v>
       </c>
       <c r="T328">
-        <v>2.1176954717860852E-2</v>
+        <v>-2.1176954717860852E-2</v>
       </c>
       <c r="U328">
-        <v>5.6546091864784209E-2</v>
+        <v>-5.6546091864784209E-2</v>
       </c>
       <c r="V328">
         <v>-0.17336636350713253</v>
@@ -28569,10 +28569,10 @@
         <v>0.11677389009921647</v>
       </c>
       <c r="T329">
-        <v>2.9851674225223057E-2</v>
+        <v>-2.9851674225223057E-2</v>
       </c>
       <c r="U329">
-        <v>6.1039768789550308E-2</v>
+        <v>-6.1039768789550308E-2</v>
       </c>
       <c r="V329">
         <v>-0.30875916141233084</v>
@@ -28664,10 +28664,10 @@
         <v>0.11539276043865676</v>
       </c>
       <c r="T330">
-        <v>3.3343405422758821E-2</v>
+        <v>-3.3343405422758821E-2</v>
       </c>
       <c r="U330">
-        <v>6.6783928863412001E-2</v>
+        <v>-6.6783928863412001E-2</v>
       </c>
       <c r="V330">
         <v>-6.1523805140129006E-2</v>
@@ -28759,10 +28759,10 @@
         <v>0.11466348699232362</v>
       </c>
       <c r="T331">
-        <v>3.1287845455896246E-2</v>
+        <v>-3.1287845455896246E-2</v>
       </c>
       <c r="U331">
-        <v>6.2935665000218854E-2</v>
+        <v>-6.2935665000218854E-2</v>
       </c>
       <c r="V331">
         <v>-0.24254910339869262</v>
@@ -28854,10 +28854,10 @@
         <v>0.11466698773076806</v>
       </c>
       <c r="T332">
-        <v>1.9326573883882148E-2</v>
+        <v>-1.9326573883882148E-2</v>
       </c>
       <c r="U332">
-        <v>5.0229368256959894E-2</v>
+        <v>-5.0229368256959894E-2</v>
       </c>
       <c r="V332">
         <v>-0.23420132507594449</v>
@@ -28949,10 +28949,10 @@
         <v>0.11440051520907794</v>
       </c>
       <c r="T333">
-        <v>2.630796267288904E-2</v>
+        <v>-2.630796267288904E-2</v>
       </c>
       <c r="U333">
-        <v>5.3226182712640124E-2</v>
+        <v>-5.3226182712640124E-2</v>
       </c>
       <c r="V333">
         <v>-0.12511575509914774</v>
@@ -29044,10 +29044,10 @@
         <v>0.11435579224014145</v>
       </c>
       <c r="T334">
-        <v>2.6998093568164627E-2</v>
+        <v>-2.6998093568164627E-2</v>
       </c>
       <c r="U334">
-        <v>4.7245946790575033E-2</v>
+        <v>-4.7245946790575033E-2</v>
       </c>
       <c r="V334">
         <v>-0.16681859053380155</v>
@@ -29139,10 +29139,10 @@
         <v>0.11419132442678957</v>
       </c>
       <c r="T335">
-        <v>3.3676684134098522E-2</v>
+        <v>-3.3676684134098522E-2</v>
       </c>
       <c r="U335">
-        <v>4.7109814704815456E-2</v>
+        <v>-4.7109814704815456E-2</v>
       </c>
       <c r="V335">
         <v>-0.25413361355057784</v>
@@ -29234,10 +29234,10 @@
         <v>0.113413467214541</v>
       </c>
       <c r="T336">
-        <v>3.8863507859421276E-2</v>
+        <v>-3.8863507859421276E-2</v>
       </c>
       <c r="U336">
-        <v>5.3990503334944151E-2</v>
+        <v>-5.3990503334944151E-2</v>
       </c>
       <c r="V336">
         <v>-7.5880809003514571E-2</v>
@@ -29329,10 +29329,10 @@
         <v>0.11320380814378012</v>
       </c>
       <c r="T337">
-        <v>3.8789428578578367E-2</v>
+        <v>-3.8789428578578367E-2</v>
       </c>
       <c r="U337">
-        <v>5.4042160892975311E-2</v>
+        <v>-5.4042160892975311E-2</v>
       </c>
       <c r="V337">
         <v>1.7735005999619524E-2</v>
@@ -29424,10 +29424,10 @@
         <v>0.11311309033608995</v>
       </c>
       <c r="T338">
-        <v>4.6750667401807E-2</v>
+        <v>-4.6750667401807E-2</v>
       </c>
       <c r="U338">
-        <v>6.6778040756654278E-2</v>
+        <v>-6.6778040756654278E-2</v>
       </c>
       <c r="V338">
         <v>-6.0834636413376053E-2</v>
@@ -29519,10 +29519,10 @@
         <v>0.11272434726375247</v>
       </c>
       <c r="T339">
-        <v>4.6299625622392426E-2</v>
+        <v>-4.6299625622392426E-2</v>
       </c>
       <c r="U339">
-        <v>6.3970399508783693E-2</v>
+        <v>-6.3970399508783693E-2</v>
       </c>
       <c r="V339">
         <v>-0.18766137701258234</v>
@@ -29614,10 +29614,10 @@
         <v>0.1125571455509386</v>
       </c>
       <c r="T340">
-        <v>4.5590492667124671E-2</v>
+        <v>-4.5590492667124671E-2</v>
       </c>
       <c r="U340">
-        <v>6.2531360588935492E-2</v>
+        <v>-6.2531360588935492E-2</v>
       </c>
       <c r="V340">
         <v>-0.26855130183525144</v>
@@ -29709,10 +29709,10 @@
         <v>0.11220785566502144</v>
       </c>
       <c r="T341">
-        <v>4.0446971102192641E-2</v>
+        <v>-4.0446971102192641E-2</v>
       </c>
       <c r="U341">
-        <v>6.9476739413976141E-2</v>
+        <v>-6.9476739413976141E-2</v>
       </c>
       <c r="V341">
         <v>-0.39218526530324649</v>
@@ -29804,10 +29804,10 @@
         <v>0.11217203153208227</v>
       </c>
       <c r="T342">
-        <v>4.238870995278976E-2</v>
+        <v>-4.238870995278976E-2</v>
       </c>
       <c r="U342">
-        <v>7.6011553909505203E-2</v>
+        <v>-7.6011553909505203E-2</v>
       </c>
       <c r="V342">
         <v>-0.43365081530410965</v>
@@ -29899,10 +29899,10 @@
         <v>0.11206044640511142</v>
       </c>
       <c r="T343">
-        <v>4.3487976151856955E-2</v>
+        <v>-4.3487976151856955E-2</v>
       </c>
       <c r="U343">
-        <v>7.2096794669662678E-2</v>
+        <v>-7.2096794669662678E-2</v>
       </c>
       <c r="V343">
         <v>-0.36155371062047692</v>
@@ -29994,10 +29994,10 @@
         <v>0.11193670743502521</v>
       </c>
       <c r="T344">
-        <v>4.6918392881023507E-2</v>
+        <v>-4.6918392881023507E-2</v>
       </c>
       <c r="U344">
-        <v>7.0748983335433557E-2</v>
+        <v>-7.0748983335433557E-2</v>
       </c>
       <c r="V344">
         <v>-0.4349508264149593</v>
@@ -30089,10 +30089,10 @@
         <v>0.11187773383927557</v>
       </c>
       <c r="T345">
-        <v>4.8697280099796458E-2</v>
+        <v>-4.8697280099796458E-2</v>
       </c>
       <c r="U345">
-        <v>7.4644372923149405E-2</v>
+        <v>-7.4644372923149405E-2</v>
       </c>
       <c r="V345">
         <v>-0.38589185758370892</v>
@@ -30184,10 +30184,10 @@
         <v>0.11153107920002514</v>
       </c>
       <c r="T346">
-        <v>5.3003365120263268E-2</v>
+        <v>-5.3003365120263268E-2</v>
       </c>
       <c r="U346">
-        <v>7.9540558635460279E-2</v>
+        <v>-7.9540558635460279E-2</v>
       </c>
       <c r="V346">
         <v>-0.50953296806912629</v>
@@ -30279,10 +30279,10 @@
         <v>0.10938602615264099</v>
       </c>
       <c r="T347">
-        <v>5.4570609056536767E-2</v>
+        <v>-5.4570609056536767E-2</v>
       </c>
       <c r="U347">
-        <v>8.2507920423546821E-2</v>
+        <v>-8.2507920423546821E-2</v>
       </c>
       <c r="V347">
         <v>-0.20967370313882405</v>
@@ -30374,10 +30374,10 @@
         <v>0.10924191851182177</v>
       </c>
       <c r="T348">
-        <v>5.517739254989884E-2</v>
+        <v>-5.517739254989884E-2</v>
       </c>
       <c r="U348">
-        <v>8.1123721760545386E-2</v>
+        <v>-8.1123721760545386E-2</v>
       </c>
       <c r="V348">
         <v>-0.28669102858935869</v>
@@ -30469,10 +30469,10 @@
         <v>0.10924127484528108</v>
       </c>
       <c r="T349">
-        <v>5.179828061026015E-2</v>
+        <v>-5.179828061026015E-2</v>
       </c>
       <c r="U349">
-        <v>8.0412486912617709E-2</v>
+        <v>-8.0412486912617709E-2</v>
       </c>
       <c r="V349">
         <v>-0.27781705327394324</v>
@@ -30564,10 +30564,10 @@
         <v>0.10924106738481744</v>
       </c>
       <c r="T350">
-        <v>4.9570945993349103E-2</v>
+        <v>-4.9570945993349103E-2</v>
       </c>
       <c r="U350">
-        <v>8.0756511509094686E-2</v>
+        <v>-8.0756511509094686E-2</v>
       </c>
       <c r="V350">
         <v>-0.27941635451278479</v>
@@ -30659,10 +30659,10 @@
         <v>0.10924113795233571</v>
       </c>
       <c r="T351">
-        <v>5.1740685238033102E-2</v>
+        <v>-5.1740685238033102E-2</v>
       </c>
       <c r="U351">
-        <v>8.8293717441012554E-2</v>
+        <v>-8.8293717441012554E-2</v>
       </c>
       <c r="V351">
         <v>-0.28016832119350799</v>
@@ -30754,10 +30754,10 @@
         <v>0.10924552945376396</v>
       </c>
       <c r="T352">
-        <v>3.3804947362736648E-2</v>
+        <v>-3.3804947362736648E-2</v>
       </c>
       <c r="U352">
-        <v>6.926424292919009E-2</v>
+        <v>-6.926424292919009E-2</v>
       </c>
       <c r="V352">
         <v>-0.27036942964226984</v>
@@ -30849,10 +30849,10 @@
         <v>0.10924441289379412</v>
       </c>
       <c r="T353">
-        <v>3.3549011939282281E-2</v>
+        <v>-3.3549011939282281E-2</v>
       </c>
       <c r="U353">
-        <v>6.2447638717744169E-2</v>
+        <v>-6.2447638717744169E-2</v>
       </c>
       <c r="V353">
         <v>-0.25978345154176186</v>
@@ -30944,10 +30944,10 @@
         <v>0.10924301526984433</v>
       </c>
       <c r="T354">
-        <v>3.0994900690528571E-2</v>
+        <v>-3.0994900690528571E-2</v>
       </c>
       <c r="U354">
-        <v>6.0321054869727497E-2</v>
+        <v>-6.0321054869727497E-2</v>
       </c>
       <c r="V354">
         <v>-0.26631070045377569</v>
@@ -31039,10 +31039,10 @@
         <v>0.10905184190402414</v>
       </c>
       <c r="T355">
-        <v>3.2407711755855217E-2</v>
+        <v>-3.2407711755855217E-2</v>
       </c>
       <c r="U355">
-        <v>6.7668323229463923E-2</v>
+        <v>-6.7668323229463923E-2</v>
       </c>
       <c r="V355">
         <v>-0.17658796954154177</v>
@@ -31134,10 +31134,10 @@
         <v>0.1088869238294284</v>
       </c>
       <c r="T356">
-        <v>3.8674434887475684E-2</v>
+        <v>-3.8674434887475684E-2</v>
       </c>
       <c r="U356">
-        <v>7.0473707799223462E-2</v>
+        <v>-7.0473707799223462E-2</v>
       </c>
       <c r="V356">
         <v>-0.26148534726124772</v>
@@ -31229,10 +31229,10 @@
         <v>0.10888692680627403</v>
       </c>
       <c r="T357">
-        <v>3.4079325793645587E-2</v>
+        <v>-3.4079325793645587E-2</v>
       </c>
       <c r="U357">
-        <v>5.5452096308927779E-2</v>
+        <v>-5.5452096308927779E-2</v>
       </c>
       <c r="V357">
         <v>-0.25498228369309484</v>
@@ -31324,10 +31324,10 @@
         <v>0.10888697401083076</v>
       </c>
       <c r="T358">
-        <v>3.5745579951584894E-2</v>
+        <v>-3.5745579951584894E-2</v>
       </c>
       <c r="U358">
-        <v>5.712244644311415E-2</v>
+        <v>-5.712244644311415E-2</v>
       </c>
       <c r="V358">
         <v>-0.25116001136744615</v>
@@ -31419,10 +31419,10 @@
         <v>0.10888690532553644</v>
       </c>
       <c r="T359">
-        <v>3.087898124526367E-2</v>
+        <v>-3.087898124526367E-2</v>
       </c>
       <c r="U359">
-        <v>6.0696652499836468E-2</v>
+        <v>-6.0696652499836468E-2</v>
       </c>
       <c r="V359">
         <v>-0.25108393619188707</v>
@@ -31514,10 +31514,10 @@
         <v>0.10888695932742611</v>
       </c>
       <c r="T360">
-        <v>2.997226059736624E-2</v>
+        <v>-2.997226059736624E-2</v>
       </c>
       <c r="U360">
-        <v>6.3098983453979685E-2</v>
+        <v>-6.3098983453979685E-2</v>
       </c>
       <c r="V360">
         <v>-0.25385420336201392</v>
@@ -31615,10 +31615,10 @@
         <v>0.17864757049709673</v>
       </c>
       <c r="T361">
-        <v>2.8491151675003046E-2</v>
+        <v>-2.8491151675003046E-2</v>
       </c>
       <c r="U361">
-        <v>5.9437950532514883E-2</v>
+        <v>-5.9437950532514883E-2</v>
       </c>
       <c r="V361">
         <v>-0.24786161406362694</v>
@@ -31722,10 +31722,10 @@
         <v>0.17855903233989817</v>
       </c>
       <c r="T362">
-        <v>4.3416150734532089E-2</v>
+        <v>-4.3416150734532089E-2</v>
       </c>
       <c r="U362">
-        <v>6.2594045869202031E-2</v>
+        <v>-6.2594045869202031E-2</v>
       </c>
       <c r="V362">
         <v>-0.24903963518061456</v>
@@ -31829,10 +31829,10 @@
         <v>0.17855560974703821</v>
       </c>
       <c r="T363">
-        <v>4.2171598801277188E-2</v>
+        <v>-4.2171598801277188E-2</v>
       </c>
       <c r="U363">
-        <v>6.8177775518007966E-2</v>
+        <v>-6.8177775518007966E-2</v>
       </c>
       <c r="V363">
         <v>-0.24405715057596034</v>
@@ -31936,10 +31936,10 @@
         <v>0.17710604764081353</v>
       </c>
       <c r="T364">
-        <v>5.0394769067740874E-2</v>
+        <v>-5.0394769067740874E-2</v>
       </c>
       <c r="U364">
-        <v>7.710227115416135E-2</v>
+        <v>-7.710227115416135E-2</v>
       </c>
       <c r="V364">
         <v>-0.26777374047470826</v>
@@ -32043,10 +32043,10 @@
         <v>0.17576476248108275</v>
       </c>
       <c r="T365">
-        <v>5.0405785332741093E-2</v>
+        <v>-5.0405785332741093E-2</v>
       </c>
       <c r="U365">
-        <v>8.3632683139500674E-2</v>
+        <v>-8.3632683139500674E-2</v>
       </c>
       <c r="V365">
         <v>-0.25657522282063194</v>
@@ -32150,10 +32150,10 @@
         <v>0.17553816522156643</v>
       </c>
       <c r="T366">
-        <v>4.9291594819744766E-2</v>
+        <v>-4.9291594819744766E-2</v>
       </c>
       <c r="U366">
-        <v>8.7653872026094426E-2</v>
+        <v>-8.7653872026094426E-2</v>
       </c>
       <c r="V366">
         <v>-0.26098381653274494</v>
@@ -32257,10 +32257,10 @@
         <v>0.1751655740235987</v>
       </c>
       <c r="T367">
-        <v>5.2597659179975942E-2</v>
+        <v>-5.2597659179975942E-2</v>
       </c>
       <c r="U367">
-        <v>9.0874488519987473E-2</v>
+        <v>-9.0874488519987473E-2</v>
       </c>
       <c r="V367">
         <v>-0.25833124101479754</v>
@@ -32364,10 +32364,10 @@
         <v>0.17438316264475695</v>
       </c>
       <c r="T368">
-        <v>4.2511025216984688E-2</v>
+        <v>-4.2511025216984688E-2</v>
       </c>
       <c r="U368">
-        <v>8.8531077197484542E-2</v>
+        <v>-8.8531077197484542E-2</v>
       </c>
       <c r="V368">
         <v>-0.2726953127741405</v>
@@ -32471,10 +32471,10 @@
         <v>0.17119160842529652</v>
       </c>
       <c r="T369">
-        <v>3.9395635916150695E-2</v>
+        <v>-3.9395635916150695E-2</v>
       </c>
       <c r="U369">
-        <v>8.4873301639376564E-2</v>
+        <v>-8.4873301639376564E-2</v>
       </c>
       <c r="V369">
         <v>-0.25822888642638153</v>
@@ -32578,10 +32578,10 @@
         <v>0.16952356485827061</v>
       </c>
       <c r="T370">
-        <v>4.4367422602631379E-2</v>
+        <v>-4.4367422602631379E-2</v>
       </c>
       <c r="U370">
-        <v>8.9096922907561105E-2</v>
+        <v>-8.9096922907561105E-2</v>
       </c>
       <c r="V370">
         <v>-0.2576961013837753</v>
@@ -32685,10 +32685,10 @@
         <v>0.16928290783740557</v>
       </c>
       <c r="T371">
-        <v>4.131884113396378E-2</v>
+        <v>-4.131884113396378E-2</v>
       </c>
       <c r="U371">
-        <v>8.08919777811834E-2</v>
+        <v>-8.08919777811834E-2</v>
       </c>
       <c r="V371">
         <v>-0.25918743747840312</v>
@@ -32792,10 +32792,10 @@
         <v>0.16922051937470103</v>
       </c>
       <c r="T372">
-        <v>3.4711082075222777E-2</v>
+        <v>-3.4711082075222777E-2</v>
       </c>
       <c r="U372">
-        <v>7.610331178944385E-2</v>
+        <v>-7.610331178944385E-2</v>
       </c>
       <c r="V372">
         <v>-0.25892924036718945</v>
@@ -32899,10 +32899,10 @@
         <v>0.16913415092145351</v>
       </c>
       <c r="T373">
-        <v>4.0091627254190687E-2</v>
+        <v>-4.0091627254190687E-2</v>
       </c>
       <c r="U373">
-        <v>8.2568718441189404E-2</v>
+        <v>-8.2568718441189404E-2</v>
       </c>
       <c r="V373">
         <v>-0.26433850669244086</v>
@@ -33006,10 +33006,10 @@
         <v>0.16850467491273685</v>
       </c>
       <c r="T374">
-        <v>3.8629709181559058E-2</v>
+        <v>-3.8629709181559058E-2</v>
       </c>
       <c r="U374">
-        <v>8.4458577746282515E-2</v>
+        <v>-8.4458577746282515E-2</v>
       </c>
       <c r="V374">
         <v>-0.25794189295373915</v>
@@ -33113,10 +33113,10 @@
         <v>0.16845890169488661</v>
       </c>
       <c r="T375">
-        <v>4.2506632123040511E-2</v>
+        <v>-4.2506632123040511E-2</v>
       </c>
       <c r="U375">
-        <v>9.0091137008097011E-2</v>
+        <v>-9.0091137008097011E-2</v>
       </c>
       <c r="V375">
         <v>-0.26581617522299927</v>
@@ -33220,10 +33220,10 @@
         <v>0.16767866478615523</v>
       </c>
       <c r="T376">
-        <v>4.270038949053534E-2</v>
+        <v>-4.270038949053534E-2</v>
       </c>
       <c r="U376">
-        <v>9.4592414973537764E-2</v>
+        <v>-9.4592414973537764E-2</v>
       </c>
       <c r="V376">
         <v>-0.26944392952563678</v>
@@ -33327,10 +33327,10 @@
         <v>0.16729180986621706</v>
       </c>
       <c r="T377">
-        <v>4.9595538686975082E-2</v>
+        <v>-4.9595538686975082E-2</v>
       </c>
       <c r="U377">
-        <v>0.10315372406669576</v>
+        <v>-0.10315372406669576</v>
       </c>
       <c r="V377">
         <v>-0.27858351597433995</v>
@@ -33434,10 +33434,10 @@
         <v>0.16639678298398802</v>
       </c>
       <c r="T378">
-        <v>5.2040151308285765E-2</v>
+        <v>-5.2040151308285765E-2</v>
       </c>
       <c r="U378">
-        <v>0.10619970003981072</v>
+        <v>-0.10619970003981072</v>
       </c>
       <c r="V378">
         <v>-0.28461245067359364</v>
@@ -33541,10 +33541,10 @@
         <v>0.16597382019209958</v>
       </c>
       <c r="T379">
-        <v>5.5885057324223109E-2</v>
+        <v>-5.5885057324223109E-2</v>
       </c>
       <c r="U379">
-        <v>0.10677911854315436</v>
+        <v>-0.10677911854315436</v>
       </c>
       <c r="V379">
         <v>-0.28446049482016011</v>
@@ -33648,10 +33648,10 @@
         <v>0.16361100676728263</v>
       </c>
       <c r="T380">
-        <v>6.0911613457848013E-2</v>
+        <v>-6.0911613457848013E-2</v>
       </c>
       <c r="U380">
-        <v>0.10961503750143153</v>
+        <v>-0.10961503750143153</v>
       </c>
       <c r="V380">
         <v>-0.28649899951691538</v>
@@ -33755,10 +33755,10 @@
         <v>0.16310828855301121</v>
       </c>
       <c r="T381">
-        <v>5.1282821302545134E-2</v>
+        <v>-5.1282821302545134E-2</v>
       </c>
       <c r="U381">
-        <v>0.10202149722674525</v>
+        <v>-0.10202149722674525</v>
       </c>
       <c r="V381">
         <v>-0.28023070733911304</v>
@@ -33862,10 +33862,10 @@
         <v>0.16157641743668963</v>
       </c>
       <c r="T382">
-        <v>6.8462393607660044E-2</v>
+        <v>-6.8462393607660044E-2</v>
       </c>
       <c r="U382">
-        <v>0.1012362251734622</v>
+        <v>-0.1012362251734622</v>
       </c>
       <c r="V382">
         <v>-0.2791349187395431</v>
@@ -33969,10 +33969,10 @@
         <v>0.16157656546632407</v>
       </c>
       <c r="T383">
-        <v>6.7186919820982904E-2</v>
+        <v>-6.7186919820982904E-2</v>
       </c>
       <c r="U383">
-        <v>9.9694969108687914E-2</v>
+        <v>-9.9694969108687914E-2</v>
       </c>
       <c r="V383">
         <v>-0.27476917758419983</v>
@@ -34076,10 +34076,10 @@
         <v>0.16154397761666051</v>
       </c>
       <c r="T384">
-        <v>6.2870199281761519E-2</v>
+        <v>-6.2870199281761519E-2</v>
       </c>
       <c r="U384">
-        <v>9.2898299037336152E-2</v>
+        <v>-9.2898299037336152E-2</v>
       </c>
       <c r="V384">
         <v>-0.26517268981973707</v>
@@ -34183,10 +34183,10 @@
         <v>0.16142342802116996</v>
       </c>
       <c r="T385">
-        <v>4.5000227191149822E-2</v>
+        <v>-4.5000227191149822E-2</v>
       </c>
       <c r="U385">
-        <v>7.6528703131351072E-2</v>
+        <v>-7.6528703131351072E-2</v>
       </c>
       <c r="V385">
         <v>-0.24433758186694909</v>
@@ -34290,10 +34290,10 @@
         <v>0.1614001024569387</v>
       </c>
       <c r="T386">
-        <v>3.2413297333167002E-2</v>
+        <v>-3.2413297333167002E-2</v>
       </c>
       <c r="U386">
-        <v>7.0302565642876846E-2</v>
+        <v>-7.0302565642876846E-2</v>
       </c>
       <c r="V386">
         <v>-0.23552391129398886</v>
@@ -34397,10 +34397,10 @@
         <v>0.15998661596844521</v>
       </c>
       <c r="T387">
-        <v>3.5347092367266075E-2</v>
+        <v>-3.5347092367266075E-2</v>
       </c>
       <c r="U387">
-        <v>6.8629838043066105E-2</v>
+        <v>-6.8629838043066105E-2</v>
       </c>
       <c r="V387">
         <v>-0.23291469394957076</v>
@@ -34504,10 +34504,10 @@
         <v>0.15720361749149958</v>
       </c>
       <c r="T388">
-        <v>3.5066993932109103E-2</v>
+        <v>-3.5066993932109103E-2</v>
       </c>
       <c r="U388">
-        <v>7.0011469697639495E-2</v>
+        <v>-7.0011469697639495E-2</v>
       </c>
       <c r="V388">
         <v>-0.23466218127622396</v>
@@ -34611,10 +34611,10 @@
         <v>0.15720357717376332</v>
       </c>
       <c r="T389">
-        <v>3.7273082852995465E-2</v>
+        <v>-3.7273082852995465E-2</v>
       </c>
       <c r="U389">
-        <v>6.7388684146074684E-2</v>
+        <v>-6.7388684146074684E-2</v>
       </c>
       <c r="V389">
         <v>-0.38417972595126137</v>
@@ -34665,6 +34665,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="dd854d95-092e-48c7-992a-80d5cc5badc3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006CC87EF38A8DD0408B89B7B34D0336DC" ma:contentTypeVersion="20" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a30c2ca5bc864785a186dec6b0346788">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe" xmlns:ns3="dd854d95-092e-48c7-992a-80d5cc5badc3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2932ec1554b414302dd4a6579c5666bc" ns2:_="" ns3:_="">
     <xsd:import namespace="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
@@ -34919,27 +34939,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dd854d95-092e-48c7-992a-80d5cc5badc3"/>
+    <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="dd854d95-092e-48c7-992a-80d5cc5badc3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BABE8802-F313-4DEC-9147-95F411D9A097}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34956,23 +34975,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="dd854d95-092e-48c7-992a-80d5cc5badc3"/>
-    <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eldorado275.sharepoint.com/sites/Compartidos/Documentos compartidos/INVERSIONES/Claude - Fernando/Dashboards ETFs/Dashboards/ETFPESOV/General/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{832548A3-27EB-4C0C-AC3C-4D25B168E83D}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{673AAD81-7E84-41F6-AA17-9552641B2E13}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI389"/>
+  <dimension ref="A1:AI390"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -34562,8 +34562,8 @@
       <c r="C389">
         <v>149077720.44977134</v>
       </c>
-      <c r="D389" t="s">
-        <v>23</v>
+      <c r="D389">
+        <v>547</v>
       </c>
       <c r="E389">
         <v>5982.21</v>
@@ -34657,6 +34657,113 @@
       </c>
       <c r="AI389">
         <v>10047.755000000001</v>
+      </c>
+    </row>
+    <row r="390" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A390" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B390">
+        <v>110.58673230898968</v>
+      </c>
+      <c r="C390">
+        <v>149015621.7863636</v>
+      </c>
+      <c r="D390" t="s">
+        <v>23</v>
+      </c>
+      <c r="E390">
+        <v>2105</v>
+      </c>
+      <c r="F390">
+        <v>2</v>
+      </c>
+      <c r="G390">
+        <v>6.2304747077615721</v>
+      </c>
+      <c r="H390">
+        <v>6.129373223079976</v>
+      </c>
+      <c r="I390">
+        <v>181.72</v>
+      </c>
+      <c r="J390">
+        <v>6.31</v>
+      </c>
+      <c r="K390">
+        <v>6.1899999999999995</v>
+      </c>
+      <c r="L390">
+        <v>10.586732308989678</v>
+      </c>
+      <c r="M390">
+        <v>11.079191052616322</v>
+      </c>
+      <c r="N390">
+        <v>6.5803131862324014</v>
+      </c>
+      <c r="O390">
+        <v>6.59</v>
+      </c>
+      <c r="P390">
+        <v>5.4989128448245158E-3</v>
+      </c>
+      <c r="Q390">
+        <v>5.2218641305133108E-3</v>
+      </c>
+      <c r="R390">
+        <v>0.1078466854227064</v>
+      </c>
+      <c r="S390">
+        <v>0.15681536223562831</v>
+      </c>
+      <c r="T390">
+        <v>-3.1813029847360674E-2</v>
+      </c>
+      <c r="U390">
+        <v>-6.1049079585928645E-2</v>
+      </c>
+      <c r="V390">
+        <v>-0.25030487093484766</v>
+      </c>
+      <c r="W390">
+        <v>-0.46282776112556157</v>
+      </c>
+      <c r="X390">
+        <v>110.79</v>
+      </c>
+      <c r="Y390">
+        <v>-2.5120016823665048</v>
+      </c>
+      <c r="Z390">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA390" s="3">
+        <v>1.8380838891447482E-3</v>
+      </c>
+      <c r="AB390" s="3">
+        <v>6.0603431449080059E-3</v>
+      </c>
+      <c r="AC390" s="3">
+        <v>5.1737156747969438E-3</v>
+      </c>
+      <c r="AD390" s="3">
+        <v>4.4457987196358665E-3</v>
+      </c>
+      <c r="AE390" s="3">
+        <v>5.0120668383469768E-3</v>
+      </c>
+      <c r="AF390">
+        <v>6823</v>
+      </c>
+      <c r="AG390">
+        <v>8662.9650000000001</v>
+      </c>
+      <c r="AH390">
+        <v>10696.294999999998</v>
+      </c>
+      <c r="AI390">
+        <v>9958.755000000001</v>
       </c>
     </row>
   </sheetData>
@@ -34665,6 +34772,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="dd854d95-092e-48c7-992a-80d5cc5badc3" xsi:nil="true"/>
@@ -34673,15 +34789,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -34940,20 +35047,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="dd854d95-092e-48c7-992a-80d5cc5badc3"/>
     <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eldorado275.sharepoint.com/sites/Compartidos/Documentos compartidos/INVERSIONES/Claude - Fernando/Dashboards ETFs/Dashboards/ETFPESOV/General/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{673AAD81-7E84-41F6-AA17-9552641B2E13}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A688B8F-5C2B-445A-A3BB-047DF36C5700}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Fecha</t>
   </si>
@@ -98,9 +98,6 @@
     <t>Slippage 60 días</t>
   </si>
   <si>
-    <t>TE 30 días</t>
-  </si>
-  <si>
     <t>VWAP</t>
   </si>
   <si>
@@ -147,6 +144,18 @@
   </si>
   <si>
     <t>Vol Mediana 360 días</t>
+  </si>
+  <si>
+    <t>TE 30 dias</t>
+  </si>
+  <si>
+    <t>BAS 7</t>
+  </si>
+  <si>
+    <t>BAS 30</t>
+  </si>
+  <si>
+    <t>BAS 90</t>
   </si>
 </sst>
 </file>
@@ -530,13 +539,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI390"/>
+  <dimension ref="A1:AL390"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -583,7 +592,7 @@
         <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="Q1" t="s">
         <v>15</v>
@@ -592,7 +601,7 @@
         <v>16</v>
       </c>
       <c r="S1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="T1" t="s">
         <v>17</v>
@@ -601,49 +610,58 @@
         <v>18</v>
       </c>
       <c r="V1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W1" t="s">
         <v>32</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE1" t="s">
         <v>33</v>
       </c>
-      <c r="X1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AF1" t="s">
         <v>27</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AG1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI1" t="s">
         <v>34</v>
       </c>
-      <c r="AF1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45748</v>
       </c>
@@ -702,7 +720,7 @@
         <v>9.5943256973129998E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45749</v>
       </c>
@@ -761,7 +779,7 @@
         <v>1.2143671677051771E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45750</v>
       </c>
@@ -820,7 +838,7 @@
         <v>9.1175034119250764E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45751</v>
       </c>
@@ -879,7 +897,7 @@
         <v>1.1159691476292588E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45754</v>
       </c>
@@ -938,7 +956,7 @@
         <v>1.3318351860941879E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45755</v>
       </c>
@@ -997,7 +1015,7 @@
         <v>1.4496105894190592E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45756</v>
       </c>
@@ -1056,7 +1074,7 @@
         <v>1.059531283173043E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>45757</v>
       </c>
@@ -1114,8 +1132,11 @@
       <c r="AA9" s="3">
         <v>9.5170229436190024E-3</v>
       </c>
-    </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ9">
+        <v>5.4664085198334574E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>45758</v>
       </c>
@@ -1173,8 +1194,11 @@
       <c r="AA10" s="3">
         <v>1.2588309241094331E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ10">
+        <v>5.3273280215036661E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>45761</v>
       </c>
@@ -1232,8 +1256,11 @@
       <c r="AA11" s="3">
         <v>3.6875895667234371E-3</v>
       </c>
-    </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ11">
+        <v>5.4761156842506016E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>45762</v>
       </c>
@@ -1291,8 +1318,11 @@
       <c r="AA12" s="3">
         <v>4.4103347852244568E-3</v>
       </c>
-    </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ12">
+        <v>7.5064481611148443E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>45763</v>
       </c>
@@ -1350,8 +1380,11 @@
       <c r="AA13" s="3">
         <v>1.069542784982902E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ13">
+        <v>9.421823280368594E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>45768</v>
       </c>
@@ -1409,8 +1442,11 @@
       <c r="AA14" s="3">
         <v>3.2775521211678704E-3</v>
       </c>
-    </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ14">
+        <v>9.1726826367041457E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>45769</v>
       </c>
@@ -1468,8 +1504,11 @@
       <c r="AA15" s="3">
         <v>8.2411514863298674E-3</v>
       </c>
-    </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ15">
+        <v>9.665483552611329E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>45770</v>
       </c>
@@ -1527,8 +1566,11 @@
       <c r="AA16" s="3">
         <v>9.8259889689884528E-3</v>
       </c>
-    </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ16">
+        <v>9.4562899082472809E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>45771</v>
       </c>
@@ -1586,8 +1628,11 @@
       <c r="AA17" s="3">
         <v>6.1477814565573663E-3</v>
       </c>
-    </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ17">
+        <v>1.0801057445594512E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>45772</v>
       </c>
@@ -1645,8 +1690,11 @@
       <c r="AA18" s="3">
         <v>7.6715295615414902E-3</v>
       </c>
-    </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ18">
+        <v>1.1793592036918684E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>45775</v>
       </c>
@@ -1704,8 +1752,11 @@
       <c r="AA19" s="3">
         <v>6.3277755685609005E-4</v>
       </c>
-    </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ19">
+        <v>1.0740421153611178E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>45776</v>
       </c>
@@ -1763,8 +1814,11 @@
       <c r="AA20" s="3">
         <v>2.1853312366791888E-3</v>
       </c>
-    </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ20">
+        <v>1.0740421153611178E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>45777</v>
       </c>
@@ -1822,8 +1876,11 @@
       <c r="AA21" s="3">
         <v>5.0849546986864169E-5</v>
       </c>
-    </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ21">
+        <v>1.2154556386551293E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>45779</v>
       </c>
@@ -1881,8 +1938,11 @@
       <c r="AA22" s="3">
         <v>5.3071721745676648E-3</v>
       </c>
-    </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ22">
+        <v>1.285482056728012E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>45782</v>
       </c>
@@ -1940,8 +2000,11 @@
       <c r="AA23" s="3">
         <v>1.5255835720811017E-3</v>
       </c>
-    </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ23">
+        <v>1.3645576960565222E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>45783</v>
       </c>
@@ -1999,8 +2062,11 @@
       <c r="AA24" s="3">
         <v>7.5744419926038198E-4</v>
       </c>
-    </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ24">
+        <v>1.2512501749924378E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>45784</v>
       </c>
@@ -2058,8 +2124,11 @@
       <c r="AA25" s="3">
         <v>3.3848643678949797E-3</v>
       </c>
-    </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ25">
+        <v>1.3069911383825291E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>45785</v>
       </c>
@@ -2117,8 +2186,11 @@
       <c r="AA26" s="3">
         <v>2.6257951324997197E-3</v>
       </c>
-    </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ26">
+        <v>1.305590681133237E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>45786</v>
       </c>
@@ -2176,8 +2248,11 @@
       <c r="AA27" s="3">
         <v>5.2926816086399375E-3</v>
       </c>
-    </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ27">
+        <v>1.1989955513331273E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>45789</v>
       </c>
@@ -2235,8 +2310,11 @@
       <c r="AA28" s="3">
         <v>3.0927042456607712E-3</v>
       </c>
-    </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ28">
+        <v>1.1907012173202969E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>45790</v>
       </c>
@@ -2294,8 +2372,11 @@
       <c r="AA29" s="3">
         <v>6.1827320898003579E-3</v>
       </c>
-    </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ29">
+        <v>1.2256028325144153E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>45791</v>
       </c>
@@ -2356,8 +2437,11 @@
       <c r="AF30">
         <v>9647.375</v>
       </c>
-    </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ30">
+        <v>1.2605044477085336E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>45792</v>
       </c>
@@ -2427,8 +2511,11 @@
       <c r="AF31">
         <v>10502.5</v>
       </c>
-    </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ31">
+        <v>1.3245775862324668E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>45793</v>
       </c>
@@ -2498,8 +2585,11 @@
       <c r="AF32">
         <v>9670</v>
       </c>
-    </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ32">
+        <v>1.4717944009614455E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>45796</v>
       </c>
@@ -2569,8 +2659,14 @@
       <c r="AF33">
         <v>9670</v>
       </c>
-    </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ33">
+        <v>1.2308207406716147E-2</v>
+      </c>
+      <c r="AK33">
+        <v>1.0310555549770695E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>45797</v>
       </c>
@@ -2640,8 +2736,14 @@
       <c r="AF34">
         <v>9670</v>
       </c>
-    </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ34">
+        <v>1.1599315806909542E-2</v>
+      </c>
+      <c r="AK34">
+        <v>1.0293064128490414E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>45798</v>
       </c>
@@ -2711,8 +2813,14 @@
       <c r="AF35">
         <v>9151.625</v>
       </c>
-    </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ35">
+        <v>1.1173692304753619E-2</v>
+      </c>
+      <c r="AK35">
+        <v>1.0343253778859142E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>45799</v>
       </c>
@@ -2782,8 +2890,14 @@
       <c r="AF36">
         <v>8644.5</v>
       </c>
-    </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ36">
+        <v>1.1104026796620909E-2</v>
+      </c>
+      <c r="AK36">
+        <v>1.073098368354891E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>45800</v>
       </c>
@@ -2853,8 +2967,14 @@
       <c r="AF37">
         <v>7933</v>
       </c>
-    </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ37">
+        <v>1.1123469055330173E-2</v>
+      </c>
+      <c r="AK37">
+        <v>1.117819018152796E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>45803</v>
       </c>
@@ -2924,8 +3044,14 @@
       <c r="AF38">
         <v>7933</v>
       </c>
-    </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ38">
+        <v>1.0902658724932535E-2</v>
+      </c>
+      <c r="AK38">
+        <v>1.1452113558798082E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>45804</v>
       </c>
@@ -2995,8 +3121,14 @@
       <c r="AF39">
         <v>7645.5</v>
       </c>
-    </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ39">
+        <v>1.1056535465755421E-2</v>
+      </c>
+      <c r="AK39">
+        <v>1.1897335154770669E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>45805</v>
       </c>
@@ -3066,8 +3198,14 @@
       <c r="AF40">
         <v>7645.5</v>
       </c>
-    </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ40">
+        <v>1.3468110815669568E-2</v>
+      </c>
+      <c r="AK40">
+        <v>1.2177619418799124E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>45806</v>
       </c>
@@ -3137,8 +3275,14 @@
       <c r="AF41">
         <v>7645.5</v>
       </c>
-    </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ41">
+        <v>1.4456831968801714E-2</v>
+      </c>
+      <c r="AK41">
+        <v>1.2423281716193299E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>45807</v>
       </c>
@@ -3208,8 +3352,14 @@
       <c r="AF42">
         <v>7498.4</v>
       </c>
-    </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ42">
+        <v>1.5580998041421393E-2</v>
+      </c>
+      <c r="AK42">
+        <v>1.2701059662198998E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>45810</v>
       </c>
@@ -3279,8 +3429,14 @@
       <c r="AF43">
         <v>7498.4</v>
       </c>
-    </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ43">
+        <v>1.5580998041421391E-2</v>
+      </c>
+      <c r="AK43">
+        <v>1.2615045322287107E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>45811</v>
       </c>
@@ -3350,8 +3506,14 @@
       <c r="AF44">
         <v>7645.5</v>
       </c>
-    </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ44">
+        <v>1.4933360450124772E-2</v>
+      </c>
+      <c r="AK44">
+        <v>1.2464215521137738E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>45812</v>
       </c>
@@ -3421,8 +3583,14 @@
       <c r="AF45">
         <v>7498.4</v>
       </c>
-    </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ45">
+        <v>1.2694072496551106E-2</v>
+      </c>
+      <c r="AK45">
+        <v>1.2273771192762375E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45813</v>
       </c>
@@ -3492,8 +3660,14 @@
       <c r="AF46">
         <v>7498.4</v>
       </c>
-    </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ46">
+        <v>1.2681909210517751E-2</v>
+      </c>
+      <c r="AK46">
+        <v>1.2601167808282167E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45814</v>
       </c>
@@ -3563,8 +3737,14 @@
       <c r="AF47">
         <v>7293.4</v>
       </c>
-    </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AJ47">
+        <v>1.1834376387929989E-2</v>
+      </c>
+      <c r="AK47">
+        <v>1.273250626405842E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>45817</v>
       </c>
@@ -3634,8 +3814,14 @@
       <c r="AF48">
         <v>7134.1</v>
       </c>
-    </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ48">
+        <v>1.2614395465856123E-2</v>
+      </c>
+      <c r="AK48">
+        <v>1.2846393920921009E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>45818</v>
       </c>
@@ -3705,8 +3891,14 @@
       <c r="AF49">
         <v>7293.4</v>
       </c>
-    </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ49">
+        <v>1.1915852895392372E-2</v>
+      </c>
+      <c r="AK49">
+        <v>1.2729587195842856E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>45819</v>
       </c>
@@ -3776,8 +3968,14 @@
       <c r="AF50">
         <v>7134.1</v>
       </c>
-    </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ50">
+        <v>1.1497139878254162E-2</v>
+      </c>
+      <c r="AK50">
+        <v>1.2791613024703802E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>45820</v>
       </c>
@@ -3847,8 +4045,14 @@
       <c r="AF51">
         <v>7134.1</v>
       </c>
-    </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ51">
+        <v>1.1357431567075901E-2</v>
+      </c>
+      <c r="AK51">
+        <v>1.2608184617612839E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>45821</v>
       </c>
@@ -3918,8 +4122,14 @@
       <c r="AF52">
         <v>7134.1</v>
       </c>
-    </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ52">
+        <v>1.3016434913368347E-2</v>
+      </c>
+      <c r="AK52">
+        <v>1.2474876182353019E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>45824</v>
       </c>
@@ -3989,8 +4199,14 @@
       <c r="AF53">
         <v>7293.4</v>
       </c>
-    </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ53">
+        <v>1.300199603090175E-2</v>
+      </c>
+      <c r="AK53">
+        <v>1.2635508749793882E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>45825</v>
       </c>
@@ -4060,8 +4276,14 @@
       <c r="AF54">
         <v>7293.4</v>
       </c>
-    </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ54">
+        <v>1.3829003167736918E-2</v>
+      </c>
+      <c r="AK54">
+        <v>1.2775305712398485E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>45826</v>
       </c>
@@ -4131,8 +4353,14 @@
       <c r="AF55">
         <v>7293.4</v>
       </c>
-    </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ55">
+        <v>1.3797748594125938E-2</v>
+      </c>
+      <c r="AK55">
+        <v>1.3146284851234702E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>45827</v>
       </c>
@@ -4202,8 +4430,14 @@
       <c r="AF56">
         <v>7454.7749999999996</v>
       </c>
-    </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ56">
+        <v>1.4838269474744254E-2</v>
+      </c>
+      <c r="AK56">
+        <v>1.3142204083723947E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>45828</v>
       </c>
@@ -4273,8 +4507,14 @@
       <c r="AF57">
         <v>7293.4</v>
       </c>
-    </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ57">
+        <v>1.5592982827882799E-2</v>
+      </c>
+      <c r="AK57">
+        <v>1.3383597428565569E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>45831</v>
       </c>
@@ -4344,8 +4584,14 @@
       <c r="AF58">
         <v>7310.0249999999996</v>
       </c>
-    </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ58">
+        <v>1.6347696181021342E-2</v>
+      </c>
+      <c r="AK58">
+        <v>1.3624990773407187E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>45832</v>
       </c>
@@ -4415,8 +4661,14 @@
       <c r="AF59">
         <v>7310.0249999999996</v>
       </c>
-    </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ59">
+        <v>1.7060898355485753E-2</v>
+      </c>
+      <c r="AK59">
+        <v>1.367744962488567E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>45833</v>
       </c>
@@ -4489,8 +4741,14 @@
       <c r="AG60">
         <v>7645.5</v>
       </c>
-    </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ60">
+        <v>1.7057315079708788E-2</v>
+      </c>
+      <c r="AK60">
+        <v>1.3674371890406019E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>45834</v>
       </c>
@@ -4572,8 +4830,14 @@
       <c r="AG61">
         <v>7645.5</v>
       </c>
-    </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ61">
+        <v>1.7046045051311284E-2</v>
+      </c>
+      <c r="AK61">
+        <v>1.3666888703470981E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>45835</v>
       </c>
@@ -4655,8 +4919,14 @@
       <c r="AG62">
         <v>7541.375</v>
       </c>
-    </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ62">
+        <v>1.7034775022913781E-2</v>
+      </c>
+      <c r="AK62">
+        <v>1.3659405516535942E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>45838</v>
       </c>
@@ -4738,8 +5008,14 @@
       <c r="AG63">
         <v>7541.375</v>
       </c>
-    </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ63">
+        <v>1.7022963853977151E-2</v>
+      </c>
+      <c r="AK63">
+        <v>1.368412281491933E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>45839</v>
       </c>
@@ -4821,8 +5097,14 @@
       <c r="AG64">
         <v>7454.7749999999996</v>
       </c>
-    </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ64">
+        <v>1.6993363123431127E-2</v>
+      </c>
+      <c r="AK64">
+        <v>1.4235407084290774E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>45840</v>
       </c>
@@ -4904,8 +5186,14 @@
       <c r="AG65">
         <v>7310.0249999999996</v>
       </c>
-    </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ65">
+        <v>1.6274607278016651E-2</v>
+      </c>
+      <c r="AK65">
+        <v>1.4474498771823892E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>45841</v>
       </c>
@@ -4987,8 +5275,14 @@
       <c r="AG66">
         <v>7310.0249999999996</v>
       </c>
-    </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ66">
+        <v>1.624515007123737E-2</v>
+      </c>
+      <c r="AK66">
+        <v>1.4808330918920063E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>45842</v>
       </c>
@@ -5070,8 +5364,14 @@
       <c r="AG67">
         <v>7191.625</v>
       </c>
-    </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ67">
+        <v>1.6257204043132224E-2</v>
+      </c>
+      <c r="AK67">
+        <v>1.4879857649071643E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>45845</v>
       </c>
@@ -5153,8 +5453,14 @@
       <c r="AG68">
         <v>7134.1</v>
       </c>
-    </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ68">
+        <v>1.6227746836352943E-2</v>
+      </c>
+      <c r="AK68">
+        <v>1.4865370039311333E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>45846</v>
       </c>
@@ -5236,8 +5542,14 @@
       <c r="AG69">
         <v>7040.1</v>
       </c>
-    </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ69">
+        <v>1.5177130785736891E-2</v>
+      </c>
+      <c r="AK69">
+        <v>1.4656782330723627E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>45847</v>
       </c>
@@ -5319,8 +5631,14 @@
       <c r="AG70">
         <v>7040.1</v>
       </c>
-    </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ70">
+        <v>1.5165433596717627E-2</v>
+      </c>
+      <c r="AK70">
+        <v>1.4642865712143849E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>45848</v>
       </c>
@@ -5402,8 +5720,14 @@
       <c r="AG71">
         <v>7040.1</v>
       </c>
-    </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ71">
+        <v>1.5159599146330147E-2</v>
+      </c>
+      <c r="AK71">
+        <v>1.4630087694778245E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>45849</v>
       </c>
@@ -5485,8 +5809,14 @@
       <c r="AG72">
         <v>6942</v>
       </c>
-    </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ72">
+        <v>1.5843091418574907E-2</v>
+      </c>
+      <c r="AK72">
+        <v>1.4797959310104306E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>45852</v>
       </c>
@@ -5568,8 +5898,14 @@
       <c r="AG73">
         <v>6942</v>
       </c>
-    </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ73">
+        <v>1.5837285052184479E-2</v>
+      </c>
+      <c r="AK73">
+        <v>1.4868131221431454E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>45853</v>
       </c>
@@ -5651,8 +5987,14 @@
       <c r="AG74">
         <v>7040.1</v>
       </c>
-    </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ74">
+        <v>1.583147868579405E-2</v>
+      </c>
+      <c r="AK74">
+        <v>1.4938303132758599E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>45854</v>
       </c>
@@ -5734,8 +6076,14 @@
       <c r="AG75">
         <v>6942</v>
       </c>
-    </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ75">
+        <v>1.444545184235874E-2</v>
+      </c>
+      <c r="AK75">
+        <v>1.4751524697499263E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>45855</v>
       </c>
@@ -5817,8 +6165,14 @@
       <c r="AG76">
         <v>6942</v>
       </c>
-    </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ76">
+        <v>1.5478564337565099E-2</v>
+      </c>
+      <c r="AK76">
+        <v>1.5306497093626895E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>45856</v>
       </c>
@@ -5900,8 +6254,14 @@
       <c r="AG77">
         <v>6852.875</v>
       </c>
-    </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ77">
+        <v>1.547275797117467E-2</v>
+      </c>
+      <c r="AK77">
+        <v>1.5294063756297131E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>45859</v>
       </c>
@@ -5983,8 +6343,14 @@
       <c r="AG78">
         <v>6737.7350000000006</v>
       </c>
-    </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ78">
+        <v>1.5120652296391071E-2</v>
+      </c>
+      <c r="AK78">
+        <v>1.5396885406752499E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>45860</v>
       </c>
@@ -6066,8 +6432,14 @@
       <c r="AG79">
         <v>6737.7350000000006</v>
       </c>
-    </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ79">
+        <v>1.4705192996343319E-2</v>
+      </c>
+      <c r="AK79">
+        <v>1.5285812067217989E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>45862</v>
       </c>
@@ -6149,8 +6521,14 @@
       <c r="AG80">
         <v>6737.7350000000006</v>
       </c>
-    </row>
-    <row r="81" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ80">
+        <v>1.4566573306863839E-2</v>
+      </c>
+      <c r="AK80">
+        <v>1.5486632650774795E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>45863</v>
       </c>
@@ -6232,8 +6610,14 @@
       <c r="AG81">
         <v>6737.7350000000006</v>
       </c>
-    </row>
-    <row r="82" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ81">
+        <v>1.4427953617384359E-2</v>
+      </c>
+      <c r="AK81">
+        <v>1.562215967188898E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>45868</v>
       </c>
@@ -6315,8 +6699,14 @@
       <c r="AG82">
         <v>6737.7350000000006</v>
       </c>
-    </row>
-    <row r="83" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ82">
+        <v>1.580817409442924E-2</v>
+      </c>
+      <c r="AK82">
+        <v>1.5790031287215039E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>45869</v>
       </c>
@@ -6398,8 +6788,14 @@
       <c r="AG83">
         <v>6852.875</v>
       </c>
-    </row>
-    <row r="84" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ83">
+        <v>1.5808174094429236E-2</v>
+      </c>
+      <c r="AK83">
+        <v>1.5957902902541104E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>45870</v>
       </c>
@@ -6481,8 +6877,14 @@
       <c r="AG84">
         <v>6737.7350000000006</v>
       </c>
-    </row>
-    <row r="85" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ84">
+        <v>1.5531068035681342E-2</v>
+      </c>
+      <c r="AK84">
+        <v>1.5884180557412367E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>45873</v>
       </c>
@@ -6564,8 +6966,14 @@
       <c r="AG85">
         <v>6737.7350000000006</v>
       </c>
-    </row>
-    <row r="86" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ85">
+        <v>1.5531068035681344E-2</v>
+      </c>
+      <c r="AK85">
+        <v>1.5794033875939532E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>45874</v>
       </c>
@@ -6647,8 +7055,14 @@
       <c r="AG86">
         <v>6808.45</v>
       </c>
-    </row>
-    <row r="87" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ86">
+        <v>1.4566306858684217E-2</v>
+      </c>
+      <c r="AK86">
+        <v>1.5465142328948252E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>45876</v>
       </c>
@@ -6730,8 +7144,14 @@
       <c r="AG87">
         <v>6808.45</v>
       </c>
-    </row>
-    <row r="88" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ87">
+        <v>1.3665241677963911E-2</v>
+      </c>
+      <c r="AK87">
+        <v>1.5212926164859385E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>45877</v>
       </c>
@@ -6813,8 +7233,14 @@
       <c r="AG88">
         <v>6852.875</v>
       </c>
-    </row>
-    <row r="89" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ88">
+        <v>1.316330686108603E-2</v>
+      </c>
+      <c r="AK88">
+        <v>1.5055235279636399E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>45880</v>
       </c>
@@ -6896,8 +7322,14 @@
       <c r="AG89">
         <v>6942</v>
       </c>
-    </row>
-    <row r="90" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ89">
+        <v>1.132469601043338E-2</v>
+      </c>
+      <c r="AK89">
+        <v>1.4617997914077845E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>45881</v>
       </c>
@@ -6979,8 +7411,14 @@
       <c r="AG90">
         <v>6852.875</v>
       </c>
-    </row>
-    <row r="91" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ90">
+        <v>9.4845828852969209E-3</v>
+      </c>
+      <c r="AK90">
+        <v>1.4190095959497039E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>45882</v>
       </c>
@@ -7062,8 +7500,14 @@
       <c r="AG91">
         <v>6808.45</v>
       </c>
-    </row>
-    <row r="92" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ91">
+        <v>7.9210412158857331E-3</v>
+      </c>
+      <c r="AK91">
+        <v>1.3752383322520319E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>45883</v>
       </c>
@@ -7145,8 +7589,14 @@
       <c r="AG92">
         <v>6808.45</v>
       </c>
-    </row>
-    <row r="93" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ92">
+        <v>6.3981638110704245E-3</v>
+      </c>
+      <c r="AK92">
+        <v>1.3312157926509414E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>45884</v>
       </c>
@@ -7228,8 +7678,14 @@
       <c r="AG93">
         <v>6737.4349999999995</v>
       </c>
-    </row>
-    <row r="94" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ93">
+        <v>5.9097137539610833E-3</v>
+      </c>
+      <c r="AK93">
+        <v>1.2872050638944501E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>45887</v>
       </c>
@@ -7311,8 +7767,17 @@
       <c r="AG94">
         <v>6652.2350000000006</v>
       </c>
-    </row>
-    <row r="95" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ94">
+        <v>5.8903686502068441E-3</v>
+      </c>
+      <c r="AK94">
+        <v>1.2622227454440383E-2</v>
+      </c>
+      <c r="AL94">
+        <v>1.2389396696167277E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>45888</v>
       </c>
@@ -7394,8 +7859,17 @@
       <c r="AG95">
         <v>6652.2350000000006</v>
       </c>
-    </row>
-    <row r="96" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ95">
+        <v>4.9335731991033971E-3</v>
+      </c>
+      <c r="AK95">
+        <v>1.2408993994556639E-2</v>
+      </c>
+      <c r="AL95">
+        <v>1.2392185631623644E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>45889</v>
       </c>
@@ -7477,8 +7951,17 @@
       <c r="AG96">
         <v>6652.2350000000006</v>
       </c>
-    </row>
-    <row r="97" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ96">
+        <v>6.266585865333971E-3</v>
+      </c>
+      <c r="AK96">
+        <v>1.2289666266033721E-2</v>
+      </c>
+      <c r="AL96">
+        <v>1.2480416987937636E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>45890</v>
       </c>
@@ -7560,8 +8043,17 @@
       <c r="AG97">
         <v>6652.2350000000006</v>
       </c>
-    </row>
-    <row r="98" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ97">
+        <v>8.0161941975284319E-3</v>
+      </c>
+      <c r="AK97">
+        <v>1.2267193662189488E-2</v>
+      </c>
+      <c r="AL97">
+        <v>1.2626011664936673E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>45891</v>
       </c>
@@ -7643,8 +8135,17 @@
       <c r="AG98">
         <v>6652.2350000000006</v>
       </c>
-    </row>
-    <row r="99" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ98">
+        <v>9.2899040857805336E-3</v>
+      </c>
+      <c r="AK98">
+        <v>1.2133553347386757E-2</v>
+      </c>
+      <c r="AL98">
+        <v>1.2725704522742009E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>45894</v>
       </c>
@@ -7726,8 +8227,17 @@
       <c r="AG99">
         <v>6611.125</v>
       </c>
-    </row>
-    <row r="100" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ99">
+        <v>1.0100050825034988E-2</v>
+      </c>
+      <c r="AK99">
+        <v>1.2127505935678969E-2</v>
+      </c>
+      <c r="AL99">
+        <v>1.2745467275066886E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>45895</v>
       </c>
@@ -7809,8 +8319,17 @@
       <c r="AG100">
         <v>6625.6100000000006</v>
       </c>
-    </row>
-    <row r="101" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ100">
+        <v>1.1463123174767132E-2</v>
+      </c>
+      <c r="AK100">
+        <v>1.2008178207156051E-2</v>
+      </c>
+      <c r="AL100">
+        <v>1.2849459691356849E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>45896</v>
       </c>
@@ -7892,8 +8411,17 @@
       <c r="AG101">
         <v>6737.4349999999995</v>
       </c>
-    </row>
-    <row r="102" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ101">
+        <v>1.0790861763846546E-2</v>
+      </c>
+      <c r="AK101">
+        <v>1.1602855398527541E-2</v>
+      </c>
+      <c r="AL101">
+        <v>1.2803520837368297E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>45897</v>
       </c>
@@ -7975,8 +8503,17 @@
       <c r="AG102">
         <v>6737.4349999999995</v>
       </c>
-    </row>
-    <row r="103" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ102">
+        <v>1.1050246401005725E-2</v>
+      </c>
+      <c r="AK102">
+        <v>1.1290663490457162E-2</v>
+      </c>
+      <c r="AL102">
+        <v>1.2837301505584918E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>45898</v>
       </c>
@@ -8058,8 +8595,17 @@
       <c r="AG103">
         <v>6737.4349999999995</v>
       </c>
-    </row>
-    <row r="104" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ103">
+        <v>1.0231356798846149E-2</v>
+      </c>
+      <c r="AK103">
+        <v>1.0981616340254775E-2</v>
+      </c>
+      <c r="AL103">
+        <v>1.2850269074628407E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>45901</v>
       </c>
@@ -8141,8 +8687,17 @@
       <c r="AG104">
         <v>6737.4349999999995</v>
       </c>
-    </row>
-    <row r="105" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ104">
+        <v>9.6643108420358115E-3</v>
+      </c>
+      <c r="AK104">
+        <v>1.0828187831979228E-2</v>
+      </c>
+      <c r="AL104">
+        <v>1.279384542900831E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>45902</v>
       </c>
@@ -8224,8 +8779,17 @@
       <c r="AG105">
         <v>6808.45</v>
       </c>
-    </row>
-    <row r="106" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ105">
+        <v>9.165891436181824E-3</v>
+      </c>
+      <c r="AK105">
+        <v>1.0901655919278809E-2</v>
+      </c>
+      <c r="AL105">
+        <v>1.2705798712638598E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>45903</v>
       </c>
@@ -8307,8 +8871,17 @@
       <c r="AG106">
         <v>6808.45</v>
       </c>
-    </row>
-    <row r="107" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ106">
+        <v>7.8857432615003914E-3</v>
+      </c>
+      <c r="AK106">
+        <v>1.0355847684597203E-2</v>
+      </c>
+      <c r="AL106">
+        <v>1.264537199032882E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>45904</v>
       </c>
@@ -8390,8 +8963,17 @@
       <c r="AG107">
         <v>6852.875</v>
       </c>
-    </row>
-    <row r="108" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ107">
+        <v>7.7341483680863007E-3</v>
+      </c>
+      <c r="AK107">
+        <v>1.0202502633102097E-2</v>
+      </c>
+      <c r="AL107">
+        <v>1.2699244732560462E-2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>45905</v>
       </c>
@@ -8473,8 +9055,17 @@
       <c r="AG108">
         <v>6942</v>
       </c>
-    </row>
-    <row r="109" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ108">
+        <v>8.9419400555029484E-3</v>
+      </c>
+      <c r="AK108">
+        <v>1.0161155875653645E-2</v>
+      </c>
+      <c r="AL108">
+        <v>1.2763515848821521E-2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>45908</v>
       </c>
@@ -8556,8 +9147,17 @@
       <c r="AG109">
         <v>6942</v>
       </c>
-    </row>
-    <row r="110" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ109">
+        <v>1.0013348422434657E-2</v>
+      </c>
+      <c r="AK109">
+        <v>1.0195899756545137E-2</v>
+      </c>
+      <c r="AL109">
+        <v>1.2776035248228042E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>45909</v>
       </c>
@@ -8639,8 +9239,17 @@
       <c r="AG110">
         <v>6991.5</v>
       </c>
-    </row>
-    <row r="111" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ110">
+        <v>9.3295830943178649E-3</v>
+      </c>
+      <c r="AK110">
+        <v>9.7596519573273765E-3</v>
+      </c>
+      <c r="AL110">
+        <v>1.265862393464834E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>45910</v>
       </c>
@@ -8722,8 +9331,17 @@
       <c r="AG111">
         <v>7008.5</v>
       </c>
-    </row>
-    <row r="112" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ111">
+        <v>8.9142618553228348E-3</v>
+      </c>
+      <c r="AK111">
+        <v>9.5416597541648721E-3</v>
+      </c>
+      <c r="AL111">
+        <v>1.2651810816919216E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>45911</v>
       </c>
@@ -8805,8 +9423,17 @@
       <c r="AG112">
         <v>7008.5</v>
       </c>
-    </row>
-    <row r="113" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ112">
+        <v>9.0367168148580406E-3</v>
+      </c>
+      <c r="AK112">
+        <v>9.3216492207121963E-3</v>
+      </c>
+      <c r="AL112">
+        <v>1.2573288375180021E-2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>45912</v>
       </c>
@@ -8888,8 +9515,17 @@
       <c r="AG113">
         <v>7008.5</v>
       </c>
-    </row>
-    <row r="114" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ113">
+        <v>1.0295591961486605E-2</v>
+      </c>
+      <c r="AK113">
+        <v>9.0695785202439243E-3</v>
+      </c>
+      <c r="AL113">
+        <v>1.2500785868379343E-2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>45915</v>
       </c>
@@ -8971,8 +9607,17 @@
       <c r="AG114">
         <v>7066.25</v>
       </c>
-    </row>
-    <row r="115" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ114">
+        <v>9.7370737626292676E-3</v>
+      </c>
+      <c r="AK114">
+        <v>8.8505706360566105E-3</v>
+      </c>
+      <c r="AL114">
+        <v>1.2456753314420947E-2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>45916</v>
       </c>
@@ -9054,8 +9699,17 @@
       <c r="AG115">
         <v>7008.5</v>
       </c>
-    </row>
-    <row r="116" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ115">
+        <v>9.1284545099422146E-3</v>
+      </c>
+      <c r="AK115">
+        <v>8.6878860983720732E-3</v>
+      </c>
+      <c r="AL115">
+        <v>1.241080018204806E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>45917</v>
       </c>
@@ -9137,8 +9791,17 @@
       <c r="AG116">
         <v>7008.5</v>
       </c>
-    </row>
-    <row r="117" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ116">
+        <v>8.5198352572551615E-3</v>
+      </c>
+      <c r="AK116">
+        <v>8.5252015606875377E-3</v>
+      </c>
+      <c r="AL116">
+        <v>1.2364847049675175E-2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>45918</v>
       </c>
@@ -9220,8 +9883,17 @@
       <c r="AG117">
         <v>7066.25</v>
       </c>
-    </row>
-    <row r="118" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ117">
+        <v>7.4437661377487214E-3</v>
+      </c>
+      <c r="AK117">
+        <v>8.533973588326858E-3</v>
+      </c>
+      <c r="AL117">
+        <v>1.2381800256169931E-2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>45919</v>
       </c>
@@ -9303,8 +9975,17 @@
       <c r="AG118">
         <v>7008.5</v>
       </c>
-    </row>
-    <row r="119" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ118">
+        <v>7.4433959698396333E-3</v>
+      </c>
+      <c r="AK118">
+        <v>8.3078879587650499E-3</v>
+      </c>
+      <c r="AL118">
+        <v>1.2221006069116119E-2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>45922</v>
       </c>
@@ -9386,8 +10067,17 @@
       <c r="AG119">
         <v>7066.25</v>
       </c>
-    </row>
-    <row r="120" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ119">
+        <v>7.0410614605041517E-3</v>
+      </c>
+      <c r="AK119">
+        <v>8.1131358273624377E-3</v>
+      </c>
+      <c r="AL119">
+        <v>1.2183989511854796E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>45923</v>
       </c>
@@ -9469,8 +10159,17 @@
       <c r="AG120">
         <v>7008.5</v>
       </c>
-    </row>
-    <row r="121" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ120">
+        <v>6.5087572486470695E-3</v>
+      </c>
+      <c r="AK120">
+        <v>8.1979301762953923E-3</v>
+      </c>
+      <c r="AL120">
+        <v>1.2146972954593469E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>45924</v>
       </c>
@@ -9552,8 +10251,17 @@
       <c r="AG121">
         <v>7066.25</v>
       </c>
-    </row>
-    <row r="122" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ121">
+        <v>6.113853752571119E-3</v>
+      </c>
+      <c r="AK121">
+        <v>8.2830750559412351E-3</v>
+      </c>
+      <c r="AL121">
+        <v>1.2050206880107973E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>45925</v>
       </c>
@@ -9635,8 +10343,17 @@
       <c r="AG122">
         <v>7210.75</v>
       </c>
-    </row>
-    <row r="123" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ122">
+        <v>6.2383795898404851E-3</v>
+      </c>
+      <c r="AK122">
+        <v>8.4579495899793893E-3</v>
+      </c>
+      <c r="AL122">
+        <v>1.1961568267635236E-2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>45926</v>
       </c>
@@ -9718,8 +10435,17 @@
       <c r="AG123">
         <v>7066.25</v>
       </c>
-    </row>
-    <row r="124" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ123">
+        <v>6.7683922128763717E-3</v>
+      </c>
+      <c r="AK123">
+        <v>8.6115881877755936E-3</v>
+      </c>
+      <c r="AL123">
+        <v>1.1861050543606977E-2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>45929</v>
       </c>
@@ -9801,8 +10527,17 @@
       <c r="AG124">
         <v>7210.75</v>
       </c>
-    </row>
-    <row r="125" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ124">
+        <v>6.9002927059565551E-3</v>
+      </c>
+      <c r="AK124">
+        <v>8.7651086771258005E-3</v>
+      </c>
+      <c r="AL124">
+        <v>1.1773760710329872E-2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>45930</v>
       </c>
@@ -9884,8 +10619,17 @@
       <c r="AG125">
         <v>7417.125</v>
       </c>
-    </row>
-    <row r="126" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ125">
+        <v>7.6314825968629351E-3</v>
+      </c>
+      <c r="AK125">
+        <v>8.7141478796514717E-3</v>
+      </c>
+      <c r="AL125">
+        <v>1.1857260806127538E-2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>45931</v>
       </c>
@@ -9967,8 +10711,17 @@
       <c r="AG126">
         <v>7210.75</v>
       </c>
-    </row>
-    <row r="127" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ126">
+        <v>7.5639385290406274E-3</v>
+      </c>
+      <c r="AK126">
+        <v>8.7268877376811237E-3</v>
+      </c>
+      <c r="AL126">
+        <v>1.1870126834687213E-2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>45932</v>
       </c>
@@ -10050,8 +10803,17 @@
       <c r="AG127">
         <v>7417.125</v>
       </c>
-    </row>
-    <row r="128" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ127">
+        <v>7.8945711033201384E-3</v>
+      </c>
+      <c r="AK127">
+        <v>8.5777933984921631E-3</v>
+      </c>
+      <c r="AL127">
+        <v>1.1891930194481979E-2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>45933</v>
       </c>
@@ -10133,8 +10895,17 @@
       <c r="AG128">
         <v>7525.25</v>
       </c>
-    </row>
-    <row r="129" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ128">
+        <v>8.4214411190468765E-3</v>
+      </c>
+      <c r="AK128">
+        <v>8.3776326709622036E-3</v>
+      </c>
+      <c r="AL128">
+        <v>1.1841561327407778E-2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>45936</v>
       </c>
@@ -10216,8 +10987,17 @@
       <c r="AG129">
         <v>7525.25</v>
       </c>
-    </row>
-    <row r="130" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ129">
+        <v>8.1032612725366517E-3</v>
+      </c>
+      <c r="AK129">
+        <v>8.1810662668891487E-3</v>
+      </c>
+      <c r="AL129">
+        <v>1.172666321786241E-2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>45937</v>
       </c>
@@ -10299,8 +11079,17 @@
       <c r="AG130">
         <v>7525.25</v>
       </c>
-    </row>
-    <row r="131" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ130">
+        <v>7.9046215663984669E-3</v>
+      </c>
+      <c r="AK130">
+        <v>8.0993213607604038E-3</v>
+      </c>
+      <c r="AL130">
+        <v>1.1627869875721E-2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>45939</v>
       </c>
@@ -10382,8 +11171,17 @@
       <c r="AG131">
         <v>7525.25</v>
       </c>
-    </row>
-    <row r="132" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ131">
+        <v>7.9707732223913124E-3</v>
+      </c>
+      <c r="AK131">
+        <v>7.9502270215714415E-3</v>
+      </c>
+      <c r="AL131">
+        <v>1.1533756980290447E-2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>45940</v>
       </c>
@@ -10465,8 +11263,17 @@
       <c r="AG132">
         <v>7525.25</v>
       </c>
-    </row>
-    <row r="133" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ132">
+        <v>7.5735565276629823E-3</v>
+      </c>
+      <c r="AK132">
+        <v>7.9634433245419703E-3</v>
+      </c>
+      <c r="AL132">
+        <v>1.1398795472615918E-2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>45943</v>
       </c>
@@ -10548,8 +11355,17 @@
       <c r="AG133">
         <v>7619.625</v>
       </c>
-    </row>
-    <row r="134" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ133">
+        <v>7.9128572146411336E-3</v>
+      </c>
+      <c r="AK133">
+        <v>7.99483026086272E-3</v>
+      </c>
+      <c r="AL133">
+        <v>1.1361151020474728E-2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>45944</v>
       </c>
@@ -10631,8 +11447,17 @@
       <c r="AG134">
         <v>7618.625</v>
       </c>
-    </row>
-    <row r="135" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ134">
+        <v>7.7197822068026953E-3</v>
+      </c>
+      <c r="AK134">
+        <v>7.9917593270153586E-3</v>
+      </c>
+      <c r="AL134">
+        <v>1.128050229623386E-2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>45945</v>
       </c>
@@ -10714,8 +11539,17 @@
       <c r="AG135">
         <v>7720</v>
       </c>
-    </row>
-    <row r="136" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ135">
+        <v>6.9292486508877498E-3</v>
+      </c>
+      <c r="AK135">
+        <v>7.7394514930276583E-3</v>
+      </c>
+      <c r="AL135">
+        <v>1.1168647485921827E-2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>45946</v>
       </c>
@@ -10797,8 +11631,17 @@
       <c r="AG136">
         <v>7720</v>
       </c>
-    </row>
-    <row r="137" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ136">
+        <v>6.5997438985510599E-3</v>
+      </c>
+      <c r="AK136">
+        <v>7.582298508108638E-3</v>
+      </c>
+      <c r="AL136">
+        <v>1.10784930416289E-2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>45947</v>
       </c>
@@ -10880,8 +11723,17 @@
       <c r="AG137">
         <v>7720</v>
       </c>
-    </row>
-    <row r="138" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ137">
+        <v>6.8000547923311025E-3</v>
+      </c>
+      <c r="AK137">
+        <v>7.8459940512875699E-3</v>
+      </c>
+      <c r="AL137">
+        <v>1.1169446276503887E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>45950</v>
       </c>
@@ -10963,8 +11815,17 @@
       <c r="AG138">
         <v>7720</v>
       </c>
-    </row>
-    <row r="139" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ138">
+        <v>6.6020026432580701E-3</v>
+      </c>
+      <c r="AK138">
+        <v>7.6860596857781906E-3</v>
+      </c>
+      <c r="AL138">
+        <v>1.106087535839247E-2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>45951</v>
       </c>
@@ -11046,8 +11907,17 @@
       <c r="AG139">
         <v>7720</v>
       </c>
-    </row>
-    <row r="140" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ139">
+        <v>6.5297620957607974E-3</v>
+      </c>
+      <c r="AK139">
+        <v>7.4006018006021372E-3</v>
+      </c>
+      <c r="AL139">
+        <v>1.098621436100276E-2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>45952</v>
       </c>
@@ -11129,8 +11999,17 @@
       <c r="AG140">
         <v>7720</v>
       </c>
-    </row>
-    <row r="141" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ140">
+        <v>6.1908635443669929E-3</v>
+      </c>
+      <c r="AK140">
+        <v>7.1029171226469311E-3</v>
+      </c>
+      <c r="AL140">
+        <v>1.0861542982136686E-2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>45953</v>
       </c>
@@ -11212,8 +12091,17 @@
       <c r="AG141">
         <v>7876</v>
       </c>
-    </row>
-    <row r="142" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ141">
+        <v>6.0515737001560436E-3</v>
+      </c>
+      <c r="AK141">
+        <v>7.2268904683776012E-3</v>
+      </c>
+      <c r="AL141">
+        <v>1.0824391692159928E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>45954</v>
       </c>
@@ -11295,8 +12183,17 @@
       <c r="AG142">
         <v>7900.5</v>
       </c>
-    </row>
-    <row r="143" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ142">
+        <v>6.5791621319972442E-3</v>
+      </c>
+      <c r="AK142">
+        <v>7.1945948909183516E-3</v>
+      </c>
+      <c r="AL142">
+        <v>1.0786138105657404E-2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>45957</v>
       </c>
@@ -11378,8 +12275,17 @@
       <c r="AG143">
         <v>7900.5</v>
       </c>
-    </row>
-    <row r="144" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ143">
+        <v>6.8402296692943705E-3</v>
+      </c>
+      <c r="AK143">
+        <v>7.0697848408104473E-3</v>
+      </c>
+      <c r="AL143">
+        <v>1.0727155116245893E-2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>45958</v>
       </c>
@@ -11461,8 +12367,17 @@
       <c r="AG144">
         <v>8071.1</v>
       </c>
-    </row>
-    <row r="145" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ144">
+        <v>7.1009475790925853E-3</v>
+      </c>
+      <c r="AK144">
+        <v>7.1005770287289639E-3</v>
+      </c>
+      <c r="AL144">
+        <v>1.0709352817171329E-2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>45959</v>
       </c>
@@ -11544,8 +12459,17 @@
       <c r="AG145">
         <v>8071.1</v>
       </c>
-    </row>
-    <row r="146" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ145">
+        <v>6.9657711509950229E-3</v>
+      </c>
+      <c r="AK145">
+        <v>7.0394224097301995E-3</v>
+      </c>
+      <c r="AL145">
+        <v>1.0591391201066393E-2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>45960</v>
       </c>
@@ -11627,8 +12551,17 @@
       <c r="AG146">
         <v>8071.1</v>
       </c>
-    </row>
-    <row r="147" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ146">
+        <v>7.3680578072202211E-3</v>
+      </c>
+      <c r="AK146">
+        <v>7.1318537289273166E-3</v>
+      </c>
+      <c r="AL146">
+        <v>1.0483696388518126E-2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>45961</v>
       </c>
@@ -11710,8 +12643,17 @@
       <c r="AG147">
         <v>8131</v>
       </c>
-    </row>
-    <row r="148" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ147">
+        <v>7.5579636259565791E-3</v>
+      </c>
+      <c r="AK147">
+        <v>7.1295632032287639E-3</v>
+      </c>
+      <c r="AL147">
+        <v>1.0376226373501289E-2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>45964</v>
       </c>
@@ -11793,8 +12735,17 @@
       <c r="AG148">
         <v>8131</v>
       </c>
-    </row>
-    <row r="149" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ148">
+        <v>7.7465477966520962E-3</v>
+      </c>
+      <c r="AK148">
+        <v>7.2976258946338421E-3</v>
+      </c>
+      <c r="AL148">
+        <v>1.0272813339419424E-2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>45965</v>
       </c>
@@ -11876,8 +12827,17 @@
       <c r="AG149">
         <v>8131</v>
       </c>
-    </row>
-    <row r="150" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ149">
+        <v>6.8129734725757901E-3</v>
+      </c>
+      <c r="AK149">
+        <v>7.1413743604017343E-3</v>
+      </c>
+      <c r="AL149">
+        <v>1.0103248489133522E-2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>45966</v>
       </c>
@@ -11959,8 +12919,17 @@
       <c r="AG150">
         <v>8131</v>
       </c>
-    </row>
-    <row r="151" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ150">
+        <v>7.4596673568178293E-3</v>
+      </c>
+      <c r="AK150">
+        <v>7.29166386605029E-3</v>
+      </c>
+      <c r="AL150">
+        <v>1.0035863985474508E-2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>45967</v>
       </c>
@@ -12042,8 +13011,17 @@
       <c r="AG151">
         <v>8213.2000000000007</v>
       </c>
-    </row>
-    <row r="152" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ151">
+        <v>6.9259066716819374E-3</v>
+      </c>
+      <c r="AK151">
+        <v>7.2900560431881541E-3</v>
+      </c>
+      <c r="AL151">
+        <v>9.9210756862088099E-3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>45968</v>
       </c>
@@ -12125,8 +13103,17 @@
       <c r="AG152">
         <v>8213.2000000000007</v>
       </c>
-    </row>
-    <row r="153" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ152">
+        <v>7.0541924526271466E-3</v>
+      </c>
+      <c r="AK152">
+        <v>7.2297787443804202E-3</v>
+      </c>
+      <c r="AL152">
+        <v>9.8133705522933743E-3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>45971</v>
       </c>
@@ -12208,8 +13195,17 @@
       <c r="AG153">
         <v>8318.7999999999993</v>
       </c>
-    </row>
-    <row r="154" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ153">
+        <v>6.7835098764939894E-3</v>
+      </c>
+      <c r="AK153">
+        <v>7.1353811837714274E-3</v>
+      </c>
+      <c r="AL153">
+        <v>9.6863757660188097E-3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>45972</v>
       </c>
@@ -12291,8 +13287,17 @@
       <c r="AG154">
         <v>8397.2999999999993</v>
       </c>
-    </row>
-    <row r="155" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ154">
+        <v>6.3890618541516788E-3</v>
+      </c>
+      <c r="AK154">
+        <v>7.0102760044742926E-3</v>
+      </c>
+      <c r="AL154">
+        <v>9.5491451068481972E-3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>45973</v>
       </c>
@@ -12374,8 +13379,17 @@
       <c r="AG155">
         <v>8397.2999999999993</v>
       </c>
-    </row>
-    <row r="156" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ155">
+        <v>6.3269226393274786E-3</v>
+      </c>
+      <c r="AK155">
+        <v>6.993228571208902E-3</v>
+      </c>
+      <c r="AL155">
+        <v>9.443201301766917E-3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>45974</v>
       </c>
@@ -12457,8 +13471,17 @@
       <c r="AG156">
         <v>8397.2999999999993</v>
       </c>
-    </row>
-    <row r="157" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ156">
+        <v>6.784393590416592E-3</v>
+      </c>
+      <c r="AK156">
+        <v>6.9594805413894607E-3</v>
+      </c>
+      <c r="AL156">
+        <v>9.3651207578757407E-3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>45975</v>
       </c>
@@ -12540,8 +13563,17 @@
       <c r="AG157">
         <v>8451.2000000000007</v>
       </c>
-    </row>
-    <row r="158" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ157">
+        <v>5.405581445581625E-3</v>
+      </c>
+      <c r="AK157">
+        <v>6.7108996125779695E-3</v>
+      </c>
+      <c r="AL157">
+        <v>9.1927864257012847E-3</v>
+      </c>
+    </row>
+    <row r="158" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>45978</v>
       </c>
@@ -12623,8 +13655,17 @@
       <c r="AG158">
         <v>8451.2000000000007</v>
       </c>
-    </row>
-    <row r="159" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ158">
+        <v>4.5464855771645577E-3</v>
+      </c>
+      <c r="AK158">
+        <v>6.3858997500822806E-3</v>
+      </c>
+      <c r="AL158">
+        <v>9.0102420277446572E-3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>45979</v>
       </c>
@@ -12706,8 +13747,17 @@
       <c r="AG159">
         <v>8522.9</v>
       </c>
-    </row>
-    <row r="160" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ159">
+        <v>4.8059191228964236E-3</v>
+      </c>
+      <c r="AK159">
+        <v>6.4603989094643658E-3</v>
+      </c>
+      <c r="AL159">
+        <v>8.9250061745800892E-3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>45980</v>
       </c>
@@ -12789,8 +13839,17 @@
       <c r="AG160">
         <v>8482.9</v>
       </c>
-    </row>
-    <row r="161" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ160">
+        <v>4.6581153757803391E-3</v>
+      </c>
+      <c r="AK160">
+        <v>6.377863072627196E-3</v>
+      </c>
+      <c r="AL160">
+        <v>8.8682301230221892E-3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>45981</v>
       </c>
@@ -12872,8 +13931,17 @@
       <c r="AG161">
         <v>8482.9</v>
       </c>
-    </row>
-    <row r="162" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ161">
+        <v>4.011420968309312E-3</v>
+      </c>
+      <c r="AK161">
+        <v>6.0864271451884907E-3</v>
+      </c>
+      <c r="AL161">
+        <v>8.6816107913053261E-3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>45982</v>
       </c>
@@ -12955,8 +14023,17 @@
       <c r="AG162">
         <v>8482.9</v>
       </c>
-    </row>
-    <row r="163" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ162">
+        <v>3.2175398181855212E-3</v>
+      </c>
+      <c r="AK162">
+        <v>5.9768246723308268E-3</v>
+      </c>
+      <c r="AL162">
+        <v>8.5143744651334455E-3</v>
+      </c>
+    </row>
+    <row r="163" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>45985</v>
       </c>
@@ -13038,8 +14115,17 @@
       <c r="AG163">
         <v>8542</v>
       </c>
-    </row>
-    <row r="164" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ163">
+        <v>2.8911904483218077E-3</v>
+      </c>
+      <c r="AK163">
+        <v>5.7877582959149493E-3</v>
+      </c>
+      <c r="AL163">
+        <v>8.3577506824116105E-3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>45986</v>
       </c>
@@ -13121,8 +14207,17 @@
       <c r="AG164">
         <v>8542</v>
       </c>
-    </row>
-    <row r="165" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ164">
+        <v>2.9562552793825033E-3</v>
+      </c>
+      <c r="AK164">
+        <v>5.5994099961799255E-3</v>
+      </c>
+      <c r="AL164">
+        <v>8.1909285544833534E-3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>45987</v>
       </c>
@@ -13204,8 +14299,17 @@
       <c r="AG165">
         <v>8542</v>
       </c>
-    </row>
-    <row r="166" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ165">
+        <v>3.1399437069873398E-3</v>
+      </c>
+      <c r="AK165">
+        <v>5.5017285965055186E-3</v>
+      </c>
+      <c r="AL165">
+        <v>8.023122640504133E-3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>45988</v>
       </c>
@@ -13287,8 +14391,17 @@
       <c r="AG166">
         <v>8542</v>
       </c>
-    </row>
-    <row r="167" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ166">
+        <v>2.7263289044988084E-3</v>
+      </c>
+      <c r="AK166">
+        <v>5.5566020775188411E-3</v>
+      </c>
+      <c r="AL166">
+        <v>8.0135188349687615E-3</v>
+      </c>
+    </row>
+    <row r="167" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>45989</v>
       </c>
@@ -13370,8 +14483,17 @@
       <c r="AG167">
         <v>8652.85</v>
       </c>
-    </row>
-    <row r="168" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ167">
+        <v>2.4084662952420619E-3</v>
+      </c>
+      <c r="AK167">
+        <v>5.3531590899730868E-3</v>
+      </c>
+      <c r="AL167">
+        <v>7.8516669419526185E-3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>45992</v>
       </c>
@@ -13453,8 +14575,17 @@
       <c r="AG168">
         <v>8652.85</v>
       </c>
-    </row>
-    <row r="169" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ168">
+        <v>2.7861664838321277E-3</v>
+      </c>
+      <c r="AK168">
+        <v>5.1960653746557723E-3</v>
+      </c>
+      <c r="AL168">
+        <v>7.6948758978453513E-3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>45993</v>
       </c>
@@ -13536,8 +14667,17 @@
       <c r="AG169">
         <v>8652.85</v>
       </c>
-    </row>
-    <row r="170" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ169">
+        <v>2.9146566011295999E-3</v>
+      </c>
+      <c r="AK169">
+        <v>5.1333000569168813E-3</v>
+      </c>
+      <c r="AL169">
+        <v>7.5650192443908852E-3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>45994</v>
       </c>
@@ -13619,8 +14759,17 @@
       <c r="AG170">
         <v>8730</v>
       </c>
-    </row>
-    <row r="171" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ170">
+        <v>2.7816286836834436E-3</v>
+      </c>
+      <c r="AK170">
+        <v>4.9922701617554546E-3</v>
+      </c>
+      <c r="AL170">
+        <v>7.4303623469825046E-3</v>
+      </c>
+    </row>
+    <row r="171" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>45995</v>
       </c>
@@ -13702,8 +14851,17 @@
       <c r="AG171">
         <v>8730</v>
       </c>
-    </row>
-    <row r="172" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ171">
+        <v>3.8208126201942387E-3</v>
+      </c>
+      <c r="AK171">
+        <v>5.0788990775221705E-3</v>
+      </c>
+      <c r="AL171">
+        <v>7.355147167742381E-3</v>
+      </c>
+    </row>
+    <row r="172" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>45996</v>
       </c>
@@ -13785,8 +14943,17 @@
       <c r="AG172">
         <v>8730</v>
       </c>
-    </row>
-    <row r="173" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ172">
+        <v>6.4511176333819382E-3</v>
+      </c>
+      <c r="AK172">
+        <v>5.4718515468286134E-3</v>
+      </c>
+      <c r="AL172">
+        <v>7.4027020639706098E-3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>46001</v>
       </c>
@@ -13868,8 +15035,17 @@
       <c r="AG173">
         <v>8730</v>
       </c>
-    </row>
-    <row r="174" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ173">
+        <v>8.4856845068368558E-3</v>
+      </c>
+      <c r="AK173">
+        <v>5.9405415396120874E-3</v>
+      </c>
+      <c r="AL173">
+        <v>7.4439918670449077E-3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>46002</v>
       </c>
@@ -13951,8 +15127,17 @@
       <c r="AG174">
         <v>8542</v>
       </c>
-    </row>
-    <row r="175" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ174">
+        <v>1.0722358509774771E-2</v>
+      </c>
+      <c r="AK174">
+        <v>6.1981549737989321E-3</v>
+      </c>
+      <c r="AL174">
+        <v>7.4561035075906036E-3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>46003</v>
       </c>
@@ -14034,8 +15219,17 @@
       <c r="AG175">
         <v>8730</v>
       </c>
-    </row>
-    <row r="176" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AJ175">
+        <v>1.1881491577190735E-2</v>
+      </c>
+      <c r="AK175">
+        <v>6.3430668074347715E-3</v>
+      </c>
+      <c r="AL175">
+        <v>7.4110199510738582E-3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>46006</v>
       </c>
@@ -14117,8 +15311,17 @@
       <c r="AG176">
         <v>8885.9</v>
       </c>
-    </row>
-    <row r="177" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ176">
+        <v>1.2522097076379749E-2</v>
+      </c>
+      <c r="AK176">
+        <v>6.3359092197207709E-3</v>
+      </c>
+      <c r="AL176">
+        <v>7.3309881697785385E-3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>46007</v>
       </c>
@@ -14200,8 +15403,17 @@
       <c r="AG177">
         <v>9733.4</v>
       </c>
-    </row>
-    <row r="178" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ177">
+        <v>1.2390878602130747E-2</v>
+      </c>
+      <c r="AK177">
+        <v>6.1199503228627624E-3</v>
+      </c>
+      <c r="AL177">
+        <v>7.2611623714727907E-3</v>
+      </c>
+    </row>
+    <row r="178" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>46008</v>
       </c>
@@ -14283,8 +15495,17 @@
       <c r="AG178">
         <v>10623.9</v>
       </c>
-    </row>
-    <row r="179" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ178">
+        <v>1.1475738272607587E-2</v>
+      </c>
+      <c r="AK178">
+        <v>5.9490435219117866E-3</v>
+      </c>
+      <c r="AL178">
+        <v>7.1848524584368894E-3</v>
+      </c>
+    </row>
+    <row r="179" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>46009</v>
       </c>
@@ -14366,8 +15587,17 @@
       <c r="AG179">
         <v>10623.9</v>
       </c>
-    </row>
-    <row r="180" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ179">
+        <v>9.4958841091028114E-3</v>
+      </c>
+      <c r="AK179">
+        <v>6.0978640286849196E-3</v>
+      </c>
+      <c r="AL179">
+        <v>7.1174580721496935E-3</v>
+      </c>
+    </row>
+    <row r="180" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>46010</v>
       </c>
@@ -14452,8 +15682,17 @@
       <c r="AH180">
         <v>8081.85</v>
       </c>
-    </row>
-    <row r="181" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ180">
+        <v>7.3311734194732884E-3</v>
+      </c>
+      <c r="AK180">
+        <v>5.9105596208983615E-3</v>
+      </c>
+      <c r="AL180">
+        <v>7.1333845544146778E-3</v>
+      </c>
+    </row>
+    <row r="181" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>46013</v>
       </c>
@@ -14547,8 +15786,17 @@
       <c r="AH181">
         <v>8131</v>
       </c>
-    </row>
-    <row r="182" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ181">
+        <v>5.2844432155172089E-3</v>
+      </c>
+      <c r="AK181">
+        <v>5.8151468340271618E-3</v>
+      </c>
+      <c r="AL181">
+        <v>7.1294259777188486E-3</v>
+      </c>
+    </row>
+    <row r="182" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>46014</v>
       </c>
@@ -14642,8 +15890,17 @@
       <c r="AH182">
         <v>8131</v>
       </c>
-    </row>
-    <row r="183" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ182">
+        <v>4.1193429112153668E-3</v>
+      </c>
+      <c r="AK182">
+        <v>5.6582685811053558E-3</v>
+      </c>
+      <c r="AL182">
+        <v>7.1153323051550534E-3</v>
+      </c>
+    </row>
+    <row r="183" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>46015</v>
       </c>
@@ -14737,8 +15994,17 @@
       <c r="AH183">
         <v>8131</v>
       </c>
-    </row>
-    <row r="184" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ183">
+        <v>4.38070821823793E-3</v>
+      </c>
+      <c r="AK183">
+        <v>5.775255499461022E-3</v>
+      </c>
+      <c r="AL183">
+        <v>7.1740749570026793E-3</v>
+      </c>
+    </row>
+    <row r="184" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>46017</v>
       </c>
@@ -14832,8 +16098,17 @@
       <c r="AH184">
         <v>8131</v>
       </c>
-    </row>
-    <row r="185" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ184">
+        <v>5.4149661787703468E-3</v>
+      </c>
+      <c r="AK184">
+        <v>5.8926613319404495E-3</v>
+      </c>
+      <c r="AL184">
+        <v>7.2226820045135122E-3</v>
+      </c>
+    </row>
+    <row r="185" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>46020</v>
       </c>
@@ -14927,8 +16202,17 @@
       <c r="AH185">
         <v>8131</v>
       </c>
-    </row>
-    <row r="186" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ185">
+        <v>5.2860925220879814E-3</v>
+      </c>
+      <c r="AK185">
+        <v>5.7061831612225684E-3</v>
+      </c>
+      <c r="AL185">
+        <v>7.1378532040276468E-3</v>
+      </c>
+    </row>
+    <row r="186" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>46021</v>
       </c>
@@ -15022,8 +16306,17 @@
       <c r="AH186">
         <v>8131</v>
       </c>
-    </row>
-    <row r="187" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ186">
+        <v>5.419732134170528E-3</v>
+      </c>
+      <c r="AK186">
+        <v>5.7794430222275033E-3</v>
+      </c>
+      <c r="AL186">
+        <v>7.1552704337660283E-3</v>
+      </c>
+    </row>
+    <row r="187" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>46022</v>
       </c>
@@ -15117,8 +16410,17 @@
       <c r="AH187">
         <v>8131</v>
       </c>
-    </row>
-    <row r="188" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ187">
+        <v>5.3046576654680599E-3</v>
+      </c>
+      <c r="AK187">
+        <v>5.8870107388718628E-3</v>
+      </c>
+      <c r="AL187">
+        <v>7.0585679166473318E-3</v>
+      </c>
+    </row>
+    <row r="188" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>46024</v>
       </c>
@@ -15212,8 +16514,17 @@
       <c r="AH188">
         <v>8131</v>
       </c>
-    </row>
-    <row r="189" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ188">
+        <v>5.3041926251095146E-3</v>
+      </c>
+      <c r="AK188">
+        <v>5.9919451452143165E-3</v>
+      </c>
+      <c r="AL188">
+        <v>6.9184925220862675E-3</v>
+      </c>
+    </row>
+    <row r="189" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>46027</v>
       </c>
@@ -15307,8 +16618,17 @@
       <c r="AH189">
         <v>8131</v>
       </c>
-    </row>
-    <row r="190" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ189">
+        <v>5.5613604206092267E-3</v>
+      </c>
+      <c r="AK189">
+        <v>5.8345382172383421E-3</v>
+      </c>
+      <c r="AL189">
+        <v>6.8253344645306194E-3</v>
+      </c>
+    </row>
+    <row r="190" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>46028</v>
       </c>
@@ -15402,8 +16722,17 @@
       <c r="AH190">
         <v>8152.4</v>
       </c>
-    </row>
-    <row r="191" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ190">
+        <v>4.9077174456081786E-3</v>
+      </c>
+      <c r="AK190">
+        <v>5.8334959824208514E-3</v>
+      </c>
+      <c r="AL190">
+        <v>6.7702268052694846E-3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>46029</v>
       </c>
@@ -15497,8 +16826,17 @@
       <c r="AH191">
         <v>8188.4250000000002</v>
       </c>
-    </row>
-    <row r="192" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ191">
+        <v>4.3838832044544862E-3</v>
+      </c>
+      <c r="AK191">
+        <v>5.97956918704099E-3</v>
+      </c>
+      <c r="AL191">
+        <v>6.6720744512669735E-3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>46030</v>
       </c>
@@ -15592,8 +16930,17 @@
       <c r="AH192">
         <v>8188.4250000000002</v>
       </c>
-    </row>
-    <row r="193" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ192">
+        <v>4.3828467008712934E-3</v>
+      </c>
+      <c r="AK192">
+        <v>5.9780881005159162E-3</v>
+      </c>
+      <c r="AL192">
+        <v>6.6394520324629036E-3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>46031</v>
       </c>
@@ -15687,8 +17034,17 @@
       <c r="AH193">
         <v>8249.2250000000004</v>
       </c>
-    </row>
-    <row r="194" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ193">
+        <v>3.4137130110900712E-3</v>
+      </c>
+      <c r="AK193">
+        <v>5.9013649535400985E-3</v>
+      </c>
+      <c r="AL193">
+        <v>6.561317836772591E-3</v>
+      </c>
+    </row>
+    <row r="194" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>46034</v>
       </c>
@@ -15782,8 +17138,17 @@
       <c r="AH194">
         <v>8318.7999999999993</v>
       </c>
-    </row>
-    <row r="195" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ194">
+        <v>3.265639352562581E-3</v>
+      </c>
+      <c r="AK194">
+        <v>5.9592003559472148E-3</v>
+      </c>
+      <c r="AL194">
+        <v>6.5167898930475008E-3</v>
+      </c>
+    </row>
+    <row r="195" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>46035</v>
       </c>
@@ -15877,8 +17242,17 @@
       <c r="AH195">
         <v>8318.7999999999993</v>
       </c>
-    </row>
-    <row r="196" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ195">
+        <v>4.0202159051553749E-3</v>
+      </c>
+      <c r="AK195">
+        <v>6.1973419914535272E-3</v>
+      </c>
+      <c r="AL195">
+        <v>6.4795073603289019E-3</v>
+      </c>
+    </row>
+    <row r="196" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>46036</v>
       </c>
@@ -15972,8 +17346,17 @@
       <c r="AH196">
         <v>8318.7999999999993</v>
       </c>
-    </row>
-    <row r="197" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ196">
+        <v>3.4423523630292851E-3</v>
+      </c>
+      <c r="AK196">
+        <v>6.0016103575621224E-3</v>
+      </c>
+      <c r="AL196">
+        <v>6.380170314396535E-3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>46037</v>
       </c>
@@ -16067,8 +17450,17 @@
       <c r="AH197">
         <v>8318.7999999999993</v>
       </c>
-    </row>
-    <row r="198" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ197">
+        <v>2.8673327178405173E-3</v>
+      </c>
+      <c r="AK197">
+        <v>5.940564814360492E-3</v>
+      </c>
+      <c r="AL197">
+        <v>6.3799059852070496E-3</v>
+      </c>
+    </row>
+    <row r="198" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>46038</v>
       </c>
@@ -16162,8 +17554,17 @@
       <c r="AH198">
         <v>8318.7999999999993</v>
       </c>
-    </row>
-    <row r="199" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ198">
+        <v>2.2538238228661184E-3</v>
+      </c>
+      <c r="AK198">
+        <v>5.8553558994822556E-3</v>
+      </c>
+      <c r="AL198">
+        <v>6.2458269866387389E-3</v>
+      </c>
+    </row>
+    <row r="199" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>46041</v>
       </c>
@@ -16257,8 +17658,17 @@
       <c r="AH199">
         <v>8367.4249999999993</v>
       </c>
-    </row>
-    <row r="200" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ199">
+        <v>3.2533002187339869E-3</v>
+      </c>
+      <c r="AK199">
+        <v>6.0571049446236066E-3</v>
+      </c>
+      <c r="AL199">
+        <v>6.1970022673808736E-3</v>
+      </c>
+    </row>
+    <row r="200" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>46042</v>
       </c>
@@ -16352,8 +17762,17 @@
       <c r="AH200">
         <v>8408.7250000000004</v>
       </c>
-    </row>
-    <row r="201" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ200">
+        <v>3.8340624271112679E-3</v>
+      </c>
+      <c r="AK200">
+        <v>6.1469328270065916E-3</v>
+      </c>
+      <c r="AL200">
+        <v>6.0807067038029933E-3</v>
+      </c>
+    </row>
+    <row r="201" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>46043</v>
       </c>
@@ -16447,8 +17866,17 @@
       <c r="AH201">
         <v>8451.2000000000007</v>
       </c>
-    </row>
-    <row r="202" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ201">
+        <v>3.3886200924037246E-3</v>
+      </c>
+      <c r="AK201">
+        <v>5.858355432796095E-3</v>
+      </c>
+      <c r="AL201">
+        <v>6.0547149928986245E-3</v>
+      </c>
+    </row>
+    <row r="202" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>46044</v>
       </c>
@@ -16542,8 +17970,17 @@
       <c r="AH202">
         <v>8451.2000000000007</v>
       </c>
-    </row>
-    <row r="203" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ202">
+        <v>2.8930722797827343E-3</v>
+      </c>
+      <c r="AK202">
+        <v>5.3671314089470444E-3</v>
+      </c>
+      <c r="AL202">
+        <v>6.0111926155646707E-3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>46045</v>
       </c>
@@ -16637,8 +18074,17 @@
       <c r="AH203">
         <v>8482.9</v>
       </c>
-    </row>
-    <row r="204" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ203">
+        <v>4.1029551306857783E-3</v>
+      </c>
+      <c r="AK203">
+        <v>4.9789735031268703E-3</v>
+      </c>
+      <c r="AL203">
+        <v>5.9964332945164692E-3</v>
+      </c>
+    </row>
+    <row r="204" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>46048</v>
       </c>
@@ -16732,8 +18178,17 @@
       <c r="AH204">
         <v>8516.6</v>
       </c>
-    </row>
-    <row r="205" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ204">
+        <v>4.6191198461358676E-3</v>
+      </c>
+      <c r="AK204">
+        <v>4.516475792844748E-3</v>
+      </c>
+      <c r="AL204">
+        <v>5.938402598457548E-3</v>
+      </c>
+    </row>
+    <row r="205" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>46049</v>
       </c>
@@ -16827,8 +18282,17 @@
       <c r="AH205">
         <v>8482.9</v>
       </c>
-    </row>
-    <row r="206" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ205">
+        <v>5.4971974587188343E-3</v>
+      </c>
+      <c r="AK205">
+        <v>4.365687271838811E-3</v>
+      </c>
+      <c r="AL205">
+        <v>5.9160588296679291E-3</v>
+      </c>
+    </row>
+    <row r="206" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>46050</v>
       </c>
@@ -16922,8 +18386,17 @@
       <c r="AH206">
         <v>8516.6</v>
       </c>
-    </row>
-    <row r="207" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ206">
+        <v>4.6283275272127168E-3</v>
+      </c>
+      <c r="AK206">
+        <v>4.2152253831512993E-3</v>
+      </c>
+      <c r="AL206">
+        <v>5.8943294439331292E-3</v>
+      </c>
+    </row>
+    <row r="207" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>46051</v>
       </c>
@@ -17017,8 +18490,17 @@
       <c r="AH207">
         <v>8556.6</v>
       </c>
-    </row>
-    <row r="208" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ207">
+        <v>4.6283275272127168E-3</v>
+      </c>
+      <c r="AK207">
+        <v>4.3356709095257167E-3</v>
+      </c>
+      <c r="AL207">
+        <v>5.8617281452057494E-3</v>
+      </c>
+    </row>
+    <row r="208" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>46052</v>
       </c>
@@ -17112,8 +18594,17 @@
       <c r="AH208">
         <v>8652.85</v>
       </c>
-    </row>
-    <row r="209" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ208">
+        <v>5.5926952092785016E-3</v>
+      </c>
+      <c r="AK208">
+        <v>4.4856453846859748E-3</v>
+      </c>
+      <c r="AL208">
+        <v>5.910771600410536E-3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>46055</v>
       </c>
@@ -17207,8 +18698,17 @@
       <c r="AH209">
         <v>8798.2000000000007</v>
       </c>
-    </row>
-    <row r="210" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ209">
+        <v>5.5885211205603325E-3</v>
+      </c>
+      <c r="AK209">
+        <v>4.4554133782871343E-3</v>
+      </c>
+      <c r="AL209">
+        <v>5.8982172557912639E-3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>46056</v>
       </c>
@@ -17302,8 +18802,17 @@
       <c r="AH210">
         <v>8798.2000000000007</v>
       </c>
-    </row>
-    <row r="211" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ210">
+        <v>4.9536290843800726E-3</v>
+      </c>
+      <c r="AK210">
+        <v>4.4242131582717861E-3</v>
+      </c>
+      <c r="AL210">
+        <v>5.8754788817401479E-3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>46057</v>
       </c>
@@ -17397,8 +18906,17 @@
       <c r="AH211">
         <v>8798.2000000000007</v>
       </c>
-    </row>
-    <row r="212" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ211">
+        <v>4.7571547674845772E-3</v>
+      </c>
+      <c r="AK211">
+        <v>4.3934418216371339E-3</v>
+      </c>
+      <c r="AL211">
+        <v>5.8328815662841513E-3</v>
+      </c>
+    </row>
+    <row r="212" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>46058</v>
       </c>
@@ -17492,8 +19010,17 @@
       <c r="AH212">
         <v>8798.2000000000007</v>
       </c>
-    </row>
-    <row r="213" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ212">
+        <v>4.879308280609178E-3</v>
+      </c>
+      <c r="AK212">
+        <v>4.5430125246973671E-3</v>
+      </c>
+      <c r="AL212">
+        <v>5.8103532833943808E-3</v>
+      </c>
+    </row>
+    <row r="213" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>46059</v>
       </c>
@@ -17587,8 +19114,17 @@
       <c r="AH213">
         <v>8798.2000000000007</v>
       </c>
-    </row>
-    <row r="214" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ213">
+        <v>5.0060983435335328E-3</v>
+      </c>
+      <c r="AK213">
+        <v>4.3611497457202745E-3</v>
+      </c>
+      <c r="AL213">
+        <v>5.7572621429842416E-3</v>
+      </c>
+    </row>
+    <row r="214" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>46062</v>
       </c>
@@ -17682,8 +19218,17 @@
       <c r="AH214">
         <v>8798.2000000000007</v>
       </c>
-    </row>
-    <row r="215" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ214">
+        <v>5.0060983435335337E-3</v>
+      </c>
+      <c r="AK214">
+        <v>4.2402684146371295E-3</v>
+      </c>
+      <c r="AL214">
+        <v>5.7144019170172903E-3</v>
+      </c>
+    </row>
+    <row r="215" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>46063</v>
       </c>
@@ -17777,8 +19322,17 @@
       <c r="AH215">
         <v>8875.35</v>
       </c>
-    </row>
-    <row r="216" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ215">
+        <v>4.2966578863194204E-3</v>
+      </c>
+      <c r="AK215">
+        <v>4.2547773030066453E-3</v>
+      </c>
+      <c r="AL215">
+        <v>5.6513963451460389E-3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>46064</v>
       </c>
@@ -17872,8 +19426,17 @@
       <c r="AH216">
         <v>8885.9</v>
       </c>
-    </row>
-    <row r="217" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ216">
+        <v>4.2911619407815108E-3</v>
+      </c>
+      <c r="AK216">
+        <v>4.1920803331630301E-3</v>
+      </c>
+      <c r="AL216">
+        <v>5.6436679655933316E-3</v>
+      </c>
+    </row>
+    <row r="217" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>46065</v>
       </c>
@@ -17967,8 +19530,17 @@
       <c r="AH217">
         <v>9058.75</v>
       </c>
-    </row>
-    <row r="218" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ217">
+        <v>4.097910974259455E-3</v>
+      </c>
+      <c r="AK217">
+        <v>4.1426389303231125E-3</v>
+      </c>
+      <c r="AL217">
+        <v>5.5801830939243152E-3</v>
+      </c>
+    </row>
+    <row r="218" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>46066</v>
       </c>
@@ -18062,8 +19634,17 @@
       <c r="AH218">
         <v>8885.9</v>
       </c>
-    </row>
-    <row r="219" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ218">
+        <v>3.9682525780302324E-3</v>
+      </c>
+      <c r="AK218">
+        <v>4.0817224773186354E-3</v>
+      </c>
+      <c r="AL218">
+        <v>5.4865224575384123E-3</v>
+      </c>
+    </row>
+    <row r="219" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>46069</v>
       </c>
@@ -18157,8 +19738,17 @@
       <c r="AH219">
         <v>9058.75</v>
       </c>
-    </row>
-    <row r="220" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ219">
+        <v>3.0692762147280167E-3</v>
+      </c>
+      <c r="AK219">
+        <v>3.9615262099917522E-3</v>
+      </c>
+      <c r="AL219">
+        <v>5.4188211122314879E-3</v>
+      </c>
+    </row>
+    <row r="220" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>46070</v>
       </c>
@@ -18252,8 +19842,17 @@
       <c r="AH220">
         <v>9273.0499999999993</v>
       </c>
-    </row>
-    <row r="221" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ220">
+        <v>3.1289474502489778E-3</v>
+      </c>
+      <c r="AK220">
+        <v>3.9461034134697934E-3</v>
+      </c>
+      <c r="AL220">
+        <v>5.3858208228392815E-3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>46071</v>
       </c>
@@ -18347,8 +19946,17 @@
       <c r="AH221">
         <v>9436.9</v>
       </c>
-    </row>
-    <row r="222" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ221">
+        <v>2.7384147665399663E-3</v>
+      </c>
+      <c r="AK221">
+        <v>3.8563257791237398E-3</v>
+      </c>
+      <c r="AL221">
+        <v>5.3074407037844084E-3</v>
+      </c>
+    </row>
+    <row r="222" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>46072</v>
       </c>
@@ -18442,8 +20050,17 @@
       <c r="AH222">
         <v>9691.5750000000007</v>
       </c>
-    </row>
-    <row r="223" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ222">
+        <v>2.6740554020744552E-3</v>
+      </c>
+      <c r="AK222">
+        <v>3.8560593332873827E-3</v>
+      </c>
+      <c r="AL222">
+        <v>5.2703240353780424E-3</v>
+      </c>
+    </row>
+    <row r="223" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>46073</v>
       </c>
@@ -18537,8 +20154,17 @@
       <c r="AH223">
         <v>9877.625</v>
       </c>
-    </row>
-    <row r="224" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ223">
+        <v>1.9730229619088898E-3</v>
+      </c>
+      <c r="AK223">
+        <v>3.8559193216874212E-3</v>
+      </c>
+      <c r="AL223">
+        <v>5.1816808570474904E-3</v>
+      </c>
+    </row>
+    <row r="224" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>46076</v>
       </c>
@@ -18632,8 +20258,17 @@
       <c r="AH224">
         <v>9877.625</v>
       </c>
-    </row>
-    <row r="225" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ224">
+        <v>1.9092333460829906E-3</v>
+      </c>
+      <c r="AK224">
+        <v>3.8261441954778748E-3</v>
+      </c>
+      <c r="AL224">
+        <v>5.1282515158683388E-3</v>
+      </c>
+    </row>
+    <row r="225" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>46077</v>
       </c>
@@ -18727,8 +20362,17 @@
       <c r="AH225">
         <v>10102.25</v>
       </c>
-    </row>
-    <row r="226" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ225">
+        <v>1.907660083986965E-3</v>
+      </c>
+      <c r="AK225">
+        <v>3.5887927857126732E-3</v>
+      </c>
+      <c r="AL225">
+        <v>5.0959544578905733E-3</v>
+      </c>
+    </row>
+    <row r="226" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>46078</v>
       </c>
@@ -18822,8 +20466,17 @@
       <c r="AH226">
         <v>10248.25</v>
       </c>
-    </row>
-    <row r="227" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ226">
+        <v>1.9078860345248853E-3</v>
+      </c>
+      <c r="AK226">
+        <v>3.6034840666740596E-3</v>
+      </c>
+      <c r="AL226">
+        <v>5.0538988339183417E-3</v>
+      </c>
+    </row>
+    <row r="227" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>46079</v>
       </c>
@@ -18917,8 +20570,17 @@
       <c r="AH227">
         <v>10583</v>
       </c>
-    </row>
-    <row r="228" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ227">
+        <v>1.5889960910413154E-3</v>
+      </c>
+      <c r="AK227">
+        <v>3.6478248672166466E-3</v>
+      </c>
+      <c r="AL227">
+        <v>4.9805162571834099E-3</v>
+      </c>
+    </row>
+    <row r="228" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>46080</v>
       </c>
@@ -19012,8 +20674,17 @@
       <c r="AH228">
         <v>10633.9</v>
       </c>
-    </row>
-    <row r="229" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ228">
+        <v>1.5887697382324355E-3</v>
+      </c>
+      <c r="AK228">
+        <v>3.7011464927092139E-3</v>
+      </c>
+      <c r="AL228">
+        <v>4.9175225889490819E-3</v>
+      </c>
+    </row>
+    <row r="229" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>46083</v>
       </c>
@@ -19107,8 +20778,17 @@
       <c r="AH229">
         <v>10633.9</v>
       </c>
-    </row>
-    <row r="230" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ229">
+        <v>2.3424938863440639E-3</v>
+      </c>
+      <c r="AK229">
+        <v>3.6435378557297337E-3</v>
+      </c>
+      <c r="AL229">
+        <v>4.944647619090076E-3</v>
+      </c>
+    </row>
+    <row r="230" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>46084</v>
       </c>
@@ -19202,8 +20882,17 @@
       <c r="AH230">
         <v>10772.25</v>
       </c>
-    </row>
-    <row r="231" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ230">
+        <v>3.4356409023886792E-3</v>
+      </c>
+      <c r="AK230">
+        <v>3.7629542992521506E-3</v>
+      </c>
+      <c r="AL230">
+        <v>4.9673857626714012E-3</v>
+      </c>
+    </row>
+    <row r="231" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>46085</v>
       </c>
@@ -19297,8 +20986,17 @@
       <c r="AH231">
         <v>10876.900000000001</v>
       </c>
-    </row>
-    <row r="232" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ231">
+        <v>3.6955542121399404E-3</v>
+      </c>
+      <c r="AK231">
+        <v>3.8977621567496579E-3</v>
+      </c>
+      <c r="AL231">
+        <v>4.9450055556893111E-3</v>
+      </c>
+    </row>
+    <row r="232" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>46086</v>
       </c>
@@ -19392,8 +21090,17 @@
       <c r="AH232">
         <v>10876.900000000001</v>
       </c>
-    </row>
-    <row r="233" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ232">
+        <v>4.4762579921577995E-3</v>
+      </c>
+      <c r="AK232">
+        <v>3.9582027852668542E-3</v>
+      </c>
+      <c r="AL232">
+        <v>4.9323952470141739E-3</v>
+      </c>
+    </row>
+    <row r="233" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>46087</v>
       </c>
@@ -19487,8 +21194,17 @@
       <c r="AH233">
         <v>10922.7</v>
       </c>
-    </row>
-    <row r="234" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ233">
+        <v>5.3843010143239858E-3</v>
+      </c>
+      <c r="AK233">
+        <v>3.9024647728563072E-3</v>
+      </c>
+      <c r="AL233">
+        <v>4.9406599385317575E-3</v>
+      </c>
+    </row>
+    <row r="234" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>46090</v>
       </c>
@@ -19582,8 +21298,17 @@
       <c r="AH234">
         <v>10985.099999999999</v>
       </c>
-    </row>
-    <row r="235" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ234">
+        <v>5.7779850088504493E-3</v>
+      </c>
+      <c r="AK234">
+        <v>3.9182267385167151E-3</v>
+      </c>
+      <c r="AL234">
+        <v>4.8776191683868007E-3</v>
+      </c>
+    </row>
+    <row r="235" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>46091</v>
       </c>
@@ -19677,8 +21402,17 @@
       <c r="AH235">
         <v>10985.099999999999</v>
       </c>
-    </row>
-    <row r="236" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ235">
+        <v>6.5618081912695303E-3</v>
+      </c>
+      <c r="AK235">
+        <v>3.9495556636377094E-3</v>
+      </c>
+      <c r="AL235">
+        <v>4.8861032476371002E-3</v>
+      </c>
+    </row>
+    <row r="236" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>46092</v>
       </c>
@@ -19772,8 +21506,17 @@
       <c r="AH236">
         <v>11084.099999999999</v>
       </c>
-    </row>
-    <row r="237" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ236">
+        <v>5.9433519708132192E-3</v>
+      </c>
+      <c r="AK236">
+        <v>3.9503768925698507E-3</v>
+      </c>
+      <c r="AL236">
+        <v>4.8338371651473096E-3</v>
+      </c>
+    </row>
+    <row r="237" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>46093</v>
       </c>
@@ -19867,8 +21610,17 @@
       <c r="AH237">
         <v>11249.65</v>
       </c>
-    </row>
-    <row r="238" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ237">
+        <v>5.8246313587611929E-3</v>
+      </c>
+      <c r="AK237">
+        <v>4.0420918599467946E-3</v>
+      </c>
+      <c r="AL237">
+        <v>4.8325710307784275E-3</v>
+      </c>
+    </row>
+    <row r="238" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>46094</v>
       </c>
@@ -19962,8 +21714,17 @@
       <c r="AH238">
         <v>11249.65</v>
       </c>
-    </row>
-    <row r="239" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ238">
+        <v>5.4409079646958475E-3</v>
+      </c>
+      <c r="AK238">
+        <v>3.8623451330137052E-3</v>
+      </c>
+      <c r="AL238">
+        <v>4.7656780132038249E-3</v>
+      </c>
+    </row>
+    <row r="239" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>46097</v>
       </c>
@@ -20057,8 +21818,17 @@
       <c r="AH239">
         <v>11347.4</v>
       </c>
-    </row>
-    <row r="240" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ239">
+        <v>5.4489109352102161E-3</v>
+      </c>
+      <c r="AK239">
+        <v>3.9256270753518265E-3</v>
+      </c>
+      <c r="AL239">
+        <v>4.8263014941079627E-3</v>
+      </c>
+    </row>
+    <row r="240" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>46098</v>
       </c>
@@ -20152,8 +21922,17 @@
       <c r="AH240">
         <v>11249.65</v>
       </c>
-    </row>
-    <row r="241" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ240">
+        <v>6.1089610366509865E-3</v>
+      </c>
+      <c r="AK240">
+        <v>4.1720422283861866E-3</v>
+      </c>
+      <c r="AL240">
+        <v>4.835605002518781E-3</v>
+      </c>
+    </row>
+    <row r="241" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>46099</v>
       </c>
@@ -20247,8 +22026,17 @@
       <c r="AH241">
         <v>11249.65</v>
       </c>
-    </row>
-    <row r="242" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ241">
+        <v>6.5038357053227632E-3</v>
+      </c>
+      <c r="AK241">
+        <v>4.3257856240122893E-3</v>
+      </c>
+      <c r="AL241">
+        <v>4.8447914265588648E-3</v>
+      </c>
+    </row>
+    <row r="242" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>46100</v>
       </c>
@@ -20342,8 +22130,17 @@
       <c r="AH242">
         <v>11347.4</v>
       </c>
-    </row>
-    <row r="243" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ242">
+        <v>6.5085711861019189E-3</v>
+      </c>
+      <c r="AK242">
+        <v>4.3297170082526818E-3</v>
+      </c>
+      <c r="AL242">
+        <v>4.8436660380184711E-3</v>
+      </c>
+    </row>
+    <row r="243" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>46101</v>
       </c>
@@ -20437,8 +22234,17 @@
       <c r="AH243">
         <v>11347.4</v>
       </c>
-    </row>
-    <row r="244" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ243">
+        <v>7.1630879640677417E-3</v>
+      </c>
+      <c r="AK243">
+        <v>4.4536744706944994E-3</v>
+      </c>
+      <c r="AL243">
+        <v>4.8633599052919337E-3</v>
+      </c>
+    </row>
+    <row r="244" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>46104</v>
       </c>
@@ -20532,8 +22338,17 @@
       <c r="AH244">
         <v>11347.4</v>
       </c>
-    </row>
-    <row r="245" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ244">
+        <v>7.1697297572190571E-3</v>
+      </c>
+      <c r="AK244">
+        <v>4.54693918980675E-3</v>
+      </c>
+      <c r="AL244">
+        <v>4.893289645461445E-3</v>
+      </c>
+    </row>
+    <row r="245" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>46105</v>
       </c>
@@ -20627,8 +22442,17 @@
       <c r="AH245">
         <v>11363.849999999999</v>
       </c>
-    </row>
-    <row r="246" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ245">
+        <v>7.8233912807039296E-3</v>
+      </c>
+      <c r="AK245">
+        <v>4.6852495917034239E-3</v>
+      </c>
+      <c r="AL245">
+        <v>4.8820700186442152E-3</v>
+      </c>
+    </row>
+    <row r="246" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>46106</v>
       </c>
@@ -20722,8 +22546,17 @@
       <c r="AH246">
         <v>11531.099999999999</v>
       </c>
-    </row>
-    <row r="247" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ246">
+        <v>7.8248164554659654E-3</v>
+      </c>
+      <c r="AK246">
+        <v>4.7501464621115324E-3</v>
+      </c>
+      <c r="AL246">
+        <v>4.9072232725006918E-3</v>
+      </c>
+    </row>
+    <row r="247" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>46107</v>
       </c>
@@ -20817,8 +22650,17 @@
       <c r="AH247">
         <v>11531.099999999999</v>
       </c>
-    </row>
-    <row r="248" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ247">
+        <v>6.5186494928656047E-3</v>
+      </c>
+      <c r="AK247">
+        <v>4.7368812160609557E-3</v>
+      </c>
+      <c r="AL247">
+        <v>4.9221769617519805E-3</v>
+      </c>
+    </row>
+    <row r="248" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>46108</v>
       </c>
@@ -20912,8 +22754,17 @@
       <c r="AH248">
         <v>11709.8</v>
       </c>
-    </row>
-    <row r="249" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ248">
+        <v>6.5224691004391235E-3</v>
+      </c>
+      <c r="AK248">
+        <v>4.9217694792410317E-3</v>
+      </c>
+      <c r="AL248">
+        <v>4.9984790339246653E-3</v>
+      </c>
+    </row>
+    <row r="249" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>46111</v>
       </c>
@@ -21007,8 +22858,17 @@
       <c r="AH249">
         <v>11709.8</v>
       </c>
-    </row>
-    <row r="250" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ249">
+        <v>5.8734428553505269E-3</v>
+      </c>
+      <c r="AK249">
+        <v>4.9840225577312677E-3</v>
+      </c>
+      <c r="AL249">
+        <v>4.9266956616537917E-3</v>
+      </c>
+    </row>
+    <row r="250" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>46112</v>
       </c>
@@ -21102,8 +22962,17 @@
       <c r="AH250">
         <v>11709.8</v>
       </c>
-    </row>
-    <row r="251" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ250">
+        <v>5.2225102978897741E-3</v>
+      </c>
+      <c r="AK250">
+        <v>4.9421724684773514E-3</v>
+      </c>
+      <c r="AL250">
+        <v>4.9072572881226698E-3</v>
+      </c>
+    </row>
+    <row r="251" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>46113</v>
       </c>
@@ -21197,8 +23066,17 @@
       <c r="AH251">
         <v>11806.5</v>
       </c>
-    </row>
-    <row r="252" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ251">
+        <v>4.4409397788259539E-3</v>
+      </c>
+      <c r="AK251">
+        <v>4.9441950260068149E-3</v>
+      </c>
+      <c r="AL251">
+        <v>4.9266966640571855E-3</v>
+      </c>
+    </row>
+    <row r="252" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>46118</v>
       </c>
@@ -21292,8 +23170,17 @@
       <c r="AH252">
         <v>11897.55</v>
       </c>
-    </row>
-    <row r="253" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ252">
+        <v>4.5861692235715954E-3</v>
+      </c>
+      <c r="AK252">
+        <v>5.1314094833860907E-3</v>
+      </c>
+      <c r="AL252">
+        <v>4.9885189723964671E-3</v>
+      </c>
+    </row>
+    <row r="253" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>46119</v>
       </c>
@@ -21387,8 +23274,17 @@
       <c r="AH253">
         <v>12104.119999999999</v>
       </c>
-    </row>
-    <row r="254" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ253">
+        <v>3.9378677398681488E-3</v>
+      </c>
+      <c r="AK253">
+        <v>5.2086102436353617E-3</v>
+      </c>
+      <c r="AL253">
+        <v>4.9886315062876311E-3</v>
+      </c>
+    </row>
+    <row r="254" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>46120</v>
       </c>
@@ -21482,8 +23378,17 @@
       <c r="AH254">
         <v>12104.119999999999</v>
       </c>
-    </row>
-    <row r="255" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ254">
+        <v>4.2086361485631132E-3</v>
+      </c>
+      <c r="AK254">
+        <v>5.2734085366396514E-3</v>
+      </c>
+      <c r="AL254">
+        <v>5.0195843626882506E-3</v>
+      </c>
+    </row>
+    <row r="255" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>46121</v>
       </c>
@@ -21577,8 +23482,17 @@
       <c r="AH255">
         <v>12104.119999999999</v>
       </c>
-    </row>
-    <row r="256" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ255">
+        <v>3.5565150572861477E-3</v>
+      </c>
+      <c r="AK255">
+        <v>5.3065023063441769E-3</v>
+      </c>
+      <c r="AL255">
+        <v>5.0308790278367956E-3</v>
+      </c>
+    </row>
+    <row r="256" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>46122</v>
       </c>
@@ -21672,8 +23586,17 @@
       <c r="AH256">
         <v>12104.119999999999</v>
       </c>
-    </row>
-    <row r="257" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ256">
+        <v>4.1491438515395248E-3</v>
+      </c>
+      <c r="AK256">
+        <v>5.5069827150346857E-3</v>
+      </c>
+      <c r="AL256">
+        <v>5.0373590464236262E-3</v>
+      </c>
+    </row>
+    <row r="257" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>46125</v>
       </c>
@@ -21767,8 +23690,17 @@
       <c r="AH257">
         <v>12331.92</v>
       </c>
-    </row>
-    <row r="258" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ257">
+        <v>4.4140485930832937E-3</v>
+      </c>
+      <c r="AK257">
+        <v>5.6013513856204818E-3</v>
+      </c>
+      <c r="AL257">
+        <v>5.06324702239921E-3</v>
+      </c>
+    </row>
+    <row r="258" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>46126</v>
       </c>
@@ -21862,8 +23794,17 @@
       <c r="AH258">
         <v>12331.92</v>
       </c>
-    </row>
-    <row r="259" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ258">
+        <v>4.4116481490971736E-3</v>
+      </c>
+      <c r="AK258">
+        <v>5.6028666552085885E-3</v>
+      </c>
+      <c r="AL258">
+        <v>5.0531230158000215E-3</v>
+      </c>
+    </row>
+    <row r="259" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>46127</v>
       </c>
@@ -21957,8 +23898,17 @@
       <c r="AH259">
         <v>12565.375</v>
       </c>
-    </row>
-    <row r="260" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ259">
+        <v>4.2773609333803808E-3</v>
+      </c>
+      <c r="AK259">
+        <v>5.5828784610278993E-3</v>
+      </c>
+      <c r="AL259">
+        <v>5.0945070871270832E-3</v>
+      </c>
+    </row>
+    <row r="260" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>46128</v>
       </c>
@@ -22052,8 +24002,17 @@
       <c r="AH260">
         <v>12565.375</v>
       </c>
-    </row>
-    <row r="261" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ260">
+        <v>4.5385182822217651E-3</v>
+      </c>
+      <c r="AK260">
+        <v>5.4659482989297499E-3</v>
+      </c>
+      <c r="AL260">
+        <v>5.1252784750628342E-3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>46129</v>
       </c>
@@ -22147,8 +24106,17 @@
       <c r="AH261">
         <v>12565.375</v>
       </c>
-    </row>
-    <row r="262" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ261">
+        <v>4.7883782155722495E-3</v>
+      </c>
+      <c r="AK261">
+        <v>5.5284008041071916E-3</v>
+      </c>
+      <c r="AL261">
+        <v>5.0948394645509848E-3</v>
+      </c>
+    </row>
+    <row r="262" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>46132</v>
       </c>
@@ -22242,8 +24210,17 @@
       <c r="AH262">
         <v>12565.375</v>
       </c>
-    </row>
-    <row r="263" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ262">
+        <v>5.3117790574969664E-3</v>
+      </c>
+      <c r="AK262">
+        <v>5.501457221589982E-3</v>
+      </c>
+      <c r="AL262">
+        <v>4.9422638052679622E-3</v>
+      </c>
+    </row>
+    <row r="263" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>46133</v>
       </c>
@@ -22337,8 +24314,17 @@
       <c r="AH263">
         <v>12882.725</v>
       </c>
-    </row>
-    <row r="264" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ263">
+        <v>5.2374163448201741E-3</v>
+      </c>
+      <c r="AK263">
+        <v>5.4727096254837959E-3</v>
+      </c>
+      <c r="AL263">
+        <v>4.7847159671556595E-3</v>
+      </c>
+    </row>
+    <row r="264" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>46134</v>
       </c>
@@ -22432,8 +24418,17 @@
       <c r="AH264">
         <v>13007.6</v>
       </c>
-    </row>
-    <row r="265" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ264">
+        <v>5.8798518556319856E-3</v>
+      </c>
+      <c r="AK264">
+        <v>5.6251203165361722E-3</v>
+      </c>
+      <c r="AL264">
+        <v>4.6866076159658805E-3</v>
+      </c>
+    </row>
+    <row r="265" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>46135</v>
       </c>
@@ -22527,8 +24522,17 @@
       <c r="AH265">
         <v>13345.05</v>
       </c>
-    </row>
-    <row r="266" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ265">
+        <v>6.5180868850248097E-3</v>
+      </c>
+      <c r="AK265">
+        <v>5.5926650170848198E-3</v>
+      </c>
+      <c r="AL265">
+        <v>4.6359693175204476E-3</v>
+      </c>
+    </row>
+    <row r="266" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>46136</v>
       </c>
@@ -22622,8 +24626,17 @@
       <c r="AH266">
         <v>13345.05</v>
       </c>
-    </row>
-    <row r="267" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ266">
+        <v>6.3641471098748615E-3</v>
+      </c>
+      <c r="AK266">
+        <v>5.6810639934756161E-3</v>
+      </c>
+      <c r="AL266">
+        <v>4.6155554230655881E-3</v>
+      </c>
+    </row>
+    <row r="267" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>46139</v>
       </c>
@@ -22717,8 +24730,17 @@
       <c r="AH267">
         <v>13345.05</v>
       </c>
-    </row>
-    <row r="268" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ267">
+        <v>6.6221975822830376E-3</v>
+      </c>
+      <c r="AK267">
+        <v>5.6520470844181776E-3</v>
+      </c>
+      <c r="AL267">
+        <v>4.6766032846302305E-3</v>
+      </c>
+    </row>
+    <row r="268" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>46140</v>
       </c>
@@ -22812,8 +24834,17 @@
       <c r="AH268">
         <v>13340.150000000001</v>
       </c>
-    </row>
-    <row r="269" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ268">
+        <v>6.6269841556818214E-3</v>
+      </c>
+      <c r="AK268">
+        <v>5.8051519153372502E-3</v>
+      </c>
+      <c r="AL268">
+        <v>4.7177141443456444E-3</v>
+      </c>
+    </row>
+    <row r="269" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>46141</v>
       </c>
@@ -22907,8 +24938,17 @@
       <c r="AH269">
         <v>12882.725</v>
       </c>
-    </row>
-    <row r="270" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ269">
+        <v>6.6261424755114486E-3</v>
+      </c>
+      <c r="AK269">
+        <v>5.7761445809936009E-3</v>
+      </c>
+      <c r="AL269">
+        <v>4.7190616782108548E-3</v>
+      </c>
+    </row>
+    <row r="270" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>46142</v>
       </c>
@@ -23002,8 +25042,17 @@
       <c r="AH270">
         <v>12882.725</v>
       </c>
-    </row>
-    <row r="271" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ270">
+        <v>6.2243772151481707E-3</v>
+      </c>
+      <c r="AK270">
+        <v>5.4996400671331368E-3</v>
+      </c>
+      <c r="AL270">
+        <v>4.6986318179303719E-3</v>
+      </c>
+    </row>
+    <row r="271" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>46146</v>
       </c>
@@ -23097,8 +25146,17 @@
       <c r="AH271">
         <v>12882.725</v>
       </c>
-    </row>
-    <row r="272" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ271">
+        <v>5.4490035982947774E-3</v>
+      </c>
+      <c r="AK271">
+        <v>5.3789928248963092E-3</v>
+      </c>
+      <c r="AL271">
+        <v>4.6994067568485792E-3</v>
+      </c>
+    </row>
+    <row r="272" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>46147</v>
       </c>
@@ -23192,8 +25250,17 @@
       <c r="AH272">
         <v>12882.725</v>
       </c>
-    </row>
-    <row r="273" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ272">
+        <v>5.1806802101243901E-3</v>
+      </c>
+      <c r="AK272">
+        <v>5.2828237893567274E-3</v>
+      </c>
+      <c r="AL272">
+        <v>4.7185177741022608E-3</v>
+      </c>
+    </row>
+    <row r="273" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>46148</v>
       </c>
@@ -23287,8 +25354,17 @@
       <c r="AH273">
         <v>13340.150000000001</v>
       </c>
-    </row>
-    <row r="274" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ273">
+        <v>5.5906986108430496E-3</v>
+      </c>
+      <c r="AK273">
+        <v>5.3141731443898535E-3</v>
+      </c>
+      <c r="AL273">
+        <v>4.7096657869348767E-3</v>
+      </c>
+    </row>
+    <row r="274" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>46149</v>
       </c>
@@ -23382,8 +25458,17 @@
       <c r="AH274">
         <v>13340.150000000001</v>
       </c>
-    </row>
-    <row r="275" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ274">
+        <v>5.5940499513478332E-3</v>
+      </c>
+      <c r="AK274">
+        <v>5.2843884630482266E-3</v>
+      </c>
+      <c r="AL274">
+        <v>4.6905320224973693E-3</v>
+      </c>
+    </row>
+    <row r="275" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>46150</v>
       </c>
@@ -23477,8 +25562,17 @@
       <c r="AH275">
         <v>13340.150000000001</v>
       </c>
-    </row>
-    <row r="276" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ275">
+        <v>5.5965657553138717E-3</v>
+      </c>
+      <c r="AK275">
+        <v>5.2855592927462374E-3</v>
+      </c>
+      <c r="AL275">
+        <v>4.7418620624854373E-3</v>
+      </c>
+    </row>
+    <row r="276" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>46153</v>
       </c>
@@ -23572,8 +25666,17 @@
       <c r="AH276">
         <v>13340.150000000001</v>
       </c>
-    </row>
-    <row r="277" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ276">
+        <v>5.3333636438213936E-3</v>
+      </c>
+      <c r="AK276">
+        <v>5.194805591609869E-3</v>
+      </c>
+      <c r="AL276">
+        <v>4.7123441289614789E-3</v>
+      </c>
+    </row>
+    <row r="277" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>46154</v>
       </c>
@@ -23667,8 +25770,17 @@
       <c r="AH277">
         <v>13701.3</v>
       </c>
-    </row>
-    <row r="278" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ277">
+        <v>5.8027280368609935E-3</v>
+      </c>
+      <c r="AK277">
+        <v>5.33259172739873E-3</v>
+      </c>
+      <c r="AL277">
+        <v>4.7373706245942672E-3</v>
+      </c>
+    </row>
+    <row r="278" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>46155</v>
       </c>
@@ -23762,8 +25874,17 @@
       <c r="AH278">
         <v>13701.3</v>
       </c>
-    </row>
-    <row r="279" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ278">
+        <v>5.4075575224650837E-3</v>
+      </c>
+      <c r="AK278">
+        <v>5.1188467900356999E-3</v>
+      </c>
+      <c r="AL278">
+        <v>4.7074462488651235E-3</v>
+      </c>
+    </row>
+    <row r="279" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>46156</v>
       </c>
@@ -23857,8 +25978,17 @@
       <c r="AH279">
         <v>13799.6</v>
       </c>
-    </row>
-    <row r="280" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ279">
+        <v>5.6881193955573206E-3</v>
+      </c>
+      <c r="AK279">
+        <v>5.239581648738314E-3</v>
+      </c>
+      <c r="AL279">
+        <v>4.7283768054871122E-3</v>
+      </c>
+    </row>
+    <row r="280" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>46157</v>
       </c>
@@ -23952,8 +26082,17 @@
       <c r="AH280">
         <v>13701.3</v>
       </c>
-    </row>
-    <row r="281" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ280">
+        <v>5.4210985409597597E-3</v>
+      </c>
+      <c r="AK280">
+        <v>5.3605104011061836E-3</v>
+      </c>
+      <c r="AL280">
+        <v>4.749595427684444E-3</v>
+      </c>
+    </row>
+    <row r="281" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>46160</v>
       </c>
@@ -24047,8 +26186,17 @@
       <c r="AH281">
         <v>13799.6</v>
       </c>
-    </row>
-    <row r="282" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ281">
+        <v>5.4341560475008807E-3</v>
+      </c>
+      <c r="AK281">
+        <v>5.5161389257390421E-3</v>
+      </c>
+      <c r="AL281">
+        <v>4.7722199102898663E-3</v>
+      </c>
+    </row>
+    <row r="282" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>46161</v>
       </c>
@@ -24142,8 +26290,17 @@
       <c r="AH282">
         <v>13799.6</v>
       </c>
-    </row>
-    <row r="283" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ282">
+        <v>4.5171455018796023E-3</v>
+      </c>
+      <c r="AK282">
+        <v>5.269453757684772E-3</v>
+      </c>
+      <c r="AL282">
+        <v>4.7523075247860834E-3</v>
+      </c>
+    </row>
+    <row r="283" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>46162</v>
       </c>
@@ -24237,8 +26394,17 @@
       <c r="AH283">
         <v>14013.900000000001</v>
       </c>
-    </row>
-    <row r="284" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ283">
+        <v>4.1252200060773745E-3</v>
+      </c>
+      <c r="AK283">
+        <v>5.2385211203920213E-3</v>
+      </c>
+      <c r="AL283">
+        <v>4.7676835619049349E-3</v>
+      </c>
+    </row>
+    <row r="284" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>46163</v>
       </c>
@@ -24332,8 +26498,17 @@
       <c r="AH284">
         <v>14321.875</v>
       </c>
-    </row>
-    <row r="285" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ284">
+        <v>4.0601229109979197E-3</v>
+      </c>
+      <c r="AK284">
+        <v>5.2979386386335153E-3</v>
+      </c>
+      <c r="AL284">
+        <v>4.7991637902503482E-3</v>
+      </c>
+    </row>
+    <row r="285" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>46164</v>
       </c>
@@ -24427,8 +26602,17 @@
       <c r="AH285">
         <v>14013.900000000001</v>
       </c>
-    </row>
-    <row r="286" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ285">
+        <v>4.5840076014783083E-3</v>
+      </c>
+      <c r="AK285">
+        <v>5.3585950503472037E-3</v>
+      </c>
+      <c r="AL285">
+        <v>4.751296714134684E-3</v>
+      </c>
+    </row>
+    <row r="286" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>46167</v>
       </c>
@@ -24522,8 +26706,17 @@
       <c r="AH286">
         <v>14013.900000000001</v>
       </c>
-    </row>
-    <row r="287" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ286">
+        <v>4.3266543043998336E-3</v>
+      </c>
+      <c r="AK286">
+        <v>5.2810007544057186E-3</v>
+      </c>
+      <c r="AL286">
+        <v>4.7971558453714881E-3</v>
+      </c>
+    </row>
+    <row r="287" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>46168</v>
       </c>
@@ -24617,8 +26810,17 @@
       <c r="AH287">
         <v>14013.900000000001</v>
       </c>
-    </row>
-    <row r="288" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ287">
+        <v>4.330832008037298E-3</v>
+      </c>
+      <c r="AK287">
+        <v>5.3410931979287844E-3</v>
+      </c>
+      <c r="AL287">
+        <v>4.8634231502553034E-3</v>
+      </c>
+    </row>
+    <row r="288" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>46169</v>
       </c>
@@ -24712,8 +26914,17 @@
       <c r="AH288">
         <v>14321.875</v>
       </c>
-    </row>
-    <row r="289" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ288">
+        <v>3.5320061633688387E-3</v>
+      </c>
+      <c r="AK288">
+        <v>5.3108891290690975E-3</v>
+      </c>
+      <c r="AL288">
+        <v>4.8716340923289653E-3</v>
+      </c>
+    </row>
+    <row r="289" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>46170</v>
       </c>
@@ -24807,8 +27018,17 @@
       <c r="AH289">
         <v>14321.875</v>
       </c>
-    </row>
-    <row r="290" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ289">
+        <v>4.4481765710646737E-3</v>
+      </c>
+      <c r="AK289">
+        <v>5.3093107398111085E-3</v>
+      </c>
+      <c r="AL289">
+        <v>4.8452423521895792E-3</v>
+      </c>
+    </row>
+    <row r="290" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>46171</v>
       </c>
@@ -24902,8 +27122,17 @@
       <c r="AH290">
         <v>14321.875</v>
       </c>
-    </row>
-    <row r="291" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ290">
+        <v>5.100788374393342E-3</v>
+      </c>
+      <c r="AK290">
+        <v>5.3697174752320564E-3</v>
+      </c>
+      <c r="AL290">
+        <v>4.8662066911379842E-3</v>
+      </c>
+    </row>
+    <row r="291" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>46174</v>
       </c>
@@ -24997,8 +27226,17 @@
       <c r="AH291">
         <v>14013.900000000001</v>
       </c>
-    </row>
-    <row r="292" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ291">
+        <v>4.8389073506784532E-3</v>
+      </c>
+      <c r="AK291">
+        <v>5.3097287701582988E-3</v>
+      </c>
+      <c r="AL291">
+        <v>4.9119639103383812E-3</v>
+      </c>
+    </row>
+    <row r="292" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>46175</v>
       </c>
@@ -25092,8 +27330,17 @@
       <c r="AH292">
         <v>14013.900000000001</v>
       </c>
-    </row>
-    <row r="293" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ292">
+        <v>5.0931777903037807E-3</v>
+      </c>
+      <c r="AK292">
+        <v>5.3075880880021275E-3</v>
+      </c>
+      <c r="AL292">
+        <v>4.9224160316196537E-3</v>
+      </c>
+    </row>
+    <row r="293" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>46176</v>
       </c>
@@ -25187,8 +27434,17 @@
       <c r="AH293">
         <v>14013.900000000001</v>
       </c>
-    </row>
-    <row r="294" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ293">
+        <v>5.3439374249221582E-3</v>
+      </c>
+      <c r="AK293">
+        <v>5.3058556730961829E-3</v>
+      </c>
+      <c r="AL293">
+        <v>4.8936766904787614E-3</v>
+      </c>
+    </row>
+    <row r="294" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>46177</v>
       </c>
@@ -25282,8 +27538,17 @@
       <c r="AH294">
         <v>14013.900000000001</v>
       </c>
-    </row>
-    <row r="295" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ294">
+        <v>5.0856490241534399E-3</v>
+      </c>
+      <c r="AK294">
+        <v>5.1557792039171229E-3</v>
+      </c>
+      <c r="AL294">
+        <v>4.8997087529900028E-3</v>
+      </c>
+    </row>
+    <row r="295" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>46178</v>
       </c>
@@ -25377,8 +27642,17 @@
       <c r="AH295">
         <v>14321.875</v>
       </c>
-    </row>
-    <row r="296" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ295">
+        <v>5.8549020890593219E-3</v>
+      </c>
+      <c r="AK295">
+        <v>5.1561460100104824E-3</v>
+      </c>
+      <c r="AL295">
+        <v>4.8994555635776703E-3</v>
+      </c>
+    </row>
+    <row r="296" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>46181</v>
       </c>
@@ -25472,8 +27746,17 @@
       <c r="AH296">
         <v>14321.875</v>
       </c>
-    </row>
-    <row r="297" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ296">
+        <v>5.8424822462075929E-3</v>
+      </c>
+      <c r="AK296">
+        <v>5.1875889382887435E-3</v>
+      </c>
+      <c r="AL296">
+        <v>4.9396766081114037E-3</v>
+      </c>
+    </row>
+    <row r="297" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>46182</v>
       </c>
@@ -25567,8 +27850,17 @@
       <c r="AH297">
         <v>14321.875</v>
       </c>
-    </row>
-    <row r="298" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ297">
+        <v>5.8276726147637832E-3</v>
+      </c>
+      <c r="AK297">
+        <v>5.1843283161442282E-3</v>
+      </c>
+      <c r="AL297">
+        <v>4.9594890868364001E-3</v>
+      </c>
+    </row>
+    <row r="298" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>46183</v>
       </c>
@@ -25662,8 +27954,17 @@
       <c r="AH298">
         <v>14321.875</v>
       </c>
-    </row>
-    <row r="299" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ298">
+        <v>6.0731280481480885E-3</v>
+      </c>
+      <c r="AK298">
+        <v>5.1804956784004255E-3</v>
+      </c>
+      <c r="AL298">
+        <v>4.9493309089171274E-3</v>
+      </c>
+    </row>
+    <row r="299" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>46184</v>
       </c>
@@ -25757,8 +28058,17 @@
       <c r="AH299">
         <v>14321.875</v>
       </c>
-    </row>
-    <row r="300" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ299">
+        <v>5.6760245445783728E-3</v>
+      </c>
+      <c r="AK299">
+        <v>5.0858939041177435E-3</v>
+      </c>
+      <c r="AL299">
+        <v>4.9292218534877233E-3</v>
+      </c>
+    </row>
+    <row r="300" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>46185</v>
       </c>
@@ -25852,8 +28162,17 @@
       <c r="AH300">
         <v>14550.474999999999</v>
       </c>
-    </row>
-    <row r="301" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ300">
+        <v>5.4106383230667346E-3</v>
+      </c>
+      <c r="AK300">
+        <v>5.1159832649438465E-3</v>
+      </c>
+      <c r="AL300">
+        <v>4.9292218534877242E-3</v>
+      </c>
+    </row>
+    <row r="301" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>46188</v>
       </c>
@@ -25947,8 +28266,17 @@
       <c r="AH301">
         <v>14550.474999999999</v>
       </c>
-    </row>
-    <row r="302" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ301">
+        <v>5.6460122339600776E-3</v>
+      </c>
+      <c r="AK301">
+        <v>5.2017478855723616E-3</v>
+      </c>
+      <c r="AL301">
+        <v>4.9688421114936522E-3</v>
+      </c>
+    </row>
+    <row r="302" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>46189</v>
       </c>
@@ -26042,8 +28370,17 @@
       <c r="AH302">
         <v>14550.474999999999</v>
       </c>
-    </row>
-    <row r="303" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ302">
+        <v>5.6363855584421986E-3</v>
+      </c>
+      <c r="AK302">
+        <v>5.2624772579513059E-3</v>
+      </c>
+      <c r="AL302">
+        <v>4.9583393518535723E-3</v>
+      </c>
+    </row>
+    <row r="303" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>46190</v>
       </c>
@@ -26137,8 +28474,17 @@
       <c r="AH303">
         <v>14806.474999999999</v>
       </c>
-    </row>
-    <row r="304" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ303">
+        <v>5.6227106500288931E-3</v>
+      </c>
+      <c r="AK303">
+        <v>5.195058414098775E-3</v>
+      </c>
+      <c r="AL303">
+        <v>4.9876353430610429E-3</v>
+      </c>
+    </row>
+    <row r="304" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>46191</v>
       </c>
@@ -26232,8 +28578,17 @@
       <c r="AH304">
         <v>14806.474999999999</v>
       </c>
-    </row>
-    <row r="305" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ304">
+        <v>5.6138941366994091E-3</v>
+      </c>
+      <c r="AK304">
+        <v>5.1889586260595979E-3</v>
+      </c>
+      <c r="AL304">
+        <v>5.0067620929715242E-3</v>
+      </c>
+    </row>
+    <row r="305" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>46192</v>
       </c>
@@ -26327,8 +28682,17 @@
       <c r="AH305">
         <v>14550.474999999999</v>
       </c>
-    </row>
-    <row r="306" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ305">
+        <v>5.6074879367791252E-3</v>
+      </c>
+      <c r="AK305">
+        <v>5.1830441874089854E-3</v>
+      </c>
+      <c r="AL305">
+        <v>5.0512843572862159E-3</v>
+      </c>
+    </row>
+    <row r="306" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>46195</v>
       </c>
@@ -26422,8 +28786,17 @@
       <c r="AH306">
         <v>14550.474999999999</v>
       </c>
-    </row>
-    <row r="307" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ306">
+        <v>5.3512435806982155E-3</v>
+      </c>
+      <c r="AK306">
+        <v>5.0900658893890012E-3</v>
+      </c>
+      <c r="AL306">
+        <v>5.0116726477034673E-3</v>
+      </c>
+    </row>
+    <row r="307" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>46196</v>
       </c>
@@ -26517,8 +28890,17 @@
       <c r="AH307">
         <v>14321.875</v>
       </c>
-    </row>
-    <row r="308" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ307">
+        <v>5.4512636502897149E-3</v>
+      </c>
+      <c r="AK307">
+        <v>5.0339749080772159E-3</v>
+      </c>
+      <c r="AL307">
+        <v>5.0344826171789658E-3</v>
+      </c>
+    </row>
+    <row r="308" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>46197</v>
       </c>
@@ -26612,8 +28994,17 @@
       <c r="AH308">
         <v>14321.875</v>
       </c>
-    </row>
-    <row r="309" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ308">
+        <v>5.4504664562532845E-3</v>
+      </c>
+      <c r="AK308">
+        <v>5.211759970122941E-3</v>
+      </c>
+      <c r="AL308">
+        <v>5.084125413133223E-3</v>
+      </c>
+    </row>
+    <row r="309" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>46198</v>
       </c>
@@ -26707,8 +29098,17 @@
       <c r="AH309">
         <v>14321.875</v>
       </c>
-    </row>
-    <row r="310" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ309">
+        <v>4.7507963552765112E-3</v>
+      </c>
+      <c r="AK309">
+        <v>5.0437685485524514E-3</v>
+      </c>
+      <c r="AL309">
+        <v>5.0891242516740093E-3</v>
+      </c>
+    </row>
+    <row r="310" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>46199</v>
       </c>
@@ -26802,8 +29202,17 @@
       <c r="AH310">
         <v>14550.474999999999</v>
       </c>
-    </row>
-    <row r="311" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ310">
+        <v>4.0517487481309547E-3</v>
+      </c>
+      <c r="AK310">
+        <v>4.8755434624387214E-3</v>
+      </c>
+      <c r="AL310">
+        <v>5.0594087773407504E-3</v>
+      </c>
+    </row>
+    <row r="311" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <v>46203</v>
       </c>
@@ -26897,8 +29306,17 @@
       <c r="AH311">
         <v>14550.474999999999</v>
       </c>
-    </row>
-    <row r="312" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ311">
+        <v>3.9857270786942123E-3</v>
+      </c>
+      <c r="AK311">
+        <v>4.8509918666713751E-3</v>
+      </c>
+      <c r="AL311">
+        <v>5.1037752728057429E-3</v>
+      </c>
+    </row>
+    <row r="312" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <v>46204</v>
       </c>
@@ -26992,8 +29410,17 @@
       <c r="AH312">
         <v>14806.474999999999</v>
       </c>
-    </row>
-    <row r="313" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ312">
+        <v>3.9857270786942123E-3</v>
+      </c>
+      <c r="AK312">
+        <v>5.0590465553323949E-3</v>
+      </c>
+      <c r="AL312">
+        <v>5.1533032654677517E-3</v>
+      </c>
+    </row>
+    <row r="313" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <v>46205</v>
       </c>
@@ -27087,8 +29514,17 @@
       <c r="AH313">
         <v>14806.474999999999</v>
       </c>
-    </row>
-    <row r="314" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ313">
+        <v>5.0002383344923277E-3</v>
+      </c>
+      <c r="AK313">
+        <v>5.2942368326858247E-3</v>
+      </c>
+      <c r="AL313">
+        <v>5.2471227322377348E-3</v>
+      </c>
+    </row>
+    <row r="314" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>46206</v>
       </c>
@@ -27182,8 +29618,17 @@
       <c r="AH314">
         <v>14806.474999999999</v>
       </c>
-    </row>
-    <row r="315" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ314">
+        <v>4.85540509064238E-3</v>
+      </c>
+      <c r="AK314">
+        <v>5.2195407499942567E-3</v>
+      </c>
+      <c r="AL314">
+        <v>5.2636293084224739E-3</v>
+      </c>
+    </row>
+    <row r="315" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>46209</v>
       </c>
@@ -27277,8 +29722,17 @@
       <c r="AH315">
         <v>14806.474999999999</v>
       </c>
-    </row>
-    <row r="316" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ315">
+        <v>4.5936622293622931E-3</v>
+      </c>
+      <c r="AK315">
+        <v>5.2140127166292044E-3</v>
+      </c>
+      <c r="AL315">
+        <v>5.2930366911068611E-3</v>
+      </c>
+    </row>
+    <row r="316" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
         <v>46210</v>
       </c>
@@ -27372,8 +29826,17 @@
       <c r="AH316">
         <v>14806.474999999999</v>
       </c>
-    </row>
-    <row r="317" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ316">
+        <v>5.2854659409626251E-3</v>
+      </c>
+      <c r="AK316">
+        <v>5.2674912637504347E-3</v>
+      </c>
+      <c r="AL316">
+        <v>5.3518249110636115E-3</v>
+      </c>
+    </row>
+    <row r="317" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A317" s="1">
         <v>46211</v>
       </c>
@@ -27467,8 +29930,17 @@
       <c r="AH317">
         <v>15026.974999999999</v>
       </c>
-    </row>
-    <row r="318" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ317">
+        <v>5.7251537541813243E-3</v>
+      </c>
+      <c r="AK317">
+        <v>5.2008852032056595E-3</v>
+      </c>
+      <c r="AL317">
+        <v>5.3811099289183071E-3</v>
+      </c>
+    </row>
+    <row r="318" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>46212</v>
       </c>
@@ -27562,8 +30034,17 @@
       <c r="AH318">
         <v>15026.974999999999</v>
       </c>
-    </row>
-    <row r="319" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ318">
+        <v>5.7836990528845342E-3</v>
+      </c>
+      <c r="AK318">
+        <v>5.3763868742250356E-3</v>
+      </c>
+      <c r="AL318">
+        <v>5.4300475528342397E-3</v>
+      </c>
+    </row>
+    <row r="319" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>46213</v>
       </c>
@@ -27657,8 +30138,17 @@
       <c r="AH319">
         <v>15205.65</v>
       </c>
-    </row>
-    <row r="320" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ319">
+        <v>5.2731578698851636E-3</v>
+      </c>
+      <c r="AK319">
+        <v>5.2515421917238413E-3</v>
+      </c>
+      <c r="AL319">
+        <v>5.3812437975209486E-3</v>
+      </c>
+    </row>
+    <row r="320" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>46216</v>
       </c>
@@ -27752,8 +30242,17 @@
       <c r="AH320">
         <v>15370.55</v>
       </c>
-    </row>
-    <row r="321" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ320">
+        <v>4.5094535100780476E-3</v>
+      </c>
+      <c r="AK320">
+        <v>5.1562586976789211E-3</v>
+      </c>
+      <c r="AL320">
+        <v>5.3306414906135738E-3</v>
+      </c>
+    </row>
+    <row r="321" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
         <v>46217</v>
       </c>
@@ -27847,8 +30346,17 @@
       <c r="AH321">
         <v>15799.95</v>
       </c>
-    </row>
-    <row r="322" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ321">
+        <v>4.2305123991613304E-3</v>
+      </c>
+      <c r="AK321">
+        <v>5.0775819279735941E-3</v>
+      </c>
+      <c r="AL321">
+        <v>5.3052371674130261E-3</v>
+      </c>
+    </row>
+    <row r="322" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
         <v>46218</v>
       </c>
@@ -27942,8 +30450,17 @@
       <c r="AH322">
         <v>15799.95</v>
       </c>
-    </row>
-    <row r="323" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ322">
+        <v>4.484360888714004E-3</v>
+      </c>
+      <c r="AK322">
+        <v>5.0719554395915892E-3</v>
+      </c>
+      <c r="AL322">
+        <v>5.2936669163945642E-3</v>
+      </c>
+    </row>
+    <row r="323" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A323" s="1">
         <v>46219</v>
       </c>
@@ -28037,8 +30554,17 @@
       <c r="AH323">
         <v>16223.75</v>
       </c>
-    </row>
-    <row r="324" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ323">
+        <v>4.1061542390075974E-3</v>
+      </c>
+      <c r="AK323">
+        <v>4.9786751870370379E-3</v>
+      </c>
+      <c r="AL323">
+        <v>5.2524134952056699E-3</v>
+      </c>
+    </row>
+    <row r="324" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>46220</v>
       </c>
@@ -28132,8 +30658,17 @@
       <c r="AH324">
         <v>15805.400000000001</v>
       </c>
-    </row>
-    <row r="325" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ324">
+        <v>4.3596116744700607E-3</v>
+      </c>
+      <c r="AK324">
+        <v>5.0314764882795383E-3</v>
+      </c>
+      <c r="AL324">
+        <v>5.2707920029109422E-3</v>
+      </c>
+    </row>
+    <row r="325" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>46223</v>
       </c>
@@ -28227,8 +30762,17 @@
       <c r="AH325">
         <v>15805.400000000001</v>
       </c>
-    </row>
-    <row r="326" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ325">
+        <v>4.2970560702632488E-3</v>
+      </c>
+      <c r="AK325">
+        <v>5.0128894698392859E-3</v>
+      </c>
+      <c r="AL325">
+        <v>5.2539001656448613E-3</v>
+      </c>
+    </row>
+    <row r="326" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>46224</v>
       </c>
@@ -28322,8 +30866,17 @@
       <c r="AH326">
         <v>15805.400000000001</v>
       </c>
-    </row>
-    <row r="327" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ326">
+        <v>4.7244642932676162E-3</v>
+      </c>
+      <c r="AK326">
+        <v>4.9906713360378489E-3</v>
+      </c>
+      <c r="AL326">
+        <v>5.2864414226007342E-3</v>
+      </c>
+    </row>
+    <row r="327" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>46225</v>
       </c>
@@ -28417,8 +30970,17 @@
       <c r="AH327">
         <v>15370.55</v>
       </c>
-    </row>
-    <row r="328" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ327">
+        <v>5.0268573746428324E-3</v>
+      </c>
+      <c r="AK327">
+        <v>4.9694018083173671E-3</v>
+      </c>
+      <c r="AL327">
+        <v>5.2685924029599223E-3</v>
+      </c>
+    </row>
+    <row r="328" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>46227</v>
       </c>
@@ -28512,8 +31074,17 @@
       <c r="AH328">
         <v>15205.65</v>
       </c>
-    </row>
-    <row r="329" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ328">
+        <v>5.0151657647946627E-3</v>
+      </c>
+      <c r="AK328">
+        <v>4.8307240618577947E-3</v>
+      </c>
+      <c r="AL328">
+        <v>5.2721238851984875E-3</v>
+      </c>
+    </row>
+    <row r="329" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
         <v>46230</v>
       </c>
@@ -28607,8 +31178,17 @@
       <c r="AH329">
         <v>15370.55</v>
       </c>
-    </row>
-    <row r="330" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ329">
+        <v>4.6238446132540563E-3</v>
+      </c>
+      <c r="AK329">
+        <v>4.8264467889492495E-3</v>
+      </c>
+      <c r="AL329">
+        <v>5.2294950913535287E-3</v>
+      </c>
+    </row>
+    <row r="330" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
         <v>46233</v>
       </c>
@@ -28702,8 +31282,17 @@
       <c r="AH330">
         <v>15370.55</v>
       </c>
-    </row>
-    <row r="331" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ330">
+        <v>4.9275790468643272E-3</v>
+      </c>
+      <c r="AK330">
+        <v>4.8659613559231428E-3</v>
+      </c>
+      <c r="AL330">
+        <v>5.1605282293333736E-3</v>
+      </c>
+    </row>
+    <row r="331" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
         <v>46234</v>
       </c>
@@ -28797,8 +31386,17 @@
       <c r="AH331">
         <v>15805.400000000001</v>
       </c>
-    </row>
-    <row r="332" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ331">
+        <v>4.6752374289383601E-3</v>
+      </c>
+      <c r="AK331">
+        <v>4.8049623671078037E-3</v>
+      </c>
+      <c r="AL331">
+        <v>5.1285676925254898E-3</v>
+      </c>
+    </row>
+    <row r="332" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>46237</v>
       </c>
@@ -28892,8 +31490,17 @@
       <c r="AH332">
         <v>16021.7</v>
       </c>
-    </row>
-    <row r="333" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ332">
+        <v>4.2845028929918618E-3</v>
+      </c>
+      <c r="AK332">
+        <v>4.6974501812342079E-3</v>
+      </c>
+      <c r="AL332">
+        <v>5.0809170761807456E-3</v>
+      </c>
+    </row>
+    <row r="333" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>46238</v>
       </c>
@@ -28987,8 +31594,17 @@
       <c r="AH333">
         <v>15597.900000000001</v>
       </c>
-    </row>
-    <row r="334" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ333">
+        <v>3.9692161020985009E-3</v>
+      </c>
+      <c r="AK333">
+        <v>4.604855941520756E-3</v>
+      </c>
+      <c r="AL333">
+        <v>5.0380291666697937E-3</v>
+      </c>
+    </row>
+    <row r="334" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
         <v>46239</v>
       </c>
@@ -29082,8 +31698,17 @@
       <c r="AH334">
         <v>15370.55</v>
       </c>
-    </row>
-    <row r="335" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ334">
+        <v>3.4644220629013356E-3</v>
+      </c>
+      <c r="AK334">
+        <v>4.4678583244311511E-3</v>
+      </c>
+      <c r="AL334">
+        <v>4.9804018045129898E-3</v>
+      </c>
+    </row>
+    <row r="335" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
         <v>46241</v>
       </c>
@@ -29177,8 +31802,17 @@
       <c r="AH335">
         <v>15370.55</v>
       </c>
-    </row>
-    <row r="336" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ335">
+        <v>3.4133070529652502E-3</v>
+      </c>
+      <c r="AK335">
+        <v>4.3187485223012256E-3</v>
+      </c>
+      <c r="AL335">
+        <v>4.9291173341521471E-3</v>
+      </c>
+    </row>
+    <row r="336" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>46244</v>
       </c>
@@ -29272,8 +31906,17 @@
       <c r="AH336">
         <v>15319.65</v>
       </c>
-    </row>
-    <row r="337" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ336">
+        <v>3.1726847947253596E-3</v>
+      </c>
+      <c r="AK336">
+        <v>4.3181164055555834E-3</v>
+      </c>
+      <c r="AL336">
+        <v>4.8676626288514831E-3</v>
+      </c>
+    </row>
+    <row r="337" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>46245</v>
       </c>
@@ -29367,8 +32010,17 @@
       <c r="AH337">
         <v>15213.34</v>
       </c>
-    </row>
-    <row r="338" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ337">
+        <v>2.8689503611150882E-3</v>
+      </c>
+      <c r="AK337">
+        <v>4.2634215884490628E-3</v>
+      </c>
+      <c r="AL337">
+        <v>4.8766627413083337E-3</v>
+      </c>
+    </row>
+    <row r="338" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
         <v>46246</v>
       </c>
@@ -29462,8 +32114,17 @@
       <c r="AH338">
         <v>15213.34</v>
       </c>
-    </row>
-    <row r="339" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ338">
+        <v>2.4892936905312169E-3</v>
+      </c>
+      <c r="AK338">
+        <v>4.1140220551059885E-3</v>
+      </c>
+      <c r="AL338">
+        <v>4.8148762717548747E-3</v>
+      </c>
+    </row>
+    <row r="339" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
         <v>46247</v>
       </c>
@@ -29557,8 +32218,17 @@
       <c r="AH339">
         <v>15213.34</v>
       </c>
-    </row>
-    <row r="340" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ339">
+        <v>2.5639871623352123E-3</v>
+      </c>
+      <c r="AK339">
+        <v>4.1871947028812384E-3</v>
+      </c>
+      <c r="AL339">
+        <v>4.8235149667239987E-3</v>
+      </c>
+    </row>
+    <row r="340" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>46248</v>
       </c>
@@ -29652,8 +32322,17 @@
       <c r="AH340">
         <v>15213.34</v>
       </c>
-    </row>
-    <row r="341" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ340">
+        <v>2.1336904887445771E-3</v>
+      </c>
+      <c r="AK340">
+        <v>4.1573090143306015E-3</v>
+      </c>
+      <c r="AL340">
+        <v>4.7977876259584998E-3</v>
+      </c>
+    </row>
+    <row r="341" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>46251</v>
       </c>
@@ -29747,8 +32426,17 @@
       <c r="AH341">
         <v>15213.34</v>
       </c>
-    </row>
-    <row r="342" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ341">
+        <v>1.9055269979274439E-3</v>
+      </c>
+      <c r="AK341">
+        <v>3.982478305585571E-3</v>
+      </c>
+      <c r="AL341">
+        <v>4.7832030326653277E-3</v>
+      </c>
+    </row>
+    <row r="342" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
         <v>46252</v>
       </c>
@@ -29842,8 +32530,17 @@
       <c r="AH342">
         <v>15319.65</v>
       </c>
-    </row>
-    <row r="343" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ342">
+        <v>2.53590826315683E-3</v>
+      </c>
+      <c r="AK342">
+        <v>3.9804574653425013E-3</v>
+      </c>
+      <c r="AL342">
+        <v>4.7696525927865543E-3</v>
+      </c>
+    </row>
+    <row r="343" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A343" s="1">
         <v>46253</v>
       </c>
@@ -29937,8 +32634,17 @@
       <c r="AH343">
         <v>15319.65</v>
       </c>
-    </row>
-    <row r="344" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ343">
+        <v>3.1670699103637026E-3</v>
+      </c>
+      <c r="AK343">
+        <v>3.8903771065922363E-3</v>
+      </c>
+      <c r="AL343">
+        <v>4.8077116865566927E-3</v>
+      </c>
+    </row>
+    <row r="344" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A344" s="1">
         <v>46254</v>
       </c>
@@ -30032,8 +32738,17 @@
       <c r="AH344">
         <v>15319.65</v>
       </c>
-    </row>
-    <row r="345" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ344">
+        <v>3.4708043439739739E-3</v>
+      </c>
+      <c r="AK344">
+        <v>3.9403480808931019E-3</v>
+      </c>
+      <c r="AL344">
+        <v>4.8192758231736235E-3</v>
+      </c>
+    </row>
+    <row r="345" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>46255</v>
       </c>
@@ -30127,8 +32842,17 @@
       <c r="AH345">
         <v>15319.65</v>
       </c>
-    </row>
-    <row r="346" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ345">
+        <v>4.0019620361308071E-3</v>
+      </c>
+      <c r="AK345">
+        <v>3.9759586766853093E-3</v>
+      </c>
+      <c r="AL345">
+        <v>4.8495221478872374E-3</v>
+      </c>
+    </row>
+    <row r="346" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
         <v>46258</v>
       </c>
@@ -30222,8 +32946,17 @@
       <c r="AH346">
         <v>15213.34</v>
       </c>
-    </row>
-    <row r="347" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ346">
+        <v>4.2804991799451093E-3</v>
+      </c>
+      <c r="AK346">
+        <v>3.9527024586438171E-3</v>
+      </c>
+      <c r="AL346">
+        <v>4.8337314922666571E-3</v>
+      </c>
+    </row>
+    <row r="347" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A347" s="1">
         <v>46259</v>
       </c>
@@ -30317,8 +33050,17 @@
       <c r="AH347">
         <v>15099.34</v>
       </c>
-    </row>
-    <row r="348" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ347">
+        <v>4.6476547390148391E-3</v>
+      </c>
+      <c r="AK347">
+        <v>3.9058925774584216E-3</v>
+      </c>
+      <c r="AL347">
+        <v>4.8159569928642879E-3</v>
+      </c>
+    </row>
+    <row r="348" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A348" s="1">
         <v>46260</v>
       </c>
@@ -30412,8 +33154,17 @@
       <c r="AH348">
         <v>15099.34</v>
       </c>
-    </row>
-    <row r="349" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ348">
+        <v>5.0148540287820375E-3</v>
+      </c>
+      <c r="AK348">
+        <v>3.8030811332949877E-3</v>
+      </c>
+      <c r="AL348">
+        <v>4.8301190455297066E-3</v>
+      </c>
+    </row>
+    <row r="349" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>46261</v>
       </c>
@@ -30507,8 +33258,17 @@
       <c r="AH349">
         <v>15213.34</v>
       </c>
-    </row>
-    <row r="350" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ349">
+        <v>4.574623572438802E-3</v>
+      </c>
+      <c r="AK349">
+        <v>3.817466129271683E-3</v>
+      </c>
+      <c r="AL349">
+        <v>4.7927730202688779E-3</v>
+      </c>
+    </row>
+    <row r="350" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>46262</v>
       </c>
@@ -30602,8 +33362,17 @@
       <c r="AH350">
         <v>15099.34</v>
       </c>
-    </row>
-    <row r="351" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ350">
+        <v>4.1336127341180806E-3</v>
+      </c>
+      <c r="AK350">
+        <v>3.8026809255349093E-3</v>
+      </c>
+      <c r="AL350">
+        <v>4.7762190328152956E-3</v>
+      </c>
+    </row>
+    <row r="351" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>46265</v>
       </c>
@@ -30697,8 +33466,17 @@
       <c r="AH351">
         <v>15099.34</v>
       </c>
-    </row>
-    <row r="352" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AJ351">
+        <v>4.2112147763817319E-3</v>
+      </c>
+      <c r="AK351">
+        <v>3.9358453022445266E-3</v>
+      </c>
+      <c r="AL351">
+        <v>4.7743853334588074E-3</v>
+      </c>
+    </row>
+    <row r="352" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>46266</v>
       </c>
@@ -30792,8 +33570,17 @@
       <c r="AH352">
         <v>15026.974999999999</v>
       </c>
-    </row>
-    <row r="353" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ352">
+        <v>4.1877604942212104E-3</v>
+      </c>
+      <c r="AK352">
+        <v>3.9067519179703221E-3</v>
+      </c>
+      <c r="AL352">
+        <v>4.7620984818546796E-3</v>
+      </c>
+    </row>
+    <row r="353" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>46267</v>
       </c>
@@ -30887,8 +33674,17 @@
       <c r="AH353">
         <v>15026.974999999999</v>
       </c>
-    </row>
-    <row r="354" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ353">
+        <v>4.233586614105684E-3</v>
+      </c>
+      <c r="AK353">
+        <v>3.9499406793883675E-3</v>
+      </c>
+      <c r="AL353">
+        <v>4.7606592910839456E-3</v>
+      </c>
+    </row>
+    <row r="354" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>46268</v>
       </c>
@@ -30982,8 +33778,17 @@
       <c r="AH354">
         <v>15099.34</v>
       </c>
-    </row>
-    <row r="355" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ354">
+        <v>4.2794127339901566E-3</v>
+      </c>
+      <c r="AK354">
+        <v>3.9931294408064137E-3</v>
+      </c>
+      <c r="AL354">
+        <v>4.7592201003132115E-3</v>
+      </c>
+    </row>
+    <row r="355" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>46269</v>
       </c>
@@ -31077,8 +33882,17 @@
       <c r="AH355">
         <v>15026.974999999999</v>
       </c>
-    </row>
-    <row r="356" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ355">
+        <v>4.5020484214727263E-3</v>
+      </c>
+      <c r="AK355">
+        <v>3.9921027931556947E-3</v>
+      </c>
+      <c r="AL355">
+        <v>4.7426653564402116E-3</v>
+      </c>
+    </row>
+    <row r="356" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>46272</v>
       </c>
@@ -31172,8 +33986,17 @@
       <c r="AH356">
         <v>15026.974999999999</v>
       </c>
-    </row>
-    <row r="357" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ356">
+        <v>4.7246841089552969E-3</v>
+      </c>
+      <c r="AK356">
+        <v>3.9910761455049758E-3</v>
+      </c>
+      <c r="AL356">
+        <v>4.7261106125672117E-3</v>
+      </c>
+    </row>
+    <row r="357" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>46273</v>
       </c>
@@ -31267,8 +34090,17 @@
       <c r="AH357">
         <v>14806.474999999999</v>
       </c>
-    </row>
-    <row r="358" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ357">
+        <v>5.1445609426687775E-3</v>
+      </c>
+      <c r="AK357">
+        <v>4.0008322701896104E-3</v>
+      </c>
+      <c r="AL357">
+        <v>4.723289250013126E-3</v>
+      </c>
+    </row>
+    <row r="358" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>46274</v>
       </c>
@@ -31362,8 +34194,17 @@
       <c r="AH358">
         <v>14806.474999999999</v>
       </c>
-    </row>
-    <row r="359" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ358">
+        <v>5.5387684572474408E-3</v>
+      </c>
+      <c r="AK358">
+        <v>4.0074704342003085E-3</v>
+      </c>
+      <c r="AL358">
+        <v>4.7285769028422991E-3</v>
+      </c>
+    </row>
+    <row r="359" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>46275</v>
       </c>
@@ -31457,8 +34298,17 @@
       <c r="AH359">
         <v>14583.625</v>
       </c>
-    </row>
-    <row r="360" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ359">
+        <v>5.7297905963120694E-3</v>
+      </c>
+      <c r="AK359">
+        <v>3.9666986772577319E-3</v>
+      </c>
+      <c r="AL359">
+        <v>4.7068096005731088E-3</v>
+      </c>
+    </row>
+    <row r="360" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>46276</v>
       </c>
@@ -31555,8 +34405,17 @@
       <c r="AI360">
         <v>10262.950000000001</v>
       </c>
-    </row>
-    <row r="361" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ360">
+        <v>5.4644736041006186E-3</v>
+      </c>
+      <c r="AK360">
+        <v>4.0406837980825833E-3</v>
+      </c>
+      <c r="AL360">
+        <v>4.6839678461136009E-3</v>
+      </c>
+    </row>
+    <row r="361" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>46279</v>
       </c>
@@ -31662,8 +34521,17 @@
       <c r="AI361">
         <v>10402.799999999999</v>
       </c>
-    </row>
-    <row r="362" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ361">
+        <v>5.5795801260300837E-3</v>
+      </c>
+      <c r="AK361">
+        <v>4.1297568709513953E-3</v>
+      </c>
+      <c r="AL361">
+        <v>4.680699188006128E-3</v>
+      </c>
+    </row>
+    <row r="362" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>46280</v>
       </c>
@@ -31769,8 +34637,17 @@
       <c r="AI362">
         <v>10402.799999999999</v>
       </c>
-    </row>
-    <row r="363" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ362">
+        <v>5.3381080132825168E-3</v>
+      </c>
+      <c r="AK362">
+        <v>4.0889195329706579E-3</v>
+      </c>
+      <c r="AL362">
+        <v>4.6902880512792143E-3</v>
+      </c>
+    </row>
+    <row r="363" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>46281</v>
       </c>
@@ -31876,8 +34753,17 @@
       <c r="AI363">
         <v>10262.950000000001</v>
       </c>
-    </row>
-    <row r="364" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ363">
+        <v>5.3370210268570946E-3</v>
+      </c>
+      <c r="AK363">
+        <v>4.1454923183526808E-3</v>
+      </c>
+      <c r="AL363">
+        <v>4.7174008570109484E-3</v>
+      </c>
+    </row>
+    <row r="364" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A364" s="1">
         <v>46282</v>
       </c>
@@ -31983,8 +34869,17 @@
       <c r="AI364">
         <v>10229.825000000001</v>
       </c>
-    </row>
-    <row r="365" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ364">
+        <v>5.3493573833636914E-3</v>
+      </c>
+      <c r="AK364">
+        <v>4.2492983179430377E-3</v>
+      </c>
+      <c r="AL364">
+        <v>4.7364085857095166E-3</v>
+      </c>
+    </row>
+    <row r="365" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A365" s="1">
         <v>46283</v>
       </c>
@@ -32090,8 +34985,17 @@
       <c r="AI365">
         <v>10229.825000000001</v>
       </c>
-    </row>
-    <row r="366" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ365">
+        <v>5.3996895639404213E-3</v>
+      </c>
+      <c r="AK365">
+        <v>4.3412475752967567E-3</v>
+      </c>
+      <c r="AL365">
+        <v>4.7137206436387623E-3</v>
+      </c>
+    </row>
+    <row r="366" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
         <v>46286</v>
       </c>
@@ -32197,8 +35101,17 @@
       <c r="AI366">
         <v>10229.825000000001</v>
       </c>
-    </row>
-    <row r="367" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ366">
+        <v>5.5137392856714207E-3</v>
+      </c>
+      <c r="AK366">
+        <v>4.4448726959040851E-3</v>
+      </c>
+      <c r="AL366">
+        <v>4.7005632154649441E-3</v>
+      </c>
+    </row>
+    <row r="367" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>46287</v>
       </c>
@@ -32304,8 +35217,17 @@
       <c r="AI367">
         <v>10191.35</v>
       </c>
-    </row>
-    <row r="368" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ367">
+        <v>5.7885803122797157E-3</v>
+      </c>
+      <c r="AK367">
+        <v>4.5949142252559591E-3</v>
+      </c>
+      <c r="AL367">
+        <v>4.6989023116553886E-3</v>
+      </c>
+    </row>
+    <row r="368" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
         <v>46288</v>
       </c>
@@ -32411,8 +35333,17 @@
       <c r="AI368">
         <v>10191.35</v>
       </c>
-    </row>
-    <row r="369" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ368">
+        <v>5.6830234293739129E-3</v>
+      </c>
+      <c r="AK368">
+        <v>4.7155025523693914E-3</v>
+      </c>
+      <c r="AL368">
+        <v>4.7078949491046584E-3</v>
+      </c>
+    </row>
+    <row r="369" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A369" s="1">
         <v>46289</v>
       </c>
@@ -32518,8 +35449,17 @@
       <c r="AI369">
         <v>10166.85</v>
       </c>
-    </row>
-    <row r="370" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ369">
+        <v>5.8189386592156769E-3</v>
+      </c>
+      <c r="AK369">
+        <v>4.7772501358607951E-3</v>
+      </c>
+      <c r="AL369">
+        <v>4.6915488774623582E-3</v>
+      </c>
+    </row>
+    <row r="370" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A370" s="1">
         <v>46290</v>
       </c>
@@ -32625,8 +35565,17 @@
       <c r="AI370">
         <v>10166.85</v>
       </c>
-    </row>
-    <row r="371" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ370">
+        <v>5.0474640902995254E-3</v>
+      </c>
+      <c r="AK370">
+        <v>4.7423987449652849E-3</v>
+      </c>
+      <c r="AL370">
+        <v>4.6893935900647384E-3</v>
+      </c>
+    </row>
+    <row r="371" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A371" s="1">
         <v>46293</v>
       </c>
@@ -32732,8 +35681,17 @@
       <c r="AI371">
         <v>10191.35</v>
       </c>
-    </row>
-    <row r="372" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ371">
+        <v>6.0821776893618647E-3</v>
+      </c>
+      <c r="AK371">
+        <v>5.0702094409159218E-3</v>
+      </c>
+      <c r="AL371">
+        <v>4.7670575641165372E-3</v>
+      </c>
+    </row>
+    <row r="372" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>46294</v>
       </c>
@@ -32839,8 +35797,17 @@
       <c r="AI372">
         <v>10191.35</v>
       </c>
-    </row>
-    <row r="373" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ372">
+        <v>6.106858947102574E-3</v>
+      </c>
+      <c r="AK372">
+        <v>5.2683202155802879E-3</v>
+      </c>
+      <c r="AL372">
+        <v>4.7670575641165372E-3</v>
+      </c>
+    </row>
+    <row r="373" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A373" s="1">
         <v>46295</v>
       </c>
@@ -32946,8 +35913,17 @@
       <c r="AI373">
         <v>10191.35</v>
       </c>
-    </row>
-    <row r="374" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ373">
+        <v>5.6201801301303169E-3</v>
+      </c>
+      <c r="AK373">
+        <v>5.3116250934180879E-3</v>
+      </c>
+      <c r="AL373">
+        <v>4.7150317552250116E-3</v>
+      </c>
+    </row>
+    <row r="374" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A374" s="1">
         <v>46296</v>
       </c>
@@ -33053,8 +36029,17 @@
       <c r="AI374">
         <v>10229.825000000001</v>
       </c>
-    </row>
-    <row r="375" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ374">
+        <v>5.6365167661188232E-3</v>
+      </c>
+      <c r="AK374">
+        <v>5.3183895426137566E-3</v>
+      </c>
+      <c r="AL374">
+        <v>4.7859645210962176E-3</v>
+      </c>
+    </row>
+    <row r="375" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
         <v>46297</v>
       </c>
@@ -33160,8 +36145,17 @@
       <c r="AI375">
         <v>10191.35</v>
       </c>
-    </row>
-    <row r="376" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ375">
+        <v>5.7790814117006503E-3</v>
+      </c>
+      <c r="AK375">
+        <v>5.3249719026813467E-3</v>
+      </c>
+      <c r="AL375">
+        <v>4.836528613986469E-3</v>
+      </c>
+    </row>
+    <row r="376" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>46300</v>
       </c>
@@ -33267,8 +36261,17 @@
       <c r="AI376">
         <v>10166.85</v>
       </c>
-    </row>
-    <row r="377" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ376">
+        <v>5.9208150844313823E-3</v>
+      </c>
+      <c r="AK376">
+        <v>5.3489193086341917E-3</v>
+      </c>
+      <c r="AL376">
+        <v>4.8362693798405165E-3</v>
+      </c>
+    </row>
+    <row r="377" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>46301</v>
       </c>
@@ -33374,8 +36377,17 @@
       <c r="AI377">
         <v>10133.625</v>
       </c>
-    </row>
-    <row r="378" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ377">
+        <v>6.4688329868179207E-3</v>
+      </c>
+      <c r="AK377">
+        <v>5.3180019667922792E-3</v>
+      </c>
+      <c r="AL377">
+        <v>4.8359911200355973E-3</v>
+      </c>
+    </row>
+    <row r="378" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>46302</v>
       </c>
@@ -33481,8 +36493,17 @@
       <c r="AI378">
         <v>10047.755000000001</v>
       </c>
-    </row>
-    <row r="379" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ378">
+        <v>5.4507397882522114E-3</v>
+      </c>
+      <c r="AK378">
+        <v>5.3432655828542473E-3</v>
+      </c>
+      <c r="AL378">
+        <v>4.8544864350828333E-3</v>
+      </c>
+    </row>
+    <row r="379" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>46304</v>
       </c>
@@ -33588,8 +36609,17 @@
       <c r="AI379">
         <v>10133.625</v>
       </c>
-    </row>
-    <row r="380" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ379">
+        <v>5.4319683117904898E-3</v>
+      </c>
+      <c r="AK379">
+        <v>5.4513267158946077E-3</v>
+      </c>
+      <c r="AL379">
+        <v>4.8527014988528957E-3</v>
+      </c>
+    </row>
+    <row r="380" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>46307</v>
       </c>
@@ -33695,8 +36725,17 @@
       <c r="AI380">
         <v>10166.85</v>
       </c>
-    </row>
-    <row r="381" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ380">
+        <v>5.7544896750588853E-3</v>
+      </c>
+      <c r="AK380">
+        <v>5.5053942224366258E-3</v>
+      </c>
+      <c r="AL380">
+        <v>4.8828390388428924E-3</v>
+      </c>
+    </row>
+    <row r="381" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>46308</v>
       </c>
@@ -33802,8 +36841,17 @@
       <c r="AI381">
         <v>10166.85</v>
       </c>
-    </row>
-    <row r="382" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ381">
+        <v>6.0770110383272817E-3</v>
+      </c>
+      <c r="AK381">
+        <v>5.5594617289786439E-3</v>
+      </c>
+      <c r="AL381">
+        <v>4.9129765788328891E-3</v>
+      </c>
+    </row>
+    <row r="382" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
         <v>46309</v>
       </c>
@@ -33909,8 +36957,17 @@
       <c r="AI382">
         <v>10133.625</v>
       </c>
-    </row>
-    <row r="383" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ382">
+        <v>6.0558179237264883E-3</v>
+      </c>
+      <c r="AK382">
+        <v>5.6640015579142158E-3</v>
+      </c>
+      <c r="AL382">
+        <v>4.9110032929699137E-3</v>
+      </c>
+    </row>
+    <row r="383" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A383" s="1">
         <v>46310</v>
       </c>
@@ -34016,8 +37073,17 @@
       <c r="AI383">
         <v>10133.625</v>
       </c>
-    </row>
-    <row r="384" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ383">
+        <v>5.7887784605581537E-3</v>
+      </c>
+      <c r="AK383">
+        <v>5.7111772388506949E-3</v>
+      </c>
+      <c r="AL383">
+        <v>4.8900389540215087E-3</v>
+      </c>
+    </row>
+    <row r="384" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A384" s="1">
         <v>46311</v>
       </c>
@@ -34123,8 +37189,17 @@
       <c r="AI384">
         <v>10133.625</v>
       </c>
-    </row>
-    <row r="385" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ384">
+        <v>5.7684163188084564E-3</v>
+      </c>
+      <c r="AK384">
+        <v>5.7122663352004244E-3</v>
+      </c>
+      <c r="AL384">
+        <v>4.9085645218061814E-3</v>
+      </c>
+    </row>
+    <row r="385" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A385" s="1">
         <v>46314</v>
       </c>
@@ -34230,8 +37305,17 @@
       <c r="AI385">
         <v>10047.755000000001</v>
       </c>
-    </row>
-    <row r="386" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ385">
+        <v>6.0051776014468971E-3</v>
+      </c>
+      <c r="AK385">
+        <v>5.74206595847827E-3</v>
+      </c>
+      <c r="AL385">
+        <v>4.9069244386800602E-3</v>
+      </c>
+    </row>
+    <row r="386" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
         <v>46315</v>
       </c>
@@ -34337,8 +37421,17 @@
       <c r="AI386">
         <v>10047.755000000001</v>
       </c>
-    </row>
-    <row r="387" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ386">
+        <v>5.7444586549534474E-3</v>
+      </c>
+      <c r="AK386">
+        <v>5.6851096310790135E-3</v>
+      </c>
+      <c r="AL386">
+        <v>4.8856380863074875E-3</v>
+      </c>
+    </row>
+    <row r="387" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A387" s="1">
         <v>46316</v>
       </c>
@@ -34444,8 +37537,17 @@
       <c r="AI387">
         <v>10047.755000000001</v>
       </c>
-    </row>
-    <row r="388" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ387">
+        <v>5.3009788260525419E-3</v>
+      </c>
+      <c r="AK387">
+        <v>5.5857954832172962E-3</v>
+      </c>
+      <c r="AL387">
+        <v>4.8694493723339359E-3</v>
+      </c>
+    </row>
+    <row r="388" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A388" s="1">
         <v>46317</v>
       </c>
@@ -34551,8 +37653,17 @@
       <c r="AI388">
         <v>10047.755000000001</v>
       </c>
-    </row>
-    <row r="389" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ388">
+        <v>5.2823623951737562E-3</v>
+      </c>
+      <c r="AK388">
+        <v>5.5916154012298058E-3</v>
+      </c>
+      <c r="AL388">
+        <v>4.8684457137529013E-3</v>
+      </c>
+    </row>
+    <row r="389" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A389" s="1">
         <v>46318</v>
       </c>
@@ -34658,8 +37769,17 @@
       <c r="AI389">
         <v>10047.755000000001</v>
       </c>
-    </row>
-    <row r="390" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ389">
+        <v>4.5076491481579953E-3</v>
+      </c>
+      <c r="AK389">
+        <v>5.4234070524600136E-3</v>
+      </c>
+      <c r="AL389">
+        <v>4.8071829408993889E-3</v>
+      </c>
+    </row>
+    <row r="390" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A390" s="1">
         <v>46321</v>
       </c>
@@ -34670,7 +37790,7 @@
         <v>149015621.7863636</v>
       </c>
       <c r="D390" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E390">
         <v>2105</v>
@@ -34764,6 +37884,15 @@
       </c>
       <c r="AI390">
         <v>9958.755000000001</v>
+      </c>
+      <c r="AJ390">
+        <v>4.7623810174793899E-3</v>
+      </c>
+      <c r="AK390">
+        <v>5.4854483371230712E-3</v>
+      </c>
+      <c r="AL390">
+        <v>4.8071829408993889E-3</v>
       </c>
     </row>
   </sheetData>
@@ -34772,15 +37901,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="dd854d95-092e-48c7-992a-80d5cc5badc3" xsi:nil="true"/>
@@ -34789,6 +37909,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -35047,20 +38176,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="dd854d95-092e-48c7-992a-80d5cc5badc3"/>
     <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eldorado275.sharepoint.com/sites/Compartidos/Documentos compartidos/INVERSIONES/Claude - Fernando/Dashboards ETFs/Dashboards/ETFPESOV/General/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A688B8F-5C2B-445A-A3BB-047DF36C5700}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57B11A0A-CE08-4EF3-BAAE-5F89E49C8D9F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>Fecha</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AL390"/>
+  <dimension ref="A1:AT391"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -1570,7 +1570,7 @@
         <v>9.4562899082472809E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>45771</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>1.0801057445594512E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>45772</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>1.1793592036918684E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>45775</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>1.0740421153611178E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>45776</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>1.0740421153611178E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>45777</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>1.2154556386551293E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>45779</v>
       </c>
@@ -1941,8 +1941,9 @@
       <c r="AJ22">
         <v>1.285482056728012E-2</v>
       </c>
-    </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AT22" s="3"/>
+    </row>
+    <row r="23" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>45782</v>
       </c>
@@ -2004,7 +2005,7 @@
         <v>1.3645576960565222E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>45783</v>
       </c>
@@ -2066,7 +2067,7 @@
         <v>1.2512501749924378E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>45784</v>
       </c>
@@ -2128,7 +2129,7 @@
         <v>1.3069911383825291E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>45785</v>
       </c>
@@ -2190,7 +2191,7 @@
         <v>1.305590681133237E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>45786</v>
       </c>
@@ -2252,7 +2253,7 @@
         <v>1.1989955513331273E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>45789</v>
       </c>
@@ -2314,7 +2315,7 @@
         <v>1.1907012173202969E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>45790</v>
       </c>
@@ -2376,7 +2377,7 @@
         <v>1.2256028325144153E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>45791</v>
       </c>
@@ -2441,7 +2442,7 @@
         <v>1.2605044477085336E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>45792</v>
       </c>
@@ -2515,7 +2516,7 @@
         <v>1.3245775862324668E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>45793</v>
       </c>
@@ -37893,6 +37894,122 @@
       </c>
       <c r="AL390">
         <v>4.8071829408993889E-3</v>
+      </c>
+    </row>
+    <row r="391" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A391" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B391">
+        <v>110.57449367869984</v>
+      </c>
+      <c r="C391">
+        <v>148999130.23204803</v>
+      </c>
+      <c r="D391" t="s">
+        <v>22</v>
+      </c>
+      <c r="E391">
+        <v>9791</v>
+      </c>
+      <c r="F391">
+        <v>5</v>
+      </c>
+      <c r="G391">
+        <v>6.226820098201709</v>
+      </c>
+      <c r="H391">
+        <v>6.1319510640682253</v>
+      </c>
+      <c r="I391">
+        <v>181.7</v>
+      </c>
+      <c r="J391">
+        <v>6.31</v>
+      </c>
+      <c r="K391">
+        <v>6.1899999999999995</v>
+      </c>
+      <c r="L391">
+        <v>10.574493678699849</v>
+      </c>
+      <c r="M391">
+        <v>11.066965739931689</v>
+      </c>
+      <c r="N391">
+        <v>6.5804257815830098</v>
+      </c>
+      <c r="O391">
+        <v>6.59</v>
+      </c>
+      <c r="P391">
+        <v>5.4888054029206771E-3</v>
+      </c>
+      <c r="Q391">
+        <v>5.2228319617534423E-3</v>
+      </c>
+      <c r="R391">
+        <v>0.10782533668747564</v>
+      </c>
+      <c r="S391">
+        <v>0.15652405037970035</v>
+      </c>
+      <c r="T391">
+        <v>-3.1805983653443448E-2</v>
+      </c>
+      <c r="U391">
+        <v>-5.9616804372386589E-2</v>
+      </c>
+      <c r="V391">
+        <v>-0.22056025797478895</v>
+      </c>
+      <c r="W391">
+        <v>-0.65649731473331752</v>
+      </c>
+      <c r="X391">
+        <v>110.01</v>
+      </c>
+      <c r="Y391">
+        <v>-2.5227906761652652</v>
+      </c>
+      <c r="Z391">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA391" s="3">
+        <v>5.1050984718058467E-3</v>
+      </c>
+      <c r="AB391" s="3">
+        <v>5.983632672158434E-3</v>
+      </c>
+      <c r="AC391" s="3">
+        <v>5.2437821197458137E-3</v>
+      </c>
+      <c r="AD391" s="3">
+        <v>4.4697599667025273E-3</v>
+      </c>
+      <c r="AE391" s="3">
+        <v>5.0248974179157215E-3</v>
+      </c>
+      <c r="AF391">
+        <v>6823</v>
+      </c>
+      <c r="AG391">
+        <v>8662.9650000000001</v>
+      </c>
+      <c r="AH391">
+        <v>10634.04</v>
+      </c>
+      <c r="AI391">
+        <v>9877.625</v>
+      </c>
+      <c r="AJ391">
+        <v>4.7777889495442443E-3</v>
+      </c>
+      <c r="AK391">
+        <v>5.5520399158039396E-3</v>
+      </c>
+      <c r="AL391">
+        <v>4.8078159252481047E-3</v>
       </c>
     </row>
   </sheetData>
@@ -37901,26 +38018,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="dd854d95-092e-48c7-992a-80d5cc5badc3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006CC87EF38A8DD0408B89B7B34D0336DC" ma:contentTypeVersion="20" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a30c2ca5bc864785a186dec6b0346788">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe" xmlns:ns3="dd854d95-092e-48c7-992a-80d5cc5badc3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2932ec1554b414302dd4a6579c5666bc" ns2:_="" ns3:_="">
     <xsd:import namespace="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
@@ -38175,26 +38272,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="dd854d95-092e-48c7-992a-80d5cc5badc3"/>
-    <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="dd854d95-092e-48c7-992a-80d5cc5badc3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BABE8802-F313-4DEC-9147-95F411D9A097}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -38211,4 +38309,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dd854d95-092e-48c7-992a-80d5cc5badc3"/>
+    <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/ETFPESOV/General/Data-ETFPESOV.xlsx
+++ b/ETFPESOV/General/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eldorado275.sharepoint.com/sites/Compartidos/Documentos compartidos/INVERSIONES/Claude - Fernando/Dashboards ETFs/Dashboards/ETFPESOV/General/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57B11A0A-CE08-4EF3-BAAE-5F89E49C8D9F}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="13_ncr:1_{92F23378-0498-4D77-8B70-1F22B2DCC606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5125336A-44F2-4847-B2F7-ECB47C059442}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Fecha</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AT391"/>
+  <dimension ref="A1:AT392"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -37790,8 +37790,8 @@
       <c r="C390">
         <v>149015621.7863636</v>
       </c>
-      <c r="D390" t="s">
-        <v>22</v>
+      <c r="D390">
+        <v>547</v>
       </c>
       <c r="E390">
         <v>2105</v>
@@ -37906,8 +37906,8 @@
       <c r="C391">
         <v>148999130.23204803</v>
       </c>
-      <c r="D391" t="s">
-        <v>22</v>
+      <c r="D391">
+        <v>550</v>
       </c>
       <c r="E391">
         <v>9791</v>
@@ -38010,6 +38010,122 @@
       </c>
       <c r="AL391">
         <v>4.8078159252481047E-3</v>
+      </c>
+    </row>
+    <row r="392" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A392" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B392">
+        <v>110.44726897189142</v>
+      </c>
+      <c r="C392">
+        <v>148827694.93962368</v>
+      </c>
+      <c r="D392" t="s">
+        <v>22</v>
+      </c>
+      <c r="E392">
+        <v>49390</v>
+      </c>
+      <c r="F392">
+        <v>2</v>
+      </c>
+      <c r="G392">
+        <v>6.2204063063619381</v>
+      </c>
+      <c r="H392">
+        <v>6.1498775469484137</v>
+      </c>
+      <c r="I392">
+        <v>181.49</v>
+      </c>
+      <c r="J392">
+        <v>6.3</v>
+      </c>
+      <c r="K392">
+        <v>6.21</v>
+      </c>
+      <c r="L392">
+        <v>10.447268971891411</v>
+      </c>
+      <c r="M392">
+        <v>10.938599956743001</v>
+      </c>
+      <c r="N392">
+        <v>6.5802944119903</v>
+      </c>
+      <c r="O392">
+        <v>6.59</v>
+      </c>
+      <c r="P392">
+        <v>5.4936314942568574E-3</v>
+      </c>
+      <c r="Q392">
+        <v>4.9611965685411761E-3</v>
+      </c>
+      <c r="R392">
+        <v>0.10782480681294901</v>
+      </c>
+      <c r="S392">
+        <v>0.15621877183546237</v>
+      </c>
+      <c r="T392">
+        <v>-2.763261309838283E-2</v>
+      </c>
+      <c r="U392">
+        <v>-7.0268117369154393E-2</v>
+      </c>
+      <c r="V392">
+        <v>-0.21351905105646551</v>
+      </c>
+      <c r="W392">
+        <v>-0.45345263381872947</v>
+      </c>
+      <c r="X392">
+        <v>110</v>
+      </c>
+      <c r="Y392">
+        <v>-2.6349459206899462</v>
+      </c>
+      <c r="Z392">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA392" s="3">
+        <v>4.0496154957462283E-3</v>
+      </c>
+      <c r="AB392" s="3">
+        <v>5.7605551990942789E-3</v>
+      </c>
+      <c r="AC392" s="3">
+        <v>5.280372822888243E-3</v>
+      </c>
+      <c r="AD392" s="3">
+        <v>4.4842705717397817E-3</v>
+      </c>
+      <c r="AE392" s="3">
+        <v>5.0253695406609717E-3</v>
+      </c>
+      <c r="AF392">
+        <v>6823</v>
+      </c>
+      <c r="AG392">
+        <v>8662.9650000000001</v>
+      </c>
+      <c r="AH392">
+        <v>10634.04</v>
+      </c>
+      <c r="AI392">
+        <v>9958.755000000001</v>
+      </c>
+      <c r="AJ392">
+        <v>4.7964053804230291E-3</v>
+      </c>
+      <c r="AK392">
+        <v>5.5593251845032932E-3</v>
+      </c>
+      <c r="AL392">
+        <v>4.8385096148013109E-3</v>
       </c>
     </row>
   </sheetData>
@@ -38273,6 +38389,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="dd854d95-092e-48c7-992a-80d5cc5badc3" xsi:nil="true"/>
@@ -38281,15 +38406,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -38312,6 +38428,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C21325A-2FA6-4D29-AED0-CA44A2859AE9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -38320,12 +38444,4 @@
     <ds:schemaRef ds:uri="0902cc7b-e4ce-48dd-a92e-a98e18ec7ffe"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDE56E9-7C64-4C15-9C33-5B738E73FACD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>